--- a/report_template.xlsx
+++ b/report_template.xlsx
@@ -8,13 +8,13 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\JosGon\Dropbox\Python Scripts\stock report\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6EB802B6-2F1D-4CF5-B872-32C5F0519060}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D5743A11-4145-43C0-BD03-47A91E9EF57F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2730" yWindow="2730" windowWidth="57600" windowHeight="15345" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="38295" yWindow="0" windowWidth="38610" windowHeight="20985" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
-    <sheet name="Sheet2" sheetId="2" state="hidden" r:id="rId2"/>
+    <sheet name="Sheet2" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -1717,11 +1717,14 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="164" fontId="9" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="10" fontId="17" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1732,41 +1735,65 @@
     <xf numFmtId="0" fontId="12" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="2" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="2" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="2" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="12" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="22" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
+    <xf numFmtId="0" fontId="12" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="2" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="2" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="6" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="6" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="6" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1810,53 +1837,26 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="11" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="22" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="10" fontId="17" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="2" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="20" fillId="6" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="2" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="18" fillId="6" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="2" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="18" fillId="6" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="2" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="2" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -4502,21 +4502,21 @@
   </cols>
   <sheetData>
     <row r="1" spans="2:16" ht="43.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B1" s="126" t="s">
+      <c r="B1" s="135" t="s">
         <v>84</v>
       </c>
-      <c r="C1" s="126"/>
-      <c r="D1" s="126"/>
-      <c r="E1" s="126"/>
-      <c r="F1" s="126"/>
-      <c r="G1" s="126"/>
-      <c r="H1" s="126"/>
-      <c r="I1" s="126"/>
-      <c r="J1" s="126"/>
-      <c r="K1" s="126"/>
-      <c r="L1" s="126"/>
-      <c r="M1" s="126"/>
-      <c r="N1" s="126"/>
+      <c r="C1" s="135"/>
+      <c r="D1" s="135"/>
+      <c r="E1" s="135"/>
+      <c r="F1" s="135"/>
+      <c r="G1" s="135"/>
+      <c r="H1" s="135"/>
+      <c r="I1" s="135"/>
+      <c r="J1" s="135"/>
+      <c r="K1" s="135"/>
+      <c r="L1" s="135"/>
+      <c r="M1" s="135"/>
+      <c r="N1" s="135"/>
       <c r="O1" s="44" t="s">
         <v>85</v>
       </c>
@@ -4526,96 +4526,96 @@
       </c>
     </row>
     <row r="2" spans="2:16" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B2" s="165" t="s">
+      <c r="B2" s="133" t="s">
         <v>294</v>
       </c>
-      <c r="C2" s="165"/>
-      <c r="D2" s="165"/>
-      <c r="E2" s="165"/>
-      <c r="F2" s="165"/>
-      <c r="G2" s="165"/>
-      <c r="H2" s="165"/>
-      <c r="J2" s="161" t="s">
+      <c r="C2" s="133"/>
+      <c r="D2" s="133"/>
+      <c r="E2" s="133"/>
+      <c r="F2" s="133"/>
+      <c r="G2" s="133"/>
+      <c r="H2" s="133"/>
+      <c r="J2" s="129" t="s">
         <v>288</v>
       </c>
-      <c r="K2" s="162"/>
-      <c r="L2" s="162"/>
-      <c r="M2" s="162"/>
-      <c r="N2" s="162"/>
-      <c r="O2" s="162"/>
-      <c r="P2" s="163"/>
+      <c r="K2" s="130"/>
+      <c r="L2" s="130"/>
+      <c r="M2" s="130"/>
+      <c r="N2" s="130"/>
+      <c r="O2" s="130"/>
+      <c r="P2" s="131"/>
     </row>
     <row r="3" spans="2:16" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B3" s="167"/>
-      <c r="C3" s="167"/>
-      <c r="D3" s="167"/>
-      <c r="E3" s="167"/>
-      <c r="F3" s="167"/>
-      <c r="G3" s="167"/>
-      <c r="H3" s="167"/>
-      <c r="J3" s="164"/>
-      <c r="K3" s="165"/>
-      <c r="L3" s="165"/>
-      <c r="M3" s="165"/>
-      <c r="N3" s="165"/>
-      <c r="O3" s="165"/>
-      <c r="P3" s="166"/>
+      <c r="B3" s="136"/>
+      <c r="C3" s="136"/>
+      <c r="D3" s="136"/>
+      <c r="E3" s="136"/>
+      <c r="F3" s="136"/>
+      <c r="G3" s="136"/>
+      <c r="H3" s="136"/>
+      <c r="J3" s="132"/>
+      <c r="K3" s="133"/>
+      <c r="L3" s="133"/>
+      <c r="M3" s="133"/>
+      <c r="N3" s="133"/>
+      <c r="O3" s="133"/>
+      <c r="P3" s="134"/>
     </row>
     <row r="4" spans="2:16" x14ac:dyDescent="0.25">
-      <c r="B4" s="137"/>
-      <c r="C4" s="138"/>
+      <c r="B4" s="146"/>
+      <c r="C4" s="147"/>
       <c r="D4" s="37" t="s">
         <v>0</v>
       </c>
-      <c r="E4" s="141"/>
-      <c r="F4" s="141"/>
-      <c r="G4" s="141"/>
-      <c r="H4" s="142"/>
+      <c r="E4" s="150"/>
+      <c r="F4" s="150"/>
+      <c r="G4" s="150"/>
+      <c r="H4" s="151"/>
       <c r="J4" s="27"/>
       <c r="P4" s="28"/>
     </row>
     <row r="5" spans="2:16" x14ac:dyDescent="0.25">
-      <c r="B5" s="139"/>
-      <c r="C5" s="140"/>
+      <c r="B5" s="148"/>
+      <c r="C5" s="149"/>
       <c r="D5" s="75" t="s">
         <v>33</v>
       </c>
-      <c r="E5" s="144"/>
-      <c r="F5" s="144"/>
-      <c r="G5" s="144"/>
-      <c r="H5" s="145"/>
+      <c r="E5" s="153"/>
+      <c r="F5" s="153"/>
+      <c r="G5" s="153"/>
+      <c r="H5" s="154"/>
       <c r="J5" s="27"/>
-      <c r="K5" s="143" t="s">
+      <c r="K5" s="152" t="s">
         <v>305</v>
       </c>
-      <c r="L5" s="143"/>
-      <c r="M5" s="143"/>
-      <c r="N5" s="143"/>
+      <c r="L5" s="152"/>
+      <c r="M5" s="152"/>
+      <c r="N5" s="152"/>
       <c r="P5" s="28"/>
     </row>
     <row r="6" spans="2:16" x14ac:dyDescent="0.25">
-      <c r="B6" s="139"/>
-      <c r="C6" s="140"/>
+      <c r="B6" s="148"/>
+      <c r="C6" s="149"/>
       <c r="D6" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="E6" s="151"/>
-      <c r="F6" s="151"/>
-      <c r="G6" s="151"/>
-      <c r="H6" s="152"/>
+      <c r="E6" s="160"/>
+      <c r="F6" s="160"/>
+      <c r="G6" s="160"/>
+      <c r="H6" s="161"/>
       <c r="J6" s="27"/>
       <c r="P6" s="28"/>
     </row>
     <row r="7" spans="2:16" x14ac:dyDescent="0.25">
-      <c r="B7" s="139"/>
-      <c r="C7" s="140"/>
+      <c r="B7" s="148"/>
+      <c r="C7" s="149"/>
       <c r="D7" s="75" t="s">
         <v>6</v>
       </c>
-      <c r="E7" s="153"/>
-      <c r="F7" s="153"/>
-      <c r="G7" s="153"/>
-      <c r="H7" s="154"/>
+      <c r="E7" s="162"/>
+      <c r="F7" s="162"/>
+      <c r="G7" s="162"/>
+      <c r="H7" s="163"/>
       <c r="J7" s="33" t="s">
         <v>14</v>
       </c>
@@ -4637,8 +4637,8 @@
       <c r="P7" s="28"/>
     </row>
     <row r="8" spans="2:16" x14ac:dyDescent="0.25">
-      <c r="B8" s="139"/>
-      <c r="C8" s="140"/>
+      <c r="B8" s="148"/>
+      <c r="C8" s="149"/>
       <c r="D8" s="1" t="s">
         <v>1</v>
       </c>
@@ -4654,13 +4654,13 @@
       <c r="P8" s="28"/>
     </row>
     <row r="9" spans="2:16" x14ac:dyDescent="0.25">
-      <c r="B9" s="139"/>
-      <c r="C9" s="140"/>
+      <c r="B9" s="148"/>
+      <c r="C9" s="149"/>
       <c r="D9" s="75" t="s">
         <v>2</v>
       </c>
-      <c r="E9" s="144"/>
-      <c r="F9" s="144"/>
+      <c r="E9" s="153"/>
+      <c r="F9" s="153"/>
       <c r="G9" s="76"/>
       <c r="H9" s="77"/>
       <c r="J9" s="35" t="s">
@@ -4674,13 +4674,13 @@
       <c r="P9" s="28"/>
     </row>
     <row r="10" spans="2:16" x14ac:dyDescent="0.25">
-      <c r="B10" s="139"/>
-      <c r="C10" s="140"/>
+      <c r="B10" s="148"/>
+      <c r="C10" s="149"/>
       <c r="D10" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="E10" s="129"/>
-      <c r="F10" s="129"/>
+      <c r="E10" s="145"/>
+      <c r="F10" s="145"/>
       <c r="H10" s="38"/>
       <c r="J10" s="27" t="s">
         <v>17</v>
@@ -4693,8 +4693,8 @@
       <c r="P10" s="28"/>
     </row>
     <row r="11" spans="2:16" x14ac:dyDescent="0.25">
-      <c r="B11" s="139"/>
-      <c r="C11" s="140"/>
+      <c r="B11" s="148"/>
+      <c r="C11" s="149"/>
       <c r="D11" s="75" t="s">
         <v>8</v>
       </c>
@@ -4715,8 +4715,8 @@
       <c r="P11" s="28"/>
     </row>
     <row r="12" spans="2:16" x14ac:dyDescent="0.25">
-      <c r="B12" s="139"/>
-      <c r="C12" s="140"/>
+      <c r="B12" s="148"/>
+      <c r="C12" s="149"/>
       <c r="D12" s="1" t="s">
         <v>5</v>
       </c>
@@ -4727,8 +4727,8 @@
       </c>
     </row>
     <row r="13" spans="2:16" x14ac:dyDescent="0.25">
-      <c r="B13" s="139"/>
-      <c r="C13" s="140"/>
+      <c r="B13" s="148"/>
+      <c r="C13" s="149"/>
       <c r="D13" s="75" t="s">
         <v>34</v>
       </c>
@@ -4736,14 +4736,14 @@
       <c r="F13" s="76"/>
       <c r="G13" s="76"/>
       <c r="H13" s="77"/>
-      <c r="J13" s="130" t="s">
+      <c r="J13" s="165" t="s">
         <v>19</v>
       </c>
-      <c r="K13" s="131"/>
-      <c r="L13" s="121"/>
-      <c r="M13" s="121"/>
-      <c r="N13" s="121"/>
-      <c r="O13" s="121"/>
+      <c r="K13" s="166"/>
+      <c r="L13" s="142"/>
+      <c r="M13" s="142"/>
+      <c r="N13" s="142"/>
+      <c r="O13" s="142"/>
       <c r="P13" s="28" t="str">
         <f>+IF(OR(L13="",L13="none"),"",VLOOKUP(L13,Sheet2!$A$1:$B$6,2,FALSE))</f>
         <v/>
@@ -4774,43 +4774,43 @@
       <c r="L15" s="81" t="s">
         <v>21</v>
       </c>
-      <c r="M15" s="121" t="str">
+      <c r="M15" s="142" t="str">
         <f>IF(K15="","",IF(K15&lt;0.8,"Low volatility",IF(K15&lt;=1.2,"Normal volatility","High volatility")))</f>
         <v/>
       </c>
-      <c r="N15" s="121"/>
-      <c r="O15" s="121"/>
+      <c r="N15" s="142"/>
+      <c r="O15" s="142"/>
       <c r="P15" s="28" t="str">
         <f>+IF(M15="","",VLOOKUP(M15,Sheet2!$A$8:$B$11,2,FALSE))</f>
         <v/>
       </c>
     </row>
     <row r="16" spans="2:16" ht="249" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B16" s="148"/>
-      <c r="C16" s="149"/>
-      <c r="D16" s="149"/>
-      <c r="E16" s="149"/>
-      <c r="F16" s="149"/>
-      <c r="G16" s="149"/>
-      <c r="H16" s="150"/>
-      <c r="J16" s="132" t="s">
+      <c r="B16" s="157"/>
+      <c r="C16" s="158"/>
+      <c r="D16" s="158"/>
+      <c r="E16" s="158"/>
+      <c r="F16" s="158"/>
+      <c r="G16" s="158"/>
+      <c r="H16" s="159"/>
+      <c r="J16" s="167" t="s">
         <v>323</v>
       </c>
-      <c r="K16" s="133"/>
-      <c r="L16" s="133"/>
-      <c r="M16" s="133"/>
-      <c r="N16" s="133"/>
-      <c r="O16" s="133"/>
-      <c r="P16" s="134"/>
+      <c r="K16" s="168"/>
+      <c r="L16" s="168"/>
+      <c r="M16" s="168"/>
+      <c r="N16" s="168"/>
+      <c r="O16" s="168"/>
+      <c r="P16" s="169"/>
     </row>
     <row r="17" spans="2:16" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B17" s="148"/>
-      <c r="C17" s="149"/>
-      <c r="D17" s="149"/>
-      <c r="E17" s="149"/>
-      <c r="F17" s="149"/>
-      <c r="G17" s="149"/>
-      <c r="H17" s="150"/>
+      <c r="B17" s="157"/>
+      <c r="C17" s="158"/>
+      <c r="D17" s="158"/>
+      <c r="E17" s="158"/>
+      <c r="F17" s="158"/>
+      <c r="G17" s="158"/>
+      <c r="H17" s="159"/>
       <c r="J17" s="89" t="s">
         <v>22</v>
       </c>
@@ -4822,26 +4822,26 @@
       <c r="P17" s="91"/>
     </row>
     <row r="18" spans="2:16" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B18" s="148"/>
-      <c r="C18" s="149"/>
-      <c r="D18" s="149"/>
-      <c r="E18" s="149"/>
-      <c r="F18" s="149"/>
-      <c r="G18" s="149"/>
-      <c r="H18" s="150"/>
+      <c r="B18" s="157"/>
+      <c r="C18" s="158"/>
+      <c r="D18" s="158"/>
+      <c r="E18" s="158"/>
+      <c r="F18" s="158"/>
+      <c r="G18" s="158"/>
+      <c r="H18" s="159"/>
       <c r="J18" s="92" t="s">
         <v>23</v>
       </c>
       <c r="P18" s="88"/>
     </row>
     <row r="19" spans="2:16" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B19" s="148"/>
-      <c r="C19" s="149"/>
-      <c r="D19" s="149"/>
-      <c r="E19" s="149"/>
-      <c r="F19" s="149"/>
-      <c r="G19" s="149"/>
-      <c r="H19" s="150"/>
+      <c r="B19" s="157"/>
+      <c r="C19" s="158"/>
+      <c r="D19" s="158"/>
+      <c r="E19" s="158"/>
+      <c r="F19" s="158"/>
+      <c r="G19" s="158"/>
+      <c r="H19" s="159"/>
       <c r="J19" s="93" t="s">
         <v>24</v>
       </c>
@@ -4853,13 +4853,13 @@
       <c r="P19" s="94"/>
     </row>
     <row r="20" spans="2:16" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B20" s="148"/>
-      <c r="C20" s="149"/>
-      <c r="D20" s="149"/>
-      <c r="E20" s="149"/>
-      <c r="F20" s="149"/>
-      <c r="G20" s="149"/>
-      <c r="H20" s="150"/>
+      <c r="B20" s="157"/>
+      <c r="C20" s="158"/>
+      <c r="D20" s="158"/>
+      <c r="E20" s="158"/>
+      <c r="F20" s="158"/>
+      <c r="G20" s="158"/>
+      <c r="H20" s="159"/>
       <c r="J20" s="92" t="s">
         <v>25</v>
       </c>
@@ -4886,17 +4886,17 @@
       <c r="F22" s="62" t="s">
         <v>36</v>
       </c>
-      <c r="G22" s="146" t="s">
+      <c r="G22" s="155" t="s">
         <v>37</v>
       </c>
-      <c r="H22" s="147"/>
+      <c r="H22" s="156"/>
       <c r="J22" s="92" t="s">
         <v>26</v>
       </c>
-      <c r="L22" s="129"/>
-      <c r="M22" s="129"/>
-      <c r="N22" s="129"/>
-      <c r="O22" s="129"/>
+      <c r="L22" s="145"/>
+      <c r="M22" s="145"/>
+      <c r="N22" s="145"/>
+      <c r="O22" s="145"/>
       <c r="P22" s="88"/>
     </row>
     <row r="23" spans="2:16" x14ac:dyDescent="0.25">
@@ -4910,10 +4910,10 @@
       <c r="J23" s="92" t="s">
         <v>306</v>
       </c>
-      <c r="L23" s="129"/>
-      <c r="M23" s="129"/>
-      <c r="N23" s="129"/>
-      <c r="O23" s="129"/>
+      <c r="L23" s="145"/>
+      <c r="M23" s="145"/>
+      <c r="N23" s="145"/>
+      <c r="O23" s="145"/>
       <c r="P23" s="88"/>
     </row>
     <row r="24" spans="2:16" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -5001,10 +5001,10 @@
       <c r="F30" s="2"/>
       <c r="G30" s="2"/>
       <c r="H30" s="40"/>
-      <c r="J30" s="128" t="s">
+      <c r="J30" s="164" t="s">
         <v>30</v>
       </c>
-      <c r="K30" s="129"/>
+      <c r="K30" s="145"/>
       <c r="P30" s="88"/>
     </row>
     <row r="31" spans="2:16" x14ac:dyDescent="0.25">
@@ -5015,10 +5015,10 @@
       <c r="F31" s="2"/>
       <c r="G31" s="2"/>
       <c r="H31" s="40"/>
-      <c r="J31" s="128" t="s">
+      <c r="J31" s="164" t="s">
         <v>31</v>
       </c>
-      <c r="K31" s="129"/>
+      <c r="K31" s="145"/>
       <c r="P31" s="88"/>
     </row>
     <row r="32" spans="2:16" x14ac:dyDescent="0.25">
@@ -5141,40 +5141,40 @@
       </c>
     </row>
     <row r="36" spans="2:16" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B36" s="125" t="s">
+      <c r="B36" s="137" t="s">
         <v>44</v>
       </c>
-      <c r="C36" s="126"/>
-      <c r="D36" s="126"/>
-      <c r="E36" s="126"/>
-      <c r="F36" s="126"/>
-      <c r="G36" s="126"/>
-      <c r="H36" s="126"/>
-      <c r="I36" s="126"/>
-      <c r="J36" s="126"/>
-      <c r="K36" s="126"/>
-      <c r="L36" s="126"/>
-      <c r="M36" s="126"/>
-      <c r="N36" s="126"/>
-      <c r="O36" s="126"/>
-      <c r="P36" s="127"/>
+      <c r="C36" s="135"/>
+      <c r="D36" s="135"/>
+      <c r="E36" s="135"/>
+      <c r="F36" s="135"/>
+      <c r="G36" s="135"/>
+      <c r="H36" s="135"/>
+      <c r="I36" s="135"/>
+      <c r="J36" s="135"/>
+      <c r="K36" s="135"/>
+      <c r="L36" s="135"/>
+      <c r="M36" s="135"/>
+      <c r="N36" s="135"/>
+      <c r="O36" s="135"/>
+      <c r="P36" s="138"/>
     </row>
     <row r="37" spans="2:16" ht="20.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B37" s="168"/>
-      <c r="C37" s="169"/>
-      <c r="D37" s="169"/>
-      <c r="E37" s="169"/>
-      <c r="F37" s="169"/>
-      <c r="G37" s="169"/>
-      <c r="H37" s="169"/>
-      <c r="I37" s="169"/>
-      <c r="J37" s="169"/>
-      <c r="K37" s="169"/>
-      <c r="L37" s="169"/>
-      <c r="M37" s="169"/>
-      <c r="N37" s="169"/>
-      <c r="O37" s="169"/>
-      <c r="P37" s="170"/>
+      <c r="B37" s="139"/>
+      <c r="C37" s="140"/>
+      <c r="D37" s="140"/>
+      <c r="E37" s="140"/>
+      <c r="F37" s="140"/>
+      <c r="G37" s="140"/>
+      <c r="H37" s="140"/>
+      <c r="I37" s="140"/>
+      <c r="J37" s="140"/>
+      <c r="K37" s="140"/>
+      <c r="L37" s="140"/>
+      <c r="M37" s="140"/>
+      <c r="N37" s="140"/>
+      <c r="O37" s="140"/>
+      <c r="P37" s="141"/>
     </row>
     <row r="38" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B38" s="46"/>
@@ -5221,13 +5221,13 @@
       <c r="J39" s="64" t="s">
         <v>38</v>
       </c>
-      <c r="K39" s="120" t="s">
+      <c r="K39" s="143" t="s">
         <v>40</v>
       </c>
-      <c r="L39" s="120"/>
-      <c r="M39" s="120"/>
-      <c r="N39" s="120"/>
-      <c r="O39" s="120"/>
+      <c r="L39" s="143"/>
+      <c r="M39" s="143"/>
+      <c r="N39" s="143"/>
+      <c r="O39" s="143"/>
       <c r="P39" s="60" t="s">
         <v>124</v>
       </c>
@@ -5243,14 +5243,14 @@
       <c r="H40" s="7"/>
       <c r="I40" s="7"/>
       <c r="J40" s="7"/>
-      <c r="K40" s="121" t="str">
+      <c r="K40" s="142" t="str">
         <f>+IF(D41="","",IF(D40&lt;0,Sheet2!$C$27,VLOOKUP(D41,Sheet2!$A$27:$C$31,3,TRUE)))</f>
         <v/>
       </c>
-      <c r="L40" s="121"/>
-      <c r="M40" s="121"/>
-      <c r="N40" s="121"/>
-      <c r="O40" s="121"/>
+      <c r="L40" s="142"/>
+      <c r="M40" s="142"/>
+      <c r="N40" s="142"/>
+      <c r="O40" s="142"/>
       <c r="P40" s="28" t="str">
         <f>+IF(K40="","",VLOOKUP(K40,Sheet2!$C$27:$D$31,2,FALSE))</f>
         <v/>
@@ -5282,14 +5282,14 @@
         <f>+IF(D41="","",AVERAGE(D41:G41))</f>
         <v/>
       </c>
-      <c r="K41" s="121" t="str">
+      <c r="K41" s="142" t="str">
         <f>+IF(J41="","",IF(AND(D40&lt;0,E40&lt;0),Sheet2!$C$35,VLOOKUP(J41,Sheet2!$A$35:$C$39,3,TRUE)))</f>
         <v/>
       </c>
-      <c r="L41" s="121"/>
-      <c r="M41" s="121"/>
-      <c r="N41" s="121"/>
-      <c r="O41" s="121"/>
+      <c r="L41" s="142"/>
+      <c r="M41" s="142"/>
+      <c r="N41" s="142"/>
+      <c r="O41" s="142"/>
       <c r="P41" s="28" t="str">
         <f>+IF(K41="","",VLOOKUP(K41,Sheet2!$C$35:$D$39,2,FALSE))</f>
         <v/>
@@ -5305,11 +5305,11 @@
       <c r="H42" s="7"/>
       <c r="I42" s="7"/>
       <c r="J42" s="7"/>
-      <c r="K42" s="121"/>
-      <c r="L42" s="121"/>
-      <c r="M42" s="121"/>
-      <c r="N42" s="121"/>
-      <c r="O42" s="121"/>
+      <c r="K42" s="142"/>
+      <c r="L42" s="142"/>
+      <c r="M42" s="142"/>
+      <c r="N42" s="142"/>
+      <c r="O42" s="142"/>
       <c r="P42" s="28"/>
     </row>
     <row r="43" spans="2:16" x14ac:dyDescent="0.25">
@@ -5341,13 +5341,13 @@
       <c r="J43" s="64" t="s">
         <v>38</v>
       </c>
-      <c r="K43" s="120" t="s">
+      <c r="K43" s="143" t="s">
         <v>40</v>
       </c>
-      <c r="L43" s="120"/>
-      <c r="M43" s="120"/>
-      <c r="N43" s="120"/>
-      <c r="O43" s="120"/>
+      <c r="L43" s="143"/>
+      <c r="M43" s="143"/>
+      <c r="N43" s="143"/>
+      <c r="O43" s="143"/>
       <c r="P43" s="60" t="s">
         <v>124</v>
       </c>
@@ -5363,14 +5363,14 @@
       <c r="H44" s="7"/>
       <c r="I44" s="7"/>
       <c r="J44" s="7"/>
-      <c r="K44" s="121" t="str">
+      <c r="K44" s="142" t="str">
         <f>+IF(D45="","",IF(D44&lt;0,Sheet2!$C$27,VLOOKUP(D45,Sheet2!$A$27:$C$31,3,TRUE)))</f>
         <v/>
       </c>
-      <c r="L44" s="121"/>
-      <c r="M44" s="121"/>
-      <c r="N44" s="121"/>
-      <c r="O44" s="121"/>
+      <c r="L44" s="142"/>
+      <c r="M44" s="142"/>
+      <c r="N44" s="142"/>
+      <c r="O44" s="142"/>
       <c r="P44" s="28" t="str">
         <f>+IF(K44="","",VLOOKUP(K44,Sheet2!$C$27:$D$31,2,FALSE))</f>
         <v/>
@@ -5402,14 +5402,14 @@
         <f>+IF(D45="","",AVERAGE(D45:G45))</f>
         <v/>
       </c>
-      <c r="K45" s="121" t="str">
+      <c r="K45" s="142" t="str">
         <f>+IF(J45="","",IF(AND(D44&lt;0,E44&lt;0),Sheet2!$C$35,VLOOKUP(J45,Sheet2!$A$35:$C$39,3,TRUE)))</f>
         <v/>
       </c>
-      <c r="L45" s="121"/>
-      <c r="M45" s="121"/>
-      <c r="N45" s="121"/>
-      <c r="O45" s="121"/>
+      <c r="L45" s="142"/>
+      <c r="M45" s="142"/>
+      <c r="N45" s="142"/>
+      <c r="O45" s="142"/>
       <c r="P45" s="28" t="str">
         <f>+IF(K45="","",VLOOKUP(K45,Sheet2!$C$35:$D$39,2,FALSE))</f>
         <v/>
@@ -5456,11 +5456,11 @@
       <c r="J47" s="64" t="s">
         <v>38</v>
       </c>
-      <c r="K47" s="120"/>
-      <c r="L47" s="120"/>
-      <c r="M47" s="120"/>
-      <c r="N47" s="120"/>
-      <c r="O47" s="120"/>
+      <c r="K47" s="143"/>
+      <c r="L47" s="143"/>
+      <c r="M47" s="143"/>
+      <c r="N47" s="143"/>
+      <c r="O47" s="143"/>
       <c r="P47" s="60"/>
     </row>
     <row r="48" spans="2:16" x14ac:dyDescent="0.25">
@@ -5474,11 +5474,11 @@
       <c r="H48" s="7"/>
       <c r="I48" s="7"/>
       <c r="J48" s="7"/>
-      <c r="K48" s="121"/>
-      <c r="L48" s="121"/>
-      <c r="M48" s="121"/>
-      <c r="N48" s="121"/>
-      <c r="O48" s="121"/>
+      <c r="K48" s="142"/>
+      <c r="L48" s="142"/>
+      <c r="M48" s="142"/>
+      <c r="N48" s="142"/>
+      <c r="O48" s="142"/>
       <c r="P48" s="28"/>
     </row>
     <row r="49" spans="2:16" x14ac:dyDescent="0.25">
@@ -5507,11 +5507,11 @@
         <f>+IF(D49="","",AVERAGE(D49:G49))</f>
         <v/>
       </c>
-      <c r="K49" s="121"/>
-      <c r="L49" s="121"/>
-      <c r="M49" s="121"/>
-      <c r="N49" s="121"/>
-      <c r="O49" s="121"/>
+      <c r="K49" s="142"/>
+      <c r="L49" s="142"/>
+      <c r="M49" s="142"/>
+      <c r="N49" s="142"/>
+      <c r="O49" s="142"/>
       <c r="P49" s="28"/>
     </row>
     <row r="50" spans="2:16" x14ac:dyDescent="0.25">
@@ -5555,11 +5555,11 @@
       <c r="J51" s="64" t="s">
         <v>38</v>
       </c>
-      <c r="K51" s="120"/>
-      <c r="L51" s="120"/>
-      <c r="M51" s="120"/>
-      <c r="N51" s="120"/>
-      <c r="O51" s="120"/>
+      <c r="K51" s="143"/>
+      <c r="L51" s="143"/>
+      <c r="M51" s="143"/>
+      <c r="N51" s="143"/>
+      <c r="O51" s="143"/>
       <c r="P51" s="60"/>
     </row>
     <row r="52" spans="2:16" x14ac:dyDescent="0.25">
@@ -5644,11 +5644,11 @@
       <c r="J55" s="64" t="s">
         <v>38</v>
       </c>
-      <c r="K55" s="120"/>
-      <c r="L55" s="120"/>
-      <c r="M55" s="120"/>
-      <c r="N55" s="120"/>
-      <c r="O55" s="120"/>
+      <c r="K55" s="143"/>
+      <c r="L55" s="143"/>
+      <c r="M55" s="143"/>
+      <c r="N55" s="143"/>
+      <c r="O55" s="143"/>
       <c r="P55" s="60"/>
     </row>
     <row r="56" spans="2:16" x14ac:dyDescent="0.25">
@@ -5733,13 +5733,13 @@
       <c r="J59" s="64" t="s">
         <v>38</v>
       </c>
-      <c r="K59" s="120" t="s">
+      <c r="K59" s="143" t="s">
         <v>40</v>
       </c>
-      <c r="L59" s="120"/>
-      <c r="M59" s="120"/>
-      <c r="N59" s="120"/>
-      <c r="O59" s="120"/>
+      <c r="L59" s="143"/>
+      <c r="M59" s="143"/>
+      <c r="N59" s="143"/>
+      <c r="O59" s="143"/>
       <c r="P59" s="60" t="s">
         <v>124</v>
       </c>
@@ -5755,14 +5755,14 @@
       <c r="H60" s="7"/>
       <c r="I60" s="7"/>
       <c r="J60" s="7"/>
-      <c r="K60" s="121" t="str">
+      <c r="K60" s="142" t="str">
         <f>+IF(D61="","",IF(D60&lt;0,Sheet2!$C$27,VLOOKUP(D61,Sheet2!$A$27:$C$31,3,TRUE)))</f>
         <v/>
       </c>
-      <c r="L60" s="121"/>
-      <c r="M60" s="121"/>
-      <c r="N60" s="121"/>
-      <c r="O60" s="121"/>
+      <c r="L60" s="142"/>
+      <c r="M60" s="142"/>
+      <c r="N60" s="142"/>
+      <c r="O60" s="142"/>
       <c r="P60" s="28" t="str">
         <f>+IF(K60="","",VLOOKUP(K60,Sheet2!$C$27:$D$31,2,FALSE))</f>
         <v/>
@@ -5794,14 +5794,14 @@
         <f>+IF(D61="","",AVERAGE(D61:G61))</f>
         <v/>
       </c>
-      <c r="K61" s="121" t="str">
+      <c r="K61" s="142" t="str">
         <f>+IF(J61="","",IF(AND(D60&lt;0,E60&lt;0),Sheet2!$C$35,VLOOKUP(J61,Sheet2!$A$35:$C$39,3,TRUE)))</f>
         <v/>
       </c>
-      <c r="L61" s="121"/>
-      <c r="M61" s="121"/>
-      <c r="N61" s="121"/>
-      <c r="O61" s="121"/>
+      <c r="L61" s="142"/>
+      <c r="M61" s="142"/>
+      <c r="N61" s="142"/>
+      <c r="O61" s="142"/>
       <c r="P61" s="28" t="str">
         <f>+IF(K61="","",VLOOKUP(K61,Sheet2!$C$35:$D$39,2,FALSE))</f>
         <v/>
@@ -5848,13 +5848,13 @@
       <c r="J63" s="64" t="s">
         <v>38</v>
       </c>
-      <c r="K63" s="120" t="s">
+      <c r="K63" s="143" t="s">
         <v>40</v>
       </c>
-      <c r="L63" s="120"/>
-      <c r="M63" s="120"/>
-      <c r="N63" s="120"/>
-      <c r="O63" s="120"/>
+      <c r="L63" s="143"/>
+      <c r="M63" s="143"/>
+      <c r="N63" s="143"/>
+      <c r="O63" s="143"/>
       <c r="P63" s="60" t="s">
         <v>124</v>
       </c>
@@ -5870,14 +5870,14 @@
       <c r="H64" s="7"/>
       <c r="I64" s="7"/>
       <c r="J64" s="7"/>
-      <c r="K64" s="121" t="str">
+      <c r="K64" s="142" t="str">
         <f>+IF(D65="","",IF(D64&lt;0,Sheet2!$C$27,VLOOKUP(D65,Sheet2!$A$27:$C$31,3,TRUE)))</f>
         <v/>
       </c>
-      <c r="L64" s="121"/>
-      <c r="M64" s="121"/>
-      <c r="N64" s="121"/>
-      <c r="O64" s="121"/>
+      <c r="L64" s="142"/>
+      <c r="M64" s="142"/>
+      <c r="N64" s="142"/>
+      <c r="O64" s="142"/>
       <c r="P64" s="28" t="str">
         <f>+IF(K64="","",VLOOKUP(K64,Sheet2!$C$27:$D$31,2,FALSE))</f>
         <v/>
@@ -5909,14 +5909,14 @@
         <f>+IF(D65="","",AVERAGE(D65:G65))</f>
         <v/>
       </c>
-      <c r="K65" s="121" t="str">
+      <c r="K65" s="142" t="str">
         <f>+IF(J65="","",IF(AND(D64&lt;0,E64&lt;0),Sheet2!$C$35,VLOOKUP(J65,Sheet2!$A$35:$C$39,3,TRUE)))</f>
         <v/>
       </c>
-      <c r="L65" s="121"/>
-      <c r="M65" s="121"/>
-      <c r="N65" s="121"/>
-      <c r="O65" s="121"/>
+      <c r="L65" s="142"/>
+      <c r="M65" s="142"/>
+      <c r="N65" s="142"/>
+      <c r="O65" s="142"/>
       <c r="P65" s="28" t="str">
         <f>+IF(K65="","",VLOOKUP(K65,Sheet2!$C$35:$D$39,2,FALSE))</f>
         <v/>
@@ -5963,13 +5963,13 @@
       <c r="J67" s="64" t="s">
         <v>38</v>
       </c>
-      <c r="K67" s="120" t="s">
+      <c r="K67" s="143" t="s">
         <v>40</v>
       </c>
-      <c r="L67" s="120"/>
-      <c r="M67" s="120"/>
-      <c r="N67" s="120"/>
-      <c r="O67" s="120"/>
+      <c r="L67" s="143"/>
+      <c r="M67" s="143"/>
+      <c r="N67" s="143"/>
+      <c r="O67" s="143"/>
       <c r="P67" s="60" t="s">
         <v>124</v>
       </c>
@@ -5985,14 +5985,14 @@
       <c r="H68" s="7"/>
       <c r="I68" s="7"/>
       <c r="J68" s="7"/>
-      <c r="K68" s="121" t="str">
+      <c r="K68" s="142" t="str">
         <f>+IF(D69="","",IF(D68&lt;0,Sheet2!$C$27,VLOOKUP(D69,Sheet2!$A$27:$C$31,3,TRUE)))</f>
         <v/>
       </c>
-      <c r="L68" s="121"/>
-      <c r="M68" s="121"/>
-      <c r="N68" s="121"/>
-      <c r="O68" s="121"/>
+      <c r="L68" s="142"/>
+      <c r="M68" s="142"/>
+      <c r="N68" s="142"/>
+      <c r="O68" s="142"/>
       <c r="P68" s="28" t="str">
         <f>+IF(K68="","",VLOOKUP(K68,Sheet2!$C$27:$D$31,2,FALSE))</f>
         <v/>
@@ -6024,14 +6024,14 @@
         <f>+IF(D69="","",AVERAGE(D69:G69))</f>
         <v/>
       </c>
-      <c r="K69" s="121" t="str">
+      <c r="K69" s="142" t="str">
         <f>+IF(J69="","",IF(AND(D68&lt;0,E68&lt;0),Sheet2!$C$35,VLOOKUP(J69,Sheet2!$A$35:$C$39,3,TRUE)))</f>
         <v/>
       </c>
-      <c r="L69" s="121"/>
-      <c r="M69" s="121"/>
-      <c r="N69" s="121"/>
-      <c r="O69" s="121"/>
+      <c r="L69" s="142"/>
+      <c r="M69" s="142"/>
+      <c r="N69" s="142"/>
+      <c r="O69" s="142"/>
       <c r="P69" s="28" t="str">
         <f>+IF(K69="","",VLOOKUP(K69,Sheet2!$C$35:$D$39,2,FALSE))</f>
         <v/>
@@ -6078,11 +6078,11 @@
       <c r="J71" s="64" t="s">
         <v>38</v>
       </c>
-      <c r="K71" s="120"/>
-      <c r="L71" s="120"/>
-      <c r="M71" s="120"/>
-      <c r="N71" s="120"/>
-      <c r="O71" s="120"/>
+      <c r="K71" s="143"/>
+      <c r="L71" s="143"/>
+      <c r="M71" s="143"/>
+      <c r="N71" s="143"/>
+      <c r="O71" s="143"/>
       <c r="P71" s="60"/>
     </row>
     <row r="72" spans="2:16" x14ac:dyDescent="0.25">
@@ -6170,11 +6170,11 @@
       <c r="J75" s="64" t="s">
         <v>38</v>
       </c>
-      <c r="K75" s="120"/>
-      <c r="L75" s="120"/>
-      <c r="M75" s="120"/>
-      <c r="N75" s="120"/>
-      <c r="O75" s="120"/>
+      <c r="K75" s="143"/>
+      <c r="L75" s="143"/>
+      <c r="M75" s="143"/>
+      <c r="N75" s="143"/>
+      <c r="O75" s="143"/>
       <c r="P75" s="60"/>
     </row>
     <row r="76" spans="2:16" x14ac:dyDescent="0.25">
@@ -6259,13 +6259,13 @@
       <c r="J79" s="64" t="s">
         <v>38</v>
       </c>
-      <c r="K79" s="120" t="s">
+      <c r="K79" s="143" t="s">
         <v>40</v>
       </c>
-      <c r="L79" s="120"/>
-      <c r="M79" s="120"/>
-      <c r="N79" s="120"/>
-      <c r="O79" s="120"/>
+      <c r="L79" s="143"/>
+      <c r="M79" s="143"/>
+      <c r="N79" s="143"/>
+      <c r="O79" s="143"/>
       <c r="P79" s="60" t="s">
         <v>124</v>
       </c>
@@ -6281,14 +6281,14 @@
       <c r="H80" s="7"/>
       <c r="I80" s="7"/>
       <c r="J80" s="7"/>
-      <c r="K80" s="121" t="str">
+      <c r="K80" s="142" t="str">
         <f>+IF(D81="","",IF(D80&lt;0,Sheet2!$C$27,VLOOKUP(D81,Sheet2!$A$27:$C$31,3,TRUE)))</f>
         <v/>
       </c>
-      <c r="L80" s="121"/>
-      <c r="M80" s="121"/>
-      <c r="N80" s="121"/>
-      <c r="O80" s="121"/>
+      <c r="L80" s="142"/>
+      <c r="M80" s="142"/>
+      <c r="N80" s="142"/>
+      <c r="O80" s="142"/>
       <c r="P80" s="28" t="str">
         <f>+IF(K80="","",VLOOKUP(K80,Sheet2!$C$27:$D$31,2,FALSE))</f>
         <v/>
@@ -6320,14 +6320,14 @@
         <f>+IF(D81="","",AVERAGE(D81:G81))</f>
         <v/>
       </c>
-      <c r="K81" s="121" t="str">
+      <c r="K81" s="142" t="str">
         <f>+IF(J81="","",IF(AND(D80&lt;0,E80&lt;0),Sheet2!$C$35,VLOOKUP(J81,Sheet2!$A$35:$C$39,3,TRUE)))</f>
         <v/>
       </c>
-      <c r="L81" s="121"/>
-      <c r="M81" s="121"/>
-      <c r="N81" s="121"/>
-      <c r="O81" s="121"/>
+      <c r="L81" s="142"/>
+      <c r="M81" s="142"/>
+      <c r="N81" s="142"/>
+      <c r="O81" s="142"/>
       <c r="P81" s="28" t="str">
         <f>+IF(K81="","",VLOOKUP(K81,Sheet2!$C$35:$D$39,2,FALSE))</f>
         <v/>
@@ -6374,13 +6374,13 @@
       <c r="J83" s="64" t="s">
         <v>38</v>
       </c>
-      <c r="K83" s="120" t="s">
+      <c r="K83" s="143" t="s">
         <v>40</v>
       </c>
-      <c r="L83" s="120"/>
-      <c r="M83" s="120"/>
-      <c r="N83" s="120"/>
-      <c r="O83" s="120"/>
+      <c r="L83" s="143"/>
+      <c r="M83" s="143"/>
+      <c r="N83" s="143"/>
+      <c r="O83" s="143"/>
       <c r="P83" s="60" t="s">
         <v>124</v>
       </c>
@@ -6396,14 +6396,14 @@
       <c r="H84" s="7"/>
       <c r="I84" s="7"/>
       <c r="J84" s="7"/>
-      <c r="K84" s="121" t="str">
+      <c r="K84" s="142" t="str">
         <f>+IF(D85="","",VLOOKUP(D85,Sheet2!$A$42:$C$43,3,TRUE))</f>
         <v/>
       </c>
-      <c r="L84" s="121"/>
-      <c r="M84" s="121"/>
-      <c r="N84" s="121"/>
-      <c r="O84" s="121"/>
+      <c r="L84" s="142"/>
+      <c r="M84" s="142"/>
+      <c r="N84" s="142"/>
+      <c r="O84" s="142"/>
       <c r="P84" s="28" t="str">
         <f>+IF(K84="","",VLOOKUP(K84,Sheet2!$C$42:$D$43,2,FALSE))</f>
         <v/>
@@ -6439,14 +6439,14 @@
         <f>+IF(D85="","",AVERAGE(D85:G85))</f>
         <v/>
       </c>
-      <c r="K85" s="121" t="str">
+      <c r="K85" s="142" t="str">
         <f>+IF(J85="","",VLOOKUP(J85,Sheet2!$A$45:$C$46,3,TRUE))</f>
         <v/>
       </c>
-      <c r="L85" s="121"/>
-      <c r="M85" s="121"/>
-      <c r="N85" s="121"/>
-      <c r="O85" s="121"/>
+      <c r="L85" s="142"/>
+      <c r="M85" s="142"/>
+      <c r="N85" s="142"/>
+      <c r="O85" s="142"/>
       <c r="P85" s="28" t="str">
         <f>+IF(K85="","",VLOOKUP(K85,Sheet2!$C$45:$D$46,2,FALSE))</f>
         <v/>
@@ -6521,13 +6521,13 @@
       <c r="J88" s="64" t="s">
         <v>38</v>
       </c>
-      <c r="K88" s="120" t="s">
+      <c r="K88" s="143" t="s">
         <v>40</v>
       </c>
-      <c r="L88" s="120"/>
-      <c r="M88" s="120"/>
-      <c r="N88" s="120"/>
-      <c r="O88" s="120"/>
+      <c r="L88" s="143"/>
+      <c r="M88" s="143"/>
+      <c r="N88" s="143"/>
+      <c r="O88" s="143"/>
       <c r="P88" s="60" t="s">
         <v>124</v>
       </c>
@@ -6569,14 +6569,14 @@
       <c r="H90" s="7"/>
       <c r="I90" s="7"/>
       <c r="J90" s="7"/>
-      <c r="K90" s="121" t="str">
+      <c r="K90" s="142" t="str">
         <f>+IF(D91="","",IF(D89&lt;0,Sheet2!$C$50,VLOOKUP(D91,Sheet2!A50:C54,3,TRUE)))</f>
         <v/>
       </c>
-      <c r="L90" s="121"/>
-      <c r="M90" s="121"/>
-      <c r="N90" s="121"/>
-      <c r="O90" s="121"/>
+      <c r="L90" s="142"/>
+      <c r="M90" s="142"/>
+      <c r="N90" s="142"/>
+      <c r="O90" s="142"/>
       <c r="P90" s="28" t="str">
         <f>+IF(K90="","",VLOOKUP(K90,Sheet2!$C$50:$D$54,2,FALSE))</f>
         <v/>
@@ -6608,14 +6608,14 @@
         <f>+IF(D91="","",AVERAGE(D91:G91))</f>
         <v/>
       </c>
-      <c r="K91" s="121" t="str">
+      <c r="K91" s="142" t="str">
         <f>+IF(J91="","",IF(AND(C89&lt;0,D89&lt;0),Sheet2!$C$56,VLOOKUP(J91,Sheet2!$A$56:$C$60,3,TRUE)))</f>
         <v/>
       </c>
-      <c r="L91" s="121"/>
-      <c r="M91" s="121"/>
-      <c r="N91" s="121"/>
-      <c r="O91" s="121"/>
+      <c r="L91" s="142"/>
+      <c r="M91" s="142"/>
+      <c r="N91" s="142"/>
+      <c r="O91" s="142"/>
       <c r="P91" s="28" t="str">
         <f>+IF(K91="","",VLOOKUP(K91,Sheet2!$C$56:$D$60,2,FALSE))</f>
         <v/>
@@ -6662,13 +6662,13 @@
       <c r="J93" s="64" t="s">
         <v>38</v>
       </c>
-      <c r="K93" s="120" t="s">
+      <c r="K93" s="143" t="s">
         <v>40</v>
       </c>
-      <c r="L93" s="120"/>
-      <c r="M93" s="120"/>
-      <c r="N93" s="120"/>
-      <c r="O93" s="120"/>
+      <c r="L93" s="143"/>
+      <c r="M93" s="143"/>
+      <c r="N93" s="143"/>
+      <c r="O93" s="143"/>
       <c r="P93" s="60" t="s">
         <v>124</v>
       </c>
@@ -6684,14 +6684,14 @@
       <c r="H94" s="7"/>
       <c r="I94" s="7"/>
       <c r="J94" s="7"/>
-      <c r="K94" s="121" t="str">
+      <c r="K94" s="142" t="str">
         <f>+IF(D95="","",IF(D94&lt;0,Sheet2!$C$64,VLOOKUP(D95,Sheet2!$A$64:$C$68,3,TRUE)))</f>
         <v/>
       </c>
-      <c r="L94" s="121"/>
-      <c r="M94" s="121"/>
-      <c r="N94" s="121"/>
-      <c r="O94" s="121"/>
+      <c r="L94" s="142"/>
+      <c r="M94" s="142"/>
+      <c r="N94" s="142"/>
+      <c r="O94" s="142"/>
       <c r="P94" s="28" t="str">
         <f>+IF(K94="","",VLOOKUP(K94,Sheet2!$C$64:$D$68,2,FALSE))</f>
         <v/>
@@ -6723,14 +6723,14 @@
         <f>+IF(D95="","",AVERAGE(D95:G95))</f>
         <v/>
       </c>
-      <c r="K95" s="121" t="str">
+      <c r="K95" s="142" t="str">
         <f>+IF(J95="","",IF(AND(C94&lt;0,D94&lt;0),Sheet2!$C$70,VLOOKUP(J95,Sheet2!$A$70:$C$74,3,TRUE)))</f>
         <v/>
       </c>
-      <c r="L95" s="121"/>
-      <c r="M95" s="121"/>
-      <c r="N95" s="121"/>
-      <c r="O95" s="121"/>
+      <c r="L95" s="142"/>
+      <c r="M95" s="142"/>
+      <c r="N95" s="142"/>
+      <c r="O95" s="142"/>
       <c r="P95" s="28" t="str">
         <f>+IF(K95="","",VLOOKUP(K95,Sheet2!$C$70:$D$74,2,FALSE))</f>
         <v/>
@@ -6777,13 +6777,13 @@
       <c r="J97" s="64" t="s">
         <v>38</v>
       </c>
-      <c r="K97" s="120" t="s">
+      <c r="K97" s="143" t="s">
         <v>40</v>
       </c>
-      <c r="L97" s="120"/>
-      <c r="M97" s="120"/>
-      <c r="N97" s="120"/>
-      <c r="O97" s="120"/>
+      <c r="L97" s="143"/>
+      <c r="M97" s="143"/>
+      <c r="N97" s="143"/>
+      <c r="O97" s="143"/>
       <c r="P97" s="60" t="s">
         <v>124</v>
       </c>
@@ -6799,14 +6799,14 @@
       <c r="H98" s="7"/>
       <c r="I98" s="7"/>
       <c r="J98" s="7"/>
-      <c r="K98" s="121" t="str">
+      <c r="K98" s="142" t="str">
         <f>+IF(D99="","",IF(D98&lt;0,Sheet2!$C$78,VLOOKUP(D99,Sheet2!$A$78:$C$82,3,TRUE)))</f>
         <v/>
       </c>
-      <c r="L98" s="121"/>
-      <c r="M98" s="121"/>
-      <c r="N98" s="121"/>
-      <c r="O98" s="121"/>
+      <c r="L98" s="142"/>
+      <c r="M98" s="142"/>
+      <c r="N98" s="142"/>
+      <c r="O98" s="142"/>
       <c r="P98" s="28" t="str">
         <f>+IF(K98="","",VLOOKUP(K98,Sheet2!$C$78:$D$82,2,FALSE))</f>
         <v/>
@@ -6838,14 +6838,14 @@
         <f>+IF(D99="","",AVERAGE(D99:G99))</f>
         <v/>
       </c>
-      <c r="K99" s="121" t="str">
+      <c r="K99" s="142" t="str">
         <f>+IF(J99="","",IF(AND(E98&lt;0,D98&lt;0),Sheet2!$C$84,VLOOKUP(J99,Sheet2!$A$84:$C$88,3,TRUE)))</f>
         <v/>
       </c>
-      <c r="L99" s="121"/>
-      <c r="M99" s="121"/>
-      <c r="N99" s="121"/>
-      <c r="O99" s="121"/>
+      <c r="L99" s="142"/>
+      <c r="M99" s="142"/>
+      <c r="N99" s="142"/>
+      <c r="O99" s="142"/>
       <c r="P99" s="28" t="str">
         <f>+IF(K99="","",VLOOKUP(K99,Sheet2!$C$84:$D$88,2,FALSE))</f>
         <v/>
@@ -6897,13 +6897,13 @@
       <c r="J101" s="64" t="s">
         <v>38</v>
       </c>
-      <c r="K101" s="120" t="s">
+      <c r="K101" s="143" t="s">
         <v>40</v>
       </c>
-      <c r="L101" s="120"/>
-      <c r="M101" s="120"/>
-      <c r="N101" s="120"/>
-      <c r="O101" s="120"/>
+      <c r="L101" s="143"/>
+      <c r="M101" s="143"/>
+      <c r="N101" s="143"/>
+      <c r="O101" s="143"/>
       <c r="P101" s="60" t="s">
         <v>124</v>
       </c>
@@ -6919,14 +6919,14 @@
       <c r="H102" s="7"/>
       <c r="I102" s="7"/>
       <c r="J102" s="7"/>
-      <c r="K102" s="121" t="str">
+      <c r="K102" s="142" t="str">
         <f>+IF(D103="","",VLOOKUP(D103,Sheet2!$A$92:$C$94,3,TRUE))</f>
         <v/>
       </c>
-      <c r="L102" s="121"/>
-      <c r="M102" s="121"/>
-      <c r="N102" s="121"/>
-      <c r="O102" s="121"/>
+      <c r="L102" s="142"/>
+      <c r="M102" s="142"/>
+      <c r="N102" s="142"/>
+      <c r="O102" s="142"/>
       <c r="P102" s="28" t="str">
         <f>+IF(D103="","",VLOOKUP(D103,Sheet2!$A$92:$C$94,2,TRUE))</f>
         <v/>
@@ -6958,14 +6958,14 @@
         <f>+IF(D103="","",AVERAGE(D103:G103))</f>
         <v/>
       </c>
-      <c r="K103" s="121" t="str">
+      <c r="K103" s="142" t="str">
         <f>+IF(J103="","",VLOOKUP(J103,Sheet2!$A$96:$C$98,3,TRUE))</f>
         <v/>
       </c>
-      <c r="L103" s="121"/>
-      <c r="M103" s="121"/>
-      <c r="N103" s="121"/>
-      <c r="O103" s="121"/>
+      <c r="L103" s="142"/>
+      <c r="M103" s="142"/>
+      <c r="N103" s="142"/>
+      <c r="O103" s="142"/>
       <c r="P103" s="28" t="str">
         <f>+IF(J103="","",VLOOKUP(J103,Sheet2!$A$96:$C$98,2,TRUE))</f>
         <v/>
@@ -7012,13 +7012,13 @@
       <c r="J105" s="64" t="s">
         <v>38</v>
       </c>
-      <c r="K105" s="120" t="s">
+      <c r="K105" s="143" t="s">
         <v>40</v>
       </c>
-      <c r="L105" s="120"/>
-      <c r="M105" s="120"/>
-      <c r="N105" s="120"/>
-      <c r="O105" s="120"/>
+      <c r="L105" s="143"/>
+      <c r="M105" s="143"/>
+      <c r="N105" s="143"/>
+      <c r="O105" s="143"/>
       <c r="P105" s="60" t="s">
         <v>124</v>
       </c>
@@ -7047,14 +7047,14 @@
       <c r="H107" s="7"/>
       <c r="I107" s="7"/>
       <c r="J107" s="7"/>
-      <c r="K107" s="121" t="str">
+      <c r="K107" s="142" t="str">
         <f>+IF(D108="","",IF(D106&lt;0,Sheet2!$C$104,VLOOKUP(D108,Sheet2!$A$102:$C$104,3,TRUE)))</f>
         <v/>
       </c>
-      <c r="L107" s="121"/>
-      <c r="M107" s="121"/>
-      <c r="N107" s="121"/>
-      <c r="O107" s="121"/>
+      <c r="L107" s="142"/>
+      <c r="M107" s="142"/>
+      <c r="N107" s="142"/>
+      <c r="O107" s="142"/>
       <c r="P107" s="28" t="str">
         <f>+IF(K107="","",VLOOKUP(K107,Sheet2!$C$102:$D$107,2,FALSE))</f>
         <v/>
@@ -7090,14 +7090,14 @@
         <f>+IF(D108="","",AVERAGE(D108:G108))</f>
         <v/>
       </c>
-      <c r="K108" s="136" t="str">
+      <c r="K108" s="144" t="str">
         <f>+IF(J108="","",IF(AND(D106&lt;0,E106&lt;0),Sheet2!$C$107,VLOOKUP(J108,Sheet2!$A$105:$C$107,3,TRUE)))</f>
         <v/>
       </c>
-      <c r="L108" s="136"/>
-      <c r="M108" s="136"/>
-      <c r="N108" s="136"/>
-      <c r="O108" s="136"/>
+      <c r="L108" s="144"/>
+      <c r="M108" s="144"/>
+      <c r="N108" s="144"/>
+      <c r="O108" s="144"/>
       <c r="P108" s="32" t="str">
         <f>+IF(K108="","",VLOOKUP(K108,Sheet2!$C$102:$D$107,2,FALSE))</f>
         <v/>
@@ -7107,40 +7107,40 @@
       <c r="P109" s="10"/>
     </row>
     <row r="110" spans="2:16" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B110" s="122" t="s">
+      <c r="B110" s="123" t="s">
         <v>48</v>
       </c>
-      <c r="C110" s="123"/>
-      <c r="D110" s="123"/>
-      <c r="E110" s="123"/>
-      <c r="F110" s="123"/>
-      <c r="G110" s="123"/>
-      <c r="H110" s="123"/>
-      <c r="I110" s="123"/>
-      <c r="J110" s="123"/>
-      <c r="K110" s="123"/>
-      <c r="L110" s="123"/>
-      <c r="M110" s="123"/>
-      <c r="N110" s="123"/>
-      <c r="O110" s="123"/>
-      <c r="P110" s="124"/>
+      <c r="C110" s="124"/>
+      <c r="D110" s="124"/>
+      <c r="E110" s="124"/>
+      <c r="F110" s="124"/>
+      <c r="G110" s="124"/>
+      <c r="H110" s="124"/>
+      <c r="I110" s="124"/>
+      <c r="J110" s="124"/>
+      <c r="K110" s="124"/>
+      <c r="L110" s="124"/>
+      <c r="M110" s="124"/>
+      <c r="N110" s="124"/>
+      <c r="O110" s="124"/>
+      <c r="P110" s="125"/>
     </row>
     <row r="111" spans="2:16" x14ac:dyDescent="0.25">
-      <c r="B111" s="125"/>
-      <c r="C111" s="126"/>
-      <c r="D111" s="126"/>
-      <c r="E111" s="126"/>
-      <c r="F111" s="126"/>
-      <c r="G111" s="126"/>
-      <c r="H111" s="126"/>
-      <c r="I111" s="126"/>
-      <c r="J111" s="126"/>
-      <c r="K111" s="126"/>
-      <c r="L111" s="126"/>
-      <c r="M111" s="126"/>
-      <c r="N111" s="126"/>
-      <c r="O111" s="126"/>
-      <c r="P111" s="127"/>
+      <c r="B111" s="137"/>
+      <c r="C111" s="135"/>
+      <c r="D111" s="135"/>
+      <c r="E111" s="135"/>
+      <c r="F111" s="135"/>
+      <c r="G111" s="135"/>
+      <c r="H111" s="135"/>
+      <c r="I111" s="135"/>
+      <c r="J111" s="135"/>
+      <c r="K111" s="135"/>
+      <c r="L111" s="135"/>
+      <c r="M111" s="135"/>
+      <c r="N111" s="135"/>
+      <c r="O111" s="135"/>
+      <c r="P111" s="138"/>
     </row>
     <row r="112" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B112" s="65"/>
@@ -7171,13 +7171,13 @@
       <c r="J112" s="64" t="s">
         <v>38</v>
       </c>
-      <c r="K112" s="120" t="s">
+      <c r="K112" s="143" t="s">
         <v>40</v>
       </c>
-      <c r="L112" s="120"/>
-      <c r="M112" s="120"/>
-      <c r="N112" s="120"/>
-      <c r="O112" s="120"/>
+      <c r="L112" s="143"/>
+      <c r="M112" s="143"/>
+      <c r="N112" s="143"/>
+      <c r="O112" s="143"/>
       <c r="P112" s="60" t="s">
         <v>124</v>
       </c>
@@ -7196,14 +7196,14 @@
         <f>+IF(D113="","",SUM(D113:H113))</f>
         <v/>
       </c>
-      <c r="K113" s="121" t="str">
+      <c r="K113" s="142" t="str">
         <f>+IF(D114="","",IF(D113&lt;0,Sheet2!$C$113,VLOOKUP(D114,Sheet2!$A$110:$C$113,3,TRUE)))</f>
         <v/>
       </c>
-      <c r="L113" s="121"/>
-      <c r="M113" s="121"/>
-      <c r="N113" s="121"/>
-      <c r="O113" s="121"/>
+      <c r="L113" s="142"/>
+      <c r="M113" s="142"/>
+      <c r="N113" s="142"/>
+      <c r="O113" s="142"/>
       <c r="P113" s="28" t="str">
         <f>+IF(K113="","",VLOOKUP(K113,Sheet2!$C$110:$D$117,2,FALSE))</f>
         <v/>
@@ -7235,14 +7235,14 @@
       </c>
       <c r="I114" s="7"/>
       <c r="J114" s="7"/>
-      <c r="K114" s="121" t="str">
+      <c r="K114" s="142" t="str">
         <f>+IF(J114="","",IF(AND(D113&lt;0,E113&lt;0),Sheet2!$C$117,VLOOKUP(J114,Sheet2!$A$114:$C$117,3,TRUE)))</f>
         <v/>
       </c>
-      <c r="L114" s="121"/>
-      <c r="M114" s="121"/>
-      <c r="N114" s="121"/>
-      <c r="O114" s="121"/>
+      <c r="L114" s="142"/>
+      <c r="M114" s="142"/>
+      <c r="N114" s="142"/>
+      <c r="O114" s="142"/>
       <c r="P114" s="28" t="str">
         <f>+IF(K114="","",VLOOKUP(K114,Sheet2!$C$110:$D$117,2,FALSE))</f>
         <v/>
@@ -7288,13 +7288,13 @@
       <c r="J116" s="64" t="s">
         <v>38</v>
       </c>
-      <c r="K116" s="120" t="s">
+      <c r="K116" s="143" t="s">
         <v>40</v>
       </c>
-      <c r="L116" s="120"/>
-      <c r="M116" s="120"/>
-      <c r="N116" s="120"/>
-      <c r="O116" s="120"/>
+      <c r="L116" s="143"/>
+      <c r="M116" s="143"/>
+      <c r="N116" s="143"/>
+      <c r="O116" s="143"/>
       <c r="P116" s="60" t="s">
         <v>124</v>
       </c>
@@ -7310,14 +7310,14 @@
       <c r="H117" s="7"/>
       <c r="I117" s="7"/>
       <c r="J117" s="7"/>
-      <c r="K117" s="121" t="str">
+      <c r="K117" s="142" t="str">
         <f>+IF(D118="","",IF(D117&lt;0,Sheet2!$C$27,VLOOKUP(D118,Sheet2!$A$27:$C$31,3,TRUE)))</f>
         <v/>
       </c>
-      <c r="L117" s="121"/>
-      <c r="M117" s="121"/>
-      <c r="N117" s="121"/>
-      <c r="O117" s="121"/>
+      <c r="L117" s="142"/>
+      <c r="M117" s="142"/>
+      <c r="N117" s="142"/>
+      <c r="O117" s="142"/>
       <c r="P117" s="28" t="str">
         <f>+IF(K117="","",VLOOKUP(K117,Sheet2!$C$27:$D$31,2,FALSE))</f>
         <v/>
@@ -7349,14 +7349,14 @@
         <f>+IF(D118="","",AVERAGE(D118:G118))</f>
         <v/>
       </c>
-      <c r="K118" s="121" t="str">
+      <c r="K118" s="142" t="str">
         <f>+IF(J118="","",IF(AND(D117&lt;0,E117&lt;0),Sheet2!$C$35,VLOOKUP(J118,Sheet2!$A$35:$C$39,3,TRUE)))</f>
         <v/>
       </c>
-      <c r="L118" s="121"/>
-      <c r="M118" s="121"/>
-      <c r="N118" s="121"/>
-      <c r="O118" s="121"/>
+      <c r="L118" s="142"/>
+      <c r="M118" s="142"/>
+      <c r="N118" s="142"/>
+      <c r="O118" s="142"/>
       <c r="P118" s="28" t="str">
         <f>+IF(K118="","",VLOOKUP(K118,Sheet2!$C$35:$D$39,2,FALSE))</f>
         <v/>
@@ -7403,13 +7403,13 @@
       <c r="J120" s="64" t="s">
         <v>38</v>
       </c>
-      <c r="K120" s="120" t="s">
+      <c r="K120" s="143" t="s">
         <v>40</v>
       </c>
-      <c r="L120" s="120"/>
-      <c r="M120" s="120"/>
-      <c r="N120" s="120"/>
-      <c r="O120" s="120"/>
+      <c r="L120" s="143"/>
+      <c r="M120" s="143"/>
+      <c r="N120" s="143"/>
+      <c r="O120" s="143"/>
       <c r="P120" s="60" t="s">
         <v>124</v>
       </c>
@@ -7425,14 +7425,14 @@
       <c r="H121" s="7"/>
       <c r="I121" s="7"/>
       <c r="J121" s="7"/>
-      <c r="K121" s="121" t="str">
+      <c r="K121" s="142" t="str">
         <f>+IF(D122="","",IF(D121&lt;0,Sheet2!$C$27,VLOOKUP(D122,Sheet2!$A$27:$C$31,3,TRUE)))</f>
         <v/>
       </c>
-      <c r="L121" s="121"/>
-      <c r="M121" s="121"/>
-      <c r="N121" s="121"/>
-      <c r="O121" s="121"/>
+      <c r="L121" s="142"/>
+      <c r="M121" s="142"/>
+      <c r="N121" s="142"/>
+      <c r="O121" s="142"/>
       <c r="P121" s="28" t="str">
         <f>+IF(K121="","",VLOOKUP(K121,Sheet2!$C$27:$D$31,2,FALSE))</f>
         <v/>
@@ -7464,14 +7464,14 @@
         <f>+IF(D122="","",AVERAGE(D122:G122))</f>
         <v/>
       </c>
-      <c r="K122" s="121" t="str">
+      <c r="K122" s="142" t="str">
         <f>+IF(J122="","",IF(AND(D121&lt;0,E121&lt;0),Sheet2!$C$35,VLOOKUP(J122,Sheet2!$A$35:$C$39,3,TRUE)))</f>
         <v/>
       </c>
-      <c r="L122" s="121"/>
-      <c r="M122" s="121"/>
-      <c r="N122" s="121"/>
-      <c r="O122" s="121"/>
+      <c r="L122" s="142"/>
+      <c r="M122" s="142"/>
+      <c r="N122" s="142"/>
+      <c r="O122" s="142"/>
       <c r="P122" s="28" t="str">
         <f>+IF(K122="","",VLOOKUP(K122,Sheet2!$C$35:$D$39,2,FALSE))</f>
         <v/>
@@ -7518,13 +7518,13 @@
       <c r="J124" s="64" t="s">
         <v>38</v>
       </c>
-      <c r="K124" s="120" t="s">
+      <c r="K124" s="143" t="s">
         <v>40</v>
       </c>
-      <c r="L124" s="120"/>
-      <c r="M124" s="120"/>
-      <c r="N124" s="120"/>
-      <c r="O124" s="120"/>
+      <c r="L124" s="143"/>
+      <c r="M124" s="143"/>
+      <c r="N124" s="143"/>
+      <c r="O124" s="143"/>
       <c r="P124" s="60" t="s">
         <v>124</v>
       </c>
@@ -7553,14 +7553,14 @@
       <c r="H126" s="7"/>
       <c r="I126" s="7"/>
       <c r="J126" s="7"/>
-      <c r="K126" s="121" t="str">
+      <c r="K126" s="142" t="str">
         <f>+IF(D127="","",IF(D127&lt;0,"Company rebought its stocks in the last year.","Company didn't rebought its stocks in the last year."))</f>
         <v/>
       </c>
-      <c r="L126" s="121"/>
-      <c r="M126" s="121"/>
-      <c r="N126" s="121"/>
-      <c r="O126" s="121"/>
+      <c r="L126" s="142"/>
+      <c r="M126" s="142"/>
+      <c r="N126" s="142"/>
+      <c r="O126" s="142"/>
       <c r="P126" s="28" t="str">
         <f>+IF(D127="","",IF(D127&lt;0,5,1))</f>
         <v/>
@@ -7595,14 +7595,14 @@
         <f>+IF(D127="","",AVERAGE(D127:H127))</f>
         <v/>
       </c>
-      <c r="K127" s="121" t="str">
+      <c r="K127" s="142" t="str">
         <f>+IF(J127="","",IF(J127&lt;0,"Company usually rebuy its stocks","Company usually don't rebuy its stocks"))</f>
         <v/>
       </c>
-      <c r="L127" s="121"/>
-      <c r="M127" s="121"/>
-      <c r="N127" s="121"/>
-      <c r="O127" s="121"/>
+      <c r="L127" s="142"/>
+      <c r="M127" s="142"/>
+      <c r="N127" s="142"/>
+      <c r="O127" s="142"/>
       <c r="P127" s="28" t="str">
         <f>+IF(J127="","",IF(J127&lt;0,5,1))</f>
         <v/>
@@ -7627,40 +7627,40 @@
     </row>
     <row r="129" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="130" spans="2:16" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B130" s="122" t="s">
+      <c r="B130" s="123" t="s">
         <v>50</v>
       </c>
-      <c r="C130" s="123"/>
-      <c r="D130" s="123"/>
-      <c r="E130" s="123"/>
-      <c r="F130" s="123"/>
-      <c r="G130" s="123"/>
-      <c r="H130" s="123"/>
-      <c r="I130" s="123"/>
-      <c r="J130" s="123"/>
-      <c r="K130" s="123"/>
-      <c r="L130" s="123"/>
-      <c r="M130" s="123"/>
-      <c r="N130" s="123"/>
-      <c r="O130" s="123"/>
-      <c r="P130" s="124"/>
+      <c r="C130" s="124"/>
+      <c r="D130" s="124"/>
+      <c r="E130" s="124"/>
+      <c r="F130" s="124"/>
+      <c r="G130" s="124"/>
+      <c r="H130" s="124"/>
+      <c r="I130" s="124"/>
+      <c r="J130" s="124"/>
+      <c r="K130" s="124"/>
+      <c r="L130" s="124"/>
+      <c r="M130" s="124"/>
+      <c r="N130" s="124"/>
+      <c r="O130" s="124"/>
+      <c r="P130" s="125"/>
     </row>
     <row r="131" spans="2:16" x14ac:dyDescent="0.25">
-      <c r="B131" s="125"/>
-      <c r="C131" s="126"/>
-      <c r="D131" s="126"/>
-      <c r="E131" s="126"/>
-      <c r="F131" s="126"/>
-      <c r="G131" s="126"/>
-      <c r="H131" s="126"/>
-      <c r="I131" s="126"/>
-      <c r="J131" s="126"/>
-      <c r="K131" s="126"/>
-      <c r="L131" s="126"/>
-      <c r="M131" s="126"/>
-      <c r="N131" s="126"/>
-      <c r="O131" s="126"/>
-      <c r="P131" s="127"/>
+      <c r="B131" s="137"/>
+      <c r="C131" s="135"/>
+      <c r="D131" s="135"/>
+      <c r="E131" s="135"/>
+      <c r="F131" s="135"/>
+      <c r="G131" s="135"/>
+      <c r="H131" s="135"/>
+      <c r="I131" s="135"/>
+      <c r="J131" s="135"/>
+      <c r="K131" s="135"/>
+      <c r="L131" s="135"/>
+      <c r="M131" s="135"/>
+      <c r="N131" s="135"/>
+      <c r="O131" s="135"/>
+      <c r="P131" s="138"/>
     </row>
     <row r="132" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B132" s="65"/>
@@ -7691,13 +7691,13 @@
       <c r="J132" s="64" t="s">
         <v>38</v>
       </c>
-      <c r="K132" s="120" t="s">
+      <c r="K132" s="143" t="s">
         <v>40</v>
       </c>
-      <c r="L132" s="120"/>
-      <c r="M132" s="120"/>
-      <c r="N132" s="120"/>
-      <c r="O132" s="120"/>
+      <c r="L132" s="143"/>
+      <c r="M132" s="143"/>
+      <c r="N132" s="143"/>
+      <c r="O132" s="143"/>
       <c r="P132" s="60" t="s">
         <v>124</v>
       </c>
@@ -7714,14 +7714,14 @@
       <c r="H133" s="7"/>
       <c r="I133" s="7"/>
       <c r="J133" s="7"/>
-      <c r="K133" s="121" t="str">
+      <c r="K133" s="142" t="str">
         <f>+IF(D134="","",IF(D133&lt;0,Sheet2!$C$121,VLOOKUP(D134,Sheet2!$A$121:$C$125,3,TRUE)))</f>
         <v/>
       </c>
-      <c r="L133" s="121"/>
-      <c r="M133" s="121"/>
-      <c r="N133" s="121"/>
-      <c r="O133" s="121"/>
+      <c r="L133" s="142"/>
+      <c r="M133" s="142"/>
+      <c r="N133" s="142"/>
+      <c r="O133" s="142"/>
       <c r="P133" s="28" t="str">
         <f>+IF(K133="","",VLOOKUP(K133,Sheet2!$C$121:$D$131,2,FALSE))</f>
         <v/>
@@ -7757,14 +7757,14 @@
         <f>+IF(D134="","",AVERAGE(D134:G134))</f>
         <v/>
       </c>
-      <c r="K134" s="121" t="str">
+      <c r="K134" s="142" t="str">
         <f>+IF(J134="","",IF(AND(D133&lt;0,E133&lt;0),Sheet2!$C$127,VLOOKUP(J134,Sheet2!$A$127:$C$131,3,TRUE)))</f>
         <v/>
       </c>
-      <c r="L134" s="121"/>
-      <c r="M134" s="121"/>
-      <c r="N134" s="121"/>
-      <c r="O134" s="121"/>
+      <c r="L134" s="142"/>
+      <c r="M134" s="142"/>
+      <c r="N134" s="142"/>
+      <c r="O134" s="142"/>
       <c r="P134" s="28" t="str">
         <f>+IF(K134="","",VLOOKUP(K134,Sheet2!$C$121:$D$131,2,FALSE))</f>
         <v/>
@@ -7794,14 +7794,14 @@
       <c r="H136" s="7"/>
       <c r="I136" s="7"/>
       <c r="J136" s="7"/>
-      <c r="K136" s="121" t="str">
+      <c r="K136" s="142" t="str">
         <f>+IF(C136="","",IF(C136&gt;C133,Sheet2!$A$133,Sheet2!$A$134))</f>
         <v/>
       </c>
-      <c r="L136" s="121"/>
-      <c r="M136" s="121"/>
-      <c r="N136" s="121"/>
-      <c r="O136" s="121"/>
+      <c r="L136" s="142"/>
+      <c r="M136" s="142"/>
+      <c r="N136" s="142"/>
+      <c r="O136" s="142"/>
       <c r="P136" s="56" t="str">
         <f>+IF(K136="","",VLOOKUP(K136,Sheet2!$A$133:$B$134,2,FALSE))</f>
         <v/>
@@ -7848,13 +7848,13 @@
       <c r="J138" s="64" t="s">
         <v>38</v>
       </c>
-      <c r="K138" s="120" t="s">
+      <c r="K138" s="143" t="s">
         <v>40</v>
       </c>
-      <c r="L138" s="120"/>
-      <c r="M138" s="120"/>
-      <c r="N138" s="120"/>
-      <c r="O138" s="120"/>
+      <c r="L138" s="143"/>
+      <c r="M138" s="143"/>
+      <c r="N138" s="143"/>
+      <c r="O138" s="143"/>
       <c r="P138" s="60" t="s">
         <v>124</v>
       </c>
@@ -7874,14 +7874,14 @@
         <f>+IF(D139="","",AVERAGE(D139:H139))</f>
         <v/>
       </c>
-      <c r="K139" s="121" t="str">
+      <c r="K139" s="142" t="str">
         <f>+IF(C139="","",VLOOKUP(C139,Sheet2!$A$138:$C$145,3,TRUE))</f>
         <v/>
       </c>
-      <c r="L139" s="121"/>
-      <c r="M139" s="121"/>
-      <c r="N139" s="121"/>
-      <c r="O139" s="121"/>
+      <c r="L139" s="142"/>
+      <c r="M139" s="142"/>
+      <c r="N139" s="142"/>
+      <c r="O139" s="142"/>
       <c r="P139" s="28" t="str">
         <f>+IF(C139="","",VLOOKUP(C139,Sheet2!$A$138:$C$145,2,TRUE))</f>
         <v/>
@@ -7915,14 +7915,14 @@
         <f>+IF(D140="","",AVERAGE(D140:G140))</f>
         <v/>
       </c>
-      <c r="K140" s="121" t="str">
+      <c r="K140" s="142" t="str">
         <f>+IF(J139="","",VLOOKUP(J139,Sheet2!$A$147:$C$153,3,TRUE))</f>
         <v/>
       </c>
-      <c r="L140" s="121"/>
-      <c r="M140" s="121"/>
-      <c r="N140" s="121"/>
-      <c r="O140" s="121"/>
+      <c r="L140" s="142"/>
+      <c r="M140" s="142"/>
+      <c r="N140" s="142"/>
+      <c r="O140" s="142"/>
       <c r="P140" s="28" t="str">
         <f>+IF(J139="","",VLOOKUP(J139,Sheet2!$A$147:$C$153,2,TRUE))</f>
         <v/>
@@ -7938,14 +7938,14 @@
       <c r="H141" s="7"/>
       <c r="I141" s="7"/>
       <c r="J141" s="7"/>
-      <c r="K141" s="121" t="str">
+      <c r="K141" s="142" t="str">
         <f>+IF(C139="","",IF(C139&lt;$C$203,Sheet2!$A$155,IF(C139&lt;($C$203*1.1),Sheet2!$A$156,IF(C139&lt;($C$203*1.2),Sheet2!$A$157,Sheet2!A158))))</f>
         <v/>
       </c>
-      <c r="L141" s="121"/>
-      <c r="M141" s="121"/>
-      <c r="N141" s="121"/>
-      <c r="O141" s="121"/>
+      <c r="L141" s="142"/>
+      <c r="M141" s="142"/>
+      <c r="N141" s="142"/>
+      <c r="O141" s="142"/>
       <c r="P141" s="56" t="str">
         <f>+IF(K141="","",VLOOKUP(K141,Sheet2!$A$155:$B$158,2,FALSE))</f>
         <v/>
@@ -7963,14 +7963,14 @@
       <c r="H142" s="7"/>
       <c r="I142" s="7"/>
       <c r="J142" s="7"/>
-      <c r="K142" s="121" t="str">
+      <c r="K142" s="142" t="str">
         <f>+IF(C142="","",IF(C142&gt;C139,Sheet2!$A$161,Sheet2!$A$160))</f>
         <v/>
       </c>
-      <c r="L142" s="121"/>
-      <c r="M142" s="121"/>
-      <c r="N142" s="121"/>
-      <c r="O142" s="121"/>
+      <c r="L142" s="142"/>
+      <c r="M142" s="142"/>
+      <c r="N142" s="142"/>
+      <c r="O142" s="142"/>
       <c r="P142" s="56" t="str">
         <f>+IF(K142="","",VLOOKUP(K142,Sheet2!$A$160:$B$161,2,FALSE))</f>
         <v/>
@@ -8017,13 +8017,13 @@
       <c r="J144" s="64" t="s">
         <v>38</v>
       </c>
-      <c r="K144" s="120" t="s">
+      <c r="K144" s="143" t="s">
         <v>40</v>
       </c>
-      <c r="L144" s="120"/>
-      <c r="M144" s="120"/>
-      <c r="N144" s="120"/>
-      <c r="O144" s="120"/>
+      <c r="L144" s="143"/>
+      <c r="M144" s="143"/>
+      <c r="N144" s="143"/>
+      <c r="O144" s="143"/>
       <c r="P144" s="60" t="s">
         <v>124</v>
       </c>
@@ -8040,14 +8040,14 @@
       <c r="H145" s="7"/>
       <c r="I145" s="7"/>
       <c r="J145" s="7"/>
-      <c r="K145" s="121" t="str">
+      <c r="K145" s="142" t="str">
         <f>+IF(C145="","",VLOOKUP(C145,Sheet2!$A$138:$C$145,3,TRUE))</f>
         <v/>
       </c>
-      <c r="L145" s="121"/>
-      <c r="M145" s="121"/>
-      <c r="N145" s="121"/>
-      <c r="O145" s="121"/>
+      <c r="L145" s="142"/>
+      <c r="M145" s="142"/>
+      <c r="N145" s="142"/>
+      <c r="O145" s="142"/>
       <c r="P145" s="28" t="str">
         <f>+IF(C145="","",VLOOKUP(C145,Sheet2!$A$138:$C$145,2,TRUE))</f>
         <v/>
@@ -8081,14 +8081,14 @@
         <f>+IF(D146="","",AVERAGE(D146:G146))</f>
         <v/>
       </c>
-      <c r="K146" s="121" t="str">
+      <c r="K146" s="142" t="str">
         <f>+IF(C145="","",IF(C145&lt;$D$203,Sheet2!$A$155,IF(C145&lt;($D$203*1.1),Sheet2!$A$156,IF(C145&lt;($D$203*1.2),Sheet2!$A$157,Sheet2!A158))))</f>
         <v/>
       </c>
-      <c r="L146" s="121"/>
-      <c r="M146" s="121"/>
-      <c r="N146" s="121"/>
-      <c r="O146" s="121"/>
+      <c r="L146" s="142"/>
+      <c r="M146" s="142"/>
+      <c r="N146" s="142"/>
+      <c r="O146" s="142"/>
       <c r="P146" s="56" t="str">
         <f>+IF(K146="","",VLOOKUP(K146,Sheet2!$A$155:$B$158,2,FALSE))</f>
         <v/>
@@ -8135,13 +8135,13 @@
       <c r="J148" s="64" t="s">
         <v>38</v>
       </c>
-      <c r="K148" s="120" t="s">
+      <c r="K148" s="143" t="s">
         <v>40</v>
       </c>
-      <c r="L148" s="120"/>
-      <c r="M148" s="120"/>
-      <c r="N148" s="120"/>
-      <c r="O148" s="120"/>
+      <c r="L148" s="143"/>
+      <c r="M148" s="143"/>
+      <c r="N148" s="143"/>
+      <c r="O148" s="143"/>
       <c r="P148" s="60" t="s">
         <v>124</v>
       </c>
@@ -8158,14 +8158,14 @@
       <c r="H149" s="7"/>
       <c r="I149" s="7"/>
       <c r="J149" s="7"/>
-      <c r="K149" s="121" t="str">
+      <c r="K149" s="142" t="str">
         <f>+IF(C149="","",VLOOKUP(C149,Sheet2!$A$164:$C$170,3,TRUE))</f>
         <v/>
       </c>
-      <c r="L149" s="121"/>
-      <c r="M149" s="121"/>
-      <c r="N149" s="121"/>
-      <c r="O149" s="121"/>
+      <c r="L149" s="142"/>
+      <c r="M149" s="142"/>
+      <c r="N149" s="142"/>
+      <c r="O149" s="142"/>
       <c r="P149" s="28" t="str">
         <f>+IF(C149="","",VLOOKUP(C149,Sheet2!$A$164:$C$170,2,TRUE))</f>
         <v/>
@@ -8199,14 +8199,14 @@
         <f>+IF(D150="","",AVERAGE(D150:G150))</f>
         <v/>
       </c>
-      <c r="K150" s="121" t="str">
+      <c r="K150" s="142" t="str">
         <f>+IF(C149="","",IF(C149&lt;$E$203,Sheet2!$A$155,IF(C149&lt;($E$203*1.1),Sheet2!$A$156,IF(C149&lt;($E$203*1.2),Sheet2!$A$157,Sheet2!A158))))</f>
         <v/>
       </c>
-      <c r="L150" s="121"/>
-      <c r="M150" s="121"/>
-      <c r="N150" s="121"/>
-      <c r="O150" s="121"/>
+      <c r="L150" s="142"/>
+      <c r="M150" s="142"/>
+      <c r="N150" s="142"/>
+      <c r="O150" s="142"/>
       <c r="P150" s="56" t="str">
         <f>+IF(K150="","",VLOOKUP(K150,Sheet2!$A$155:$B$158,2,FALSE))</f>
         <v/>
@@ -8253,13 +8253,13 @@
       <c r="J152" s="64" t="s">
         <v>38</v>
       </c>
-      <c r="K152" s="120" t="s">
+      <c r="K152" s="143" t="s">
         <v>40</v>
       </c>
-      <c r="L152" s="120"/>
-      <c r="M152" s="120"/>
-      <c r="N152" s="120"/>
-      <c r="O152" s="120"/>
+      <c r="L152" s="143"/>
+      <c r="M152" s="143"/>
+      <c r="N152" s="143"/>
+      <c r="O152" s="143"/>
       <c r="P152" s="60" t="s">
         <v>124</v>
       </c>
@@ -8276,11 +8276,11 @@
       <c r="H153" s="7"/>
       <c r="I153" s="7"/>
       <c r="J153" s="7"/>
-      <c r="K153" s="121"/>
-      <c r="L153" s="121"/>
-      <c r="M153" s="121"/>
-      <c r="N153" s="121"/>
-      <c r="O153" s="121"/>
+      <c r="K153" s="142"/>
+      <c r="L153" s="142"/>
+      <c r="M153" s="142"/>
+      <c r="N153" s="142"/>
+      <c r="O153" s="142"/>
       <c r="P153" s="28"/>
     </row>
     <row r="154" spans="2:16" x14ac:dyDescent="0.25">
@@ -8311,14 +8311,14 @@
         <f>+IF(D154="","",AVERAGE(D154:G154))</f>
         <v/>
       </c>
-      <c r="K154" s="121" t="str">
+      <c r="K154" s="142" t="str">
         <f>+IF(C153="","",IF(C153&lt;$F$203,Sheet2!$A$155,IF(C153&lt;($F$203*1.1),Sheet2!$A$156,IF(C153&lt;($F$203*1.2),Sheet2!$A$157,Sheet2!A158))))</f>
         <v/>
       </c>
-      <c r="L154" s="121"/>
-      <c r="M154" s="121"/>
-      <c r="N154" s="121"/>
-      <c r="O154" s="121"/>
+      <c r="L154" s="142"/>
+      <c r="M154" s="142"/>
+      <c r="N154" s="142"/>
+      <c r="O154" s="142"/>
       <c r="P154" s="56" t="str">
         <f>+IF(K154="","",VLOOKUP(K154,Sheet2!$A$155:$B$158,2,FALSE))</f>
         <v/>
@@ -8365,13 +8365,13 @@
       <c r="J156" s="64" t="s">
         <v>38</v>
       </c>
-      <c r="K156" s="120" t="s">
+      <c r="K156" s="143" t="s">
         <v>40</v>
       </c>
-      <c r="L156" s="120"/>
-      <c r="M156" s="120"/>
-      <c r="N156" s="120"/>
-      <c r="O156" s="120"/>
+      <c r="L156" s="143"/>
+      <c r="M156" s="143"/>
+      <c r="N156" s="143"/>
+      <c r="O156" s="143"/>
       <c r="P156" s="60" t="s">
         <v>124</v>
       </c>
@@ -8388,14 +8388,14 @@
       <c r="H157" s="7"/>
       <c r="I157" s="7"/>
       <c r="J157" s="7"/>
-      <c r="K157" s="121" t="str">
+      <c r="K157" s="142" t="str">
         <f>+IF(C157="","",VLOOKUP(C157,Sheet2!$A$173:$C$179,3,TRUE))</f>
         <v/>
       </c>
-      <c r="L157" s="121"/>
-      <c r="M157" s="121"/>
-      <c r="N157" s="121"/>
-      <c r="O157" s="121"/>
+      <c r="L157" s="142"/>
+      <c r="M157" s="142"/>
+      <c r="N157" s="142"/>
+      <c r="O157" s="142"/>
       <c r="P157" s="28" t="str">
         <f>+IF(C157="","",VLOOKUP(C157,Sheet2!$A$173:$C$179,2,TRUE))</f>
         <v/>
@@ -8429,14 +8429,14 @@
         <f>+IF(D158="","",AVERAGE(D158:G158))</f>
         <v/>
       </c>
-      <c r="K158" s="121" t="str">
+      <c r="K158" s="142" t="str">
         <f>+IF(C157="","",IF(C157&lt;$G$203,Sheet2!$A$155,IF(C157&lt;($G$203*1.1),Sheet2!$A$156,IF(C157&lt;($G$203*1.2),Sheet2!$A$157,Sheet2!A158))))</f>
         <v/>
       </c>
-      <c r="L158" s="121"/>
-      <c r="M158" s="121"/>
-      <c r="N158" s="121"/>
-      <c r="O158" s="121"/>
+      <c r="L158" s="142"/>
+      <c r="M158" s="142"/>
+      <c r="N158" s="142"/>
+      <c r="O158" s="142"/>
       <c r="P158" s="56" t="str">
         <f>+IF(K158="","",VLOOKUP(K158,Sheet2!$A$155:$B$158,2,FALSE))</f>
         <v/>
@@ -8466,13 +8466,13 @@
       <c r="H160" s="66"/>
       <c r="I160" s="66"/>
       <c r="J160" s="66"/>
-      <c r="K160" s="120" t="s">
+      <c r="K160" s="143" t="s">
         <v>40</v>
       </c>
-      <c r="L160" s="120"/>
-      <c r="M160" s="120"/>
-      <c r="N160" s="120"/>
-      <c r="O160" s="120"/>
+      <c r="L160" s="143"/>
+      <c r="M160" s="143"/>
+      <c r="N160" s="143"/>
+      <c r="O160" s="143"/>
       <c r="P160" s="60" t="s">
         <v>124</v>
       </c>
@@ -8492,14 +8492,14 @@
       <c r="H161" s="7"/>
       <c r="I161" s="7"/>
       <c r="J161" s="7"/>
-      <c r="K161" s="121" t="str">
+      <c r="K161" s="142" t="str">
         <f>+IF(C161="","",IF(C161&gt;($J$203*1.1),Sheet2!$A$182,IF(Sheet1!C161&gt;(Sheet1!$J$203*0.8),Sheet2!A183,IF(Sheet1!C161&gt;(Sheet1!J203*0.6),Sheet2!A184,Sheet2!A185))))</f>
         <v/>
       </c>
-      <c r="L161" s="121"/>
-      <c r="M161" s="121"/>
-      <c r="N161" s="121"/>
-      <c r="O161" s="121"/>
+      <c r="L161" s="142"/>
+      <c r="M161" s="142"/>
+      <c r="N161" s="142"/>
+      <c r="O161" s="142"/>
       <c r="P161" s="56" t="str">
         <f>+IF(K161="","",VLOOKUP(K161,Sheet2!$A$182:$B$185,2,FALSE))</f>
         <v/>
@@ -8520,14 +8520,14 @@
       <c r="H162" s="7"/>
       <c r="I162" s="7"/>
       <c r="J162" s="7"/>
-      <c r="K162" s="121" t="str">
+      <c r="K162" s="142" t="str">
         <f>+IF(C162="","",IF(C162&gt;($K$203*1.1),Sheet2!$A$182,IF(Sheet1!C162&gt;(Sheet1!$K$203*0.8),Sheet2!A183,IF(Sheet1!C162&gt;(Sheet1!K203*0.6),Sheet2!A184,Sheet2!A185))))</f>
         <v/>
       </c>
-      <c r="L162" s="121"/>
-      <c r="M162" s="121"/>
-      <c r="N162" s="121"/>
-      <c r="O162" s="121"/>
+      <c r="L162" s="142"/>
+      <c r="M162" s="142"/>
+      <c r="N162" s="142"/>
+      <c r="O162" s="142"/>
       <c r="P162" s="56" t="str">
         <f>+IF(K162="","",VLOOKUP(K162,Sheet2!$A$182:$B$185,2,FALSE))</f>
         <v/>
@@ -8574,13 +8574,13 @@
       <c r="J164" s="64" t="s">
         <v>38</v>
       </c>
-      <c r="K164" s="120" t="s">
+      <c r="K164" s="143" t="s">
         <v>40</v>
       </c>
-      <c r="L164" s="120"/>
-      <c r="M164" s="120"/>
-      <c r="N164" s="120"/>
-      <c r="O164" s="120"/>
+      <c r="L164" s="143"/>
+      <c r="M164" s="143"/>
+      <c r="N164" s="143"/>
+      <c r="O164" s="143"/>
       <c r="P164" s="60" t="s">
         <v>124</v>
       </c>
@@ -8600,14 +8600,14 @@
         <f>+IF(D165="","",AVERAGE(D165:H165))</f>
         <v/>
       </c>
-      <c r="K165" s="121" t="str">
+      <c r="K165" s="142" t="str">
         <f>+IF(C165="","",VLOOKUP(C165,Sheet2!$A$189:$C$195,3,TRUE))</f>
         <v/>
       </c>
-      <c r="L165" s="121"/>
-      <c r="M165" s="121"/>
-      <c r="N165" s="121"/>
-      <c r="O165" s="121"/>
+      <c r="L165" s="142"/>
+      <c r="M165" s="142"/>
+      <c r="N165" s="142"/>
+      <c r="O165" s="142"/>
       <c r="P165" s="28" t="str">
         <f>+IF(C165="","",VLOOKUP(C165,Sheet2!$A$189:$C$195,2,TRUE))</f>
         <v/>
@@ -8638,14 +8638,14 @@
       <c r="H166" s="7"/>
       <c r="I166" s="7"/>
       <c r="J166" s="5"/>
-      <c r="K166" s="121" t="str">
+      <c r="K166" s="142" t="str">
         <f>+IF(J165="","",VLOOKUP(J165,Sheet2!$A$198:$C$204,3,TRUE))</f>
         <v/>
       </c>
-      <c r="L166" s="121"/>
-      <c r="M166" s="121"/>
-      <c r="N166" s="121"/>
-      <c r="O166" s="121"/>
+      <c r="L166" s="142"/>
+      <c r="M166" s="142"/>
+      <c r="N166" s="142"/>
+      <c r="O166" s="142"/>
       <c r="P166" s="28" t="str">
         <f>+IF(J165="","",VLOOKUP(J165,Sheet2!$A$198:$C$204,2,TRUE))</f>
         <v/>
@@ -8661,14 +8661,14 @@
       <c r="H167" s="7"/>
       <c r="I167" s="7"/>
       <c r="J167" s="7"/>
-      <c r="K167" s="121" t="str">
+      <c r="K167" s="142" t="str">
         <f>+IF(C165="","",IF(C165&gt;(1.15*$L$203),Sheet2!$A$206,IF(Sheet1!C165&gt;Sheet1!$L$203,Sheet2!$A$207,IF(Sheet1!C165&gt;(0.7*Sheet1!$L$203),Sheet2!$A$208,IF(Sheet1!C165&gt;(0.6*Sheet1!$L$203),Sheet2!$A$209,Sheet2!$A$210)))))</f>
         <v/>
       </c>
-      <c r="L167" s="121"/>
-      <c r="M167" s="121"/>
-      <c r="N167" s="121"/>
-      <c r="O167" s="121"/>
+      <c r="L167" s="142"/>
+      <c r="M167" s="142"/>
+      <c r="N167" s="142"/>
+      <c r="O167" s="142"/>
       <c r="P167" s="56" t="str">
         <f>+IF(K167="","",VLOOKUP(K167,Sheet2!$A$206:$B$210,2,FALSE))</f>
         <v/>
@@ -8720,13 +8720,13 @@
       <c r="J169" s="64" t="s">
         <v>38</v>
       </c>
-      <c r="K169" s="120" t="s">
+      <c r="K169" s="143" t="s">
         <v>40</v>
       </c>
-      <c r="L169" s="120"/>
-      <c r="M169" s="120"/>
-      <c r="N169" s="120"/>
-      <c r="O169" s="120"/>
+      <c r="L169" s="143"/>
+      <c r="M169" s="143"/>
+      <c r="N169" s="143"/>
+      <c r="O169" s="143"/>
       <c r="P169" s="60" t="s">
         <v>124</v>
       </c>
@@ -8746,14 +8746,14 @@
         <f>+IF(D170="","",AVERAGE(D170:H170))</f>
         <v/>
       </c>
-      <c r="K170" s="121" t="str">
+      <c r="K170" s="142" t="str">
         <f>+IF(C170="","",VLOOKUP(C170,Sheet2!$A$189:$C$195,3,TRUE))</f>
         <v/>
       </c>
-      <c r="L170" s="121"/>
-      <c r="M170" s="121"/>
-      <c r="N170" s="121"/>
-      <c r="O170" s="121"/>
+      <c r="L170" s="142"/>
+      <c r="M170" s="142"/>
+      <c r="N170" s="142"/>
+      <c r="O170" s="142"/>
       <c r="P170" s="28" t="str">
         <f>+IF(C170="","",VLOOKUP(C170,Sheet2!$A$189:$C$195,2,TRUE))</f>
         <v/>
@@ -8786,14 +8786,14 @@
       <c r="H171" s="7"/>
       <c r="I171" s="7"/>
       <c r="J171" s="5"/>
-      <c r="K171" s="121" t="str">
+      <c r="K171" s="142" t="str">
         <f>+IF(J170="","",VLOOKUP(J170,Sheet2!$A$198:$C$204,3,TRUE))</f>
         <v/>
       </c>
-      <c r="L171" s="121"/>
-      <c r="M171" s="121"/>
-      <c r="N171" s="121"/>
-      <c r="O171" s="121"/>
+      <c r="L171" s="142"/>
+      <c r="M171" s="142"/>
+      <c r="N171" s="142"/>
+      <c r="O171" s="142"/>
       <c r="P171" s="28" t="str">
         <f>+IF(J170="","",VLOOKUP(J170,Sheet2!$A$198:$C$204,2,TRUE))</f>
         <v/>
@@ -8809,14 +8809,14 @@
       <c r="H172" s="7"/>
       <c r="I172" s="7"/>
       <c r="J172" s="7"/>
-      <c r="K172" s="121" t="str">
+      <c r="K172" s="142" t="str">
         <f>+IF(C170="","",IF(C170&gt;(1.15*$M$203),Sheet2!$A$206,IF(Sheet1!C170&gt;Sheet1!$M$203,Sheet2!$A$207,IF(Sheet1!C170&gt;(0.7*Sheet1!$M$203),Sheet2!$A$208,IF(Sheet1!C170&gt;(0.6*Sheet1!$M$203),Sheet2!$A$209,Sheet2!$A$210)))))</f>
         <v/>
       </c>
-      <c r="L172" s="121"/>
-      <c r="M172" s="121"/>
-      <c r="N172" s="121"/>
-      <c r="O172" s="121"/>
+      <c r="L172" s="142"/>
+      <c r="M172" s="142"/>
+      <c r="N172" s="142"/>
+      <c r="O172" s="142"/>
       <c r="P172" s="56" t="str">
         <f>+IF(K172="","",VLOOKUP(K172,Sheet2!$A$206:$B$210,2,FALSE))</f>
         <v/>
@@ -8863,13 +8863,13 @@
       <c r="J174" s="64" t="s">
         <v>38</v>
       </c>
-      <c r="K174" s="120" t="s">
+      <c r="K174" s="143" t="s">
         <v>40</v>
       </c>
-      <c r="L174" s="120"/>
-      <c r="M174" s="120"/>
-      <c r="N174" s="120"/>
-      <c r="O174" s="120"/>
+      <c r="L174" s="143"/>
+      <c r="M174" s="143"/>
+      <c r="N174" s="143"/>
+      <c r="O174" s="143"/>
       <c r="P174" s="60" t="s">
         <v>124</v>
       </c>
@@ -8889,14 +8889,14 @@
         <f>+IF(D175="","",AVERAGE(D175:H175))</f>
         <v/>
       </c>
-      <c r="K175" s="121" t="str">
+      <c r="K175" s="142" t="str">
         <f>+IF(C175="","",VLOOKUP(C175,Sheet2!$A$214:$C$220,3,TRUE))</f>
         <v/>
       </c>
-      <c r="L175" s="121"/>
-      <c r="M175" s="121"/>
-      <c r="N175" s="121"/>
-      <c r="O175" s="121"/>
+      <c r="L175" s="142"/>
+      <c r="M175" s="142"/>
+      <c r="N175" s="142"/>
+      <c r="O175" s="142"/>
       <c r="P175" s="28" t="str">
         <f>+IF(C175="","",VLOOKUP(C175,Sheet2!$A$214:$C$220,2,TRUE))</f>
         <v/>
@@ -8927,14 +8927,14 @@
       <c r="H176" s="7"/>
       <c r="I176" s="7"/>
       <c r="J176" s="5"/>
-      <c r="K176" s="121" t="str">
+      <c r="K176" s="142" t="str">
         <f>+IF(J175="","",VLOOKUP(J175,Sheet2!$A$223:$C$229,3,TRUE))</f>
         <v/>
       </c>
-      <c r="L176" s="121"/>
-      <c r="M176" s="121"/>
-      <c r="N176" s="121"/>
-      <c r="O176" s="121"/>
+      <c r="L176" s="142"/>
+      <c r="M176" s="142"/>
+      <c r="N176" s="142"/>
+      <c r="O176" s="142"/>
       <c r="P176" s="28" t="str">
         <f>+IF(J175="","",VLOOKUP(J175,Sheet2!$A$223:$C$229,2,TRUE))</f>
         <v/>
@@ -8950,14 +8950,14 @@
       <c r="H177" s="7"/>
       <c r="I177" s="7"/>
       <c r="J177" s="7"/>
-      <c r="K177" s="121" t="str">
+      <c r="K177" s="142" t="str">
         <f>+IF(C175="","",IF(C175&gt;(1.15*$N$203),Sheet2!$A$231,IF(Sheet1!C175&gt;Sheet1!$N$203,Sheet2!$A$232,IF(Sheet1!C175&gt;(0.7*Sheet1!$N$203),Sheet2!$A$233,IF(Sheet1!C175&gt;(0.6*Sheet1!$N$203),Sheet2!$A$234,Sheet2!$A$235)))))</f>
         <v/>
       </c>
-      <c r="L177" s="121"/>
-      <c r="M177" s="121"/>
-      <c r="N177" s="121"/>
-      <c r="O177" s="121"/>
+      <c r="L177" s="142"/>
+      <c r="M177" s="142"/>
+      <c r="N177" s="142"/>
+      <c r="O177" s="142"/>
       <c r="P177" s="56" t="str">
         <f>+IF(K177="","",VLOOKUP(K177,Sheet2!$A$231:$B$235,2,FALSE))</f>
         <v/>
@@ -9004,13 +9004,13 @@
       <c r="J179" s="64" t="s">
         <v>38</v>
       </c>
-      <c r="K179" s="120" t="s">
+      <c r="K179" s="143" t="s">
         <v>40</v>
       </c>
-      <c r="L179" s="120"/>
-      <c r="M179" s="120"/>
-      <c r="N179" s="120"/>
-      <c r="O179" s="120"/>
+      <c r="L179" s="143"/>
+      <c r="M179" s="143"/>
+      <c r="N179" s="143"/>
+      <c r="O179" s="143"/>
       <c r="P179" s="60" t="s">
         <v>124</v>
       </c>
@@ -9045,14 +9045,14 @@
         <f>+IF(D180="","",AVERAGE(D180:H180))</f>
         <v/>
       </c>
-      <c r="K180" s="121" t="str">
+      <c r="K180" s="142" t="str">
         <f>+IF(D180="","",VLOOKUP(D180,Sheet2!$A$239:$C$245,3,TRUE))</f>
         <v/>
       </c>
-      <c r="L180" s="121"/>
-      <c r="M180" s="121"/>
-      <c r="N180" s="121"/>
-      <c r="O180" s="121"/>
+      <c r="L180" s="142"/>
+      <c r="M180" s="142"/>
+      <c r="N180" s="142"/>
+      <c r="O180" s="142"/>
       <c r="P180" s="28" t="str">
         <f>+IF(D180="","",VLOOKUP(D180,Sheet2!$A$239:$C$245,2,TRUE))</f>
         <v/>
@@ -9128,13 +9128,13 @@
       <c r="J183" s="64" t="s">
         <v>38</v>
       </c>
-      <c r="K183" s="120" t="s">
+      <c r="K183" s="143" t="s">
         <v>40</v>
       </c>
-      <c r="L183" s="120"/>
-      <c r="M183" s="120"/>
-      <c r="N183" s="120"/>
-      <c r="O183" s="120"/>
+      <c r="L183" s="143"/>
+      <c r="M183" s="143"/>
+      <c r="N183" s="143"/>
+      <c r="O183" s="143"/>
       <c r="P183" s="60" t="s">
         <v>124</v>
       </c>
@@ -9154,14 +9154,14 @@
         <f>+IF(D184="","",AVERAGE(D184:H184))</f>
         <v/>
       </c>
-      <c r="K184" s="121" t="str">
+      <c r="K184" s="142" t="str">
         <f>+IF(C184="","",VLOOKUP(C184,Sheet2!$A$248:$C$252,3,TRUE))</f>
         <v/>
       </c>
-      <c r="L184" s="121"/>
-      <c r="M184" s="121"/>
-      <c r="N184" s="121"/>
-      <c r="O184" s="121"/>
+      <c r="L184" s="142"/>
+      <c r="M184" s="142"/>
+      <c r="N184" s="142"/>
+      <c r="O184" s="142"/>
       <c r="P184" s="28" t="str">
         <f>+IF(C184="","",VLOOKUP(C184,Sheet2!$A$248:$C$252,2,TRUE))</f>
         <v/>
@@ -9240,13 +9240,13 @@
       <c r="J187" s="64" t="s">
         <v>38</v>
       </c>
-      <c r="K187" s="120" t="s">
+      <c r="K187" s="143" t="s">
         <v>40</v>
       </c>
-      <c r="L187" s="120"/>
-      <c r="M187" s="120"/>
-      <c r="N187" s="120"/>
-      <c r="O187" s="120"/>
+      <c r="L187" s="143"/>
+      <c r="M187" s="143"/>
+      <c r="N187" s="143"/>
+      <c r="O187" s="143"/>
       <c r="P187" s="60" t="s">
         <v>124</v>
       </c>
@@ -9266,14 +9266,14 @@
         <f>+IF(D188="","",AVERAGE(D188:H188))</f>
         <v/>
       </c>
-      <c r="K188" s="121" t="str">
+      <c r="K188" s="142" t="str">
         <f>+IF(C188="","",VLOOKUP(C188,Sheet2!$A$255:$C$259,3,TRUE))</f>
         <v/>
       </c>
-      <c r="L188" s="121"/>
-      <c r="M188" s="121"/>
-      <c r="N188" s="121"/>
-      <c r="O188" s="121"/>
+      <c r="L188" s="142"/>
+      <c r="M188" s="142"/>
+      <c r="N188" s="142"/>
+      <c r="O188" s="142"/>
       <c r="P188" s="28" t="str">
         <f>+IF(C188="","",VLOOKUP(C188,Sheet2!$A$255:$C$259,2,TRUE))</f>
         <v/>
@@ -9571,23 +9571,23 @@
     </row>
     <row r="204" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="205" spans="2:16" ht="23.25" x14ac:dyDescent="0.25">
-      <c r="B205" s="122" t="s">
+      <c r="B205" s="123" t="s">
         <v>71</v>
       </c>
-      <c r="C205" s="123"/>
-      <c r="D205" s="123"/>
-      <c r="E205" s="123"/>
-      <c r="F205" s="123"/>
-      <c r="G205" s="123"/>
-      <c r="H205" s="123"/>
-      <c r="I205" s="123"/>
-      <c r="J205" s="123"/>
-      <c r="K205" s="123"/>
-      <c r="L205" s="123"/>
-      <c r="M205" s="123"/>
-      <c r="N205" s="123"/>
-      <c r="O205" s="123"/>
-      <c r="P205" s="124"/>
+      <c r="C205" s="124"/>
+      <c r="D205" s="124"/>
+      <c r="E205" s="124"/>
+      <c r="F205" s="124"/>
+      <c r="G205" s="124"/>
+      <c r="H205" s="124"/>
+      <c r="I205" s="124"/>
+      <c r="J205" s="124"/>
+      <c r="K205" s="124"/>
+      <c r="L205" s="124"/>
+      <c r="M205" s="124"/>
+      <c r="N205" s="124"/>
+      <c r="O205" s="124"/>
+      <c r="P205" s="125"/>
     </row>
     <row r="206" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B206" s="27" t="s">
@@ -9632,13 +9632,13 @@
       <c r="J208" s="64" t="s">
         <v>38</v>
       </c>
-      <c r="K208" s="120" t="s">
+      <c r="K208" s="143" t="s">
         <v>40</v>
       </c>
-      <c r="L208" s="120"/>
-      <c r="M208" s="120"/>
-      <c r="N208" s="120"/>
-      <c r="O208" s="120"/>
+      <c r="L208" s="143"/>
+      <c r="M208" s="143"/>
+      <c r="N208" s="143"/>
+      <c r="O208" s="143"/>
       <c r="P208" s="60" t="s">
         <v>124</v>
       </c>
@@ -9716,14 +9716,14 @@
       </c>
       <c r="I211" s="7"/>
       <c r="J211" s="7"/>
-      <c r="K211" s="121" t="str">
+      <c r="K211" s="142" t="str">
         <f>+IF(D211="","",IF(D211&gt;0,"Company manages to pay their dividends","Company doesn't manage to pay their dividends"))</f>
         <v/>
       </c>
-      <c r="L211" s="121"/>
-      <c r="M211" s="121"/>
-      <c r="N211" s="121"/>
-      <c r="O211" s="121"/>
+      <c r="L211" s="142"/>
+      <c r="M211" s="142"/>
+      <c r="N211" s="142"/>
+      <c r="O211" s="142"/>
       <c r="P211" s="28" t="str">
         <f>+IF(D211="","",IF(D211&gt;0,5,0))</f>
         <v/>
@@ -9770,11 +9770,11 @@
       <c r="J213" s="64" t="s">
         <v>38</v>
       </c>
-      <c r="K213" s="120"/>
-      <c r="L213" s="120"/>
-      <c r="M213" s="120"/>
-      <c r="N213" s="120"/>
-      <c r="O213" s="120"/>
+      <c r="K213" s="143"/>
+      <c r="L213" s="143"/>
+      <c r="M213" s="143"/>
+      <c r="N213" s="143"/>
+      <c r="O213" s="143"/>
       <c r="P213" s="68"/>
     </row>
     <row r="214" spans="2:16" x14ac:dyDescent="0.25">
@@ -9864,13 +9864,13 @@
       <c r="J217" s="64" t="s">
         <v>38</v>
       </c>
-      <c r="K217" s="120" t="s">
+      <c r="K217" s="143" t="s">
         <v>40</v>
       </c>
-      <c r="L217" s="120"/>
-      <c r="M217" s="120"/>
-      <c r="N217" s="120"/>
-      <c r="O217" s="120"/>
+      <c r="L217" s="143"/>
+      <c r="M217" s="143"/>
+      <c r="N217" s="143"/>
+      <c r="O217" s="143"/>
       <c r="P217" s="60" t="s">
         <v>124</v>
       </c>
@@ -9887,14 +9887,14 @@
       <c r="H218" s="7"/>
       <c r="I218" s="7"/>
       <c r="J218" s="7"/>
-      <c r="K218" s="121" t="str">
+      <c r="K218" s="142" t="str">
         <f>+IF(C218="","",IF(C218&gt;60%,"Company's dividends at risk of being cut","Company's dividends are not at risk of being cut"))</f>
         <v/>
       </c>
-      <c r="L218" s="121"/>
-      <c r="M218" s="121"/>
-      <c r="N218" s="121"/>
-      <c r="O218" s="121"/>
+      <c r="L218" s="142"/>
+      <c r="M218" s="142"/>
+      <c r="N218" s="142"/>
+      <c r="O218" s="142"/>
       <c r="P218" s="28" t="str">
         <f>+IF(C218="","",IF(C218&gt;60%,0,5))</f>
         <v/>
@@ -9973,13 +9973,13 @@
       <c r="J221" s="64" t="s">
         <v>38</v>
       </c>
-      <c r="K221" s="120" t="s">
+      <c r="K221" s="143" t="s">
         <v>40</v>
       </c>
-      <c r="L221" s="120"/>
-      <c r="M221" s="120"/>
-      <c r="N221" s="120"/>
-      <c r="O221" s="120"/>
+      <c r="L221" s="143"/>
+      <c r="M221" s="143"/>
+      <c r="N221" s="143"/>
+      <c r="O221" s="143"/>
       <c r="P221" s="60" t="s">
         <v>124</v>
       </c>
@@ -9999,14 +9999,14 @@
         <f>+IF(D222="","",AVERAGE(D222:H222))</f>
         <v/>
       </c>
-      <c r="K222" s="136" t="str">
+      <c r="K222" s="144" t="str">
         <f>+IF(J222="","",VLOOKUP(J222,Sheet2!$A$262:$C$268,3,TRUE))</f>
         <v/>
       </c>
-      <c r="L222" s="136"/>
-      <c r="M222" s="136"/>
-      <c r="N222" s="136"/>
-      <c r="O222" s="136"/>
+      <c r="L222" s="144"/>
+      <c r="M222" s="144"/>
+      <c r="N222" s="144"/>
+      <c r="O222" s="144"/>
       <c r="P222" s="32" t="str">
         <f>+IF(J222="","",VLOOKUP(J222,Sheet2!$A$262:$C$268,2,TRUE))</f>
         <v/>
@@ -10014,23 +10014,23 @@
     </row>
     <row r="223" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="224" spans="2:16" ht="23.25" x14ac:dyDescent="0.25">
-      <c r="B224" s="122" t="s">
+      <c r="B224" s="123" t="s">
         <v>79</v>
       </c>
-      <c r="C224" s="123"/>
-      <c r="D224" s="123"/>
-      <c r="E224" s="123"/>
-      <c r="F224" s="123"/>
-      <c r="G224" s="123"/>
-      <c r="H224" s="123"/>
-      <c r="I224" s="123"/>
-      <c r="J224" s="123"/>
-      <c r="K224" s="123"/>
-      <c r="L224" s="123"/>
-      <c r="M224" s="123"/>
-      <c r="N224" s="123"/>
-      <c r="O224" s="123"/>
-      <c r="P224" s="124"/>
+      <c r="C224" s="124"/>
+      <c r="D224" s="124"/>
+      <c r="E224" s="124"/>
+      <c r="F224" s="124"/>
+      <c r="G224" s="124"/>
+      <c r="H224" s="124"/>
+      <c r="I224" s="124"/>
+      <c r="J224" s="124"/>
+      <c r="K224" s="124"/>
+      <c r="L224" s="124"/>
+      <c r="M224" s="124"/>
+      <c r="N224" s="124"/>
+      <c r="O224" s="124"/>
+      <c r="P224" s="125"/>
     </row>
     <row r="225" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B225" s="27"/>
@@ -10063,13 +10063,13 @@
       </c>
       <c r="I226" s="63"/>
       <c r="J226" s="63"/>
-      <c r="K226" s="120" t="s">
+      <c r="K226" s="143" t="s">
         <v>40</v>
       </c>
-      <c r="L226" s="120"/>
-      <c r="M226" s="120"/>
-      <c r="N226" s="120"/>
-      <c r="O226" s="120"/>
+      <c r="L226" s="143"/>
+      <c r="M226" s="143"/>
+      <c r="N226" s="143"/>
+      <c r="O226" s="143"/>
       <c r="P226" s="60" t="s">
         <v>124</v>
       </c>
@@ -10097,14 +10097,14 @@
         <f>+IF(AND(C227="",D227=""),"",IF(C227="",D227*0.8,C227*0.8))</f>
         <v/>
       </c>
-      <c r="K228" s="121" t="str">
-        <f>+IF(C228="","",IF(E11&gt;1.5*C228,Sheet2!A272,IF(E11&gt;1.2*C228,Sheet2!A273,Sheet2!A274)))</f>
-        <v/>
-      </c>
-      <c r="L228" s="121"/>
-      <c r="M228" s="121"/>
-      <c r="N228" s="121"/>
-      <c r="O228" s="121"/>
+      <c r="K228" s="142" t="str">
+        <f>+IF(C228="","",IF(E11&gt;1.5*C228,Sheet2!A274,IF(E11&gt;1.2*C228,Sheet2!A273,Sheet2!A272)))</f>
+        <v/>
+      </c>
+      <c r="L228" s="142"/>
+      <c r="M228" s="142"/>
+      <c r="N228" s="142"/>
+      <c r="O228" s="142"/>
       <c r="P228" s="28" t="str">
         <f>+IF(K228="","",VLOOKUP(K228,Sheet2!$A$272:$B$274,2,FALSE))</f>
         <v/>
@@ -10129,13 +10129,13 @@
       <c r="H230" s="59"/>
       <c r="I230" s="59"/>
       <c r="J230" s="59"/>
-      <c r="K230" s="120" t="s">
+      <c r="K230" s="143" t="s">
         <v>40</v>
       </c>
-      <c r="L230" s="120"/>
-      <c r="M230" s="120"/>
-      <c r="N230" s="120"/>
-      <c r="O230" s="120"/>
+      <c r="L230" s="143"/>
+      <c r="M230" s="143"/>
+      <c r="N230" s="143"/>
+      <c r="O230" s="143"/>
       <c r="P230" s="60" t="s">
         <v>124</v>
       </c>
@@ -10171,14 +10171,14 @@
       <c r="H233" s="31"/>
       <c r="I233" s="31"/>
       <c r="J233" s="31"/>
-      <c r="K233" s="136" t="str">
+      <c r="K233" s="144" t="str">
         <f>+IF(C233="","",IF(C233&gt;$E$11*1.5,Sheet2!$A$272,IF(C233&gt;$E$11*1.1,Sheet2!$A$273,Sheet2!$A$274)))</f>
         <v/>
       </c>
-      <c r="L233" s="136"/>
-      <c r="M233" s="136"/>
-      <c r="N233" s="136"/>
-      <c r="O233" s="136"/>
+      <c r="L233" s="144"/>
+      <c r="M233" s="144"/>
+      <c r="N233" s="144"/>
+      <c r="O233" s="144"/>
       <c r="P233" s="32" t="str">
         <f>+IF(K233="","",VLOOKUP(K233,Sheet2!$A$272:$B$274,2,FALSE))</f>
         <v/>
@@ -10194,13 +10194,13 @@
       <c r="P234" s="10"/>
     </row>
     <row r="235" spans="2:16" ht="15.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="K235" s="135" t="s">
+      <c r="K235" s="170" t="s">
         <v>40</v>
       </c>
-      <c r="L235" s="135"/>
-      <c r="M235" s="135"/>
-      <c r="N235" s="135"/>
-      <c r="O235" s="135"/>
+      <c r="L235" s="170"/>
+      <c r="M235" s="170"/>
+      <c r="N235" s="170"/>
+      <c r="O235" s="170"/>
     </row>
     <row r="236" spans="2:16" ht="15.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B236" s="1" t="s">
@@ -10208,13 +10208,13 @@
       </c>
     </row>
     <row r="237" spans="2:16" ht="15.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="K237" s="135" t="s">
+      <c r="K237" s="170" t="s">
         <v>40</v>
       </c>
-      <c r="L237" s="135"/>
-      <c r="M237" s="135"/>
-      <c r="N237" s="135"/>
-      <c r="O237" s="135"/>
+      <c r="L237" s="170"/>
+      <c r="M237" s="170"/>
+      <c r="N237" s="170"/>
+      <c r="O237" s="170"/>
     </row>
     <row r="238" spans="2:16" ht="15.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B238" s="1" t="s">
@@ -10222,13 +10222,13 @@
       </c>
     </row>
     <row r="239" spans="2:16" ht="15.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="K239" s="135" t="s">
+      <c r="K239" s="170" t="s">
         <v>40</v>
       </c>
-      <c r="L239" s="135"/>
-      <c r="M239" s="135"/>
-      <c r="N239" s="135"/>
-      <c r="O239" s="135"/>
+      <c r="L239" s="170"/>
+      <c r="M239" s="170"/>
+      <c r="N239" s="170"/>
+      <c r="O239" s="170"/>
     </row>
     <row r="240" spans="2:16" ht="15.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B240" s="1" t="s">
@@ -10236,13 +10236,13 @@
       </c>
     </row>
     <row r="241" spans="2:38" ht="15.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="K241" s="135" t="s">
+      <c r="K241" s="170" t="s">
         <v>40</v>
       </c>
-      <c r="L241" s="135"/>
-      <c r="M241" s="135"/>
-      <c r="N241" s="135"/>
-      <c r="O241" s="135"/>
+      <c r="L241" s="170"/>
+      <c r="M241" s="170"/>
+      <c r="N241" s="170"/>
+      <c r="O241" s="170"/>
     </row>
     <row r="242" spans="2:38" ht="15.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B242" s="1" t="s">
@@ -10253,23 +10253,23 @@
     <row r="244" spans="2:38" ht="15.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="245" spans="2:38" ht="15.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="246" spans="2:38" ht="23.25" x14ac:dyDescent="0.25">
-      <c r="B246" s="158" t="s">
+      <c r="B246" s="126" t="s">
         <v>322</v>
       </c>
-      <c r="C246" s="159"/>
-      <c r="D246" s="159"/>
-      <c r="E246" s="159"/>
-      <c r="F246" s="159"/>
-      <c r="G246" s="159"/>
-      <c r="H246" s="159"/>
-      <c r="I246" s="159"/>
-      <c r="J246" s="159"/>
-      <c r="K246" s="159"/>
-      <c r="L246" s="159"/>
-      <c r="M246" s="159"/>
-      <c r="N246" s="159"/>
-      <c r="O246" s="159"/>
-      <c r="P246" s="160"/>
+      <c r="C246" s="127"/>
+      <c r="D246" s="127"/>
+      <c r="E246" s="127"/>
+      <c r="F246" s="127"/>
+      <c r="G246" s="127"/>
+      <c r="H246" s="127"/>
+      <c r="I246" s="127"/>
+      <c r="J246" s="127"/>
+      <c r="K246" s="127"/>
+      <c r="L246" s="127"/>
+      <c r="M246" s="127"/>
+      <c r="N246" s="127"/>
+      <c r="O246" s="127"/>
+      <c r="P246" s="128"/>
       <c r="Y246" s="106"/>
       <c r="Z246" s="106"/>
       <c r="AA246" s="106"/>
@@ -10564,11 +10564,11 @@
         <f t="shared" ref="D254:D265" si="81">+IF(C254="","",U254)</f>
         <v/>
       </c>
-      <c r="E254" s="155" t="s">
+      <c r="E254" s="120" t="s">
         <v>299</v>
       </c>
-      <c r="F254" s="155"/>
-      <c r="G254" s="155"/>
+      <c r="F254" s="120"/>
+      <c r="G254" s="120"/>
       <c r="P254" s="112"/>
       <c r="U254" s="119">
         <v>0.03</v>
@@ -10611,9 +10611,9 @@
         <f t="shared" si="81"/>
         <v/>
       </c>
-      <c r="E255" s="155"/>
-      <c r="F255" s="155"/>
-      <c r="G255" s="155"/>
+      <c r="E255" s="120"/>
+      <c r="F255" s="120"/>
+      <c r="G255" s="120"/>
       <c r="P255" s="112"/>
       <c r="U255" s="119">
         <v>0.01</v>
@@ -10656,14 +10656,14 @@
         <f t="shared" si="81"/>
         <v/>
       </c>
-      <c r="E256" s="155"/>
-      <c r="F256" s="155"/>
-      <c r="G256" s="155"/>
-      <c r="J256" s="156">
+      <c r="E256" s="120"/>
+      <c r="F256" s="120"/>
+      <c r="G256" s="120"/>
+      <c r="J256" s="121">
         <f>+K253</f>
         <v>0</v>
       </c>
-      <c r="K256" s="157"/>
+      <c r="K256" s="122"/>
       <c r="P256" s="112"/>
       <c r="U256" s="119">
         <v>0.05</v>
@@ -10706,11 +10706,11 @@
         <f t="shared" si="81"/>
         <v/>
       </c>
-      <c r="E257" s="155"/>
-      <c r="F257" s="155"/>
-      <c r="G257" s="155"/>
-      <c r="J257" s="157"/>
-      <c r="K257" s="157"/>
+      <c r="E257" s="120"/>
+      <c r="F257" s="120"/>
+      <c r="G257" s="120"/>
+      <c r="J257" s="122"/>
+      <c r="K257" s="122"/>
       <c r="P257" s="112"/>
       <c r="U257" s="119">
         <v>0.05</v>
@@ -10761,9 +10761,9 @@
         <f t="shared" si="81"/>
         <v/>
       </c>
-      <c r="E258" s="155"/>
-      <c r="F258" s="155"/>
-      <c r="G258" s="155"/>
+      <c r="E258" s="120"/>
+      <c r="F258" s="120"/>
+      <c r="G258" s="120"/>
       <c r="P258" s="112"/>
       <c r="U258" s="119">
         <v>0.01</v>
@@ -10814,9 +10814,9 @@
         <f t="shared" si="81"/>
         <v/>
       </c>
-      <c r="E259" s="155"/>
-      <c r="F259" s="155"/>
-      <c r="G259" s="155"/>
+      <c r="E259" s="120"/>
+      <c r="F259" s="120"/>
+      <c r="G259" s="120"/>
       <c r="P259" s="112"/>
       <c r="U259" s="119">
         <v>0.02</v>
@@ -12088,6 +12088,124 @@
     </row>
   </sheetData>
   <mergeCells count="142">
+    <mergeCell ref="K116:O116"/>
+    <mergeCell ref="K114:O114"/>
+    <mergeCell ref="K126:O126"/>
+    <mergeCell ref="K127:O127"/>
+    <mergeCell ref="K102:O102"/>
+    <mergeCell ref="K103:O103"/>
+    <mergeCell ref="K107:O107"/>
+    <mergeCell ref="K175:O175"/>
+    <mergeCell ref="K176:O176"/>
+    <mergeCell ref="K164:O164"/>
+    <mergeCell ref="K169:O169"/>
+    <mergeCell ref="K174:O174"/>
+    <mergeCell ref="K117:O117"/>
+    <mergeCell ref="K118:O118"/>
+    <mergeCell ref="K121:O121"/>
+    <mergeCell ref="K122:O122"/>
+    <mergeCell ref="K179:O179"/>
+    <mergeCell ref="K183:O183"/>
+    <mergeCell ref="B130:P131"/>
+    <mergeCell ref="K166:O166"/>
+    <mergeCell ref="K167:O167"/>
+    <mergeCell ref="K170:O170"/>
+    <mergeCell ref="K171:O171"/>
+    <mergeCell ref="K172:O172"/>
+    <mergeCell ref="K177:O177"/>
+    <mergeCell ref="K180:O180"/>
+    <mergeCell ref="K145:O145"/>
+    <mergeCell ref="K146:O146"/>
+    <mergeCell ref="K149:O149"/>
+    <mergeCell ref="K150:O150"/>
+    <mergeCell ref="K153:O153"/>
+    <mergeCell ref="K132:O132"/>
+    <mergeCell ref="K154:O154"/>
+    <mergeCell ref="K157:O157"/>
+    <mergeCell ref="K158:O158"/>
+    <mergeCell ref="K161:O161"/>
+    <mergeCell ref="K162:O162"/>
+    <mergeCell ref="K165:O165"/>
+    <mergeCell ref="J30:K30"/>
+    <mergeCell ref="J31:K31"/>
+    <mergeCell ref="J13:K13"/>
+    <mergeCell ref="J16:P16"/>
+    <mergeCell ref="K239:O239"/>
+    <mergeCell ref="K241:O241"/>
+    <mergeCell ref="K226:O226"/>
+    <mergeCell ref="K230:O230"/>
+    <mergeCell ref="K235:O235"/>
+    <mergeCell ref="K237:O237"/>
+    <mergeCell ref="K208:O208"/>
+    <mergeCell ref="K213:O213"/>
+    <mergeCell ref="K217:O217"/>
+    <mergeCell ref="K221:O221"/>
+    <mergeCell ref="K211:O211"/>
+    <mergeCell ref="K218:O218"/>
+    <mergeCell ref="K222:O222"/>
+    <mergeCell ref="K228:O228"/>
+    <mergeCell ref="K233:O233"/>
+    <mergeCell ref="K184:O184"/>
+    <mergeCell ref="K188:O188"/>
+    <mergeCell ref="K120:O120"/>
+    <mergeCell ref="K124:O124"/>
+    <mergeCell ref="B110:P111"/>
+    <mergeCell ref="L23:O23"/>
+    <mergeCell ref="B4:C13"/>
+    <mergeCell ref="E4:H4"/>
+    <mergeCell ref="K5:N5"/>
+    <mergeCell ref="M15:O15"/>
+    <mergeCell ref="L22:O22"/>
+    <mergeCell ref="E5:H5"/>
+    <mergeCell ref="G22:H22"/>
+    <mergeCell ref="B16:H20"/>
+    <mergeCell ref="E6:H6"/>
+    <mergeCell ref="E7:H7"/>
+    <mergeCell ref="E9:F9"/>
+    <mergeCell ref="E10:F10"/>
+    <mergeCell ref="L13:O13"/>
+    <mergeCell ref="K40:O40"/>
+    <mergeCell ref="K39:O39"/>
+    <mergeCell ref="K43:O43"/>
+    <mergeCell ref="K47:O47"/>
+    <mergeCell ref="K51:O51"/>
+    <mergeCell ref="K55:O55"/>
+    <mergeCell ref="K101:O101"/>
+    <mergeCell ref="K41:O41"/>
+    <mergeCell ref="K42:O42"/>
+    <mergeCell ref="K45:O45"/>
+    <mergeCell ref="K44:O44"/>
+    <mergeCell ref="K48:O48"/>
+    <mergeCell ref="K49:O49"/>
+    <mergeCell ref="K85:O85"/>
+    <mergeCell ref="K84:O84"/>
+    <mergeCell ref="K90:O90"/>
+    <mergeCell ref="K59:O59"/>
+    <mergeCell ref="K63:O63"/>
+    <mergeCell ref="K67:O67"/>
+    <mergeCell ref="K71:O71"/>
+    <mergeCell ref="K75:O75"/>
+    <mergeCell ref="K79:O79"/>
+    <mergeCell ref="K83:O83"/>
+    <mergeCell ref="K61:O61"/>
+    <mergeCell ref="K64:O64"/>
+    <mergeCell ref="K65:O65"/>
+    <mergeCell ref="K68:O68"/>
+    <mergeCell ref="K69:O69"/>
+    <mergeCell ref="K80:O80"/>
+    <mergeCell ref="K81:O81"/>
+    <mergeCell ref="K108:O108"/>
+    <mergeCell ref="K113:O113"/>
+    <mergeCell ref="K91:O91"/>
+    <mergeCell ref="K94:O94"/>
+    <mergeCell ref="K95:O95"/>
+    <mergeCell ref="K98:O98"/>
+    <mergeCell ref="K88:O88"/>
+    <mergeCell ref="K93:O93"/>
+    <mergeCell ref="K97:O97"/>
+    <mergeCell ref="K99:O99"/>
+    <mergeCell ref="K112:O112"/>
+    <mergeCell ref="K105:O105"/>
     <mergeCell ref="E254:G259"/>
     <mergeCell ref="J256:K257"/>
     <mergeCell ref="B205:P205"/>
@@ -12112,124 +12230,6 @@
     <mergeCell ref="K156:O156"/>
     <mergeCell ref="K160:O160"/>
     <mergeCell ref="K60:O60"/>
-    <mergeCell ref="K64:O64"/>
-    <mergeCell ref="K65:O65"/>
-    <mergeCell ref="K68:O68"/>
-    <mergeCell ref="K69:O69"/>
-    <mergeCell ref="K80:O80"/>
-    <mergeCell ref="K81:O81"/>
-    <mergeCell ref="K108:O108"/>
-    <mergeCell ref="K113:O113"/>
-    <mergeCell ref="K91:O91"/>
-    <mergeCell ref="K94:O94"/>
-    <mergeCell ref="K95:O95"/>
-    <mergeCell ref="K98:O98"/>
-    <mergeCell ref="K88:O88"/>
-    <mergeCell ref="K93:O93"/>
-    <mergeCell ref="K97:O97"/>
-    <mergeCell ref="K99:O99"/>
-    <mergeCell ref="K112:O112"/>
-    <mergeCell ref="K105:O105"/>
-    <mergeCell ref="K40:O40"/>
-    <mergeCell ref="K39:O39"/>
-    <mergeCell ref="K43:O43"/>
-    <mergeCell ref="K47:O47"/>
-    <mergeCell ref="K51:O51"/>
-    <mergeCell ref="K55:O55"/>
-    <mergeCell ref="K101:O101"/>
-    <mergeCell ref="K41:O41"/>
-    <mergeCell ref="K42:O42"/>
-    <mergeCell ref="K45:O45"/>
-    <mergeCell ref="K44:O44"/>
-    <mergeCell ref="K48:O48"/>
-    <mergeCell ref="K49:O49"/>
-    <mergeCell ref="K85:O85"/>
-    <mergeCell ref="K84:O84"/>
-    <mergeCell ref="K90:O90"/>
-    <mergeCell ref="K59:O59"/>
-    <mergeCell ref="K63:O63"/>
-    <mergeCell ref="K67:O67"/>
-    <mergeCell ref="K71:O71"/>
-    <mergeCell ref="K75:O75"/>
-    <mergeCell ref="K79:O79"/>
-    <mergeCell ref="K83:O83"/>
-    <mergeCell ref="K61:O61"/>
-    <mergeCell ref="L23:O23"/>
-    <mergeCell ref="B4:C13"/>
-    <mergeCell ref="E4:H4"/>
-    <mergeCell ref="K5:N5"/>
-    <mergeCell ref="M15:O15"/>
-    <mergeCell ref="L22:O22"/>
-    <mergeCell ref="E5:H5"/>
-    <mergeCell ref="G22:H22"/>
-    <mergeCell ref="B16:H20"/>
-    <mergeCell ref="E6:H6"/>
-    <mergeCell ref="E7:H7"/>
-    <mergeCell ref="E9:F9"/>
-    <mergeCell ref="E10:F10"/>
-    <mergeCell ref="L13:O13"/>
-    <mergeCell ref="J30:K30"/>
-    <mergeCell ref="J31:K31"/>
-    <mergeCell ref="J13:K13"/>
-    <mergeCell ref="J16:P16"/>
-    <mergeCell ref="K239:O239"/>
-    <mergeCell ref="K241:O241"/>
-    <mergeCell ref="K226:O226"/>
-    <mergeCell ref="K230:O230"/>
-    <mergeCell ref="K235:O235"/>
-    <mergeCell ref="K237:O237"/>
-    <mergeCell ref="K208:O208"/>
-    <mergeCell ref="K213:O213"/>
-    <mergeCell ref="K217:O217"/>
-    <mergeCell ref="K221:O221"/>
-    <mergeCell ref="K211:O211"/>
-    <mergeCell ref="K218:O218"/>
-    <mergeCell ref="K222:O222"/>
-    <mergeCell ref="K228:O228"/>
-    <mergeCell ref="K233:O233"/>
-    <mergeCell ref="K184:O184"/>
-    <mergeCell ref="K188:O188"/>
-    <mergeCell ref="K120:O120"/>
-    <mergeCell ref="K124:O124"/>
-    <mergeCell ref="B110:P111"/>
-    <mergeCell ref="K179:O179"/>
-    <mergeCell ref="K183:O183"/>
-    <mergeCell ref="B130:P131"/>
-    <mergeCell ref="K166:O166"/>
-    <mergeCell ref="K167:O167"/>
-    <mergeCell ref="K170:O170"/>
-    <mergeCell ref="K171:O171"/>
-    <mergeCell ref="K172:O172"/>
-    <mergeCell ref="K177:O177"/>
-    <mergeCell ref="K180:O180"/>
-    <mergeCell ref="K145:O145"/>
-    <mergeCell ref="K146:O146"/>
-    <mergeCell ref="K149:O149"/>
-    <mergeCell ref="K150:O150"/>
-    <mergeCell ref="K153:O153"/>
-    <mergeCell ref="K132:O132"/>
-    <mergeCell ref="K154:O154"/>
-    <mergeCell ref="K157:O157"/>
-    <mergeCell ref="K158:O158"/>
-    <mergeCell ref="K161:O161"/>
-    <mergeCell ref="K162:O162"/>
-    <mergeCell ref="K165:O165"/>
-    <mergeCell ref="K116:O116"/>
-    <mergeCell ref="K114:O114"/>
-    <mergeCell ref="K126:O126"/>
-    <mergeCell ref="K127:O127"/>
-    <mergeCell ref="K102:O102"/>
-    <mergeCell ref="K103:O103"/>
-    <mergeCell ref="K107:O107"/>
-    <mergeCell ref="K175:O175"/>
-    <mergeCell ref="K176:O176"/>
-    <mergeCell ref="K164:O164"/>
-    <mergeCell ref="K169:O169"/>
-    <mergeCell ref="K174:O174"/>
-    <mergeCell ref="K117:O117"/>
-    <mergeCell ref="K118:O118"/>
-    <mergeCell ref="K121:O121"/>
-    <mergeCell ref="K122:O122"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <conditionalFormatting sqref="M15:O15">

--- a/report_template.xlsx
+++ b/report_template.xlsx
@@ -8,13 +8,13 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\JosGon\Dropbox\Python Scripts\stock report\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D5743A11-4145-43C0-BD03-47A91E9EF57F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{67696FEA-CD50-46A0-97DA-049974CE1061}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="38295" yWindow="0" windowWidth="38610" windowHeight="20985" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="975" windowWidth="57600" windowHeight="15345" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
-    <sheet name="Sheet2" sheetId="2" r:id="rId2"/>
+    <sheet name="Sheet2" sheetId="2" state="hidden" r:id="rId2"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -1717,14 +1717,11 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="164" fontId="9" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="10" fontId="17" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1735,65 +1732,41 @@
     <xf numFmtId="0" fontId="12" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="2" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="2" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="2" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="12" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="2" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="2" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="22" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="6" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="6" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="6" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1837,26 +1810,53 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="11" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="22" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="10" fontId="17" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="6" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
+    <xf numFmtId="0" fontId="12" fillId="2" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="6" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
+    <xf numFmtId="0" fontId="12" fillId="2" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="6" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
+    <xf numFmtId="0" fontId="12" fillId="2" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="2" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="2" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -4502,21 +4502,21 @@
   </cols>
   <sheetData>
     <row r="1" spans="2:16" ht="43.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B1" s="135" t="s">
+      <c r="B1" s="126" t="s">
         <v>84</v>
       </c>
-      <c r="C1" s="135"/>
-      <c r="D1" s="135"/>
-      <c r="E1" s="135"/>
-      <c r="F1" s="135"/>
-      <c r="G1" s="135"/>
-      <c r="H1" s="135"/>
-      <c r="I1" s="135"/>
-      <c r="J1" s="135"/>
-      <c r="K1" s="135"/>
-      <c r="L1" s="135"/>
-      <c r="M1" s="135"/>
-      <c r="N1" s="135"/>
+      <c r="C1" s="126"/>
+      <c r="D1" s="126"/>
+      <c r="E1" s="126"/>
+      <c r="F1" s="126"/>
+      <c r="G1" s="126"/>
+      <c r="H1" s="126"/>
+      <c r="I1" s="126"/>
+      <c r="J1" s="126"/>
+      <c r="K1" s="126"/>
+      <c r="L1" s="126"/>
+      <c r="M1" s="126"/>
+      <c r="N1" s="126"/>
       <c r="O1" s="44" t="s">
         <v>85</v>
       </c>
@@ -4526,96 +4526,96 @@
       </c>
     </row>
     <row r="2" spans="2:16" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B2" s="133" t="s">
+      <c r="B2" s="165" t="s">
         <v>294</v>
       </c>
-      <c r="C2" s="133"/>
-      <c r="D2" s="133"/>
-      <c r="E2" s="133"/>
-      <c r="F2" s="133"/>
-      <c r="G2" s="133"/>
-      <c r="H2" s="133"/>
-      <c r="J2" s="129" t="s">
+      <c r="C2" s="165"/>
+      <c r="D2" s="165"/>
+      <c r="E2" s="165"/>
+      <c r="F2" s="165"/>
+      <c r="G2" s="165"/>
+      <c r="H2" s="165"/>
+      <c r="J2" s="161" t="s">
         <v>288</v>
       </c>
-      <c r="K2" s="130"/>
-      <c r="L2" s="130"/>
-      <c r="M2" s="130"/>
-      <c r="N2" s="130"/>
-      <c r="O2" s="130"/>
-      <c r="P2" s="131"/>
+      <c r="K2" s="162"/>
+      <c r="L2" s="162"/>
+      <c r="M2" s="162"/>
+      <c r="N2" s="162"/>
+      <c r="O2" s="162"/>
+      <c r="P2" s="163"/>
     </row>
     <row r="3" spans="2:16" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B3" s="136"/>
-      <c r="C3" s="136"/>
-      <c r="D3" s="136"/>
-      <c r="E3" s="136"/>
-      <c r="F3" s="136"/>
-      <c r="G3" s="136"/>
-      <c r="H3" s="136"/>
-      <c r="J3" s="132"/>
-      <c r="K3" s="133"/>
-      <c r="L3" s="133"/>
-      <c r="M3" s="133"/>
-      <c r="N3" s="133"/>
-      <c r="O3" s="133"/>
-      <c r="P3" s="134"/>
+      <c r="B3" s="167"/>
+      <c r="C3" s="167"/>
+      <c r="D3" s="167"/>
+      <c r="E3" s="167"/>
+      <c r="F3" s="167"/>
+      <c r="G3" s="167"/>
+      <c r="H3" s="167"/>
+      <c r="J3" s="164"/>
+      <c r="K3" s="165"/>
+      <c r="L3" s="165"/>
+      <c r="M3" s="165"/>
+      <c r="N3" s="165"/>
+      <c r="O3" s="165"/>
+      <c r="P3" s="166"/>
     </row>
     <row r="4" spans="2:16" x14ac:dyDescent="0.25">
-      <c r="B4" s="146"/>
-      <c r="C4" s="147"/>
+      <c r="B4" s="137"/>
+      <c r="C4" s="138"/>
       <c r="D4" s="37" t="s">
         <v>0</v>
       </c>
-      <c r="E4" s="150"/>
-      <c r="F4" s="150"/>
-      <c r="G4" s="150"/>
-      <c r="H4" s="151"/>
+      <c r="E4" s="141"/>
+      <c r="F4" s="141"/>
+      <c r="G4" s="141"/>
+      <c r="H4" s="142"/>
       <c r="J4" s="27"/>
       <c r="P4" s="28"/>
     </row>
     <row r="5" spans="2:16" x14ac:dyDescent="0.25">
-      <c r="B5" s="148"/>
-      <c r="C5" s="149"/>
+      <c r="B5" s="139"/>
+      <c r="C5" s="140"/>
       <c r="D5" s="75" t="s">
         <v>33</v>
       </c>
-      <c r="E5" s="153"/>
-      <c r="F5" s="153"/>
-      <c r="G5" s="153"/>
-      <c r="H5" s="154"/>
+      <c r="E5" s="144"/>
+      <c r="F5" s="144"/>
+      <c r="G5" s="144"/>
+      <c r="H5" s="145"/>
       <c r="J5" s="27"/>
-      <c r="K5" s="152" t="s">
+      <c r="K5" s="143" t="s">
         <v>305</v>
       </c>
-      <c r="L5" s="152"/>
-      <c r="M5" s="152"/>
-      <c r="N5" s="152"/>
+      <c r="L5" s="143"/>
+      <c r="M5" s="143"/>
+      <c r="N5" s="143"/>
       <c r="P5" s="28"/>
     </row>
     <row r="6" spans="2:16" x14ac:dyDescent="0.25">
-      <c r="B6" s="148"/>
-      <c r="C6" s="149"/>
+      <c r="B6" s="139"/>
+      <c r="C6" s="140"/>
       <c r="D6" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="E6" s="160"/>
-      <c r="F6" s="160"/>
-      <c r="G6" s="160"/>
-      <c r="H6" s="161"/>
+      <c r="E6" s="151"/>
+      <c r="F6" s="151"/>
+      <c r="G6" s="151"/>
+      <c r="H6" s="152"/>
       <c r="J6" s="27"/>
       <c r="P6" s="28"/>
     </row>
     <row r="7" spans="2:16" x14ac:dyDescent="0.25">
-      <c r="B7" s="148"/>
-      <c r="C7" s="149"/>
+      <c r="B7" s="139"/>
+      <c r="C7" s="140"/>
       <c r="D7" s="75" t="s">
         <v>6</v>
       </c>
-      <c r="E7" s="162"/>
-      <c r="F7" s="162"/>
-      <c r="G7" s="162"/>
-      <c r="H7" s="163"/>
+      <c r="E7" s="153"/>
+      <c r="F7" s="153"/>
+      <c r="G7" s="153"/>
+      <c r="H7" s="154"/>
       <c r="J7" s="33" t="s">
         <v>14</v>
       </c>
@@ -4637,8 +4637,8 @@
       <c r="P7" s="28"/>
     </row>
     <row r="8" spans="2:16" x14ac:dyDescent="0.25">
-      <c r="B8" s="148"/>
-      <c r="C8" s="149"/>
+      <c r="B8" s="139"/>
+      <c r="C8" s="140"/>
       <c r="D8" s="1" t="s">
         <v>1</v>
       </c>
@@ -4654,13 +4654,13 @@
       <c r="P8" s="28"/>
     </row>
     <row r="9" spans="2:16" x14ac:dyDescent="0.25">
-      <c r="B9" s="148"/>
-      <c r="C9" s="149"/>
+      <c r="B9" s="139"/>
+      <c r="C9" s="140"/>
       <c r="D9" s="75" t="s">
         <v>2</v>
       </c>
-      <c r="E9" s="153"/>
-      <c r="F9" s="153"/>
+      <c r="E9" s="144"/>
+      <c r="F9" s="144"/>
       <c r="G9" s="76"/>
       <c r="H9" s="77"/>
       <c r="J9" s="35" t="s">
@@ -4674,13 +4674,13 @@
       <c r="P9" s="28"/>
     </row>
     <row r="10" spans="2:16" x14ac:dyDescent="0.25">
-      <c r="B10" s="148"/>
-      <c r="C10" s="149"/>
+      <c r="B10" s="139"/>
+      <c r="C10" s="140"/>
       <c r="D10" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="E10" s="145"/>
-      <c r="F10" s="145"/>
+      <c r="E10" s="129"/>
+      <c r="F10" s="129"/>
       <c r="H10" s="38"/>
       <c r="J10" s="27" t="s">
         <v>17</v>
@@ -4693,8 +4693,8 @@
       <c r="P10" s="28"/>
     </row>
     <row r="11" spans="2:16" x14ac:dyDescent="0.25">
-      <c r="B11" s="148"/>
-      <c r="C11" s="149"/>
+      <c r="B11" s="139"/>
+      <c r="C11" s="140"/>
       <c r="D11" s="75" t="s">
         <v>8</v>
       </c>
@@ -4715,8 +4715,8 @@
       <c r="P11" s="28"/>
     </row>
     <row r="12" spans="2:16" x14ac:dyDescent="0.25">
-      <c r="B12" s="148"/>
-      <c r="C12" s="149"/>
+      <c r="B12" s="139"/>
+      <c r="C12" s="140"/>
       <c r="D12" s="1" t="s">
         <v>5</v>
       </c>
@@ -4727,8 +4727,8 @@
       </c>
     </row>
     <row r="13" spans="2:16" x14ac:dyDescent="0.25">
-      <c r="B13" s="148"/>
-      <c r="C13" s="149"/>
+      <c r="B13" s="139"/>
+      <c r="C13" s="140"/>
       <c r="D13" s="75" t="s">
         <v>34</v>
       </c>
@@ -4736,14 +4736,14 @@
       <c r="F13" s="76"/>
       <c r="G13" s="76"/>
       <c r="H13" s="77"/>
-      <c r="J13" s="165" t="s">
+      <c r="J13" s="130" t="s">
         <v>19</v>
       </c>
-      <c r="K13" s="166"/>
-      <c r="L13" s="142"/>
-      <c r="M13" s="142"/>
-      <c r="N13" s="142"/>
-      <c r="O13" s="142"/>
+      <c r="K13" s="131"/>
+      <c r="L13" s="121"/>
+      <c r="M13" s="121"/>
+      <c r="N13" s="121"/>
+      <c r="O13" s="121"/>
       <c r="P13" s="28" t="str">
         <f>+IF(OR(L13="",L13="none"),"",VLOOKUP(L13,Sheet2!$A$1:$B$6,2,FALSE))</f>
         <v/>
@@ -4774,43 +4774,43 @@
       <c r="L15" s="81" t="s">
         <v>21</v>
       </c>
-      <c r="M15" s="142" t="str">
+      <c r="M15" s="121" t="str">
         <f>IF(K15="","",IF(K15&lt;0.8,"Low volatility",IF(K15&lt;=1.2,"Normal volatility","High volatility")))</f>
         <v/>
       </c>
-      <c r="N15" s="142"/>
-      <c r="O15" s="142"/>
+      <c r="N15" s="121"/>
+      <c r="O15" s="121"/>
       <c r="P15" s="28" t="str">
         <f>+IF(M15="","",VLOOKUP(M15,Sheet2!$A$8:$B$11,2,FALSE))</f>
         <v/>
       </c>
     </row>
     <row r="16" spans="2:16" ht="249" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B16" s="157"/>
-      <c r="C16" s="158"/>
-      <c r="D16" s="158"/>
-      <c r="E16" s="158"/>
-      <c r="F16" s="158"/>
-      <c r="G16" s="158"/>
-      <c r="H16" s="159"/>
-      <c r="J16" s="167" t="s">
+      <c r="B16" s="148"/>
+      <c r="C16" s="149"/>
+      <c r="D16" s="149"/>
+      <c r="E16" s="149"/>
+      <c r="F16" s="149"/>
+      <c r="G16" s="149"/>
+      <c r="H16" s="150"/>
+      <c r="J16" s="132" t="s">
         <v>323</v>
       </c>
-      <c r="K16" s="168"/>
-      <c r="L16" s="168"/>
-      <c r="M16" s="168"/>
-      <c r="N16" s="168"/>
-      <c r="O16" s="168"/>
-      <c r="P16" s="169"/>
+      <c r="K16" s="133"/>
+      <c r="L16" s="133"/>
+      <c r="M16" s="133"/>
+      <c r="N16" s="133"/>
+      <c r="O16" s="133"/>
+      <c r="P16" s="134"/>
     </row>
     <row r="17" spans="2:16" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B17" s="157"/>
-      <c r="C17" s="158"/>
-      <c r="D17" s="158"/>
-      <c r="E17" s="158"/>
-      <c r="F17" s="158"/>
-      <c r="G17" s="158"/>
-      <c r="H17" s="159"/>
+      <c r="B17" s="148"/>
+      <c r="C17" s="149"/>
+      <c r="D17" s="149"/>
+      <c r="E17" s="149"/>
+      <c r="F17" s="149"/>
+      <c r="G17" s="149"/>
+      <c r="H17" s="150"/>
       <c r="J17" s="89" t="s">
         <v>22</v>
       </c>
@@ -4822,26 +4822,26 @@
       <c r="P17" s="91"/>
     </row>
     <row r="18" spans="2:16" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B18" s="157"/>
-      <c r="C18" s="158"/>
-      <c r="D18" s="158"/>
-      <c r="E18" s="158"/>
-      <c r="F18" s="158"/>
-      <c r="G18" s="158"/>
-      <c r="H18" s="159"/>
+      <c r="B18" s="148"/>
+      <c r="C18" s="149"/>
+      <c r="D18" s="149"/>
+      <c r="E18" s="149"/>
+      <c r="F18" s="149"/>
+      <c r="G18" s="149"/>
+      <c r="H18" s="150"/>
       <c r="J18" s="92" t="s">
         <v>23</v>
       </c>
       <c r="P18" s="88"/>
     </row>
     <row r="19" spans="2:16" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B19" s="157"/>
-      <c r="C19" s="158"/>
-      <c r="D19" s="158"/>
-      <c r="E19" s="158"/>
-      <c r="F19" s="158"/>
-      <c r="G19" s="158"/>
-      <c r="H19" s="159"/>
+      <c r="B19" s="148"/>
+      <c r="C19" s="149"/>
+      <c r="D19" s="149"/>
+      <c r="E19" s="149"/>
+      <c r="F19" s="149"/>
+      <c r="G19" s="149"/>
+      <c r="H19" s="150"/>
       <c r="J19" s="93" t="s">
         <v>24</v>
       </c>
@@ -4853,13 +4853,13 @@
       <c r="P19" s="94"/>
     </row>
     <row r="20" spans="2:16" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B20" s="157"/>
-      <c r="C20" s="158"/>
-      <c r="D20" s="158"/>
-      <c r="E20" s="158"/>
-      <c r="F20" s="158"/>
-      <c r="G20" s="158"/>
-      <c r="H20" s="159"/>
+      <c r="B20" s="148"/>
+      <c r="C20" s="149"/>
+      <c r="D20" s="149"/>
+      <c r="E20" s="149"/>
+      <c r="F20" s="149"/>
+      <c r="G20" s="149"/>
+      <c r="H20" s="150"/>
       <c r="J20" s="92" t="s">
         <v>25</v>
       </c>
@@ -4886,17 +4886,17 @@
       <c r="F22" s="62" t="s">
         <v>36</v>
       </c>
-      <c r="G22" s="155" t="s">
+      <c r="G22" s="146" t="s">
         <v>37</v>
       </c>
-      <c r="H22" s="156"/>
+      <c r="H22" s="147"/>
       <c r="J22" s="92" t="s">
         <v>26</v>
       </c>
-      <c r="L22" s="145"/>
-      <c r="M22" s="145"/>
-      <c r="N22" s="145"/>
-      <c r="O22" s="145"/>
+      <c r="L22" s="129"/>
+      <c r="M22" s="129"/>
+      <c r="N22" s="129"/>
+      <c r="O22" s="129"/>
       <c r="P22" s="88"/>
     </row>
     <row r="23" spans="2:16" x14ac:dyDescent="0.25">
@@ -4910,10 +4910,10 @@
       <c r="J23" s="92" t="s">
         <v>306</v>
       </c>
-      <c r="L23" s="145"/>
-      <c r="M23" s="145"/>
-      <c r="N23" s="145"/>
-      <c r="O23" s="145"/>
+      <c r="L23" s="129"/>
+      <c r="M23" s="129"/>
+      <c r="N23" s="129"/>
+      <c r="O23" s="129"/>
       <c r="P23" s="88"/>
     </row>
     <row r="24" spans="2:16" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -5001,10 +5001,10 @@
       <c r="F30" s="2"/>
       <c r="G30" s="2"/>
       <c r="H30" s="40"/>
-      <c r="J30" s="164" t="s">
+      <c r="J30" s="128" t="s">
         <v>30</v>
       </c>
-      <c r="K30" s="145"/>
+      <c r="K30" s="129"/>
       <c r="P30" s="88"/>
     </row>
     <row r="31" spans="2:16" x14ac:dyDescent="0.25">
@@ -5015,10 +5015,10 @@
       <c r="F31" s="2"/>
       <c r="G31" s="2"/>
       <c r="H31" s="40"/>
-      <c r="J31" s="164" t="s">
+      <c r="J31" s="128" t="s">
         <v>31</v>
       </c>
-      <c r="K31" s="145"/>
+      <c r="K31" s="129"/>
       <c r="P31" s="88"/>
     </row>
     <row r="32" spans="2:16" x14ac:dyDescent="0.25">
@@ -5141,40 +5141,40 @@
       </c>
     </row>
     <row r="36" spans="2:16" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B36" s="137" t="s">
+      <c r="B36" s="125" t="s">
         <v>44</v>
       </c>
-      <c r="C36" s="135"/>
-      <c r="D36" s="135"/>
-      <c r="E36" s="135"/>
-      <c r="F36" s="135"/>
-      <c r="G36" s="135"/>
-      <c r="H36" s="135"/>
-      <c r="I36" s="135"/>
-      <c r="J36" s="135"/>
-      <c r="K36" s="135"/>
-      <c r="L36" s="135"/>
-      <c r="M36" s="135"/>
-      <c r="N36" s="135"/>
-      <c r="O36" s="135"/>
-      <c r="P36" s="138"/>
+      <c r="C36" s="126"/>
+      <c r="D36" s="126"/>
+      <c r="E36" s="126"/>
+      <c r="F36" s="126"/>
+      <c r="G36" s="126"/>
+      <c r="H36" s="126"/>
+      <c r="I36" s="126"/>
+      <c r="J36" s="126"/>
+      <c r="K36" s="126"/>
+      <c r="L36" s="126"/>
+      <c r="M36" s="126"/>
+      <c r="N36" s="126"/>
+      <c r="O36" s="126"/>
+      <c r="P36" s="127"/>
     </row>
     <row r="37" spans="2:16" ht="20.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B37" s="139"/>
-      <c r="C37" s="140"/>
-      <c r="D37" s="140"/>
-      <c r="E37" s="140"/>
-      <c r="F37" s="140"/>
-      <c r="G37" s="140"/>
-      <c r="H37" s="140"/>
-      <c r="I37" s="140"/>
-      <c r="J37" s="140"/>
-      <c r="K37" s="140"/>
-      <c r="L37" s="140"/>
-      <c r="M37" s="140"/>
-      <c r="N37" s="140"/>
-      <c r="O37" s="140"/>
-      <c r="P37" s="141"/>
+      <c r="B37" s="168"/>
+      <c r="C37" s="169"/>
+      <c r="D37" s="169"/>
+      <c r="E37" s="169"/>
+      <c r="F37" s="169"/>
+      <c r="G37" s="169"/>
+      <c r="H37" s="169"/>
+      <c r="I37" s="169"/>
+      <c r="J37" s="169"/>
+      <c r="K37" s="169"/>
+      <c r="L37" s="169"/>
+      <c r="M37" s="169"/>
+      <c r="N37" s="169"/>
+      <c r="O37" s="169"/>
+      <c r="P37" s="170"/>
     </row>
     <row r="38" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B38" s="46"/>
@@ -5221,13 +5221,13 @@
       <c r="J39" s="64" t="s">
         <v>38</v>
       </c>
-      <c r="K39" s="143" t="s">
+      <c r="K39" s="120" t="s">
         <v>40</v>
       </c>
-      <c r="L39" s="143"/>
-      <c r="M39" s="143"/>
-      <c r="N39" s="143"/>
-      <c r="O39" s="143"/>
+      <c r="L39" s="120"/>
+      <c r="M39" s="120"/>
+      <c r="N39" s="120"/>
+      <c r="O39" s="120"/>
       <c r="P39" s="60" t="s">
         <v>124</v>
       </c>
@@ -5243,14 +5243,14 @@
       <c r="H40" s="7"/>
       <c r="I40" s="7"/>
       <c r="J40" s="7"/>
-      <c r="K40" s="142" t="str">
+      <c r="K40" s="121" t="str">
         <f>+IF(D41="","",IF(D40&lt;0,Sheet2!$C$27,VLOOKUP(D41,Sheet2!$A$27:$C$31,3,TRUE)))</f>
         <v/>
       </c>
-      <c r="L40" s="142"/>
-      <c r="M40" s="142"/>
-      <c r="N40" s="142"/>
-      <c r="O40" s="142"/>
+      <c r="L40" s="121"/>
+      <c r="M40" s="121"/>
+      <c r="N40" s="121"/>
+      <c r="O40" s="121"/>
       <c r="P40" s="28" t="str">
         <f>+IF(K40="","",VLOOKUP(K40,Sheet2!$C$27:$D$31,2,FALSE))</f>
         <v/>
@@ -5282,14 +5282,14 @@
         <f>+IF(D41="","",AVERAGE(D41:G41))</f>
         <v/>
       </c>
-      <c r="K41" s="142" t="str">
+      <c r="K41" s="121" t="str">
         <f>+IF(J41="","",IF(AND(D40&lt;0,E40&lt;0),Sheet2!$C$35,VLOOKUP(J41,Sheet2!$A$35:$C$39,3,TRUE)))</f>
         <v/>
       </c>
-      <c r="L41" s="142"/>
-      <c r="M41" s="142"/>
-      <c r="N41" s="142"/>
-      <c r="O41" s="142"/>
+      <c r="L41" s="121"/>
+      <c r="M41" s="121"/>
+      <c r="N41" s="121"/>
+      <c r="O41" s="121"/>
       <c r="P41" s="28" t="str">
         <f>+IF(K41="","",VLOOKUP(K41,Sheet2!$C$35:$D$39,2,FALSE))</f>
         <v/>
@@ -5305,11 +5305,11 @@
       <c r="H42" s="7"/>
       <c r="I42" s="7"/>
       <c r="J42" s="7"/>
-      <c r="K42" s="142"/>
-      <c r="L42" s="142"/>
-      <c r="M42" s="142"/>
-      <c r="N42" s="142"/>
-      <c r="O42" s="142"/>
+      <c r="K42" s="121"/>
+      <c r="L42" s="121"/>
+      <c r="M42" s="121"/>
+      <c r="N42" s="121"/>
+      <c r="O42" s="121"/>
       <c r="P42" s="28"/>
     </row>
     <row r="43" spans="2:16" x14ac:dyDescent="0.25">
@@ -5341,13 +5341,13 @@
       <c r="J43" s="64" t="s">
         <v>38</v>
       </c>
-      <c r="K43" s="143" t="s">
+      <c r="K43" s="120" t="s">
         <v>40</v>
       </c>
-      <c r="L43" s="143"/>
-      <c r="M43" s="143"/>
-      <c r="N43" s="143"/>
-      <c r="O43" s="143"/>
+      <c r="L43" s="120"/>
+      <c r="M43" s="120"/>
+      <c r="N43" s="120"/>
+      <c r="O43" s="120"/>
       <c r="P43" s="60" t="s">
         <v>124</v>
       </c>
@@ -5363,14 +5363,14 @@
       <c r="H44" s="7"/>
       <c r="I44" s="7"/>
       <c r="J44" s="7"/>
-      <c r="K44" s="142" t="str">
+      <c r="K44" s="121" t="str">
         <f>+IF(D45="","",IF(D44&lt;0,Sheet2!$C$27,VLOOKUP(D45,Sheet2!$A$27:$C$31,3,TRUE)))</f>
         <v/>
       </c>
-      <c r="L44" s="142"/>
-      <c r="M44" s="142"/>
-      <c r="N44" s="142"/>
-      <c r="O44" s="142"/>
+      <c r="L44" s="121"/>
+      <c r="M44" s="121"/>
+      <c r="N44" s="121"/>
+      <c r="O44" s="121"/>
       <c r="P44" s="28" t="str">
         <f>+IF(K44="","",VLOOKUP(K44,Sheet2!$C$27:$D$31,2,FALSE))</f>
         <v/>
@@ -5402,14 +5402,14 @@
         <f>+IF(D45="","",AVERAGE(D45:G45))</f>
         <v/>
       </c>
-      <c r="K45" s="142" t="str">
+      <c r="K45" s="121" t="str">
         <f>+IF(J45="","",IF(AND(D44&lt;0,E44&lt;0),Sheet2!$C$35,VLOOKUP(J45,Sheet2!$A$35:$C$39,3,TRUE)))</f>
         <v/>
       </c>
-      <c r="L45" s="142"/>
-      <c r="M45" s="142"/>
-      <c r="N45" s="142"/>
-      <c r="O45" s="142"/>
+      <c r="L45" s="121"/>
+      <c r="M45" s="121"/>
+      <c r="N45" s="121"/>
+      <c r="O45" s="121"/>
       <c r="P45" s="28" t="str">
         <f>+IF(K45="","",VLOOKUP(K45,Sheet2!$C$35:$D$39,2,FALSE))</f>
         <v/>
@@ -5456,11 +5456,11 @@
       <c r="J47" s="64" t="s">
         <v>38</v>
       </c>
-      <c r="K47" s="143"/>
-      <c r="L47" s="143"/>
-      <c r="M47" s="143"/>
-      <c r="N47" s="143"/>
-      <c r="O47" s="143"/>
+      <c r="K47" s="120"/>
+      <c r="L47" s="120"/>
+      <c r="M47" s="120"/>
+      <c r="N47" s="120"/>
+      <c r="O47" s="120"/>
       <c r="P47" s="60"/>
     </row>
     <row r="48" spans="2:16" x14ac:dyDescent="0.25">
@@ -5474,11 +5474,11 @@
       <c r="H48" s="7"/>
       <c r="I48" s="7"/>
       <c r="J48" s="7"/>
-      <c r="K48" s="142"/>
-      <c r="L48" s="142"/>
-      <c r="M48" s="142"/>
-      <c r="N48" s="142"/>
-      <c r="O48" s="142"/>
+      <c r="K48" s="121"/>
+      <c r="L48" s="121"/>
+      <c r="M48" s="121"/>
+      <c r="N48" s="121"/>
+      <c r="O48" s="121"/>
       <c r="P48" s="28"/>
     </row>
     <row r="49" spans="2:16" x14ac:dyDescent="0.25">
@@ -5507,11 +5507,11 @@
         <f>+IF(D49="","",AVERAGE(D49:G49))</f>
         <v/>
       </c>
-      <c r="K49" s="142"/>
-      <c r="L49" s="142"/>
-      <c r="M49" s="142"/>
-      <c r="N49" s="142"/>
-      <c r="O49" s="142"/>
+      <c r="K49" s="121"/>
+      <c r="L49" s="121"/>
+      <c r="M49" s="121"/>
+      <c r="N49" s="121"/>
+      <c r="O49" s="121"/>
       <c r="P49" s="28"/>
     </row>
     <row r="50" spans="2:16" x14ac:dyDescent="0.25">
@@ -5555,11 +5555,11 @@
       <c r="J51" s="64" t="s">
         <v>38</v>
       </c>
-      <c r="K51" s="143"/>
-      <c r="L51" s="143"/>
-      <c r="M51" s="143"/>
-      <c r="N51" s="143"/>
-      <c r="O51" s="143"/>
+      <c r="K51" s="120"/>
+      <c r="L51" s="120"/>
+      <c r="M51" s="120"/>
+      <c r="N51" s="120"/>
+      <c r="O51" s="120"/>
       <c r="P51" s="60"/>
     </row>
     <row r="52" spans="2:16" x14ac:dyDescent="0.25">
@@ -5644,11 +5644,11 @@
       <c r="J55" s="64" t="s">
         <v>38</v>
       </c>
-      <c r="K55" s="143"/>
-      <c r="L55" s="143"/>
-      <c r="M55" s="143"/>
-      <c r="N55" s="143"/>
-      <c r="O55" s="143"/>
+      <c r="K55" s="120"/>
+      <c r="L55" s="120"/>
+      <c r="M55" s="120"/>
+      <c r="N55" s="120"/>
+      <c r="O55" s="120"/>
       <c r="P55" s="60"/>
     </row>
     <row r="56" spans="2:16" x14ac:dyDescent="0.25">
@@ -5733,13 +5733,13 @@
       <c r="J59" s="64" t="s">
         <v>38</v>
       </c>
-      <c r="K59" s="143" t="s">
+      <c r="K59" s="120" t="s">
         <v>40</v>
       </c>
-      <c r="L59" s="143"/>
-      <c r="M59" s="143"/>
-      <c r="N59" s="143"/>
-      <c r="O59" s="143"/>
+      <c r="L59" s="120"/>
+      <c r="M59" s="120"/>
+      <c r="N59" s="120"/>
+      <c r="O59" s="120"/>
       <c r="P59" s="60" t="s">
         <v>124</v>
       </c>
@@ -5755,14 +5755,14 @@
       <c r="H60" s="7"/>
       <c r="I60" s="7"/>
       <c r="J60" s="7"/>
-      <c r="K60" s="142" t="str">
+      <c r="K60" s="121" t="str">
         <f>+IF(D61="","",IF(D60&lt;0,Sheet2!$C$27,VLOOKUP(D61,Sheet2!$A$27:$C$31,3,TRUE)))</f>
         <v/>
       </c>
-      <c r="L60" s="142"/>
-      <c r="M60" s="142"/>
-      <c r="N60" s="142"/>
-      <c r="O60" s="142"/>
+      <c r="L60" s="121"/>
+      <c r="M60" s="121"/>
+      <c r="N60" s="121"/>
+      <c r="O60" s="121"/>
       <c r="P60" s="28" t="str">
         <f>+IF(K60="","",VLOOKUP(K60,Sheet2!$C$27:$D$31,2,FALSE))</f>
         <v/>
@@ -5794,14 +5794,14 @@
         <f>+IF(D61="","",AVERAGE(D61:G61))</f>
         <v/>
       </c>
-      <c r="K61" s="142" t="str">
+      <c r="K61" s="121" t="str">
         <f>+IF(J61="","",IF(AND(D60&lt;0,E60&lt;0),Sheet2!$C$35,VLOOKUP(J61,Sheet2!$A$35:$C$39,3,TRUE)))</f>
         <v/>
       </c>
-      <c r="L61" s="142"/>
-      <c r="M61" s="142"/>
-      <c r="N61" s="142"/>
-      <c r="O61" s="142"/>
+      <c r="L61" s="121"/>
+      <c r="M61" s="121"/>
+      <c r="N61" s="121"/>
+      <c r="O61" s="121"/>
       <c r="P61" s="28" t="str">
         <f>+IF(K61="","",VLOOKUP(K61,Sheet2!$C$35:$D$39,2,FALSE))</f>
         <v/>
@@ -5848,13 +5848,13 @@
       <c r="J63" s="64" t="s">
         <v>38</v>
       </c>
-      <c r="K63" s="143" t="s">
+      <c r="K63" s="120" t="s">
         <v>40</v>
       </c>
-      <c r="L63" s="143"/>
-      <c r="M63" s="143"/>
-      <c r="N63" s="143"/>
-      <c r="O63" s="143"/>
+      <c r="L63" s="120"/>
+      <c r="M63" s="120"/>
+      <c r="N63" s="120"/>
+      <c r="O63" s="120"/>
       <c r="P63" s="60" t="s">
         <v>124</v>
       </c>
@@ -5870,14 +5870,14 @@
       <c r="H64" s="7"/>
       <c r="I64" s="7"/>
       <c r="J64" s="7"/>
-      <c r="K64" s="142" t="str">
+      <c r="K64" s="121" t="str">
         <f>+IF(D65="","",IF(D64&lt;0,Sheet2!$C$27,VLOOKUP(D65,Sheet2!$A$27:$C$31,3,TRUE)))</f>
         <v/>
       </c>
-      <c r="L64" s="142"/>
-      <c r="M64" s="142"/>
-      <c r="N64" s="142"/>
-      <c r="O64" s="142"/>
+      <c r="L64" s="121"/>
+      <c r="M64" s="121"/>
+      <c r="N64" s="121"/>
+      <c r="O64" s="121"/>
       <c r="P64" s="28" t="str">
         <f>+IF(K64="","",VLOOKUP(K64,Sheet2!$C$27:$D$31,2,FALSE))</f>
         <v/>
@@ -5909,14 +5909,14 @@
         <f>+IF(D65="","",AVERAGE(D65:G65))</f>
         <v/>
       </c>
-      <c r="K65" s="142" t="str">
+      <c r="K65" s="121" t="str">
         <f>+IF(J65="","",IF(AND(D64&lt;0,E64&lt;0),Sheet2!$C$35,VLOOKUP(J65,Sheet2!$A$35:$C$39,3,TRUE)))</f>
         <v/>
       </c>
-      <c r="L65" s="142"/>
-      <c r="M65" s="142"/>
-      <c r="N65" s="142"/>
-      <c r="O65" s="142"/>
+      <c r="L65" s="121"/>
+      <c r="M65" s="121"/>
+      <c r="N65" s="121"/>
+      <c r="O65" s="121"/>
       <c r="P65" s="28" t="str">
         <f>+IF(K65="","",VLOOKUP(K65,Sheet2!$C$35:$D$39,2,FALSE))</f>
         <v/>
@@ -5963,13 +5963,13 @@
       <c r="J67" s="64" t="s">
         <v>38</v>
       </c>
-      <c r="K67" s="143" t="s">
+      <c r="K67" s="120" t="s">
         <v>40</v>
       </c>
-      <c r="L67" s="143"/>
-      <c r="M67" s="143"/>
-      <c r="N67" s="143"/>
-      <c r="O67" s="143"/>
+      <c r="L67" s="120"/>
+      <c r="M67" s="120"/>
+      <c r="N67" s="120"/>
+      <c r="O67" s="120"/>
       <c r="P67" s="60" t="s">
         <v>124</v>
       </c>
@@ -5985,14 +5985,14 @@
       <c r="H68" s="7"/>
       <c r="I68" s="7"/>
       <c r="J68" s="7"/>
-      <c r="K68" s="142" t="str">
+      <c r="K68" s="121" t="str">
         <f>+IF(D69="","",IF(D68&lt;0,Sheet2!$C$27,VLOOKUP(D69,Sheet2!$A$27:$C$31,3,TRUE)))</f>
         <v/>
       </c>
-      <c r="L68" s="142"/>
-      <c r="M68" s="142"/>
-      <c r="N68" s="142"/>
-      <c r="O68" s="142"/>
+      <c r="L68" s="121"/>
+      <c r="M68" s="121"/>
+      <c r="N68" s="121"/>
+      <c r="O68" s="121"/>
       <c r="P68" s="28" t="str">
         <f>+IF(K68="","",VLOOKUP(K68,Sheet2!$C$27:$D$31,2,FALSE))</f>
         <v/>
@@ -6024,14 +6024,14 @@
         <f>+IF(D69="","",AVERAGE(D69:G69))</f>
         <v/>
       </c>
-      <c r="K69" s="142" t="str">
+      <c r="K69" s="121" t="str">
         <f>+IF(J69="","",IF(AND(D68&lt;0,E68&lt;0),Sheet2!$C$35,VLOOKUP(J69,Sheet2!$A$35:$C$39,3,TRUE)))</f>
         <v/>
       </c>
-      <c r="L69" s="142"/>
-      <c r="M69" s="142"/>
-      <c r="N69" s="142"/>
-      <c r="O69" s="142"/>
+      <c r="L69" s="121"/>
+      <c r="M69" s="121"/>
+      <c r="N69" s="121"/>
+      <c r="O69" s="121"/>
       <c r="P69" s="28" t="str">
         <f>+IF(K69="","",VLOOKUP(K69,Sheet2!$C$35:$D$39,2,FALSE))</f>
         <v/>
@@ -6078,11 +6078,11 @@
       <c r="J71" s="64" t="s">
         <v>38</v>
       </c>
-      <c r="K71" s="143"/>
-      <c r="L71" s="143"/>
-      <c r="M71" s="143"/>
-      <c r="N71" s="143"/>
-      <c r="O71" s="143"/>
+      <c r="K71" s="120"/>
+      <c r="L71" s="120"/>
+      <c r="M71" s="120"/>
+      <c r="N71" s="120"/>
+      <c r="O71" s="120"/>
       <c r="P71" s="60"/>
     </row>
     <row r="72" spans="2:16" x14ac:dyDescent="0.25">
@@ -6170,11 +6170,11 @@
       <c r="J75" s="64" t="s">
         <v>38</v>
       </c>
-      <c r="K75" s="143"/>
-      <c r="L75" s="143"/>
-      <c r="M75" s="143"/>
-      <c r="N75" s="143"/>
-      <c r="O75" s="143"/>
+      <c r="K75" s="120"/>
+      <c r="L75" s="120"/>
+      <c r="M75" s="120"/>
+      <c r="N75" s="120"/>
+      <c r="O75" s="120"/>
       <c r="P75" s="60"/>
     </row>
     <row r="76" spans="2:16" x14ac:dyDescent="0.25">
@@ -6259,13 +6259,13 @@
       <c r="J79" s="64" t="s">
         <v>38</v>
       </c>
-      <c r="K79" s="143" t="s">
+      <c r="K79" s="120" t="s">
         <v>40</v>
       </c>
-      <c r="L79" s="143"/>
-      <c r="M79" s="143"/>
-      <c r="N79" s="143"/>
-      <c r="O79" s="143"/>
+      <c r="L79" s="120"/>
+      <c r="M79" s="120"/>
+      <c r="N79" s="120"/>
+      <c r="O79" s="120"/>
       <c r="P79" s="60" t="s">
         <v>124</v>
       </c>
@@ -6281,14 +6281,14 @@
       <c r="H80" s="7"/>
       <c r="I80" s="7"/>
       <c r="J80" s="7"/>
-      <c r="K80" s="142" t="str">
+      <c r="K80" s="121" t="str">
         <f>+IF(D81="","",IF(D80&lt;0,Sheet2!$C$27,VLOOKUP(D81,Sheet2!$A$27:$C$31,3,TRUE)))</f>
         <v/>
       </c>
-      <c r="L80" s="142"/>
-      <c r="M80" s="142"/>
-      <c r="N80" s="142"/>
-      <c r="O80" s="142"/>
+      <c r="L80" s="121"/>
+      <c r="M80" s="121"/>
+      <c r="N80" s="121"/>
+      <c r="O80" s="121"/>
       <c r="P80" s="28" t="str">
         <f>+IF(K80="","",VLOOKUP(K80,Sheet2!$C$27:$D$31,2,FALSE))</f>
         <v/>
@@ -6320,14 +6320,14 @@
         <f>+IF(D81="","",AVERAGE(D81:G81))</f>
         <v/>
       </c>
-      <c r="K81" s="142" t="str">
+      <c r="K81" s="121" t="str">
         <f>+IF(J81="","",IF(AND(D80&lt;0,E80&lt;0),Sheet2!$C$35,VLOOKUP(J81,Sheet2!$A$35:$C$39,3,TRUE)))</f>
         <v/>
       </c>
-      <c r="L81" s="142"/>
-      <c r="M81" s="142"/>
-      <c r="N81" s="142"/>
-      <c r="O81" s="142"/>
+      <c r="L81" s="121"/>
+      <c r="M81" s="121"/>
+      <c r="N81" s="121"/>
+      <c r="O81" s="121"/>
       <c r="P81" s="28" t="str">
         <f>+IF(K81="","",VLOOKUP(K81,Sheet2!$C$35:$D$39,2,FALSE))</f>
         <v/>
@@ -6374,13 +6374,13 @@
       <c r="J83" s="64" t="s">
         <v>38</v>
       </c>
-      <c r="K83" s="143" t="s">
+      <c r="K83" s="120" t="s">
         <v>40</v>
       </c>
-      <c r="L83" s="143"/>
-      <c r="M83" s="143"/>
-      <c r="N83" s="143"/>
-      <c r="O83" s="143"/>
+      <c r="L83" s="120"/>
+      <c r="M83" s="120"/>
+      <c r="N83" s="120"/>
+      <c r="O83" s="120"/>
       <c r="P83" s="60" t="s">
         <v>124</v>
       </c>
@@ -6396,14 +6396,14 @@
       <c r="H84" s="7"/>
       <c r="I84" s="7"/>
       <c r="J84" s="7"/>
-      <c r="K84" s="142" t="str">
+      <c r="K84" s="121" t="str">
         <f>+IF(D85="","",VLOOKUP(D85,Sheet2!$A$42:$C$43,3,TRUE))</f>
         <v/>
       </c>
-      <c r="L84" s="142"/>
-      <c r="M84" s="142"/>
-      <c r="N84" s="142"/>
-      <c r="O84" s="142"/>
+      <c r="L84" s="121"/>
+      <c r="M84" s="121"/>
+      <c r="N84" s="121"/>
+      <c r="O84" s="121"/>
       <c r="P84" s="28" t="str">
         <f>+IF(K84="","",VLOOKUP(K84,Sheet2!$C$42:$D$43,2,FALSE))</f>
         <v/>
@@ -6439,14 +6439,14 @@
         <f>+IF(D85="","",AVERAGE(D85:G85))</f>
         <v/>
       </c>
-      <c r="K85" s="142" t="str">
+      <c r="K85" s="121" t="str">
         <f>+IF(J85="","",VLOOKUP(J85,Sheet2!$A$45:$C$46,3,TRUE))</f>
         <v/>
       </c>
-      <c r="L85" s="142"/>
-      <c r="M85" s="142"/>
-      <c r="N85" s="142"/>
-      <c r="O85" s="142"/>
+      <c r="L85" s="121"/>
+      <c r="M85" s="121"/>
+      <c r="N85" s="121"/>
+      <c r="O85" s="121"/>
       <c r="P85" s="28" t="str">
         <f>+IF(K85="","",VLOOKUP(K85,Sheet2!$C$45:$D$46,2,FALSE))</f>
         <v/>
@@ -6521,13 +6521,13 @@
       <c r="J88" s="64" t="s">
         <v>38</v>
       </c>
-      <c r="K88" s="143" t="s">
+      <c r="K88" s="120" t="s">
         <v>40</v>
       </c>
-      <c r="L88" s="143"/>
-      <c r="M88" s="143"/>
-      <c r="N88" s="143"/>
-      <c r="O88" s="143"/>
+      <c r="L88" s="120"/>
+      <c r="M88" s="120"/>
+      <c r="N88" s="120"/>
+      <c r="O88" s="120"/>
       <c r="P88" s="60" t="s">
         <v>124</v>
       </c>
@@ -6569,14 +6569,14 @@
       <c r="H90" s="7"/>
       <c r="I90" s="7"/>
       <c r="J90" s="7"/>
-      <c r="K90" s="142" t="str">
+      <c r="K90" s="121" t="str">
         <f>+IF(D91="","",IF(D89&lt;0,Sheet2!$C$50,VLOOKUP(D91,Sheet2!A50:C54,3,TRUE)))</f>
         <v/>
       </c>
-      <c r="L90" s="142"/>
-      <c r="M90" s="142"/>
-      <c r="N90" s="142"/>
-      <c r="O90" s="142"/>
+      <c r="L90" s="121"/>
+      <c r="M90" s="121"/>
+      <c r="N90" s="121"/>
+      <c r="O90" s="121"/>
       <c r="P90" s="28" t="str">
         <f>+IF(K90="","",VLOOKUP(K90,Sheet2!$C$50:$D$54,2,FALSE))</f>
         <v/>
@@ -6608,14 +6608,14 @@
         <f>+IF(D91="","",AVERAGE(D91:G91))</f>
         <v/>
       </c>
-      <c r="K91" s="142" t="str">
+      <c r="K91" s="121" t="str">
         <f>+IF(J91="","",IF(AND(C89&lt;0,D89&lt;0),Sheet2!$C$56,VLOOKUP(J91,Sheet2!$A$56:$C$60,3,TRUE)))</f>
         <v/>
       </c>
-      <c r="L91" s="142"/>
-      <c r="M91" s="142"/>
-      <c r="N91" s="142"/>
-      <c r="O91" s="142"/>
+      <c r="L91" s="121"/>
+      <c r="M91" s="121"/>
+      <c r="N91" s="121"/>
+      <c r="O91" s="121"/>
       <c r="P91" s="28" t="str">
         <f>+IF(K91="","",VLOOKUP(K91,Sheet2!$C$56:$D$60,2,FALSE))</f>
         <v/>
@@ -6662,13 +6662,13 @@
       <c r="J93" s="64" t="s">
         <v>38</v>
       </c>
-      <c r="K93" s="143" t="s">
+      <c r="K93" s="120" t="s">
         <v>40</v>
       </c>
-      <c r="L93" s="143"/>
-      <c r="M93" s="143"/>
-      <c r="N93" s="143"/>
-      <c r="O93" s="143"/>
+      <c r="L93" s="120"/>
+      <c r="M93" s="120"/>
+      <c r="N93" s="120"/>
+      <c r="O93" s="120"/>
       <c r="P93" s="60" t="s">
         <v>124</v>
       </c>
@@ -6684,14 +6684,14 @@
       <c r="H94" s="7"/>
       <c r="I94" s="7"/>
       <c r="J94" s="7"/>
-      <c r="K94" s="142" t="str">
+      <c r="K94" s="121" t="str">
         <f>+IF(D95="","",IF(D94&lt;0,Sheet2!$C$64,VLOOKUP(D95,Sheet2!$A$64:$C$68,3,TRUE)))</f>
         <v/>
       </c>
-      <c r="L94" s="142"/>
-      <c r="M94" s="142"/>
-      <c r="N94" s="142"/>
-      <c r="O94" s="142"/>
+      <c r="L94" s="121"/>
+      <c r="M94" s="121"/>
+      <c r="N94" s="121"/>
+      <c r="O94" s="121"/>
       <c r="P94" s="28" t="str">
         <f>+IF(K94="","",VLOOKUP(K94,Sheet2!$C$64:$D$68,2,FALSE))</f>
         <v/>
@@ -6723,14 +6723,14 @@
         <f>+IF(D95="","",AVERAGE(D95:G95))</f>
         <v/>
       </c>
-      <c r="K95" s="142" t="str">
+      <c r="K95" s="121" t="str">
         <f>+IF(J95="","",IF(AND(C94&lt;0,D94&lt;0),Sheet2!$C$70,VLOOKUP(J95,Sheet2!$A$70:$C$74,3,TRUE)))</f>
         <v/>
       </c>
-      <c r="L95" s="142"/>
-      <c r="M95" s="142"/>
-      <c r="N95" s="142"/>
-      <c r="O95" s="142"/>
+      <c r="L95" s="121"/>
+      <c r="M95" s="121"/>
+      <c r="N95" s="121"/>
+      <c r="O95" s="121"/>
       <c r="P95" s="28" t="str">
         <f>+IF(K95="","",VLOOKUP(K95,Sheet2!$C$70:$D$74,2,FALSE))</f>
         <v/>
@@ -6777,13 +6777,13 @@
       <c r="J97" s="64" t="s">
         <v>38</v>
       </c>
-      <c r="K97" s="143" t="s">
+      <c r="K97" s="120" t="s">
         <v>40</v>
       </c>
-      <c r="L97" s="143"/>
-      <c r="M97" s="143"/>
-      <c r="N97" s="143"/>
-      <c r="O97" s="143"/>
+      <c r="L97" s="120"/>
+      <c r="M97" s="120"/>
+      <c r="N97" s="120"/>
+      <c r="O97" s="120"/>
       <c r="P97" s="60" t="s">
         <v>124</v>
       </c>
@@ -6799,14 +6799,14 @@
       <c r="H98" s="7"/>
       <c r="I98" s="7"/>
       <c r="J98" s="7"/>
-      <c r="K98" s="142" t="str">
+      <c r="K98" s="121" t="str">
         <f>+IF(D99="","",IF(D98&lt;0,Sheet2!$C$78,VLOOKUP(D99,Sheet2!$A$78:$C$82,3,TRUE)))</f>
         <v/>
       </c>
-      <c r="L98" s="142"/>
-      <c r="M98" s="142"/>
-      <c r="N98" s="142"/>
-      <c r="O98" s="142"/>
+      <c r="L98" s="121"/>
+      <c r="M98" s="121"/>
+      <c r="N98" s="121"/>
+      <c r="O98" s="121"/>
       <c r="P98" s="28" t="str">
         <f>+IF(K98="","",VLOOKUP(K98,Sheet2!$C$78:$D$82,2,FALSE))</f>
         <v/>
@@ -6838,14 +6838,14 @@
         <f>+IF(D99="","",AVERAGE(D99:G99))</f>
         <v/>
       </c>
-      <c r="K99" s="142" t="str">
+      <c r="K99" s="121" t="str">
         <f>+IF(J99="","",IF(AND(E98&lt;0,D98&lt;0),Sheet2!$C$84,VLOOKUP(J99,Sheet2!$A$84:$C$88,3,TRUE)))</f>
         <v/>
       </c>
-      <c r="L99" s="142"/>
-      <c r="M99" s="142"/>
-      <c r="N99" s="142"/>
-      <c r="O99" s="142"/>
+      <c r="L99" s="121"/>
+      <c r="M99" s="121"/>
+      <c r="N99" s="121"/>
+      <c r="O99" s="121"/>
       <c r="P99" s="28" t="str">
         <f>+IF(K99="","",VLOOKUP(K99,Sheet2!$C$84:$D$88,2,FALSE))</f>
         <v/>
@@ -6897,13 +6897,13 @@
       <c r="J101" s="64" t="s">
         <v>38</v>
       </c>
-      <c r="K101" s="143" t="s">
+      <c r="K101" s="120" t="s">
         <v>40</v>
       </c>
-      <c r="L101" s="143"/>
-      <c r="M101" s="143"/>
-      <c r="N101" s="143"/>
-      <c r="O101" s="143"/>
+      <c r="L101" s="120"/>
+      <c r="M101" s="120"/>
+      <c r="N101" s="120"/>
+      <c r="O101" s="120"/>
       <c r="P101" s="60" t="s">
         <v>124</v>
       </c>
@@ -6919,14 +6919,14 @@
       <c r="H102" s="7"/>
       <c r="I102" s="7"/>
       <c r="J102" s="7"/>
-      <c r="K102" s="142" t="str">
+      <c r="K102" s="121" t="str">
         <f>+IF(D103="","",VLOOKUP(D103,Sheet2!$A$92:$C$94,3,TRUE))</f>
         <v/>
       </c>
-      <c r="L102" s="142"/>
-      <c r="M102" s="142"/>
-      <c r="N102" s="142"/>
-      <c r="O102" s="142"/>
+      <c r="L102" s="121"/>
+      <c r="M102" s="121"/>
+      <c r="N102" s="121"/>
+      <c r="O102" s="121"/>
       <c r="P102" s="28" t="str">
         <f>+IF(D103="","",VLOOKUP(D103,Sheet2!$A$92:$C$94,2,TRUE))</f>
         <v/>
@@ -6958,14 +6958,14 @@
         <f>+IF(D103="","",AVERAGE(D103:G103))</f>
         <v/>
       </c>
-      <c r="K103" s="142" t="str">
+      <c r="K103" s="121" t="str">
         <f>+IF(J103="","",VLOOKUP(J103,Sheet2!$A$96:$C$98,3,TRUE))</f>
         <v/>
       </c>
-      <c r="L103" s="142"/>
-      <c r="M103" s="142"/>
-      <c r="N103" s="142"/>
-      <c r="O103" s="142"/>
+      <c r="L103" s="121"/>
+      <c r="M103" s="121"/>
+      <c r="N103" s="121"/>
+      <c r="O103" s="121"/>
       <c r="P103" s="28" t="str">
         <f>+IF(J103="","",VLOOKUP(J103,Sheet2!$A$96:$C$98,2,TRUE))</f>
         <v/>
@@ -7012,13 +7012,13 @@
       <c r="J105" s="64" t="s">
         <v>38</v>
       </c>
-      <c r="K105" s="143" t="s">
+      <c r="K105" s="120" t="s">
         <v>40</v>
       </c>
-      <c r="L105" s="143"/>
-      <c r="M105" s="143"/>
-      <c r="N105" s="143"/>
-      <c r="O105" s="143"/>
+      <c r="L105" s="120"/>
+      <c r="M105" s="120"/>
+      <c r="N105" s="120"/>
+      <c r="O105" s="120"/>
       <c r="P105" s="60" t="s">
         <v>124</v>
       </c>
@@ -7047,14 +7047,14 @@
       <c r="H107" s="7"/>
       <c r="I107" s="7"/>
       <c r="J107" s="7"/>
-      <c r="K107" s="142" t="str">
+      <c r="K107" s="121" t="str">
         <f>+IF(D108="","",IF(D106&lt;0,Sheet2!$C$104,VLOOKUP(D108,Sheet2!$A$102:$C$104,3,TRUE)))</f>
         <v/>
       </c>
-      <c r="L107" s="142"/>
-      <c r="M107" s="142"/>
-      <c r="N107" s="142"/>
-      <c r="O107" s="142"/>
+      <c r="L107" s="121"/>
+      <c r="M107" s="121"/>
+      <c r="N107" s="121"/>
+      <c r="O107" s="121"/>
       <c r="P107" s="28" t="str">
         <f>+IF(K107="","",VLOOKUP(K107,Sheet2!$C$102:$D$107,2,FALSE))</f>
         <v/>
@@ -7090,14 +7090,14 @@
         <f>+IF(D108="","",AVERAGE(D108:G108))</f>
         <v/>
       </c>
-      <c r="K108" s="144" t="str">
+      <c r="K108" s="136" t="str">
         <f>+IF(J108="","",IF(AND(D106&lt;0,E106&lt;0),Sheet2!$C$107,VLOOKUP(J108,Sheet2!$A$105:$C$107,3,TRUE)))</f>
         <v/>
       </c>
-      <c r="L108" s="144"/>
-      <c r="M108" s="144"/>
-      <c r="N108" s="144"/>
-      <c r="O108" s="144"/>
+      <c r="L108" s="136"/>
+      <c r="M108" s="136"/>
+      <c r="N108" s="136"/>
+      <c r="O108" s="136"/>
       <c r="P108" s="32" t="str">
         <f>+IF(K108="","",VLOOKUP(K108,Sheet2!$C$102:$D$107,2,FALSE))</f>
         <v/>
@@ -7107,40 +7107,40 @@
       <c r="P109" s="10"/>
     </row>
     <row r="110" spans="2:16" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B110" s="123" t="s">
+      <c r="B110" s="122" t="s">
         <v>48</v>
       </c>
-      <c r="C110" s="124"/>
-      <c r="D110" s="124"/>
-      <c r="E110" s="124"/>
-      <c r="F110" s="124"/>
-      <c r="G110" s="124"/>
-      <c r="H110" s="124"/>
-      <c r="I110" s="124"/>
-      <c r="J110" s="124"/>
-      <c r="K110" s="124"/>
-      <c r="L110" s="124"/>
-      <c r="M110" s="124"/>
-      <c r="N110" s="124"/>
-      <c r="O110" s="124"/>
-      <c r="P110" s="125"/>
+      <c r="C110" s="123"/>
+      <c r="D110" s="123"/>
+      <c r="E110" s="123"/>
+      <c r="F110" s="123"/>
+      <c r="G110" s="123"/>
+      <c r="H110" s="123"/>
+      <c r="I110" s="123"/>
+      <c r="J110" s="123"/>
+      <c r="K110" s="123"/>
+      <c r="L110" s="123"/>
+      <c r="M110" s="123"/>
+      <c r="N110" s="123"/>
+      <c r="O110" s="123"/>
+      <c r="P110" s="124"/>
     </row>
     <row r="111" spans="2:16" x14ac:dyDescent="0.25">
-      <c r="B111" s="137"/>
-      <c r="C111" s="135"/>
-      <c r="D111" s="135"/>
-      <c r="E111" s="135"/>
-      <c r="F111" s="135"/>
-      <c r="G111" s="135"/>
-      <c r="H111" s="135"/>
-      <c r="I111" s="135"/>
-      <c r="J111" s="135"/>
-      <c r="K111" s="135"/>
-      <c r="L111" s="135"/>
-      <c r="M111" s="135"/>
-      <c r="N111" s="135"/>
-      <c r="O111" s="135"/>
-      <c r="P111" s="138"/>
+      <c r="B111" s="125"/>
+      <c r="C111" s="126"/>
+      <c r="D111" s="126"/>
+      <c r="E111" s="126"/>
+      <c r="F111" s="126"/>
+      <c r="G111" s="126"/>
+      <c r="H111" s="126"/>
+      <c r="I111" s="126"/>
+      <c r="J111" s="126"/>
+      <c r="K111" s="126"/>
+      <c r="L111" s="126"/>
+      <c r="M111" s="126"/>
+      <c r="N111" s="126"/>
+      <c r="O111" s="126"/>
+      <c r="P111" s="127"/>
     </row>
     <row r="112" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B112" s="65"/>
@@ -7171,13 +7171,13 @@
       <c r="J112" s="64" t="s">
         <v>38</v>
       </c>
-      <c r="K112" s="143" t="s">
+      <c r="K112" s="120" t="s">
         <v>40</v>
       </c>
-      <c r="L112" s="143"/>
-      <c r="M112" s="143"/>
-      <c r="N112" s="143"/>
-      <c r="O112" s="143"/>
+      <c r="L112" s="120"/>
+      <c r="M112" s="120"/>
+      <c r="N112" s="120"/>
+      <c r="O112" s="120"/>
       <c r="P112" s="60" t="s">
         <v>124</v>
       </c>
@@ -7196,14 +7196,14 @@
         <f>+IF(D113="","",SUM(D113:H113))</f>
         <v/>
       </c>
-      <c r="K113" s="142" t="str">
+      <c r="K113" s="121" t="str">
         <f>+IF(D114="","",IF(D113&lt;0,Sheet2!$C$113,VLOOKUP(D114,Sheet2!$A$110:$C$113,3,TRUE)))</f>
         <v/>
       </c>
-      <c r="L113" s="142"/>
-      <c r="M113" s="142"/>
-      <c r="N113" s="142"/>
-      <c r="O113" s="142"/>
+      <c r="L113" s="121"/>
+      <c r="M113" s="121"/>
+      <c r="N113" s="121"/>
+      <c r="O113" s="121"/>
       <c r="P113" s="28" t="str">
         <f>+IF(K113="","",VLOOKUP(K113,Sheet2!$C$110:$D$117,2,FALSE))</f>
         <v/>
@@ -7235,14 +7235,14 @@
       </c>
       <c r="I114" s="7"/>
       <c r="J114" s="7"/>
-      <c r="K114" s="142" t="str">
+      <c r="K114" s="121" t="str">
         <f>+IF(J114="","",IF(AND(D113&lt;0,E113&lt;0),Sheet2!$C$117,VLOOKUP(J114,Sheet2!$A$114:$C$117,3,TRUE)))</f>
         <v/>
       </c>
-      <c r="L114" s="142"/>
-      <c r="M114" s="142"/>
-      <c r="N114" s="142"/>
-      <c r="O114" s="142"/>
+      <c r="L114" s="121"/>
+      <c r="M114" s="121"/>
+      <c r="N114" s="121"/>
+      <c r="O114" s="121"/>
       <c r="P114" s="28" t="str">
         <f>+IF(K114="","",VLOOKUP(K114,Sheet2!$C$110:$D$117,2,FALSE))</f>
         <v/>
@@ -7288,13 +7288,13 @@
       <c r="J116" s="64" t="s">
         <v>38</v>
       </c>
-      <c r="K116" s="143" t="s">
+      <c r="K116" s="120" t="s">
         <v>40</v>
       </c>
-      <c r="L116" s="143"/>
-      <c r="M116" s="143"/>
-      <c r="N116" s="143"/>
-      <c r="O116" s="143"/>
+      <c r="L116" s="120"/>
+      <c r="M116" s="120"/>
+      <c r="N116" s="120"/>
+      <c r="O116" s="120"/>
       <c r="P116" s="60" t="s">
         <v>124</v>
       </c>
@@ -7310,14 +7310,14 @@
       <c r="H117" s="7"/>
       <c r="I117" s="7"/>
       <c r="J117" s="7"/>
-      <c r="K117" s="142" t="str">
+      <c r="K117" s="121" t="str">
         <f>+IF(D118="","",IF(D117&lt;0,Sheet2!$C$27,VLOOKUP(D118,Sheet2!$A$27:$C$31,3,TRUE)))</f>
         <v/>
       </c>
-      <c r="L117" s="142"/>
-      <c r="M117" s="142"/>
-      <c r="N117" s="142"/>
-      <c r="O117" s="142"/>
+      <c r="L117" s="121"/>
+      <c r="M117" s="121"/>
+      <c r="N117" s="121"/>
+      <c r="O117" s="121"/>
       <c r="P117" s="28" t="str">
         <f>+IF(K117="","",VLOOKUP(K117,Sheet2!$C$27:$D$31,2,FALSE))</f>
         <v/>
@@ -7349,14 +7349,14 @@
         <f>+IF(D118="","",AVERAGE(D118:G118))</f>
         <v/>
       </c>
-      <c r="K118" s="142" t="str">
+      <c r="K118" s="121" t="str">
         <f>+IF(J118="","",IF(AND(D117&lt;0,E117&lt;0),Sheet2!$C$35,VLOOKUP(J118,Sheet2!$A$35:$C$39,3,TRUE)))</f>
         <v/>
       </c>
-      <c r="L118" s="142"/>
-      <c r="M118" s="142"/>
-      <c r="N118" s="142"/>
-      <c r="O118" s="142"/>
+      <c r="L118" s="121"/>
+      <c r="M118" s="121"/>
+      <c r="N118" s="121"/>
+      <c r="O118" s="121"/>
       <c r="P118" s="28" t="str">
         <f>+IF(K118="","",VLOOKUP(K118,Sheet2!$C$35:$D$39,2,FALSE))</f>
         <v/>
@@ -7403,13 +7403,13 @@
       <c r="J120" s="64" t="s">
         <v>38</v>
       </c>
-      <c r="K120" s="143" t="s">
+      <c r="K120" s="120" t="s">
         <v>40</v>
       </c>
-      <c r="L120" s="143"/>
-      <c r="M120" s="143"/>
-      <c r="N120" s="143"/>
-      <c r="O120" s="143"/>
+      <c r="L120" s="120"/>
+      <c r="M120" s="120"/>
+      <c r="N120" s="120"/>
+      <c r="O120" s="120"/>
       <c r="P120" s="60" t="s">
         <v>124</v>
       </c>
@@ -7425,14 +7425,14 @@
       <c r="H121" s="7"/>
       <c r="I121" s="7"/>
       <c r="J121" s="7"/>
-      <c r="K121" s="142" t="str">
+      <c r="K121" s="121" t="str">
         <f>+IF(D122="","",IF(D121&lt;0,Sheet2!$C$27,VLOOKUP(D122,Sheet2!$A$27:$C$31,3,TRUE)))</f>
         <v/>
       </c>
-      <c r="L121" s="142"/>
-      <c r="M121" s="142"/>
-      <c r="N121" s="142"/>
-      <c r="O121" s="142"/>
+      <c r="L121" s="121"/>
+      <c r="M121" s="121"/>
+      <c r="N121" s="121"/>
+      <c r="O121" s="121"/>
       <c r="P121" s="28" t="str">
         <f>+IF(K121="","",VLOOKUP(K121,Sheet2!$C$27:$D$31,2,FALSE))</f>
         <v/>
@@ -7464,14 +7464,14 @@
         <f>+IF(D122="","",AVERAGE(D122:G122))</f>
         <v/>
       </c>
-      <c r="K122" s="142" t="str">
+      <c r="K122" s="121" t="str">
         <f>+IF(J122="","",IF(AND(D121&lt;0,E121&lt;0),Sheet2!$C$35,VLOOKUP(J122,Sheet2!$A$35:$C$39,3,TRUE)))</f>
         <v/>
       </c>
-      <c r="L122" s="142"/>
-      <c r="M122" s="142"/>
-      <c r="N122" s="142"/>
-      <c r="O122" s="142"/>
+      <c r="L122" s="121"/>
+      <c r="M122" s="121"/>
+      <c r="N122" s="121"/>
+      <c r="O122" s="121"/>
       <c r="P122" s="28" t="str">
         <f>+IF(K122="","",VLOOKUP(K122,Sheet2!$C$35:$D$39,2,FALSE))</f>
         <v/>
@@ -7518,13 +7518,13 @@
       <c r="J124" s="64" t="s">
         <v>38</v>
       </c>
-      <c r="K124" s="143" t="s">
+      <c r="K124" s="120" t="s">
         <v>40</v>
       </c>
-      <c r="L124" s="143"/>
-      <c r="M124" s="143"/>
-      <c r="N124" s="143"/>
-      <c r="O124" s="143"/>
+      <c r="L124" s="120"/>
+      <c r="M124" s="120"/>
+      <c r="N124" s="120"/>
+      <c r="O124" s="120"/>
       <c r="P124" s="60" t="s">
         <v>124</v>
       </c>
@@ -7553,14 +7553,14 @@
       <c r="H126" s="7"/>
       <c r="I126" s="7"/>
       <c r="J126" s="7"/>
-      <c r="K126" s="142" t="str">
+      <c r="K126" s="121" t="str">
         <f>+IF(D127="","",IF(D127&lt;0,"Company rebought its stocks in the last year.","Company didn't rebought its stocks in the last year."))</f>
         <v/>
       </c>
-      <c r="L126" s="142"/>
-      <c r="M126" s="142"/>
-      <c r="N126" s="142"/>
-      <c r="O126" s="142"/>
+      <c r="L126" s="121"/>
+      <c r="M126" s="121"/>
+      <c r="N126" s="121"/>
+      <c r="O126" s="121"/>
       <c r="P126" s="28" t="str">
         <f>+IF(D127="","",IF(D127&lt;0,5,1))</f>
         <v/>
@@ -7595,14 +7595,14 @@
         <f>+IF(D127="","",AVERAGE(D127:H127))</f>
         <v/>
       </c>
-      <c r="K127" s="142" t="str">
+      <c r="K127" s="121" t="str">
         <f>+IF(J127="","",IF(J127&lt;0,"Company usually rebuy its stocks","Company usually don't rebuy its stocks"))</f>
         <v/>
       </c>
-      <c r="L127" s="142"/>
-      <c r="M127" s="142"/>
-      <c r="N127" s="142"/>
-      <c r="O127" s="142"/>
+      <c r="L127" s="121"/>
+      <c r="M127" s="121"/>
+      <c r="N127" s="121"/>
+      <c r="O127" s="121"/>
       <c r="P127" s="28" t="str">
         <f>+IF(J127="","",IF(J127&lt;0,5,1))</f>
         <v/>
@@ -7627,40 +7627,40 @@
     </row>
     <row r="129" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="130" spans="2:16" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B130" s="123" t="s">
+      <c r="B130" s="122" t="s">
         <v>50</v>
       </c>
-      <c r="C130" s="124"/>
-      <c r="D130" s="124"/>
-      <c r="E130" s="124"/>
-      <c r="F130" s="124"/>
-      <c r="G130" s="124"/>
-      <c r="H130" s="124"/>
-      <c r="I130" s="124"/>
-      <c r="J130" s="124"/>
-      <c r="K130" s="124"/>
-      <c r="L130" s="124"/>
-      <c r="M130" s="124"/>
-      <c r="N130" s="124"/>
-      <c r="O130" s="124"/>
-      <c r="P130" s="125"/>
+      <c r="C130" s="123"/>
+      <c r="D130" s="123"/>
+      <c r="E130" s="123"/>
+      <c r="F130" s="123"/>
+      <c r="G130" s="123"/>
+      <c r="H130" s="123"/>
+      <c r="I130" s="123"/>
+      <c r="J130" s="123"/>
+      <c r="K130" s="123"/>
+      <c r="L130" s="123"/>
+      <c r="M130" s="123"/>
+      <c r="N130" s="123"/>
+      <c r="O130" s="123"/>
+      <c r="P130" s="124"/>
     </row>
     <row r="131" spans="2:16" x14ac:dyDescent="0.25">
-      <c r="B131" s="137"/>
-      <c r="C131" s="135"/>
-      <c r="D131" s="135"/>
-      <c r="E131" s="135"/>
-      <c r="F131" s="135"/>
-      <c r="G131" s="135"/>
-      <c r="H131" s="135"/>
-      <c r="I131" s="135"/>
-      <c r="J131" s="135"/>
-      <c r="K131" s="135"/>
-      <c r="L131" s="135"/>
-      <c r="M131" s="135"/>
-      <c r="N131" s="135"/>
-      <c r="O131" s="135"/>
-      <c r="P131" s="138"/>
+      <c r="B131" s="125"/>
+      <c r="C131" s="126"/>
+      <c r="D131" s="126"/>
+      <c r="E131" s="126"/>
+      <c r="F131" s="126"/>
+      <c r="G131" s="126"/>
+      <c r="H131" s="126"/>
+      <c r="I131" s="126"/>
+      <c r="J131" s="126"/>
+      <c r="K131" s="126"/>
+      <c r="L131" s="126"/>
+      <c r="M131" s="126"/>
+      <c r="N131" s="126"/>
+      <c r="O131" s="126"/>
+      <c r="P131" s="127"/>
     </row>
     <row r="132" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B132" s="65"/>
@@ -7691,13 +7691,13 @@
       <c r="J132" s="64" t="s">
         <v>38</v>
       </c>
-      <c r="K132" s="143" t="s">
+      <c r="K132" s="120" t="s">
         <v>40</v>
       </c>
-      <c r="L132" s="143"/>
-      <c r="M132" s="143"/>
-      <c r="N132" s="143"/>
-      <c r="O132" s="143"/>
+      <c r="L132" s="120"/>
+      <c r="M132" s="120"/>
+      <c r="N132" s="120"/>
+      <c r="O132" s="120"/>
       <c r="P132" s="60" t="s">
         <v>124</v>
       </c>
@@ -7714,14 +7714,14 @@
       <c r="H133" s="7"/>
       <c r="I133" s="7"/>
       <c r="J133" s="7"/>
-      <c r="K133" s="142" t="str">
+      <c r="K133" s="121" t="str">
         <f>+IF(D134="","",IF(D133&lt;0,Sheet2!$C$121,VLOOKUP(D134,Sheet2!$A$121:$C$125,3,TRUE)))</f>
         <v/>
       </c>
-      <c r="L133" s="142"/>
-      <c r="M133" s="142"/>
-      <c r="N133" s="142"/>
-      <c r="O133" s="142"/>
+      <c r="L133" s="121"/>
+      <c r="M133" s="121"/>
+      <c r="N133" s="121"/>
+      <c r="O133" s="121"/>
       <c r="P133" s="28" t="str">
         <f>+IF(K133="","",VLOOKUP(K133,Sheet2!$C$121:$D$131,2,FALSE))</f>
         <v/>
@@ -7757,14 +7757,14 @@
         <f>+IF(D134="","",AVERAGE(D134:G134))</f>
         <v/>
       </c>
-      <c r="K134" s="142" t="str">
+      <c r="K134" s="121" t="str">
         <f>+IF(J134="","",IF(AND(D133&lt;0,E133&lt;0),Sheet2!$C$127,VLOOKUP(J134,Sheet2!$A$127:$C$131,3,TRUE)))</f>
         <v/>
       </c>
-      <c r="L134" s="142"/>
-      <c r="M134" s="142"/>
-      <c r="N134" s="142"/>
-      <c r="O134" s="142"/>
+      <c r="L134" s="121"/>
+      <c r="M134" s="121"/>
+      <c r="N134" s="121"/>
+      <c r="O134" s="121"/>
       <c r="P134" s="28" t="str">
         <f>+IF(K134="","",VLOOKUP(K134,Sheet2!$C$121:$D$131,2,FALSE))</f>
         <v/>
@@ -7794,14 +7794,14 @@
       <c r="H136" s="7"/>
       <c r="I136" s="7"/>
       <c r="J136" s="7"/>
-      <c r="K136" s="142" t="str">
+      <c r="K136" s="121" t="str">
         <f>+IF(C136="","",IF(C136&gt;C133,Sheet2!$A$133,Sheet2!$A$134))</f>
         <v/>
       </c>
-      <c r="L136" s="142"/>
-      <c r="M136" s="142"/>
-      <c r="N136" s="142"/>
-      <c r="O136" s="142"/>
+      <c r="L136" s="121"/>
+      <c r="M136" s="121"/>
+      <c r="N136" s="121"/>
+      <c r="O136" s="121"/>
       <c r="P136" s="56" t="str">
         <f>+IF(K136="","",VLOOKUP(K136,Sheet2!$A$133:$B$134,2,FALSE))</f>
         <v/>
@@ -7848,13 +7848,13 @@
       <c r="J138" s="64" t="s">
         <v>38</v>
       </c>
-      <c r="K138" s="143" t="s">
+      <c r="K138" s="120" t="s">
         <v>40</v>
       </c>
-      <c r="L138" s="143"/>
-      <c r="M138" s="143"/>
-      <c r="N138" s="143"/>
-      <c r="O138" s="143"/>
+      <c r="L138" s="120"/>
+      <c r="M138" s="120"/>
+      <c r="N138" s="120"/>
+      <c r="O138" s="120"/>
       <c r="P138" s="60" t="s">
         <v>124</v>
       </c>
@@ -7874,14 +7874,14 @@
         <f>+IF(D139="","",AVERAGE(D139:H139))</f>
         <v/>
       </c>
-      <c r="K139" s="142" t="str">
+      <c r="K139" s="121" t="str">
         <f>+IF(C139="","",VLOOKUP(C139,Sheet2!$A$138:$C$145,3,TRUE))</f>
         <v/>
       </c>
-      <c r="L139" s="142"/>
-      <c r="M139" s="142"/>
-      <c r="N139" s="142"/>
-      <c r="O139" s="142"/>
+      <c r="L139" s="121"/>
+      <c r="M139" s="121"/>
+      <c r="N139" s="121"/>
+      <c r="O139" s="121"/>
       <c r="P139" s="28" t="str">
         <f>+IF(C139="","",VLOOKUP(C139,Sheet2!$A$138:$C$145,2,TRUE))</f>
         <v/>
@@ -7915,14 +7915,14 @@
         <f>+IF(D140="","",AVERAGE(D140:G140))</f>
         <v/>
       </c>
-      <c r="K140" s="142" t="str">
+      <c r="K140" s="121" t="str">
         <f>+IF(J139="","",VLOOKUP(J139,Sheet2!$A$147:$C$153,3,TRUE))</f>
         <v/>
       </c>
-      <c r="L140" s="142"/>
-      <c r="M140" s="142"/>
-      <c r="N140" s="142"/>
-      <c r="O140" s="142"/>
+      <c r="L140" s="121"/>
+      <c r="M140" s="121"/>
+      <c r="N140" s="121"/>
+      <c r="O140" s="121"/>
       <c r="P140" s="28" t="str">
         <f>+IF(J139="","",VLOOKUP(J139,Sheet2!$A$147:$C$153,2,TRUE))</f>
         <v/>
@@ -7938,14 +7938,14 @@
       <c r="H141" s="7"/>
       <c r="I141" s="7"/>
       <c r="J141" s="7"/>
-      <c r="K141" s="142" t="str">
+      <c r="K141" s="121" t="str">
         <f>+IF(C139="","",IF(C139&lt;$C$203,Sheet2!$A$155,IF(C139&lt;($C$203*1.1),Sheet2!$A$156,IF(C139&lt;($C$203*1.2),Sheet2!$A$157,Sheet2!A158))))</f>
         <v/>
       </c>
-      <c r="L141" s="142"/>
-      <c r="M141" s="142"/>
-      <c r="N141" s="142"/>
-      <c r="O141" s="142"/>
+      <c r="L141" s="121"/>
+      <c r="M141" s="121"/>
+      <c r="N141" s="121"/>
+      <c r="O141" s="121"/>
       <c r="P141" s="56" t="str">
         <f>+IF(K141="","",VLOOKUP(K141,Sheet2!$A$155:$B$158,2,FALSE))</f>
         <v/>
@@ -7963,14 +7963,14 @@
       <c r="H142" s="7"/>
       <c r="I142" s="7"/>
       <c r="J142" s="7"/>
-      <c r="K142" s="142" t="str">
+      <c r="K142" s="121" t="str">
         <f>+IF(C142="","",IF(C142&gt;C139,Sheet2!$A$161,Sheet2!$A$160))</f>
         <v/>
       </c>
-      <c r="L142" s="142"/>
-      <c r="M142" s="142"/>
-      <c r="N142" s="142"/>
-      <c r="O142" s="142"/>
+      <c r="L142" s="121"/>
+      <c r="M142" s="121"/>
+      <c r="N142" s="121"/>
+      <c r="O142" s="121"/>
       <c r="P142" s="56" t="str">
         <f>+IF(K142="","",VLOOKUP(K142,Sheet2!$A$160:$B$161,2,FALSE))</f>
         <v/>
@@ -8017,13 +8017,13 @@
       <c r="J144" s="64" t="s">
         <v>38</v>
       </c>
-      <c r="K144" s="143" t="s">
+      <c r="K144" s="120" t="s">
         <v>40</v>
       </c>
-      <c r="L144" s="143"/>
-      <c r="M144" s="143"/>
-      <c r="N144" s="143"/>
-      <c r="O144" s="143"/>
+      <c r="L144" s="120"/>
+      <c r="M144" s="120"/>
+      <c r="N144" s="120"/>
+      <c r="O144" s="120"/>
       <c r="P144" s="60" t="s">
         <v>124</v>
       </c>
@@ -8040,14 +8040,14 @@
       <c r="H145" s="7"/>
       <c r="I145" s="7"/>
       <c r="J145" s="7"/>
-      <c r="K145" s="142" t="str">
+      <c r="K145" s="121" t="str">
         <f>+IF(C145="","",VLOOKUP(C145,Sheet2!$A$138:$C$145,3,TRUE))</f>
         <v/>
       </c>
-      <c r="L145" s="142"/>
-      <c r="M145" s="142"/>
-      <c r="N145" s="142"/>
-      <c r="O145" s="142"/>
+      <c r="L145" s="121"/>
+      <c r="M145" s="121"/>
+      <c r="N145" s="121"/>
+      <c r="O145" s="121"/>
       <c r="P145" s="28" t="str">
         <f>+IF(C145="","",VLOOKUP(C145,Sheet2!$A$138:$C$145,2,TRUE))</f>
         <v/>
@@ -8081,14 +8081,14 @@
         <f>+IF(D146="","",AVERAGE(D146:G146))</f>
         <v/>
       </c>
-      <c r="K146" s="142" t="str">
+      <c r="K146" s="121" t="str">
         <f>+IF(C145="","",IF(C145&lt;$D$203,Sheet2!$A$155,IF(C145&lt;($D$203*1.1),Sheet2!$A$156,IF(C145&lt;($D$203*1.2),Sheet2!$A$157,Sheet2!A158))))</f>
         <v/>
       </c>
-      <c r="L146" s="142"/>
-      <c r="M146" s="142"/>
-      <c r="N146" s="142"/>
-      <c r="O146" s="142"/>
+      <c r="L146" s="121"/>
+      <c r="M146" s="121"/>
+      <c r="N146" s="121"/>
+      <c r="O146" s="121"/>
       <c r="P146" s="56" t="str">
         <f>+IF(K146="","",VLOOKUP(K146,Sheet2!$A$155:$B$158,2,FALSE))</f>
         <v/>
@@ -8135,13 +8135,13 @@
       <c r="J148" s="64" t="s">
         <v>38</v>
       </c>
-      <c r="K148" s="143" t="s">
+      <c r="K148" s="120" t="s">
         <v>40</v>
       </c>
-      <c r="L148" s="143"/>
-      <c r="M148" s="143"/>
-      <c r="N148" s="143"/>
-      <c r="O148" s="143"/>
+      <c r="L148" s="120"/>
+      <c r="M148" s="120"/>
+      <c r="N148" s="120"/>
+      <c r="O148" s="120"/>
       <c r="P148" s="60" t="s">
         <v>124</v>
       </c>
@@ -8158,14 +8158,14 @@
       <c r="H149" s="7"/>
       <c r="I149" s="7"/>
       <c r="J149" s="7"/>
-      <c r="K149" s="142" t="str">
+      <c r="K149" s="121" t="str">
         <f>+IF(C149="","",VLOOKUP(C149,Sheet2!$A$164:$C$170,3,TRUE))</f>
         <v/>
       </c>
-      <c r="L149" s="142"/>
-      <c r="M149" s="142"/>
-      <c r="N149" s="142"/>
-      <c r="O149" s="142"/>
+      <c r="L149" s="121"/>
+      <c r="M149" s="121"/>
+      <c r="N149" s="121"/>
+      <c r="O149" s="121"/>
       <c r="P149" s="28" t="str">
         <f>+IF(C149="","",VLOOKUP(C149,Sheet2!$A$164:$C$170,2,TRUE))</f>
         <v/>
@@ -8199,14 +8199,14 @@
         <f>+IF(D150="","",AVERAGE(D150:G150))</f>
         <v/>
       </c>
-      <c r="K150" s="142" t="str">
+      <c r="K150" s="121" t="str">
         <f>+IF(C149="","",IF(C149&lt;$E$203,Sheet2!$A$155,IF(C149&lt;($E$203*1.1),Sheet2!$A$156,IF(C149&lt;($E$203*1.2),Sheet2!$A$157,Sheet2!A158))))</f>
         <v/>
       </c>
-      <c r="L150" s="142"/>
-      <c r="M150" s="142"/>
-      <c r="N150" s="142"/>
-      <c r="O150" s="142"/>
+      <c r="L150" s="121"/>
+      <c r="M150" s="121"/>
+      <c r="N150" s="121"/>
+      <c r="O150" s="121"/>
       <c r="P150" s="56" t="str">
         <f>+IF(K150="","",VLOOKUP(K150,Sheet2!$A$155:$B$158,2,FALSE))</f>
         <v/>
@@ -8253,13 +8253,13 @@
       <c r="J152" s="64" t="s">
         <v>38</v>
       </c>
-      <c r="K152" s="143" t="s">
+      <c r="K152" s="120" t="s">
         <v>40</v>
       </c>
-      <c r="L152" s="143"/>
-      <c r="M152" s="143"/>
-      <c r="N152" s="143"/>
-      <c r="O152" s="143"/>
+      <c r="L152" s="120"/>
+      <c r="M152" s="120"/>
+      <c r="N152" s="120"/>
+      <c r="O152" s="120"/>
       <c r="P152" s="60" t="s">
         <v>124</v>
       </c>
@@ -8276,11 +8276,11 @@
       <c r="H153" s="7"/>
       <c r="I153" s="7"/>
       <c r="J153" s="7"/>
-      <c r="K153" s="142"/>
-      <c r="L153" s="142"/>
-      <c r="M153" s="142"/>
-      <c r="N153" s="142"/>
-      <c r="O153" s="142"/>
+      <c r="K153" s="121"/>
+      <c r="L153" s="121"/>
+      <c r="M153" s="121"/>
+      <c r="N153" s="121"/>
+      <c r="O153" s="121"/>
       <c r="P153" s="28"/>
     </row>
     <row r="154" spans="2:16" x14ac:dyDescent="0.25">
@@ -8311,14 +8311,14 @@
         <f>+IF(D154="","",AVERAGE(D154:G154))</f>
         <v/>
       </c>
-      <c r="K154" s="142" t="str">
+      <c r="K154" s="121" t="str">
         <f>+IF(C153="","",IF(C153&lt;$F$203,Sheet2!$A$155,IF(C153&lt;($F$203*1.1),Sheet2!$A$156,IF(C153&lt;($F$203*1.2),Sheet2!$A$157,Sheet2!A158))))</f>
         <v/>
       </c>
-      <c r="L154" s="142"/>
-      <c r="M154" s="142"/>
-      <c r="N154" s="142"/>
-      <c r="O154" s="142"/>
+      <c r="L154" s="121"/>
+      <c r="M154" s="121"/>
+      <c r="N154" s="121"/>
+      <c r="O154" s="121"/>
       <c r="P154" s="56" t="str">
         <f>+IF(K154="","",VLOOKUP(K154,Sheet2!$A$155:$B$158,2,FALSE))</f>
         <v/>
@@ -8365,13 +8365,13 @@
       <c r="J156" s="64" t="s">
         <v>38</v>
       </c>
-      <c r="K156" s="143" t="s">
+      <c r="K156" s="120" t="s">
         <v>40</v>
       </c>
-      <c r="L156" s="143"/>
-      <c r="M156" s="143"/>
-      <c r="N156" s="143"/>
-      <c r="O156" s="143"/>
+      <c r="L156" s="120"/>
+      <c r="M156" s="120"/>
+      <c r="N156" s="120"/>
+      <c r="O156" s="120"/>
       <c r="P156" s="60" t="s">
         <v>124</v>
       </c>
@@ -8388,14 +8388,14 @@
       <c r="H157" s="7"/>
       <c r="I157" s="7"/>
       <c r="J157" s="7"/>
-      <c r="K157" s="142" t="str">
+      <c r="K157" s="121" t="str">
         <f>+IF(C157="","",VLOOKUP(C157,Sheet2!$A$173:$C$179,3,TRUE))</f>
         <v/>
       </c>
-      <c r="L157" s="142"/>
-      <c r="M157" s="142"/>
-      <c r="N157" s="142"/>
-      <c r="O157" s="142"/>
+      <c r="L157" s="121"/>
+      <c r="M157" s="121"/>
+      <c r="N157" s="121"/>
+      <c r="O157" s="121"/>
       <c r="P157" s="28" t="str">
         <f>+IF(C157="","",VLOOKUP(C157,Sheet2!$A$173:$C$179,2,TRUE))</f>
         <v/>
@@ -8429,14 +8429,14 @@
         <f>+IF(D158="","",AVERAGE(D158:G158))</f>
         <v/>
       </c>
-      <c r="K158" s="142" t="str">
+      <c r="K158" s="121" t="str">
         <f>+IF(C157="","",IF(C157&lt;$G$203,Sheet2!$A$155,IF(C157&lt;($G$203*1.1),Sheet2!$A$156,IF(C157&lt;($G$203*1.2),Sheet2!$A$157,Sheet2!A158))))</f>
         <v/>
       </c>
-      <c r="L158" s="142"/>
-      <c r="M158" s="142"/>
-      <c r="N158" s="142"/>
-      <c r="O158" s="142"/>
+      <c r="L158" s="121"/>
+      <c r="M158" s="121"/>
+      <c r="N158" s="121"/>
+      <c r="O158" s="121"/>
       <c r="P158" s="56" t="str">
         <f>+IF(K158="","",VLOOKUP(K158,Sheet2!$A$155:$B$158,2,FALSE))</f>
         <v/>
@@ -8466,13 +8466,13 @@
       <c r="H160" s="66"/>
       <c r="I160" s="66"/>
       <c r="J160" s="66"/>
-      <c r="K160" s="143" t="s">
+      <c r="K160" s="120" t="s">
         <v>40</v>
       </c>
-      <c r="L160" s="143"/>
-      <c r="M160" s="143"/>
-      <c r="N160" s="143"/>
-      <c r="O160" s="143"/>
+      <c r="L160" s="120"/>
+      <c r="M160" s="120"/>
+      <c r="N160" s="120"/>
+      <c r="O160" s="120"/>
       <c r="P160" s="60" t="s">
         <v>124</v>
       </c>
@@ -8492,14 +8492,14 @@
       <c r="H161" s="7"/>
       <c r="I161" s="7"/>
       <c r="J161" s="7"/>
-      <c r="K161" s="142" t="str">
+      <c r="K161" s="121" t="str">
         <f>+IF(C161="","",IF(C161&gt;($J$203*1.1),Sheet2!$A$182,IF(Sheet1!C161&gt;(Sheet1!$J$203*0.8),Sheet2!A183,IF(Sheet1!C161&gt;(Sheet1!J203*0.6),Sheet2!A184,Sheet2!A185))))</f>
         <v/>
       </c>
-      <c r="L161" s="142"/>
-      <c r="M161" s="142"/>
-      <c r="N161" s="142"/>
-      <c r="O161" s="142"/>
+      <c r="L161" s="121"/>
+      <c r="M161" s="121"/>
+      <c r="N161" s="121"/>
+      <c r="O161" s="121"/>
       <c r="P161" s="56" t="str">
         <f>+IF(K161="","",VLOOKUP(K161,Sheet2!$A$182:$B$185,2,FALSE))</f>
         <v/>
@@ -8520,14 +8520,14 @@
       <c r="H162" s="7"/>
       <c r="I162" s="7"/>
       <c r="J162" s="7"/>
-      <c r="K162" s="142" t="str">
+      <c r="K162" s="121" t="str">
         <f>+IF(C162="","",IF(C162&gt;($K$203*1.1),Sheet2!$A$182,IF(Sheet1!C162&gt;(Sheet1!$K$203*0.8),Sheet2!A183,IF(Sheet1!C162&gt;(Sheet1!K203*0.6),Sheet2!A184,Sheet2!A185))))</f>
         <v/>
       </c>
-      <c r="L162" s="142"/>
-      <c r="M162" s="142"/>
-      <c r="N162" s="142"/>
-      <c r="O162" s="142"/>
+      <c r="L162" s="121"/>
+      <c r="M162" s="121"/>
+      <c r="N162" s="121"/>
+      <c r="O162" s="121"/>
       <c r="P162" s="56" t="str">
         <f>+IF(K162="","",VLOOKUP(K162,Sheet2!$A$182:$B$185,2,FALSE))</f>
         <v/>
@@ -8574,13 +8574,13 @@
       <c r="J164" s="64" t="s">
         <v>38</v>
       </c>
-      <c r="K164" s="143" t="s">
+      <c r="K164" s="120" t="s">
         <v>40</v>
       </c>
-      <c r="L164" s="143"/>
-      <c r="M164" s="143"/>
-      <c r="N164" s="143"/>
-      <c r="O164" s="143"/>
+      <c r="L164" s="120"/>
+      <c r="M164" s="120"/>
+      <c r="N164" s="120"/>
+      <c r="O164" s="120"/>
       <c r="P164" s="60" t="s">
         <v>124</v>
       </c>
@@ -8600,14 +8600,14 @@
         <f>+IF(D165="","",AVERAGE(D165:H165))</f>
         <v/>
       </c>
-      <c r="K165" s="142" t="str">
+      <c r="K165" s="121" t="str">
         <f>+IF(C165="","",VLOOKUP(C165,Sheet2!$A$189:$C$195,3,TRUE))</f>
         <v/>
       </c>
-      <c r="L165" s="142"/>
-      <c r="M165" s="142"/>
-      <c r="N165" s="142"/>
-      <c r="O165" s="142"/>
+      <c r="L165" s="121"/>
+      <c r="M165" s="121"/>
+      <c r="N165" s="121"/>
+      <c r="O165" s="121"/>
       <c r="P165" s="28" t="str">
         <f>+IF(C165="","",VLOOKUP(C165,Sheet2!$A$189:$C$195,2,TRUE))</f>
         <v/>
@@ -8638,14 +8638,14 @@
       <c r="H166" s="7"/>
       <c r="I166" s="7"/>
       <c r="J166" s="5"/>
-      <c r="K166" s="142" t="str">
+      <c r="K166" s="121" t="str">
         <f>+IF(J165="","",VLOOKUP(J165,Sheet2!$A$198:$C$204,3,TRUE))</f>
         <v/>
       </c>
-      <c r="L166" s="142"/>
-      <c r="M166" s="142"/>
-      <c r="N166" s="142"/>
-      <c r="O166" s="142"/>
+      <c r="L166" s="121"/>
+      <c r="M166" s="121"/>
+      <c r="N166" s="121"/>
+      <c r="O166" s="121"/>
       <c r="P166" s="28" t="str">
         <f>+IF(J165="","",VLOOKUP(J165,Sheet2!$A$198:$C$204,2,TRUE))</f>
         <v/>
@@ -8661,14 +8661,14 @@
       <c r="H167" s="7"/>
       <c r="I167" s="7"/>
       <c r="J167" s="7"/>
-      <c r="K167" s="142" t="str">
+      <c r="K167" s="121" t="str">
         <f>+IF(C165="","",IF(C165&gt;(1.15*$L$203),Sheet2!$A$206,IF(Sheet1!C165&gt;Sheet1!$L$203,Sheet2!$A$207,IF(Sheet1!C165&gt;(0.7*Sheet1!$L$203),Sheet2!$A$208,IF(Sheet1!C165&gt;(0.6*Sheet1!$L$203),Sheet2!$A$209,Sheet2!$A$210)))))</f>
         <v/>
       </c>
-      <c r="L167" s="142"/>
-      <c r="M167" s="142"/>
-      <c r="N167" s="142"/>
-      <c r="O167" s="142"/>
+      <c r="L167" s="121"/>
+      <c r="M167" s="121"/>
+      <c r="N167" s="121"/>
+      <c r="O167" s="121"/>
       <c r="P167" s="56" t="str">
         <f>+IF(K167="","",VLOOKUP(K167,Sheet2!$A$206:$B$210,2,FALSE))</f>
         <v/>
@@ -8720,13 +8720,13 @@
       <c r="J169" s="64" t="s">
         <v>38</v>
       </c>
-      <c r="K169" s="143" t="s">
+      <c r="K169" s="120" t="s">
         <v>40</v>
       </c>
-      <c r="L169" s="143"/>
-      <c r="M169" s="143"/>
-      <c r="N169" s="143"/>
-      <c r="O169" s="143"/>
+      <c r="L169" s="120"/>
+      <c r="M169" s="120"/>
+      <c r="N169" s="120"/>
+      <c r="O169" s="120"/>
       <c r="P169" s="60" t="s">
         <v>124</v>
       </c>
@@ -8746,14 +8746,14 @@
         <f>+IF(D170="","",AVERAGE(D170:H170))</f>
         <v/>
       </c>
-      <c r="K170" s="142" t="str">
+      <c r="K170" s="121" t="str">
         <f>+IF(C170="","",VLOOKUP(C170,Sheet2!$A$189:$C$195,3,TRUE))</f>
         <v/>
       </c>
-      <c r="L170" s="142"/>
-      <c r="M170" s="142"/>
-      <c r="N170" s="142"/>
-      <c r="O170" s="142"/>
+      <c r="L170" s="121"/>
+      <c r="M170" s="121"/>
+      <c r="N170" s="121"/>
+      <c r="O170" s="121"/>
       <c r="P170" s="28" t="str">
         <f>+IF(C170="","",VLOOKUP(C170,Sheet2!$A$189:$C$195,2,TRUE))</f>
         <v/>
@@ -8786,14 +8786,14 @@
       <c r="H171" s="7"/>
       <c r="I171" s="7"/>
       <c r="J171" s="5"/>
-      <c r="K171" s="142" t="str">
+      <c r="K171" s="121" t="str">
         <f>+IF(J170="","",VLOOKUP(J170,Sheet2!$A$198:$C$204,3,TRUE))</f>
         <v/>
       </c>
-      <c r="L171" s="142"/>
-      <c r="M171" s="142"/>
-      <c r="N171" s="142"/>
-      <c r="O171" s="142"/>
+      <c r="L171" s="121"/>
+      <c r="M171" s="121"/>
+      <c r="N171" s="121"/>
+      <c r="O171" s="121"/>
       <c r="P171" s="28" t="str">
         <f>+IF(J170="","",VLOOKUP(J170,Sheet2!$A$198:$C$204,2,TRUE))</f>
         <v/>
@@ -8809,14 +8809,14 @@
       <c r="H172" s="7"/>
       <c r="I172" s="7"/>
       <c r="J172" s="7"/>
-      <c r="K172" s="142" t="str">
+      <c r="K172" s="121" t="str">
         <f>+IF(C170="","",IF(C170&gt;(1.15*$M$203),Sheet2!$A$206,IF(Sheet1!C170&gt;Sheet1!$M$203,Sheet2!$A$207,IF(Sheet1!C170&gt;(0.7*Sheet1!$M$203),Sheet2!$A$208,IF(Sheet1!C170&gt;(0.6*Sheet1!$M$203),Sheet2!$A$209,Sheet2!$A$210)))))</f>
         <v/>
       </c>
-      <c r="L172" s="142"/>
-      <c r="M172" s="142"/>
-      <c r="N172" s="142"/>
-      <c r="O172" s="142"/>
+      <c r="L172" s="121"/>
+      <c r="M172" s="121"/>
+      <c r="N172" s="121"/>
+      <c r="O172" s="121"/>
       <c r="P172" s="56" t="str">
         <f>+IF(K172="","",VLOOKUP(K172,Sheet2!$A$206:$B$210,2,FALSE))</f>
         <v/>
@@ -8863,13 +8863,13 @@
       <c r="J174" s="64" t="s">
         <v>38</v>
       </c>
-      <c r="K174" s="143" t="s">
+      <c r="K174" s="120" t="s">
         <v>40</v>
       </c>
-      <c r="L174" s="143"/>
-      <c r="M174" s="143"/>
-      <c r="N174" s="143"/>
-      <c r="O174" s="143"/>
+      <c r="L174" s="120"/>
+      <c r="M174" s="120"/>
+      <c r="N174" s="120"/>
+      <c r="O174" s="120"/>
       <c r="P174" s="60" t="s">
         <v>124</v>
       </c>
@@ -8889,14 +8889,14 @@
         <f>+IF(D175="","",AVERAGE(D175:H175))</f>
         <v/>
       </c>
-      <c r="K175" s="142" t="str">
+      <c r="K175" s="121" t="str">
         <f>+IF(C175="","",VLOOKUP(C175,Sheet2!$A$214:$C$220,3,TRUE))</f>
         <v/>
       </c>
-      <c r="L175" s="142"/>
-      <c r="M175" s="142"/>
-      <c r="N175" s="142"/>
-      <c r="O175" s="142"/>
+      <c r="L175" s="121"/>
+      <c r="M175" s="121"/>
+      <c r="N175" s="121"/>
+      <c r="O175" s="121"/>
       <c r="P175" s="28" t="str">
         <f>+IF(C175="","",VLOOKUP(C175,Sheet2!$A$214:$C$220,2,TRUE))</f>
         <v/>
@@ -8927,14 +8927,14 @@
       <c r="H176" s="7"/>
       <c r="I176" s="7"/>
       <c r="J176" s="5"/>
-      <c r="K176" s="142" t="str">
+      <c r="K176" s="121" t="str">
         <f>+IF(J175="","",VLOOKUP(J175,Sheet2!$A$223:$C$229,3,TRUE))</f>
         <v/>
       </c>
-      <c r="L176" s="142"/>
-      <c r="M176" s="142"/>
-      <c r="N176" s="142"/>
-      <c r="O176" s="142"/>
+      <c r="L176" s="121"/>
+      <c r="M176" s="121"/>
+      <c r="N176" s="121"/>
+      <c r="O176" s="121"/>
       <c r="P176" s="28" t="str">
         <f>+IF(J175="","",VLOOKUP(J175,Sheet2!$A$223:$C$229,2,TRUE))</f>
         <v/>
@@ -8950,14 +8950,14 @@
       <c r="H177" s="7"/>
       <c r="I177" s="7"/>
       <c r="J177" s="7"/>
-      <c r="K177" s="142" t="str">
+      <c r="K177" s="121" t="str">
         <f>+IF(C175="","",IF(C175&gt;(1.15*$N$203),Sheet2!$A$231,IF(Sheet1!C175&gt;Sheet1!$N$203,Sheet2!$A$232,IF(Sheet1!C175&gt;(0.7*Sheet1!$N$203),Sheet2!$A$233,IF(Sheet1!C175&gt;(0.6*Sheet1!$N$203),Sheet2!$A$234,Sheet2!$A$235)))))</f>
         <v/>
       </c>
-      <c r="L177" s="142"/>
-      <c r="M177" s="142"/>
-      <c r="N177" s="142"/>
-      <c r="O177" s="142"/>
+      <c r="L177" s="121"/>
+      <c r="M177" s="121"/>
+      <c r="N177" s="121"/>
+      <c r="O177" s="121"/>
       <c r="P177" s="56" t="str">
         <f>+IF(K177="","",VLOOKUP(K177,Sheet2!$A$231:$B$235,2,FALSE))</f>
         <v/>
@@ -9004,13 +9004,13 @@
       <c r="J179" s="64" t="s">
         <v>38</v>
       </c>
-      <c r="K179" s="143" t="s">
+      <c r="K179" s="120" t="s">
         <v>40</v>
       </c>
-      <c r="L179" s="143"/>
-      <c r="M179" s="143"/>
-      <c r="N179" s="143"/>
-      <c r="O179" s="143"/>
+      <c r="L179" s="120"/>
+      <c r="M179" s="120"/>
+      <c r="N179" s="120"/>
+      <c r="O179" s="120"/>
       <c r="P179" s="60" t="s">
         <v>124</v>
       </c>
@@ -9045,14 +9045,14 @@
         <f>+IF(D180="","",AVERAGE(D180:H180))</f>
         <v/>
       </c>
-      <c r="K180" s="142" t="str">
+      <c r="K180" s="121" t="str">
         <f>+IF(D180="","",VLOOKUP(D180,Sheet2!$A$239:$C$245,3,TRUE))</f>
         <v/>
       </c>
-      <c r="L180" s="142"/>
-      <c r="M180" s="142"/>
-      <c r="N180" s="142"/>
-      <c r="O180" s="142"/>
+      <c r="L180" s="121"/>
+      <c r="M180" s="121"/>
+      <c r="N180" s="121"/>
+      <c r="O180" s="121"/>
       <c r="P180" s="28" t="str">
         <f>+IF(D180="","",VLOOKUP(D180,Sheet2!$A$239:$C$245,2,TRUE))</f>
         <v/>
@@ -9128,13 +9128,13 @@
       <c r="J183" s="64" t="s">
         <v>38</v>
       </c>
-      <c r="K183" s="143" t="s">
+      <c r="K183" s="120" t="s">
         <v>40</v>
       </c>
-      <c r="L183" s="143"/>
-      <c r="M183" s="143"/>
-      <c r="N183" s="143"/>
-      <c r="O183" s="143"/>
+      <c r="L183" s="120"/>
+      <c r="M183" s="120"/>
+      <c r="N183" s="120"/>
+      <c r="O183" s="120"/>
       <c r="P183" s="60" t="s">
         <v>124</v>
       </c>
@@ -9154,14 +9154,14 @@
         <f>+IF(D184="","",AVERAGE(D184:H184))</f>
         <v/>
       </c>
-      <c r="K184" s="142" t="str">
+      <c r="K184" s="121" t="str">
         <f>+IF(C184="","",VLOOKUP(C184,Sheet2!$A$248:$C$252,3,TRUE))</f>
         <v/>
       </c>
-      <c r="L184" s="142"/>
-      <c r="M184" s="142"/>
-      <c r="N184" s="142"/>
-      <c r="O184" s="142"/>
+      <c r="L184" s="121"/>
+      <c r="M184" s="121"/>
+      <c r="N184" s="121"/>
+      <c r="O184" s="121"/>
       <c r="P184" s="28" t="str">
         <f>+IF(C184="","",VLOOKUP(C184,Sheet2!$A$248:$C$252,2,TRUE))</f>
         <v/>
@@ -9240,13 +9240,13 @@
       <c r="J187" s="64" t="s">
         <v>38</v>
       </c>
-      <c r="K187" s="143" t="s">
+      <c r="K187" s="120" t="s">
         <v>40</v>
       </c>
-      <c r="L187" s="143"/>
-      <c r="M187" s="143"/>
-      <c r="N187" s="143"/>
-      <c r="O187" s="143"/>
+      <c r="L187" s="120"/>
+      <c r="M187" s="120"/>
+      <c r="N187" s="120"/>
+      <c r="O187" s="120"/>
       <c r="P187" s="60" t="s">
         <v>124</v>
       </c>
@@ -9266,14 +9266,14 @@
         <f>+IF(D188="","",AVERAGE(D188:H188))</f>
         <v/>
       </c>
-      <c r="K188" s="142" t="str">
+      <c r="K188" s="121" t="str">
         <f>+IF(C188="","",VLOOKUP(C188,Sheet2!$A$255:$C$259,3,TRUE))</f>
         <v/>
       </c>
-      <c r="L188" s="142"/>
-      <c r="M188" s="142"/>
-      <c r="N188" s="142"/>
-      <c r="O188" s="142"/>
+      <c r="L188" s="121"/>
+      <c r="M188" s="121"/>
+      <c r="N188" s="121"/>
+      <c r="O188" s="121"/>
       <c r="P188" s="28" t="str">
         <f>+IF(C188="","",VLOOKUP(C188,Sheet2!$A$255:$C$259,2,TRUE))</f>
         <v/>
@@ -9571,23 +9571,23 @@
     </row>
     <row r="204" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="205" spans="2:16" ht="23.25" x14ac:dyDescent="0.25">
-      <c r="B205" s="123" t="s">
+      <c r="B205" s="122" t="s">
         <v>71</v>
       </c>
-      <c r="C205" s="124"/>
-      <c r="D205" s="124"/>
-      <c r="E205" s="124"/>
-      <c r="F205" s="124"/>
-      <c r="G205" s="124"/>
-      <c r="H205" s="124"/>
-      <c r="I205" s="124"/>
-      <c r="J205" s="124"/>
-      <c r="K205" s="124"/>
-      <c r="L205" s="124"/>
-      <c r="M205" s="124"/>
-      <c r="N205" s="124"/>
-      <c r="O205" s="124"/>
-      <c r="P205" s="125"/>
+      <c r="C205" s="123"/>
+      <c r="D205" s="123"/>
+      <c r="E205" s="123"/>
+      <c r="F205" s="123"/>
+      <c r="G205" s="123"/>
+      <c r="H205" s="123"/>
+      <c r="I205" s="123"/>
+      <c r="J205" s="123"/>
+      <c r="K205" s="123"/>
+      <c r="L205" s="123"/>
+      <c r="M205" s="123"/>
+      <c r="N205" s="123"/>
+      <c r="O205" s="123"/>
+      <c r="P205" s="124"/>
     </row>
     <row r="206" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B206" s="27" t="s">
@@ -9632,13 +9632,13 @@
       <c r="J208" s="64" t="s">
         <v>38</v>
       </c>
-      <c r="K208" s="143" t="s">
+      <c r="K208" s="120" t="s">
         <v>40</v>
       </c>
-      <c r="L208" s="143"/>
-      <c r="M208" s="143"/>
-      <c r="N208" s="143"/>
-      <c r="O208" s="143"/>
+      <c r="L208" s="120"/>
+      <c r="M208" s="120"/>
+      <c r="N208" s="120"/>
+      <c r="O208" s="120"/>
       <c r="P208" s="60" t="s">
         <v>124</v>
       </c>
@@ -9716,14 +9716,14 @@
       </c>
       <c r="I211" s="7"/>
       <c r="J211" s="7"/>
-      <c r="K211" s="142" t="str">
+      <c r="K211" s="121" t="str">
         <f>+IF(D211="","",IF(D211&gt;0,"Company manages to pay their dividends","Company doesn't manage to pay their dividends"))</f>
         <v/>
       </c>
-      <c r="L211" s="142"/>
-      <c r="M211" s="142"/>
-      <c r="N211" s="142"/>
-      <c r="O211" s="142"/>
+      <c r="L211" s="121"/>
+      <c r="M211" s="121"/>
+      <c r="N211" s="121"/>
+      <c r="O211" s="121"/>
       <c r="P211" s="28" t="str">
         <f>+IF(D211="","",IF(D211&gt;0,5,0))</f>
         <v/>
@@ -9770,11 +9770,11 @@
       <c r="J213" s="64" t="s">
         <v>38</v>
       </c>
-      <c r="K213" s="143"/>
-      <c r="L213" s="143"/>
-      <c r="M213" s="143"/>
-      <c r="N213" s="143"/>
-      <c r="O213" s="143"/>
+      <c r="K213" s="120"/>
+      <c r="L213" s="120"/>
+      <c r="M213" s="120"/>
+      <c r="N213" s="120"/>
+      <c r="O213" s="120"/>
       <c r="P213" s="68"/>
     </row>
     <row r="214" spans="2:16" x14ac:dyDescent="0.25">
@@ -9864,13 +9864,13 @@
       <c r="J217" s="64" t="s">
         <v>38</v>
       </c>
-      <c r="K217" s="143" t="s">
+      <c r="K217" s="120" t="s">
         <v>40</v>
       </c>
-      <c r="L217" s="143"/>
-      <c r="M217" s="143"/>
-      <c r="N217" s="143"/>
-      <c r="O217" s="143"/>
+      <c r="L217" s="120"/>
+      <c r="M217" s="120"/>
+      <c r="N217" s="120"/>
+      <c r="O217" s="120"/>
       <c r="P217" s="60" t="s">
         <v>124</v>
       </c>
@@ -9887,14 +9887,14 @@
       <c r="H218" s="7"/>
       <c r="I218" s="7"/>
       <c r="J218" s="7"/>
-      <c r="K218" s="142" t="str">
+      <c r="K218" s="121" t="str">
         <f>+IF(C218="","",IF(C218&gt;60%,"Company's dividends at risk of being cut","Company's dividends are not at risk of being cut"))</f>
         <v/>
       </c>
-      <c r="L218" s="142"/>
-      <c r="M218" s="142"/>
-      <c r="N218" s="142"/>
-      <c r="O218" s="142"/>
+      <c r="L218" s="121"/>
+      <c r="M218" s="121"/>
+      <c r="N218" s="121"/>
+      <c r="O218" s="121"/>
       <c r="P218" s="28" t="str">
         <f>+IF(C218="","",IF(C218&gt;60%,0,5))</f>
         <v/>
@@ -9973,13 +9973,13 @@
       <c r="J221" s="64" t="s">
         <v>38</v>
       </c>
-      <c r="K221" s="143" t="s">
+      <c r="K221" s="120" t="s">
         <v>40</v>
       </c>
-      <c r="L221" s="143"/>
-      <c r="M221" s="143"/>
-      <c r="N221" s="143"/>
-      <c r="O221" s="143"/>
+      <c r="L221" s="120"/>
+      <c r="M221" s="120"/>
+      <c r="N221" s="120"/>
+      <c r="O221" s="120"/>
       <c r="P221" s="60" t="s">
         <v>124</v>
       </c>
@@ -9999,14 +9999,14 @@
         <f>+IF(D222="","",AVERAGE(D222:H222))</f>
         <v/>
       </c>
-      <c r="K222" s="144" t="str">
+      <c r="K222" s="136" t="str">
         <f>+IF(J222="","",VLOOKUP(J222,Sheet2!$A$262:$C$268,3,TRUE))</f>
         <v/>
       </c>
-      <c r="L222" s="144"/>
-      <c r="M222" s="144"/>
-      <c r="N222" s="144"/>
-      <c r="O222" s="144"/>
+      <c r="L222" s="136"/>
+      <c r="M222" s="136"/>
+      <c r="N222" s="136"/>
+      <c r="O222" s="136"/>
       <c r="P222" s="32" t="str">
         <f>+IF(J222="","",VLOOKUP(J222,Sheet2!$A$262:$C$268,2,TRUE))</f>
         <v/>
@@ -10014,23 +10014,23 @@
     </row>
     <row r="223" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="224" spans="2:16" ht="23.25" x14ac:dyDescent="0.25">
-      <c r="B224" s="123" t="s">
+      <c r="B224" s="122" t="s">
         <v>79</v>
       </c>
-      <c r="C224" s="124"/>
-      <c r="D224" s="124"/>
-      <c r="E224" s="124"/>
-      <c r="F224" s="124"/>
-      <c r="G224" s="124"/>
-      <c r="H224" s="124"/>
-      <c r="I224" s="124"/>
-      <c r="J224" s="124"/>
-      <c r="K224" s="124"/>
-      <c r="L224" s="124"/>
-      <c r="M224" s="124"/>
-      <c r="N224" s="124"/>
-      <c r="O224" s="124"/>
-      <c r="P224" s="125"/>
+      <c r="C224" s="123"/>
+      <c r="D224" s="123"/>
+      <c r="E224" s="123"/>
+      <c r="F224" s="123"/>
+      <c r="G224" s="123"/>
+      <c r="H224" s="123"/>
+      <c r="I224" s="123"/>
+      <c r="J224" s="123"/>
+      <c r="K224" s="123"/>
+      <c r="L224" s="123"/>
+      <c r="M224" s="123"/>
+      <c r="N224" s="123"/>
+      <c r="O224" s="123"/>
+      <c r="P224" s="124"/>
     </row>
     <row r="225" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B225" s="27"/>
@@ -10063,13 +10063,13 @@
       </c>
       <c r="I226" s="63"/>
       <c r="J226" s="63"/>
-      <c r="K226" s="143" t="s">
+      <c r="K226" s="120" t="s">
         <v>40</v>
       </c>
-      <c r="L226" s="143"/>
-      <c r="M226" s="143"/>
-      <c r="N226" s="143"/>
-      <c r="O226" s="143"/>
+      <c r="L226" s="120"/>
+      <c r="M226" s="120"/>
+      <c r="N226" s="120"/>
+      <c r="O226" s="120"/>
       <c r="P226" s="60" t="s">
         <v>124</v>
       </c>
@@ -10097,14 +10097,14 @@
         <f>+IF(AND(C227="",D227=""),"",IF(C227="",D227*0.8,C227*0.8))</f>
         <v/>
       </c>
-      <c r="K228" s="142" t="str">
+      <c r="K228" s="121" t="str">
         <f>+IF(C228="","",IF(E11&gt;1.5*C228,Sheet2!A274,IF(E11&gt;1.2*C228,Sheet2!A273,Sheet2!A272)))</f>
         <v/>
       </c>
-      <c r="L228" s="142"/>
-      <c r="M228" s="142"/>
-      <c r="N228" s="142"/>
-      <c r="O228" s="142"/>
+      <c r="L228" s="121"/>
+      <c r="M228" s="121"/>
+      <c r="N228" s="121"/>
+      <c r="O228" s="121"/>
       <c r="P228" s="28" t="str">
         <f>+IF(K228="","",VLOOKUP(K228,Sheet2!$A$272:$B$274,2,FALSE))</f>
         <v/>
@@ -10129,13 +10129,13 @@
       <c r="H230" s="59"/>
       <c r="I230" s="59"/>
       <c r="J230" s="59"/>
-      <c r="K230" s="143" t="s">
+      <c r="K230" s="120" t="s">
         <v>40</v>
       </c>
-      <c r="L230" s="143"/>
-      <c r="M230" s="143"/>
-      <c r="N230" s="143"/>
-      <c r="O230" s="143"/>
+      <c r="L230" s="120"/>
+      <c r="M230" s="120"/>
+      <c r="N230" s="120"/>
+      <c r="O230" s="120"/>
       <c r="P230" s="60" t="s">
         <v>124</v>
       </c>
@@ -10171,14 +10171,14 @@
       <c r="H233" s="31"/>
       <c r="I233" s="31"/>
       <c r="J233" s="31"/>
-      <c r="K233" s="144" t="str">
+      <c r="K233" s="136" t="str">
         <f>+IF(C233="","",IF(C233&gt;$E$11*1.5,Sheet2!$A$272,IF(C233&gt;$E$11*1.1,Sheet2!$A$273,Sheet2!$A$274)))</f>
         <v/>
       </c>
-      <c r="L233" s="144"/>
-      <c r="M233" s="144"/>
-      <c r="N233" s="144"/>
-      <c r="O233" s="144"/>
+      <c r="L233" s="136"/>
+      <c r="M233" s="136"/>
+      <c r="N233" s="136"/>
+      <c r="O233" s="136"/>
       <c r="P233" s="32" t="str">
         <f>+IF(K233="","",VLOOKUP(K233,Sheet2!$A$272:$B$274,2,FALSE))</f>
         <v/>
@@ -10194,13 +10194,13 @@
       <c r="P234" s="10"/>
     </row>
     <row r="235" spans="2:16" ht="15.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="K235" s="170" t="s">
+      <c r="K235" s="135" t="s">
         <v>40</v>
       </c>
-      <c r="L235" s="170"/>
-      <c r="M235" s="170"/>
-      <c r="N235" s="170"/>
-      <c r="O235" s="170"/>
+      <c r="L235" s="135"/>
+      <c r="M235" s="135"/>
+      <c r="N235" s="135"/>
+      <c r="O235" s="135"/>
     </row>
     <row r="236" spans="2:16" ht="15.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B236" s="1" t="s">
@@ -10208,13 +10208,13 @@
       </c>
     </row>
     <row r="237" spans="2:16" ht="15.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="K237" s="170" t="s">
+      <c r="K237" s="135" t="s">
         <v>40</v>
       </c>
-      <c r="L237" s="170"/>
-      <c r="M237" s="170"/>
-      <c r="N237" s="170"/>
-      <c r="O237" s="170"/>
+      <c r="L237" s="135"/>
+      <c r="M237" s="135"/>
+      <c r="N237" s="135"/>
+      <c r="O237" s="135"/>
     </row>
     <row r="238" spans="2:16" ht="15.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B238" s="1" t="s">
@@ -10222,13 +10222,13 @@
       </c>
     </row>
     <row r="239" spans="2:16" ht="15.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="K239" s="170" t="s">
+      <c r="K239" s="135" t="s">
         <v>40</v>
       </c>
-      <c r="L239" s="170"/>
-      <c r="M239" s="170"/>
-      <c r="N239" s="170"/>
-      <c r="O239" s="170"/>
+      <c r="L239" s="135"/>
+      <c r="M239" s="135"/>
+      <c r="N239" s="135"/>
+      <c r="O239" s="135"/>
     </row>
     <row r="240" spans="2:16" ht="15.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B240" s="1" t="s">
@@ -10236,13 +10236,13 @@
       </c>
     </row>
     <row r="241" spans="2:38" ht="15.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="K241" s="170" t="s">
+      <c r="K241" s="135" t="s">
         <v>40</v>
       </c>
-      <c r="L241" s="170"/>
-      <c r="M241" s="170"/>
-      <c r="N241" s="170"/>
-      <c r="O241" s="170"/>
+      <c r="L241" s="135"/>
+      <c r="M241" s="135"/>
+      <c r="N241" s="135"/>
+      <c r="O241" s="135"/>
     </row>
     <row r="242" spans="2:38" ht="15.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B242" s="1" t="s">
@@ -10253,23 +10253,23 @@
     <row r="244" spans="2:38" ht="15.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="245" spans="2:38" ht="15.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="246" spans="2:38" ht="23.25" x14ac:dyDescent="0.25">
-      <c r="B246" s="126" t="s">
+      <c r="B246" s="158" t="s">
         <v>322</v>
       </c>
-      <c r="C246" s="127"/>
-      <c r="D246" s="127"/>
-      <c r="E246" s="127"/>
-      <c r="F246" s="127"/>
-      <c r="G246" s="127"/>
-      <c r="H246" s="127"/>
-      <c r="I246" s="127"/>
-      <c r="J246" s="127"/>
-      <c r="K246" s="127"/>
-      <c r="L246" s="127"/>
-      <c r="M246" s="127"/>
-      <c r="N246" s="127"/>
-      <c r="O246" s="127"/>
-      <c r="P246" s="128"/>
+      <c r="C246" s="159"/>
+      <c r="D246" s="159"/>
+      <c r="E246" s="159"/>
+      <c r="F246" s="159"/>
+      <c r="G246" s="159"/>
+      <c r="H246" s="159"/>
+      <c r="I246" s="159"/>
+      <c r="J246" s="159"/>
+      <c r="K246" s="159"/>
+      <c r="L246" s="159"/>
+      <c r="M246" s="159"/>
+      <c r="N246" s="159"/>
+      <c r="O246" s="159"/>
+      <c r="P246" s="160"/>
       <c r="Y246" s="106"/>
       <c r="Z246" s="106"/>
       <c r="AA246" s="106"/>
@@ -10564,11 +10564,11 @@
         <f t="shared" ref="D254:D265" si="81">+IF(C254="","",U254)</f>
         <v/>
       </c>
-      <c r="E254" s="120" t="s">
+      <c r="E254" s="155" t="s">
         <v>299</v>
       </c>
-      <c r="F254" s="120"/>
-      <c r="G254" s="120"/>
+      <c r="F254" s="155"/>
+      <c r="G254" s="155"/>
       <c r="P254" s="112"/>
       <c r="U254" s="119">
         <v>0.03</v>
@@ -10611,9 +10611,9 @@
         <f t="shared" si="81"/>
         <v/>
       </c>
-      <c r="E255" s="120"/>
-      <c r="F255" s="120"/>
-      <c r="G255" s="120"/>
+      <c r="E255" s="155"/>
+      <c r="F255" s="155"/>
+      <c r="G255" s="155"/>
       <c r="P255" s="112"/>
       <c r="U255" s="119">
         <v>0.01</v>
@@ -10656,14 +10656,14 @@
         <f t="shared" si="81"/>
         <v/>
       </c>
-      <c r="E256" s="120"/>
-      <c r="F256" s="120"/>
-      <c r="G256" s="120"/>
-      <c r="J256" s="121">
+      <c r="E256" s="155"/>
+      <c r="F256" s="155"/>
+      <c r="G256" s="155"/>
+      <c r="J256" s="156">
         <f>+K253</f>
         <v>0</v>
       </c>
-      <c r="K256" s="122"/>
+      <c r="K256" s="157"/>
       <c r="P256" s="112"/>
       <c r="U256" s="119">
         <v>0.05</v>
@@ -10706,11 +10706,11 @@
         <f t="shared" si="81"/>
         <v/>
       </c>
-      <c r="E257" s="120"/>
-      <c r="F257" s="120"/>
-      <c r="G257" s="120"/>
-      <c r="J257" s="122"/>
-      <c r="K257" s="122"/>
+      <c r="E257" s="155"/>
+      <c r="F257" s="155"/>
+      <c r="G257" s="155"/>
+      <c r="J257" s="157"/>
+      <c r="K257" s="157"/>
       <c r="P257" s="112"/>
       <c r="U257" s="119">
         <v>0.05</v>
@@ -10761,9 +10761,9 @@
         <f t="shared" si="81"/>
         <v/>
       </c>
-      <c r="E258" s="120"/>
-      <c r="F258" s="120"/>
-      <c r="G258" s="120"/>
+      <c r="E258" s="155"/>
+      <c r="F258" s="155"/>
+      <c r="G258" s="155"/>
       <c r="P258" s="112"/>
       <c r="U258" s="119">
         <v>0.01</v>
@@ -10814,9 +10814,9 @@
         <f t="shared" si="81"/>
         <v/>
       </c>
-      <c r="E259" s="120"/>
-      <c r="F259" s="120"/>
-      <c r="G259" s="120"/>
+      <c r="E259" s="155"/>
+      <c r="F259" s="155"/>
+      <c r="G259" s="155"/>
       <c r="P259" s="112"/>
       <c r="U259" s="119">
         <v>0.02</v>
@@ -12088,44 +12088,86 @@
     </row>
   </sheetData>
   <mergeCells count="142">
-    <mergeCell ref="K116:O116"/>
-    <mergeCell ref="K114:O114"/>
-    <mergeCell ref="K126:O126"/>
-    <mergeCell ref="K127:O127"/>
-    <mergeCell ref="K102:O102"/>
-    <mergeCell ref="K103:O103"/>
-    <mergeCell ref="K107:O107"/>
-    <mergeCell ref="K175:O175"/>
-    <mergeCell ref="K176:O176"/>
-    <mergeCell ref="K164:O164"/>
-    <mergeCell ref="K169:O169"/>
-    <mergeCell ref="K174:O174"/>
-    <mergeCell ref="K117:O117"/>
-    <mergeCell ref="K118:O118"/>
-    <mergeCell ref="K121:O121"/>
-    <mergeCell ref="K122:O122"/>
-    <mergeCell ref="K179:O179"/>
-    <mergeCell ref="K183:O183"/>
-    <mergeCell ref="B130:P131"/>
-    <mergeCell ref="K166:O166"/>
-    <mergeCell ref="K167:O167"/>
-    <mergeCell ref="K170:O170"/>
-    <mergeCell ref="K171:O171"/>
-    <mergeCell ref="K172:O172"/>
-    <mergeCell ref="K177:O177"/>
-    <mergeCell ref="K180:O180"/>
-    <mergeCell ref="K145:O145"/>
-    <mergeCell ref="K146:O146"/>
-    <mergeCell ref="K149:O149"/>
-    <mergeCell ref="K150:O150"/>
-    <mergeCell ref="K153:O153"/>
-    <mergeCell ref="K132:O132"/>
-    <mergeCell ref="K154:O154"/>
-    <mergeCell ref="K157:O157"/>
-    <mergeCell ref="K158:O158"/>
-    <mergeCell ref="K161:O161"/>
-    <mergeCell ref="K162:O162"/>
-    <mergeCell ref="K165:O165"/>
+    <mergeCell ref="E254:G259"/>
+    <mergeCell ref="J256:K257"/>
+    <mergeCell ref="B205:P205"/>
+    <mergeCell ref="B224:P224"/>
+    <mergeCell ref="B246:P246"/>
+    <mergeCell ref="J2:P3"/>
+    <mergeCell ref="B1:N1"/>
+    <mergeCell ref="B2:H3"/>
+    <mergeCell ref="B36:P37"/>
+    <mergeCell ref="K133:O133"/>
+    <mergeCell ref="K134:O134"/>
+    <mergeCell ref="K136:O136"/>
+    <mergeCell ref="K139:O139"/>
+    <mergeCell ref="K140:O140"/>
+    <mergeCell ref="K141:O141"/>
+    <mergeCell ref="K142:O142"/>
+    <mergeCell ref="K187:O187"/>
+    <mergeCell ref="K138:O138"/>
+    <mergeCell ref="K144:O144"/>
+    <mergeCell ref="K148:O148"/>
+    <mergeCell ref="K152:O152"/>
+    <mergeCell ref="K156:O156"/>
+    <mergeCell ref="K160:O160"/>
+    <mergeCell ref="K60:O60"/>
+    <mergeCell ref="K64:O64"/>
+    <mergeCell ref="K65:O65"/>
+    <mergeCell ref="K68:O68"/>
+    <mergeCell ref="K69:O69"/>
+    <mergeCell ref="K80:O80"/>
+    <mergeCell ref="K81:O81"/>
+    <mergeCell ref="K108:O108"/>
+    <mergeCell ref="K113:O113"/>
+    <mergeCell ref="K91:O91"/>
+    <mergeCell ref="K94:O94"/>
+    <mergeCell ref="K95:O95"/>
+    <mergeCell ref="K98:O98"/>
+    <mergeCell ref="K88:O88"/>
+    <mergeCell ref="K93:O93"/>
+    <mergeCell ref="K97:O97"/>
+    <mergeCell ref="K99:O99"/>
+    <mergeCell ref="K112:O112"/>
+    <mergeCell ref="K105:O105"/>
+    <mergeCell ref="K40:O40"/>
+    <mergeCell ref="K39:O39"/>
+    <mergeCell ref="K43:O43"/>
+    <mergeCell ref="K47:O47"/>
+    <mergeCell ref="K51:O51"/>
+    <mergeCell ref="K55:O55"/>
+    <mergeCell ref="K101:O101"/>
+    <mergeCell ref="K41:O41"/>
+    <mergeCell ref="K42:O42"/>
+    <mergeCell ref="K45:O45"/>
+    <mergeCell ref="K44:O44"/>
+    <mergeCell ref="K48:O48"/>
+    <mergeCell ref="K49:O49"/>
+    <mergeCell ref="K85:O85"/>
+    <mergeCell ref="K84:O84"/>
+    <mergeCell ref="K90:O90"/>
+    <mergeCell ref="K59:O59"/>
+    <mergeCell ref="K63:O63"/>
+    <mergeCell ref="K67:O67"/>
+    <mergeCell ref="K71:O71"/>
+    <mergeCell ref="K75:O75"/>
+    <mergeCell ref="K79:O79"/>
+    <mergeCell ref="K83:O83"/>
+    <mergeCell ref="K61:O61"/>
+    <mergeCell ref="L23:O23"/>
+    <mergeCell ref="B4:C13"/>
+    <mergeCell ref="E4:H4"/>
+    <mergeCell ref="K5:N5"/>
+    <mergeCell ref="M15:O15"/>
+    <mergeCell ref="L22:O22"/>
+    <mergeCell ref="E5:H5"/>
+    <mergeCell ref="G22:H22"/>
+    <mergeCell ref="B16:H20"/>
+    <mergeCell ref="E6:H6"/>
+    <mergeCell ref="E7:H7"/>
+    <mergeCell ref="E9:F9"/>
+    <mergeCell ref="E10:F10"/>
+    <mergeCell ref="L13:O13"/>
     <mergeCell ref="J30:K30"/>
     <mergeCell ref="J31:K31"/>
     <mergeCell ref="J13:K13"/>
@@ -12150,86 +12192,44 @@
     <mergeCell ref="K120:O120"/>
     <mergeCell ref="K124:O124"/>
     <mergeCell ref="B110:P111"/>
-    <mergeCell ref="L23:O23"/>
-    <mergeCell ref="B4:C13"/>
-    <mergeCell ref="E4:H4"/>
-    <mergeCell ref="K5:N5"/>
-    <mergeCell ref="M15:O15"/>
-    <mergeCell ref="L22:O22"/>
-    <mergeCell ref="E5:H5"/>
-    <mergeCell ref="G22:H22"/>
-    <mergeCell ref="B16:H20"/>
-    <mergeCell ref="E6:H6"/>
-    <mergeCell ref="E7:H7"/>
-    <mergeCell ref="E9:F9"/>
-    <mergeCell ref="E10:F10"/>
-    <mergeCell ref="L13:O13"/>
-    <mergeCell ref="K40:O40"/>
-    <mergeCell ref="K39:O39"/>
-    <mergeCell ref="K43:O43"/>
-    <mergeCell ref="K47:O47"/>
-    <mergeCell ref="K51:O51"/>
-    <mergeCell ref="K55:O55"/>
-    <mergeCell ref="K101:O101"/>
-    <mergeCell ref="K41:O41"/>
-    <mergeCell ref="K42:O42"/>
-    <mergeCell ref="K45:O45"/>
-    <mergeCell ref="K44:O44"/>
-    <mergeCell ref="K48:O48"/>
-    <mergeCell ref="K49:O49"/>
-    <mergeCell ref="K85:O85"/>
-    <mergeCell ref="K84:O84"/>
-    <mergeCell ref="K90:O90"/>
-    <mergeCell ref="K59:O59"/>
-    <mergeCell ref="K63:O63"/>
-    <mergeCell ref="K67:O67"/>
-    <mergeCell ref="K71:O71"/>
-    <mergeCell ref="K75:O75"/>
-    <mergeCell ref="K79:O79"/>
-    <mergeCell ref="K83:O83"/>
-    <mergeCell ref="K61:O61"/>
-    <mergeCell ref="K64:O64"/>
-    <mergeCell ref="K65:O65"/>
-    <mergeCell ref="K68:O68"/>
-    <mergeCell ref="K69:O69"/>
-    <mergeCell ref="K80:O80"/>
-    <mergeCell ref="K81:O81"/>
-    <mergeCell ref="K108:O108"/>
-    <mergeCell ref="K113:O113"/>
-    <mergeCell ref="K91:O91"/>
-    <mergeCell ref="K94:O94"/>
-    <mergeCell ref="K95:O95"/>
-    <mergeCell ref="K98:O98"/>
-    <mergeCell ref="K88:O88"/>
-    <mergeCell ref="K93:O93"/>
-    <mergeCell ref="K97:O97"/>
-    <mergeCell ref="K99:O99"/>
-    <mergeCell ref="K112:O112"/>
-    <mergeCell ref="K105:O105"/>
-    <mergeCell ref="E254:G259"/>
-    <mergeCell ref="J256:K257"/>
-    <mergeCell ref="B205:P205"/>
-    <mergeCell ref="B224:P224"/>
-    <mergeCell ref="B246:P246"/>
-    <mergeCell ref="J2:P3"/>
-    <mergeCell ref="B1:N1"/>
-    <mergeCell ref="B2:H3"/>
-    <mergeCell ref="B36:P37"/>
-    <mergeCell ref="K133:O133"/>
-    <mergeCell ref="K134:O134"/>
-    <mergeCell ref="K136:O136"/>
-    <mergeCell ref="K139:O139"/>
-    <mergeCell ref="K140:O140"/>
-    <mergeCell ref="K141:O141"/>
-    <mergeCell ref="K142:O142"/>
-    <mergeCell ref="K187:O187"/>
-    <mergeCell ref="K138:O138"/>
-    <mergeCell ref="K144:O144"/>
-    <mergeCell ref="K148:O148"/>
-    <mergeCell ref="K152:O152"/>
-    <mergeCell ref="K156:O156"/>
-    <mergeCell ref="K160:O160"/>
-    <mergeCell ref="K60:O60"/>
+    <mergeCell ref="K179:O179"/>
+    <mergeCell ref="K183:O183"/>
+    <mergeCell ref="B130:P131"/>
+    <mergeCell ref="K166:O166"/>
+    <mergeCell ref="K167:O167"/>
+    <mergeCell ref="K170:O170"/>
+    <mergeCell ref="K171:O171"/>
+    <mergeCell ref="K172:O172"/>
+    <mergeCell ref="K177:O177"/>
+    <mergeCell ref="K180:O180"/>
+    <mergeCell ref="K145:O145"/>
+    <mergeCell ref="K146:O146"/>
+    <mergeCell ref="K149:O149"/>
+    <mergeCell ref="K150:O150"/>
+    <mergeCell ref="K153:O153"/>
+    <mergeCell ref="K132:O132"/>
+    <mergeCell ref="K154:O154"/>
+    <mergeCell ref="K157:O157"/>
+    <mergeCell ref="K158:O158"/>
+    <mergeCell ref="K161:O161"/>
+    <mergeCell ref="K162:O162"/>
+    <mergeCell ref="K165:O165"/>
+    <mergeCell ref="K116:O116"/>
+    <mergeCell ref="K114:O114"/>
+    <mergeCell ref="K126:O126"/>
+    <mergeCell ref="K127:O127"/>
+    <mergeCell ref="K102:O102"/>
+    <mergeCell ref="K103:O103"/>
+    <mergeCell ref="K107:O107"/>
+    <mergeCell ref="K175:O175"/>
+    <mergeCell ref="K176:O176"/>
+    <mergeCell ref="K164:O164"/>
+    <mergeCell ref="K169:O169"/>
+    <mergeCell ref="K174:O174"/>
+    <mergeCell ref="K117:O117"/>
+    <mergeCell ref="K118:O118"/>
+    <mergeCell ref="K121:O121"/>
+    <mergeCell ref="K122:O122"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <conditionalFormatting sqref="M15:O15">

--- a/report_template.xlsx
+++ b/report_template.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29530"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29725"/>
   <workbookPr codeName="ThisWorkbook" autoCompressPictures="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\JosGon\Dropbox\Python Scripts\stock report\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{67696FEA-CD50-46A0-97DA-049974CE1061}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D504820E-A1FA-4887-BAF9-701B86983C59}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="975" windowWidth="57600" windowHeight="15345" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="17130" yWindow="4380" windowWidth="57600" windowHeight="15345" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -1717,11 +1717,14 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="164" fontId="9" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="10" fontId="17" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1732,41 +1735,65 @@
     <xf numFmtId="0" fontId="12" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="2" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="2" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="2" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="12" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="22" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
+    <xf numFmtId="0" fontId="12" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="2" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="2" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="6" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="6" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="6" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1810,53 +1837,26 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="11" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="22" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="10" fontId="17" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="2" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="20" fillId="6" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="2" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="18" fillId="6" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="2" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="18" fillId="6" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="2" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="2" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -4502,120 +4502,120 @@
   </cols>
   <sheetData>
     <row r="1" spans="2:16" ht="43.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B1" s="126" t="s">
+      <c r="B1" s="135" t="s">
         <v>84</v>
       </c>
-      <c r="C1" s="126"/>
-      <c r="D1" s="126"/>
-      <c r="E1" s="126"/>
-      <c r="F1" s="126"/>
-      <c r="G1" s="126"/>
-      <c r="H1" s="126"/>
-      <c r="I1" s="126"/>
-      <c r="J1" s="126"/>
-      <c r="K1" s="126"/>
-      <c r="L1" s="126"/>
-      <c r="M1" s="126"/>
-      <c r="N1" s="126"/>
+      <c r="C1" s="135"/>
+      <c r="D1" s="135"/>
+      <c r="E1" s="135"/>
+      <c r="F1" s="135"/>
+      <c r="G1" s="135"/>
+      <c r="H1" s="135"/>
+      <c r="I1" s="135"/>
+      <c r="J1" s="135"/>
+      <c r="K1" s="135"/>
+      <c r="L1" s="135"/>
+      <c r="M1" s="135"/>
+      <c r="N1" s="135"/>
       <c r="O1" s="44" t="s">
         <v>85</v>
       </c>
       <c r="P1" s="45">
         <f ca="1">+TODAY()</f>
-        <v>46076</v>
+        <v>46114</v>
       </c>
     </row>
     <row r="2" spans="2:16" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B2" s="165" t="s">
+      <c r="B2" s="133" t="s">
         <v>294</v>
       </c>
-      <c r="C2" s="165"/>
-      <c r="D2" s="165"/>
-      <c r="E2" s="165"/>
-      <c r="F2" s="165"/>
-      <c r="G2" s="165"/>
-      <c r="H2" s="165"/>
-      <c r="J2" s="161" t="s">
+      <c r="C2" s="133"/>
+      <c r="D2" s="133"/>
+      <c r="E2" s="133"/>
+      <c r="F2" s="133"/>
+      <c r="G2" s="133"/>
+      <c r="H2" s="133"/>
+      <c r="J2" s="129" t="s">
         <v>288</v>
       </c>
-      <c r="K2" s="162"/>
-      <c r="L2" s="162"/>
-      <c r="M2" s="162"/>
-      <c r="N2" s="162"/>
-      <c r="O2" s="162"/>
-      <c r="P2" s="163"/>
+      <c r="K2" s="130"/>
+      <c r="L2" s="130"/>
+      <c r="M2" s="130"/>
+      <c r="N2" s="130"/>
+      <c r="O2" s="130"/>
+      <c r="P2" s="131"/>
     </row>
     <row r="3" spans="2:16" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B3" s="167"/>
-      <c r="C3" s="167"/>
-      <c r="D3" s="167"/>
-      <c r="E3" s="167"/>
-      <c r="F3" s="167"/>
-      <c r="G3" s="167"/>
-      <c r="H3" s="167"/>
-      <c r="J3" s="164"/>
-      <c r="K3" s="165"/>
-      <c r="L3" s="165"/>
-      <c r="M3" s="165"/>
-      <c r="N3" s="165"/>
-      <c r="O3" s="165"/>
-      <c r="P3" s="166"/>
+      <c r="B3" s="136"/>
+      <c r="C3" s="136"/>
+      <c r="D3" s="136"/>
+      <c r="E3" s="136"/>
+      <c r="F3" s="136"/>
+      <c r="G3" s="136"/>
+      <c r="H3" s="136"/>
+      <c r="J3" s="132"/>
+      <c r="K3" s="133"/>
+      <c r="L3" s="133"/>
+      <c r="M3" s="133"/>
+      <c r="N3" s="133"/>
+      <c r="O3" s="133"/>
+      <c r="P3" s="134"/>
     </row>
     <row r="4" spans="2:16" x14ac:dyDescent="0.25">
-      <c r="B4" s="137"/>
-      <c r="C4" s="138"/>
+      <c r="B4" s="146"/>
+      <c r="C4" s="147"/>
       <c r="D4" s="37" t="s">
         <v>0</v>
       </c>
-      <c r="E4" s="141"/>
-      <c r="F4" s="141"/>
-      <c r="G4" s="141"/>
-      <c r="H4" s="142"/>
+      <c r="E4" s="150"/>
+      <c r="F4" s="150"/>
+      <c r="G4" s="150"/>
+      <c r="H4" s="151"/>
       <c r="J4" s="27"/>
       <c r="P4" s="28"/>
     </row>
     <row r="5" spans="2:16" x14ac:dyDescent="0.25">
-      <c r="B5" s="139"/>
-      <c r="C5" s="140"/>
+      <c r="B5" s="148"/>
+      <c r="C5" s="149"/>
       <c r="D5" s="75" t="s">
         <v>33</v>
       </c>
-      <c r="E5" s="144"/>
-      <c r="F5" s="144"/>
-      <c r="G5" s="144"/>
-      <c r="H5" s="145"/>
+      <c r="E5" s="153"/>
+      <c r="F5" s="153"/>
+      <c r="G5" s="153"/>
+      <c r="H5" s="154"/>
       <c r="J5" s="27"/>
-      <c r="K5" s="143" t="s">
+      <c r="K5" s="152" t="s">
         <v>305</v>
       </c>
-      <c r="L5" s="143"/>
-      <c r="M5" s="143"/>
-      <c r="N5" s="143"/>
+      <c r="L5" s="152"/>
+      <c r="M5" s="152"/>
+      <c r="N5" s="152"/>
       <c r="P5" s="28"/>
     </row>
     <row r="6" spans="2:16" x14ac:dyDescent="0.25">
-      <c r="B6" s="139"/>
-      <c r="C6" s="140"/>
+      <c r="B6" s="148"/>
+      <c r="C6" s="149"/>
       <c r="D6" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="E6" s="151"/>
-      <c r="F6" s="151"/>
-      <c r="G6" s="151"/>
-      <c r="H6" s="152"/>
+      <c r="E6" s="160"/>
+      <c r="F6" s="160"/>
+      <c r="G6" s="160"/>
+      <c r="H6" s="161"/>
       <c r="J6" s="27"/>
       <c r="P6" s="28"/>
     </row>
     <row r="7" spans="2:16" x14ac:dyDescent="0.25">
-      <c r="B7" s="139"/>
-      <c r="C7" s="140"/>
+      <c r="B7" s="148"/>
+      <c r="C7" s="149"/>
       <c r="D7" s="75" t="s">
         <v>6</v>
       </c>
-      <c r="E7" s="153"/>
-      <c r="F7" s="153"/>
-      <c r="G7" s="153"/>
-      <c r="H7" s="154"/>
+      <c r="E7" s="162"/>
+      <c r="F7" s="162"/>
+      <c r="G7" s="162"/>
+      <c r="H7" s="163"/>
       <c r="J7" s="33" t="s">
         <v>14</v>
       </c>
@@ -4637,8 +4637,8 @@
       <c r="P7" s="28"/>
     </row>
     <row r="8" spans="2:16" x14ac:dyDescent="0.25">
-      <c r="B8" s="139"/>
-      <c r="C8" s="140"/>
+      <c r="B8" s="148"/>
+      <c r="C8" s="149"/>
       <c r="D8" s="1" t="s">
         <v>1</v>
       </c>
@@ -4654,13 +4654,13 @@
       <c r="P8" s="28"/>
     </row>
     <row r="9" spans="2:16" x14ac:dyDescent="0.25">
-      <c r="B9" s="139"/>
-      <c r="C9" s="140"/>
+      <c r="B9" s="148"/>
+      <c r="C9" s="149"/>
       <c r="D9" s="75" t="s">
         <v>2</v>
       </c>
-      <c r="E9" s="144"/>
-      <c r="F9" s="144"/>
+      <c r="E9" s="153"/>
+      <c r="F9" s="153"/>
       <c r="G9" s="76"/>
       <c r="H9" s="77"/>
       <c r="J9" s="35" t="s">
@@ -4674,13 +4674,13 @@
       <c r="P9" s="28"/>
     </row>
     <row r="10" spans="2:16" x14ac:dyDescent="0.25">
-      <c r="B10" s="139"/>
-      <c r="C10" s="140"/>
+      <c r="B10" s="148"/>
+      <c r="C10" s="149"/>
       <c r="D10" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="E10" s="129"/>
-      <c r="F10" s="129"/>
+      <c r="E10" s="145"/>
+      <c r="F10" s="145"/>
       <c r="H10" s="38"/>
       <c r="J10" s="27" t="s">
         <v>17</v>
@@ -4693,8 +4693,8 @@
       <c r="P10" s="28"/>
     </row>
     <row r="11" spans="2:16" x14ac:dyDescent="0.25">
-      <c r="B11" s="139"/>
-      <c r="C11" s="140"/>
+      <c r="B11" s="148"/>
+      <c r="C11" s="149"/>
       <c r="D11" s="75" t="s">
         <v>8</v>
       </c>
@@ -4715,8 +4715,8 @@
       <c r="P11" s="28"/>
     </row>
     <row r="12" spans="2:16" x14ac:dyDescent="0.25">
-      <c r="B12" s="139"/>
-      <c r="C12" s="140"/>
+      <c r="B12" s="148"/>
+      <c r="C12" s="149"/>
       <c r="D12" s="1" t="s">
         <v>5</v>
       </c>
@@ -4727,8 +4727,8 @@
       </c>
     </row>
     <row r="13" spans="2:16" x14ac:dyDescent="0.25">
-      <c r="B13" s="139"/>
-      <c r="C13" s="140"/>
+      <c r="B13" s="148"/>
+      <c r="C13" s="149"/>
       <c r="D13" s="75" t="s">
         <v>34</v>
       </c>
@@ -4736,16 +4736,16 @@
       <c r="F13" s="76"/>
       <c r="G13" s="76"/>
       <c r="H13" s="77"/>
-      <c r="J13" s="130" t="s">
+      <c r="J13" s="165" t="s">
         <v>19</v>
       </c>
-      <c r="K13" s="131"/>
-      <c r="L13" s="121"/>
-      <c r="M13" s="121"/>
-      <c r="N13" s="121"/>
-      <c r="O13" s="121"/>
+      <c r="K13" s="166"/>
+      <c r="L13" s="142"/>
+      <c r="M13" s="142"/>
+      <c r="N13" s="142"/>
+      <c r="O13" s="142"/>
       <c r="P13" s="28" t="str">
-        <f>+IF(OR(L13="",L13="none"),"",VLOOKUP(L13,Sheet2!$A$1:$B$6,2,FALSE))</f>
+        <f>+IF(L13="","",VLOOKUP(L13,Sheet2!$A$1:$B$7,2,FALSE))</f>
         <v/>
       </c>
     </row>
@@ -4774,43 +4774,43 @@
       <c r="L15" s="81" t="s">
         <v>21</v>
       </c>
-      <c r="M15" s="121" t="str">
+      <c r="M15" s="142" t="str">
         <f>IF(K15="","",IF(K15&lt;0.8,"Low volatility",IF(K15&lt;=1.2,"Normal volatility","High volatility")))</f>
         <v/>
       </c>
-      <c r="N15" s="121"/>
-      <c r="O15" s="121"/>
+      <c r="N15" s="142"/>
+      <c r="O15" s="142"/>
       <c r="P15" s="28" t="str">
         <f>+IF(M15="","",VLOOKUP(M15,Sheet2!$A$8:$B$11,2,FALSE))</f>
         <v/>
       </c>
     </row>
     <row r="16" spans="2:16" ht="249" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B16" s="148"/>
-      <c r="C16" s="149"/>
-      <c r="D16" s="149"/>
-      <c r="E16" s="149"/>
-      <c r="F16" s="149"/>
-      <c r="G16" s="149"/>
-      <c r="H16" s="150"/>
-      <c r="J16" s="132" t="s">
+      <c r="B16" s="157"/>
+      <c r="C16" s="158"/>
+      <c r="D16" s="158"/>
+      <c r="E16" s="158"/>
+      <c r="F16" s="158"/>
+      <c r="G16" s="158"/>
+      <c r="H16" s="159"/>
+      <c r="J16" s="167" t="s">
         <v>323</v>
       </c>
-      <c r="K16" s="133"/>
-      <c r="L16" s="133"/>
-      <c r="M16" s="133"/>
-      <c r="N16" s="133"/>
-      <c r="O16" s="133"/>
-      <c r="P16" s="134"/>
+      <c r="K16" s="168"/>
+      <c r="L16" s="168"/>
+      <c r="M16" s="168"/>
+      <c r="N16" s="168"/>
+      <c r="O16" s="168"/>
+      <c r="P16" s="169"/>
     </row>
     <row r="17" spans="2:16" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B17" s="148"/>
-      <c r="C17" s="149"/>
-      <c r="D17" s="149"/>
-      <c r="E17" s="149"/>
-      <c r="F17" s="149"/>
-      <c r="G17" s="149"/>
-      <c r="H17" s="150"/>
+      <c r="B17" s="157"/>
+      <c r="C17" s="158"/>
+      <c r="D17" s="158"/>
+      <c r="E17" s="158"/>
+      <c r="F17" s="158"/>
+      <c r="G17" s="158"/>
+      <c r="H17" s="159"/>
       <c r="J17" s="89" t="s">
         <v>22</v>
       </c>
@@ -4822,26 +4822,26 @@
       <c r="P17" s="91"/>
     </row>
     <row r="18" spans="2:16" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B18" s="148"/>
-      <c r="C18" s="149"/>
-      <c r="D18" s="149"/>
-      <c r="E18" s="149"/>
-      <c r="F18" s="149"/>
-      <c r="G18" s="149"/>
-      <c r="H18" s="150"/>
+      <c r="B18" s="157"/>
+      <c r="C18" s="158"/>
+      <c r="D18" s="158"/>
+      <c r="E18" s="158"/>
+      <c r="F18" s="158"/>
+      <c r="G18" s="158"/>
+      <c r="H18" s="159"/>
       <c r="J18" s="92" t="s">
         <v>23</v>
       </c>
       <c r="P18" s="88"/>
     </row>
     <row r="19" spans="2:16" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B19" s="148"/>
-      <c r="C19" s="149"/>
-      <c r="D19" s="149"/>
-      <c r="E19" s="149"/>
-      <c r="F19" s="149"/>
-      <c r="G19" s="149"/>
-      <c r="H19" s="150"/>
+      <c r="B19" s="157"/>
+      <c r="C19" s="158"/>
+      <c r="D19" s="158"/>
+      <c r="E19" s="158"/>
+      <c r="F19" s="158"/>
+      <c r="G19" s="158"/>
+      <c r="H19" s="159"/>
       <c r="J19" s="93" t="s">
         <v>24</v>
       </c>
@@ -4853,13 +4853,13 @@
       <c r="P19" s="94"/>
     </row>
     <row r="20" spans="2:16" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B20" s="148"/>
-      <c r="C20" s="149"/>
-      <c r="D20" s="149"/>
-      <c r="E20" s="149"/>
-      <c r="F20" s="149"/>
-      <c r="G20" s="149"/>
-      <c r="H20" s="150"/>
+      <c r="B20" s="157"/>
+      <c r="C20" s="158"/>
+      <c r="D20" s="158"/>
+      <c r="E20" s="158"/>
+      <c r="F20" s="158"/>
+      <c r="G20" s="158"/>
+      <c r="H20" s="159"/>
       <c r="J20" s="92" t="s">
         <v>25</v>
       </c>
@@ -4886,17 +4886,17 @@
       <c r="F22" s="62" t="s">
         <v>36</v>
       </c>
-      <c r="G22" s="146" t="s">
+      <c r="G22" s="155" t="s">
         <v>37</v>
       </c>
-      <c r="H22" s="147"/>
+      <c r="H22" s="156"/>
       <c r="J22" s="92" t="s">
         <v>26</v>
       </c>
-      <c r="L22" s="129"/>
-      <c r="M22" s="129"/>
-      <c r="N22" s="129"/>
-      <c r="O22" s="129"/>
+      <c r="L22" s="145"/>
+      <c r="M22" s="145"/>
+      <c r="N22" s="145"/>
+      <c r="O22" s="145"/>
       <c r="P22" s="88"/>
     </row>
     <row r="23" spans="2:16" x14ac:dyDescent="0.25">
@@ -4910,10 +4910,10 @@
       <c r="J23" s="92" t="s">
         <v>306</v>
       </c>
-      <c r="L23" s="129"/>
-      <c r="M23" s="129"/>
-      <c r="N23" s="129"/>
-      <c r="O23" s="129"/>
+      <c r="L23" s="145"/>
+      <c r="M23" s="145"/>
+      <c r="N23" s="145"/>
+      <c r="O23" s="145"/>
       <c r="P23" s="88"/>
     </row>
     <row r="24" spans="2:16" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -5001,10 +5001,10 @@
       <c r="F30" s="2"/>
       <c r="G30" s="2"/>
       <c r="H30" s="40"/>
-      <c r="J30" s="128" t="s">
+      <c r="J30" s="164" t="s">
         <v>30</v>
       </c>
-      <c r="K30" s="129"/>
+      <c r="K30" s="145"/>
       <c r="P30" s="88"/>
     </row>
     <row r="31" spans="2:16" x14ac:dyDescent="0.25">
@@ -5015,10 +5015,10 @@
       <c r="F31" s="2"/>
       <c r="G31" s="2"/>
       <c r="H31" s="40"/>
-      <c r="J31" s="128" t="s">
+      <c r="J31" s="164" t="s">
         <v>31</v>
       </c>
-      <c r="K31" s="129"/>
+      <c r="K31" s="145"/>
       <c r="P31" s="88"/>
     </row>
     <row r="32" spans="2:16" x14ac:dyDescent="0.25">
@@ -5141,40 +5141,40 @@
       </c>
     </row>
     <row r="36" spans="2:16" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B36" s="125" t="s">
+      <c r="B36" s="137" t="s">
         <v>44</v>
       </c>
-      <c r="C36" s="126"/>
-      <c r="D36" s="126"/>
-      <c r="E36" s="126"/>
-      <c r="F36" s="126"/>
-      <c r="G36" s="126"/>
-      <c r="H36" s="126"/>
-      <c r="I36" s="126"/>
-      <c r="J36" s="126"/>
-      <c r="K36" s="126"/>
-      <c r="L36" s="126"/>
-      <c r="M36" s="126"/>
-      <c r="N36" s="126"/>
-      <c r="O36" s="126"/>
-      <c r="P36" s="127"/>
+      <c r="C36" s="135"/>
+      <c r="D36" s="135"/>
+      <c r="E36" s="135"/>
+      <c r="F36" s="135"/>
+      <c r="G36" s="135"/>
+      <c r="H36" s="135"/>
+      <c r="I36" s="135"/>
+      <c r="J36" s="135"/>
+      <c r="K36" s="135"/>
+      <c r="L36" s="135"/>
+      <c r="M36" s="135"/>
+      <c r="N36" s="135"/>
+      <c r="O36" s="135"/>
+      <c r="P36" s="138"/>
     </row>
     <row r="37" spans="2:16" ht="20.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B37" s="168"/>
-      <c r="C37" s="169"/>
-      <c r="D37" s="169"/>
-      <c r="E37" s="169"/>
-      <c r="F37" s="169"/>
-      <c r="G37" s="169"/>
-      <c r="H37" s="169"/>
-      <c r="I37" s="169"/>
-      <c r="J37" s="169"/>
-      <c r="K37" s="169"/>
-      <c r="L37" s="169"/>
-      <c r="M37" s="169"/>
-      <c r="N37" s="169"/>
-      <c r="O37" s="169"/>
-      <c r="P37" s="170"/>
+      <c r="B37" s="139"/>
+      <c r="C37" s="140"/>
+      <c r="D37" s="140"/>
+      <c r="E37" s="140"/>
+      <c r="F37" s="140"/>
+      <c r="G37" s="140"/>
+      <c r="H37" s="140"/>
+      <c r="I37" s="140"/>
+      <c r="J37" s="140"/>
+      <c r="K37" s="140"/>
+      <c r="L37" s="140"/>
+      <c r="M37" s="140"/>
+      <c r="N37" s="140"/>
+      <c r="O37" s="140"/>
+      <c r="P37" s="141"/>
     </row>
     <row r="38" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B38" s="46"/>
@@ -5221,13 +5221,13 @@
       <c r="J39" s="64" t="s">
         <v>38</v>
       </c>
-      <c r="K39" s="120" t="s">
+      <c r="K39" s="143" t="s">
         <v>40</v>
       </c>
-      <c r="L39" s="120"/>
-      <c r="M39" s="120"/>
-      <c r="N39" s="120"/>
-      <c r="O39" s="120"/>
+      <c r="L39" s="143"/>
+      <c r="M39" s="143"/>
+      <c r="N39" s="143"/>
+      <c r="O39" s="143"/>
       <c r="P39" s="60" t="s">
         <v>124</v>
       </c>
@@ -5243,14 +5243,14 @@
       <c r="H40" s="7"/>
       <c r="I40" s="7"/>
       <c r="J40" s="7"/>
-      <c r="K40" s="121" t="str">
+      <c r="K40" s="142" t="str">
         <f>+IF(D41="","",IF(D40&lt;0,Sheet2!$C$27,VLOOKUP(D41,Sheet2!$A$27:$C$31,3,TRUE)))</f>
         <v/>
       </c>
-      <c r="L40" s="121"/>
-      <c r="M40" s="121"/>
-      <c r="N40" s="121"/>
-      <c r="O40" s="121"/>
+      <c r="L40" s="142"/>
+      <c r="M40" s="142"/>
+      <c r="N40" s="142"/>
+      <c r="O40" s="142"/>
       <c r="P40" s="28" t="str">
         <f>+IF(K40="","",VLOOKUP(K40,Sheet2!$C$27:$D$31,2,FALSE))</f>
         <v/>
@@ -5282,14 +5282,14 @@
         <f>+IF(D41="","",AVERAGE(D41:G41))</f>
         <v/>
       </c>
-      <c r="K41" s="121" t="str">
+      <c r="K41" s="142" t="str">
         <f>+IF(J41="","",IF(AND(D40&lt;0,E40&lt;0),Sheet2!$C$35,VLOOKUP(J41,Sheet2!$A$35:$C$39,3,TRUE)))</f>
         <v/>
       </c>
-      <c r="L41" s="121"/>
-      <c r="M41" s="121"/>
-      <c r="N41" s="121"/>
-      <c r="O41" s="121"/>
+      <c r="L41" s="142"/>
+      <c r="M41" s="142"/>
+      <c r="N41" s="142"/>
+      <c r="O41" s="142"/>
       <c r="P41" s="28" t="str">
         <f>+IF(K41="","",VLOOKUP(K41,Sheet2!$C$35:$D$39,2,FALSE))</f>
         <v/>
@@ -5305,11 +5305,11 @@
       <c r="H42" s="7"/>
       <c r="I42" s="7"/>
       <c r="J42" s="7"/>
-      <c r="K42" s="121"/>
-      <c r="L42" s="121"/>
-      <c r="M42" s="121"/>
-      <c r="N42" s="121"/>
-      <c r="O42" s="121"/>
+      <c r="K42" s="142"/>
+      <c r="L42" s="142"/>
+      <c r="M42" s="142"/>
+      <c r="N42" s="142"/>
+      <c r="O42" s="142"/>
       <c r="P42" s="28"/>
     </row>
     <row r="43" spans="2:16" x14ac:dyDescent="0.25">
@@ -5341,13 +5341,13 @@
       <c r="J43" s="64" t="s">
         <v>38</v>
       </c>
-      <c r="K43" s="120" t="s">
+      <c r="K43" s="143" t="s">
         <v>40</v>
       </c>
-      <c r="L43" s="120"/>
-      <c r="M43" s="120"/>
-      <c r="N43" s="120"/>
-      <c r="O43" s="120"/>
+      <c r="L43" s="143"/>
+      <c r="M43" s="143"/>
+      <c r="N43" s="143"/>
+      <c r="O43" s="143"/>
       <c r="P43" s="60" t="s">
         <v>124</v>
       </c>
@@ -5363,14 +5363,14 @@
       <c r="H44" s="7"/>
       <c r="I44" s="7"/>
       <c r="J44" s="7"/>
-      <c r="K44" s="121" t="str">
+      <c r="K44" s="142" t="str">
         <f>+IF(D45="","",IF(D44&lt;0,Sheet2!$C$27,VLOOKUP(D45,Sheet2!$A$27:$C$31,3,TRUE)))</f>
         <v/>
       </c>
-      <c r="L44" s="121"/>
-      <c r="M44" s="121"/>
-      <c r="N44" s="121"/>
-      <c r="O44" s="121"/>
+      <c r="L44" s="142"/>
+      <c r="M44" s="142"/>
+      <c r="N44" s="142"/>
+      <c r="O44" s="142"/>
       <c r="P44" s="28" t="str">
         <f>+IF(K44="","",VLOOKUP(K44,Sheet2!$C$27:$D$31,2,FALSE))</f>
         <v/>
@@ -5402,14 +5402,14 @@
         <f>+IF(D45="","",AVERAGE(D45:G45))</f>
         <v/>
       </c>
-      <c r="K45" s="121" t="str">
+      <c r="K45" s="142" t="str">
         <f>+IF(J45="","",IF(AND(D44&lt;0,E44&lt;0),Sheet2!$C$35,VLOOKUP(J45,Sheet2!$A$35:$C$39,3,TRUE)))</f>
         <v/>
       </c>
-      <c r="L45" s="121"/>
-      <c r="M45" s="121"/>
-      <c r="N45" s="121"/>
-      <c r="O45" s="121"/>
+      <c r="L45" s="142"/>
+      <c r="M45" s="142"/>
+      <c r="N45" s="142"/>
+      <c r="O45" s="142"/>
       <c r="P45" s="28" t="str">
         <f>+IF(K45="","",VLOOKUP(K45,Sheet2!$C$35:$D$39,2,FALSE))</f>
         <v/>
@@ -5456,11 +5456,11 @@
       <c r="J47" s="64" t="s">
         <v>38</v>
       </c>
-      <c r="K47" s="120"/>
-      <c r="L47" s="120"/>
-      <c r="M47" s="120"/>
-      <c r="N47" s="120"/>
-      <c r="O47" s="120"/>
+      <c r="K47" s="143"/>
+      <c r="L47" s="143"/>
+      <c r="M47" s="143"/>
+      <c r="N47" s="143"/>
+      <c r="O47" s="143"/>
       <c r="P47" s="60"/>
     </row>
     <row r="48" spans="2:16" x14ac:dyDescent="0.25">
@@ -5474,11 +5474,11 @@
       <c r="H48" s="7"/>
       <c r="I48" s="7"/>
       <c r="J48" s="7"/>
-      <c r="K48" s="121"/>
-      <c r="L48" s="121"/>
-      <c r="M48" s="121"/>
-      <c r="N48" s="121"/>
-      <c r="O48" s="121"/>
+      <c r="K48" s="142"/>
+      <c r="L48" s="142"/>
+      <c r="M48" s="142"/>
+      <c r="N48" s="142"/>
+      <c r="O48" s="142"/>
       <c r="P48" s="28"/>
     </row>
     <row r="49" spans="2:16" x14ac:dyDescent="0.25">
@@ -5507,11 +5507,11 @@
         <f>+IF(D49="","",AVERAGE(D49:G49))</f>
         <v/>
       </c>
-      <c r="K49" s="121"/>
-      <c r="L49" s="121"/>
-      <c r="M49" s="121"/>
-      <c r="N49" s="121"/>
-      <c r="O49" s="121"/>
+      <c r="K49" s="142"/>
+      <c r="L49" s="142"/>
+      <c r="M49" s="142"/>
+      <c r="N49" s="142"/>
+      <c r="O49" s="142"/>
       <c r="P49" s="28"/>
     </row>
     <row r="50" spans="2:16" x14ac:dyDescent="0.25">
@@ -5555,11 +5555,11 @@
       <c r="J51" s="64" t="s">
         <v>38</v>
       </c>
-      <c r="K51" s="120"/>
-      <c r="L51" s="120"/>
-      <c r="M51" s="120"/>
-      <c r="N51" s="120"/>
-      <c r="O51" s="120"/>
+      <c r="K51" s="143"/>
+      <c r="L51" s="143"/>
+      <c r="M51" s="143"/>
+      <c r="N51" s="143"/>
+      <c r="O51" s="143"/>
       <c r="P51" s="60"/>
     </row>
     <row r="52" spans="2:16" x14ac:dyDescent="0.25">
@@ -5644,11 +5644,11 @@
       <c r="J55" s="64" t="s">
         <v>38</v>
       </c>
-      <c r="K55" s="120"/>
-      <c r="L55" s="120"/>
-      <c r="M55" s="120"/>
-      <c r="N55" s="120"/>
-      <c r="O55" s="120"/>
+      <c r="K55" s="143"/>
+      <c r="L55" s="143"/>
+      <c r="M55" s="143"/>
+      <c r="N55" s="143"/>
+      <c r="O55" s="143"/>
       <c r="P55" s="60"/>
     </row>
     <row r="56" spans="2:16" x14ac:dyDescent="0.25">
@@ -5733,13 +5733,13 @@
       <c r="J59" s="64" t="s">
         <v>38</v>
       </c>
-      <c r="K59" s="120" t="s">
+      <c r="K59" s="143" t="s">
         <v>40</v>
       </c>
-      <c r="L59" s="120"/>
-      <c r="M59" s="120"/>
-      <c r="N59" s="120"/>
-      <c r="O59" s="120"/>
+      <c r="L59" s="143"/>
+      <c r="M59" s="143"/>
+      <c r="N59" s="143"/>
+      <c r="O59" s="143"/>
       <c r="P59" s="60" t="s">
         <v>124</v>
       </c>
@@ -5755,14 +5755,14 @@
       <c r="H60" s="7"/>
       <c r="I60" s="7"/>
       <c r="J60" s="7"/>
-      <c r="K60" s="121" t="str">
+      <c r="K60" s="142" t="str">
         <f>+IF(D61="","",IF(D60&lt;0,Sheet2!$C$27,VLOOKUP(D61,Sheet2!$A$27:$C$31,3,TRUE)))</f>
         <v/>
       </c>
-      <c r="L60" s="121"/>
-      <c r="M60" s="121"/>
-      <c r="N60" s="121"/>
-      <c r="O60" s="121"/>
+      <c r="L60" s="142"/>
+      <c r="M60" s="142"/>
+      <c r="N60" s="142"/>
+      <c r="O60" s="142"/>
       <c r="P60" s="28" t="str">
         <f>+IF(K60="","",VLOOKUP(K60,Sheet2!$C$27:$D$31,2,FALSE))</f>
         <v/>
@@ -5794,14 +5794,14 @@
         <f>+IF(D61="","",AVERAGE(D61:G61))</f>
         <v/>
       </c>
-      <c r="K61" s="121" t="str">
+      <c r="K61" s="142" t="str">
         <f>+IF(J61="","",IF(AND(D60&lt;0,E60&lt;0),Sheet2!$C$35,VLOOKUP(J61,Sheet2!$A$35:$C$39,3,TRUE)))</f>
         <v/>
       </c>
-      <c r="L61" s="121"/>
-      <c r="M61" s="121"/>
-      <c r="N61" s="121"/>
-      <c r="O61" s="121"/>
+      <c r="L61" s="142"/>
+      <c r="M61" s="142"/>
+      <c r="N61" s="142"/>
+      <c r="O61" s="142"/>
       <c r="P61" s="28" t="str">
         <f>+IF(K61="","",VLOOKUP(K61,Sheet2!$C$35:$D$39,2,FALSE))</f>
         <v/>
@@ -5848,13 +5848,13 @@
       <c r="J63" s="64" t="s">
         <v>38</v>
       </c>
-      <c r="K63" s="120" t="s">
+      <c r="K63" s="143" t="s">
         <v>40</v>
       </c>
-      <c r="L63" s="120"/>
-      <c r="M63" s="120"/>
-      <c r="N63" s="120"/>
-      <c r="O63" s="120"/>
+      <c r="L63" s="143"/>
+      <c r="M63" s="143"/>
+      <c r="N63" s="143"/>
+      <c r="O63" s="143"/>
       <c r="P63" s="60" t="s">
         <v>124</v>
       </c>
@@ -5870,14 +5870,14 @@
       <c r="H64" s="7"/>
       <c r="I64" s="7"/>
       <c r="J64" s="7"/>
-      <c r="K64" s="121" t="str">
+      <c r="K64" s="142" t="str">
         <f>+IF(D65="","",IF(D64&lt;0,Sheet2!$C$27,VLOOKUP(D65,Sheet2!$A$27:$C$31,3,TRUE)))</f>
         <v/>
       </c>
-      <c r="L64" s="121"/>
-      <c r="M64" s="121"/>
-      <c r="N64" s="121"/>
-      <c r="O64" s="121"/>
+      <c r="L64" s="142"/>
+      <c r="M64" s="142"/>
+      <c r="N64" s="142"/>
+      <c r="O64" s="142"/>
       <c r="P64" s="28" t="str">
         <f>+IF(K64="","",VLOOKUP(K64,Sheet2!$C$27:$D$31,2,FALSE))</f>
         <v/>
@@ -5909,14 +5909,14 @@
         <f>+IF(D65="","",AVERAGE(D65:G65))</f>
         <v/>
       </c>
-      <c r="K65" s="121" t="str">
+      <c r="K65" s="142" t="str">
         <f>+IF(J65="","",IF(AND(D64&lt;0,E64&lt;0),Sheet2!$C$35,VLOOKUP(J65,Sheet2!$A$35:$C$39,3,TRUE)))</f>
         <v/>
       </c>
-      <c r="L65" s="121"/>
-      <c r="M65" s="121"/>
-      <c r="N65" s="121"/>
-      <c r="O65" s="121"/>
+      <c r="L65" s="142"/>
+      <c r="M65" s="142"/>
+      <c r="N65" s="142"/>
+      <c r="O65" s="142"/>
       <c r="P65" s="28" t="str">
         <f>+IF(K65="","",VLOOKUP(K65,Sheet2!$C$35:$D$39,2,FALSE))</f>
         <v/>
@@ -5963,13 +5963,13 @@
       <c r="J67" s="64" t="s">
         <v>38</v>
       </c>
-      <c r="K67" s="120" t="s">
+      <c r="K67" s="143" t="s">
         <v>40</v>
       </c>
-      <c r="L67" s="120"/>
-      <c r="M67" s="120"/>
-      <c r="N67" s="120"/>
-      <c r="O67" s="120"/>
+      <c r="L67" s="143"/>
+      <c r="M67" s="143"/>
+      <c r="N67" s="143"/>
+      <c r="O67" s="143"/>
       <c r="P67" s="60" t="s">
         <v>124</v>
       </c>
@@ -5985,14 +5985,14 @@
       <c r="H68" s="7"/>
       <c r="I68" s="7"/>
       <c r="J68" s="7"/>
-      <c r="K68" s="121" t="str">
+      <c r="K68" s="142" t="str">
         <f>+IF(D69="","",IF(D68&lt;0,Sheet2!$C$27,VLOOKUP(D69,Sheet2!$A$27:$C$31,3,TRUE)))</f>
         <v/>
       </c>
-      <c r="L68" s="121"/>
-      <c r="M68" s="121"/>
-      <c r="N68" s="121"/>
-      <c r="O68" s="121"/>
+      <c r="L68" s="142"/>
+      <c r="M68" s="142"/>
+      <c r="N68" s="142"/>
+      <c r="O68" s="142"/>
       <c r="P68" s="28" t="str">
         <f>+IF(K68="","",VLOOKUP(K68,Sheet2!$C$27:$D$31,2,FALSE))</f>
         <v/>
@@ -6024,14 +6024,14 @@
         <f>+IF(D69="","",AVERAGE(D69:G69))</f>
         <v/>
       </c>
-      <c r="K69" s="121" t="str">
+      <c r="K69" s="142" t="str">
         <f>+IF(J69="","",IF(AND(D68&lt;0,E68&lt;0),Sheet2!$C$35,VLOOKUP(J69,Sheet2!$A$35:$C$39,3,TRUE)))</f>
         <v/>
       </c>
-      <c r="L69" s="121"/>
-      <c r="M69" s="121"/>
-      <c r="N69" s="121"/>
-      <c r="O69" s="121"/>
+      <c r="L69" s="142"/>
+      <c r="M69" s="142"/>
+      <c r="N69" s="142"/>
+      <c r="O69" s="142"/>
       <c r="P69" s="28" t="str">
         <f>+IF(K69="","",VLOOKUP(K69,Sheet2!$C$35:$D$39,2,FALSE))</f>
         <v/>
@@ -6078,11 +6078,11 @@
       <c r="J71" s="64" t="s">
         <v>38</v>
       </c>
-      <c r="K71" s="120"/>
-      <c r="L71" s="120"/>
-      <c r="M71" s="120"/>
-      <c r="N71" s="120"/>
-      <c r="O71" s="120"/>
+      <c r="K71" s="143"/>
+      <c r="L71" s="143"/>
+      <c r="M71" s="143"/>
+      <c r="N71" s="143"/>
+      <c r="O71" s="143"/>
       <c r="P71" s="60"/>
     </row>
     <row r="72" spans="2:16" x14ac:dyDescent="0.25">
@@ -6170,11 +6170,11 @@
       <c r="J75" s="64" t="s">
         <v>38</v>
       </c>
-      <c r="K75" s="120"/>
-      <c r="L75" s="120"/>
-      <c r="M75" s="120"/>
-      <c r="N75" s="120"/>
-      <c r="O75" s="120"/>
+      <c r="K75" s="143"/>
+      <c r="L75" s="143"/>
+      <c r="M75" s="143"/>
+      <c r="N75" s="143"/>
+      <c r="O75" s="143"/>
       <c r="P75" s="60"/>
     </row>
     <row r="76" spans="2:16" x14ac:dyDescent="0.25">
@@ -6259,13 +6259,13 @@
       <c r="J79" s="64" t="s">
         <v>38</v>
       </c>
-      <c r="K79" s="120" t="s">
+      <c r="K79" s="143" t="s">
         <v>40</v>
       </c>
-      <c r="L79" s="120"/>
-      <c r="M79" s="120"/>
-      <c r="N79" s="120"/>
-      <c r="O79" s="120"/>
+      <c r="L79" s="143"/>
+      <c r="M79" s="143"/>
+      <c r="N79" s="143"/>
+      <c r="O79" s="143"/>
       <c r="P79" s="60" t="s">
         <v>124</v>
       </c>
@@ -6281,14 +6281,14 @@
       <c r="H80" s="7"/>
       <c r="I80" s="7"/>
       <c r="J80" s="7"/>
-      <c r="K80" s="121" t="str">
+      <c r="K80" s="142" t="str">
         <f>+IF(D81="","",IF(D80&lt;0,Sheet2!$C$27,VLOOKUP(D81,Sheet2!$A$27:$C$31,3,TRUE)))</f>
         <v/>
       </c>
-      <c r="L80" s="121"/>
-      <c r="M80" s="121"/>
-      <c r="N80" s="121"/>
-      <c r="O80" s="121"/>
+      <c r="L80" s="142"/>
+      <c r="M80" s="142"/>
+      <c r="N80" s="142"/>
+      <c r="O80" s="142"/>
       <c r="P80" s="28" t="str">
         <f>+IF(K80="","",VLOOKUP(K80,Sheet2!$C$27:$D$31,2,FALSE))</f>
         <v/>
@@ -6320,14 +6320,14 @@
         <f>+IF(D81="","",AVERAGE(D81:G81))</f>
         <v/>
       </c>
-      <c r="K81" s="121" t="str">
+      <c r="K81" s="142" t="str">
         <f>+IF(J81="","",IF(AND(D80&lt;0,E80&lt;0),Sheet2!$C$35,VLOOKUP(J81,Sheet2!$A$35:$C$39,3,TRUE)))</f>
         <v/>
       </c>
-      <c r="L81" s="121"/>
-      <c r="M81" s="121"/>
-      <c r="N81" s="121"/>
-      <c r="O81" s="121"/>
+      <c r="L81" s="142"/>
+      <c r="M81" s="142"/>
+      <c r="N81" s="142"/>
+      <c r="O81" s="142"/>
       <c r="P81" s="28" t="str">
         <f>+IF(K81="","",VLOOKUP(K81,Sheet2!$C$35:$D$39,2,FALSE))</f>
         <v/>
@@ -6374,13 +6374,13 @@
       <c r="J83" s="64" t="s">
         <v>38</v>
       </c>
-      <c r="K83" s="120" t="s">
+      <c r="K83" s="143" t="s">
         <v>40</v>
       </c>
-      <c r="L83" s="120"/>
-      <c r="M83" s="120"/>
-      <c r="N83" s="120"/>
-      <c r="O83" s="120"/>
+      <c r="L83" s="143"/>
+      <c r="M83" s="143"/>
+      <c r="N83" s="143"/>
+      <c r="O83" s="143"/>
       <c r="P83" s="60" t="s">
         <v>124</v>
       </c>
@@ -6396,14 +6396,14 @@
       <c r="H84" s="7"/>
       <c r="I84" s="7"/>
       <c r="J84" s="7"/>
-      <c r="K84" s="121" t="str">
+      <c r="K84" s="142" t="str">
         <f>+IF(D85="","",VLOOKUP(D85,Sheet2!$A$42:$C$43,3,TRUE))</f>
         <v/>
       </c>
-      <c r="L84" s="121"/>
-      <c r="M84" s="121"/>
-      <c r="N84" s="121"/>
-      <c r="O84" s="121"/>
+      <c r="L84" s="142"/>
+      <c r="M84" s="142"/>
+      <c r="N84" s="142"/>
+      <c r="O84" s="142"/>
       <c r="P84" s="28" t="str">
         <f>+IF(K84="","",VLOOKUP(K84,Sheet2!$C$42:$D$43,2,FALSE))</f>
         <v/>
@@ -6439,14 +6439,14 @@
         <f>+IF(D85="","",AVERAGE(D85:G85))</f>
         <v/>
       </c>
-      <c r="K85" s="121" t="str">
+      <c r="K85" s="142" t="str">
         <f>+IF(J85="","",VLOOKUP(J85,Sheet2!$A$45:$C$46,3,TRUE))</f>
         <v/>
       </c>
-      <c r="L85" s="121"/>
-      <c r="M85" s="121"/>
-      <c r="N85" s="121"/>
-      <c r="O85" s="121"/>
+      <c r="L85" s="142"/>
+      <c r="M85" s="142"/>
+      <c r="N85" s="142"/>
+      <c r="O85" s="142"/>
       <c r="P85" s="28" t="str">
         <f>+IF(K85="","",VLOOKUP(K85,Sheet2!$C$45:$D$46,2,FALSE))</f>
         <v/>
@@ -6521,13 +6521,13 @@
       <c r="J88" s="64" t="s">
         <v>38</v>
       </c>
-      <c r="K88" s="120" t="s">
+      <c r="K88" s="143" t="s">
         <v>40</v>
       </c>
-      <c r="L88" s="120"/>
-      <c r="M88" s="120"/>
-      <c r="N88" s="120"/>
-      <c r="O88" s="120"/>
+      <c r="L88" s="143"/>
+      <c r="M88" s="143"/>
+      <c r="N88" s="143"/>
+      <c r="O88" s="143"/>
       <c r="P88" s="60" t="s">
         <v>124</v>
       </c>
@@ -6569,14 +6569,14 @@
       <c r="H90" s="7"/>
       <c r="I90" s="7"/>
       <c r="J90" s="7"/>
-      <c r="K90" s="121" t="str">
+      <c r="K90" s="142" t="str">
         <f>+IF(D91="","",IF(D89&lt;0,Sheet2!$C$50,VLOOKUP(D91,Sheet2!A50:C54,3,TRUE)))</f>
         <v/>
       </c>
-      <c r="L90" s="121"/>
-      <c r="M90" s="121"/>
-      <c r="N90" s="121"/>
-      <c r="O90" s="121"/>
+      <c r="L90" s="142"/>
+      <c r="M90" s="142"/>
+      <c r="N90" s="142"/>
+      <c r="O90" s="142"/>
       <c r="P90" s="28" t="str">
         <f>+IF(K90="","",VLOOKUP(K90,Sheet2!$C$50:$D$54,2,FALSE))</f>
         <v/>
@@ -6608,14 +6608,14 @@
         <f>+IF(D91="","",AVERAGE(D91:G91))</f>
         <v/>
       </c>
-      <c r="K91" s="121" t="str">
+      <c r="K91" s="142" t="str">
         <f>+IF(J91="","",IF(AND(C89&lt;0,D89&lt;0),Sheet2!$C$56,VLOOKUP(J91,Sheet2!$A$56:$C$60,3,TRUE)))</f>
         <v/>
       </c>
-      <c r="L91" s="121"/>
-      <c r="M91" s="121"/>
-      <c r="N91" s="121"/>
-      <c r="O91" s="121"/>
+      <c r="L91" s="142"/>
+      <c r="M91" s="142"/>
+      <c r="N91" s="142"/>
+      <c r="O91" s="142"/>
       <c r="P91" s="28" t="str">
         <f>+IF(K91="","",VLOOKUP(K91,Sheet2!$C$56:$D$60,2,FALSE))</f>
         <v/>
@@ -6662,13 +6662,13 @@
       <c r="J93" s="64" t="s">
         <v>38</v>
       </c>
-      <c r="K93" s="120" t="s">
+      <c r="K93" s="143" t="s">
         <v>40</v>
       </c>
-      <c r="L93" s="120"/>
-      <c r="M93" s="120"/>
-      <c r="N93" s="120"/>
-      <c r="O93" s="120"/>
+      <c r="L93" s="143"/>
+      <c r="M93" s="143"/>
+      <c r="N93" s="143"/>
+      <c r="O93" s="143"/>
       <c r="P93" s="60" t="s">
         <v>124</v>
       </c>
@@ -6684,14 +6684,14 @@
       <c r="H94" s="7"/>
       <c r="I94" s="7"/>
       <c r="J94" s="7"/>
-      <c r="K94" s="121" t="str">
+      <c r="K94" s="142" t="str">
         <f>+IF(D95="","",IF(D94&lt;0,Sheet2!$C$64,VLOOKUP(D95,Sheet2!$A$64:$C$68,3,TRUE)))</f>
         <v/>
       </c>
-      <c r="L94" s="121"/>
-      <c r="M94" s="121"/>
-      <c r="N94" s="121"/>
-      <c r="O94" s="121"/>
+      <c r="L94" s="142"/>
+      <c r="M94" s="142"/>
+      <c r="N94" s="142"/>
+      <c r="O94" s="142"/>
       <c r="P94" s="28" t="str">
         <f>+IF(K94="","",VLOOKUP(K94,Sheet2!$C$64:$D$68,2,FALSE))</f>
         <v/>
@@ -6723,14 +6723,14 @@
         <f>+IF(D95="","",AVERAGE(D95:G95))</f>
         <v/>
       </c>
-      <c r="K95" s="121" t="str">
+      <c r="K95" s="142" t="str">
         <f>+IF(J95="","",IF(AND(C94&lt;0,D94&lt;0),Sheet2!$C$70,VLOOKUP(J95,Sheet2!$A$70:$C$74,3,TRUE)))</f>
         <v/>
       </c>
-      <c r="L95" s="121"/>
-      <c r="M95" s="121"/>
-      <c r="N95" s="121"/>
-      <c r="O95" s="121"/>
+      <c r="L95" s="142"/>
+      <c r="M95" s="142"/>
+      <c r="N95" s="142"/>
+      <c r="O95" s="142"/>
       <c r="P95" s="28" t="str">
         <f>+IF(K95="","",VLOOKUP(K95,Sheet2!$C$70:$D$74,2,FALSE))</f>
         <v/>
@@ -6777,13 +6777,13 @@
       <c r="J97" s="64" t="s">
         <v>38</v>
       </c>
-      <c r="K97" s="120" t="s">
+      <c r="K97" s="143" t="s">
         <v>40</v>
       </c>
-      <c r="L97" s="120"/>
-      <c r="M97" s="120"/>
-      <c r="N97" s="120"/>
-      <c r="O97" s="120"/>
+      <c r="L97" s="143"/>
+      <c r="M97" s="143"/>
+      <c r="N97" s="143"/>
+      <c r="O97" s="143"/>
       <c r="P97" s="60" t="s">
         <v>124</v>
       </c>
@@ -6799,14 +6799,14 @@
       <c r="H98" s="7"/>
       <c r="I98" s="7"/>
       <c r="J98" s="7"/>
-      <c r="K98" s="121" t="str">
+      <c r="K98" s="142" t="str">
         <f>+IF(D99="","",IF(D98&lt;0,Sheet2!$C$78,VLOOKUP(D99,Sheet2!$A$78:$C$82,3,TRUE)))</f>
         <v/>
       </c>
-      <c r="L98" s="121"/>
-      <c r="M98" s="121"/>
-      <c r="N98" s="121"/>
-      <c r="O98" s="121"/>
+      <c r="L98" s="142"/>
+      <c r="M98" s="142"/>
+      <c r="N98" s="142"/>
+      <c r="O98" s="142"/>
       <c r="P98" s="28" t="str">
         <f>+IF(K98="","",VLOOKUP(K98,Sheet2!$C$78:$D$82,2,FALSE))</f>
         <v/>
@@ -6838,14 +6838,14 @@
         <f>+IF(D99="","",AVERAGE(D99:G99))</f>
         <v/>
       </c>
-      <c r="K99" s="121" t="str">
+      <c r="K99" s="142" t="str">
         <f>+IF(J99="","",IF(AND(E98&lt;0,D98&lt;0),Sheet2!$C$84,VLOOKUP(J99,Sheet2!$A$84:$C$88,3,TRUE)))</f>
         <v/>
       </c>
-      <c r="L99" s="121"/>
-      <c r="M99" s="121"/>
-      <c r="N99" s="121"/>
-      <c r="O99" s="121"/>
+      <c r="L99" s="142"/>
+      <c r="M99" s="142"/>
+      <c r="N99" s="142"/>
+      <c r="O99" s="142"/>
       <c r="P99" s="28" t="str">
         <f>+IF(K99="","",VLOOKUP(K99,Sheet2!$C$84:$D$88,2,FALSE))</f>
         <v/>
@@ -6897,13 +6897,13 @@
       <c r="J101" s="64" t="s">
         <v>38</v>
       </c>
-      <c r="K101" s="120" t="s">
+      <c r="K101" s="143" t="s">
         <v>40</v>
       </c>
-      <c r="L101" s="120"/>
-      <c r="M101" s="120"/>
-      <c r="N101" s="120"/>
-      <c r="O101" s="120"/>
+      <c r="L101" s="143"/>
+      <c r="M101" s="143"/>
+      <c r="N101" s="143"/>
+      <c r="O101" s="143"/>
       <c r="P101" s="60" t="s">
         <v>124</v>
       </c>
@@ -6919,14 +6919,14 @@
       <c r="H102" s="7"/>
       <c r="I102" s="7"/>
       <c r="J102" s="7"/>
-      <c r="K102" s="121" t="str">
+      <c r="K102" s="142" t="str">
         <f>+IF(D103="","",VLOOKUP(D103,Sheet2!$A$92:$C$94,3,TRUE))</f>
         <v/>
       </c>
-      <c r="L102" s="121"/>
-      <c r="M102" s="121"/>
-      <c r="N102" s="121"/>
-      <c r="O102" s="121"/>
+      <c r="L102" s="142"/>
+      <c r="M102" s="142"/>
+      <c r="N102" s="142"/>
+      <c r="O102" s="142"/>
       <c r="P102" s="28" t="str">
         <f>+IF(D103="","",VLOOKUP(D103,Sheet2!$A$92:$C$94,2,TRUE))</f>
         <v/>
@@ -6958,14 +6958,14 @@
         <f>+IF(D103="","",AVERAGE(D103:G103))</f>
         <v/>
       </c>
-      <c r="K103" s="121" t="str">
+      <c r="K103" s="142" t="str">
         <f>+IF(J103="","",VLOOKUP(J103,Sheet2!$A$96:$C$98,3,TRUE))</f>
         <v/>
       </c>
-      <c r="L103" s="121"/>
-      <c r="M103" s="121"/>
-      <c r="N103" s="121"/>
-      <c r="O103" s="121"/>
+      <c r="L103" s="142"/>
+      <c r="M103" s="142"/>
+      <c r="N103" s="142"/>
+      <c r="O103" s="142"/>
       <c r="P103" s="28" t="str">
         <f>+IF(J103="","",VLOOKUP(J103,Sheet2!$A$96:$C$98,2,TRUE))</f>
         <v/>
@@ -7012,13 +7012,13 @@
       <c r="J105" s="64" t="s">
         <v>38</v>
       </c>
-      <c r="K105" s="120" t="s">
+      <c r="K105" s="143" t="s">
         <v>40</v>
       </c>
-      <c r="L105" s="120"/>
-      <c r="M105" s="120"/>
-      <c r="N105" s="120"/>
-      <c r="O105" s="120"/>
+      <c r="L105" s="143"/>
+      <c r="M105" s="143"/>
+      <c r="N105" s="143"/>
+      <c r="O105" s="143"/>
       <c r="P105" s="60" t="s">
         <v>124</v>
       </c>
@@ -7047,14 +7047,14 @@
       <c r="H107" s="7"/>
       <c r="I107" s="7"/>
       <c r="J107" s="7"/>
-      <c r="K107" s="121" t="str">
+      <c r="K107" s="142" t="str">
         <f>+IF(D108="","",IF(D106&lt;0,Sheet2!$C$104,VLOOKUP(D108,Sheet2!$A$102:$C$104,3,TRUE)))</f>
         <v/>
       </c>
-      <c r="L107" s="121"/>
-      <c r="M107" s="121"/>
-      <c r="N107" s="121"/>
-      <c r="O107" s="121"/>
+      <c r="L107" s="142"/>
+      <c r="M107" s="142"/>
+      <c r="N107" s="142"/>
+      <c r="O107" s="142"/>
       <c r="P107" s="28" t="str">
         <f>+IF(K107="","",VLOOKUP(K107,Sheet2!$C$102:$D$107,2,FALSE))</f>
         <v/>
@@ -7090,14 +7090,14 @@
         <f>+IF(D108="","",AVERAGE(D108:G108))</f>
         <v/>
       </c>
-      <c r="K108" s="136" t="str">
+      <c r="K108" s="144" t="str">
         <f>+IF(J108="","",IF(AND(D106&lt;0,E106&lt;0),Sheet2!$C$107,VLOOKUP(J108,Sheet2!$A$105:$C$107,3,TRUE)))</f>
         <v/>
       </c>
-      <c r="L108" s="136"/>
-      <c r="M108" s="136"/>
-      <c r="N108" s="136"/>
-      <c r="O108" s="136"/>
+      <c r="L108" s="144"/>
+      <c r="M108" s="144"/>
+      <c r="N108" s="144"/>
+      <c r="O108" s="144"/>
       <c r="P108" s="32" t="str">
         <f>+IF(K108="","",VLOOKUP(K108,Sheet2!$C$102:$D$107,2,FALSE))</f>
         <v/>
@@ -7107,40 +7107,40 @@
       <c r="P109" s="10"/>
     </row>
     <row r="110" spans="2:16" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B110" s="122" t="s">
+      <c r="B110" s="123" t="s">
         <v>48</v>
       </c>
-      <c r="C110" s="123"/>
-      <c r="D110" s="123"/>
-      <c r="E110" s="123"/>
-      <c r="F110" s="123"/>
-      <c r="G110" s="123"/>
-      <c r="H110" s="123"/>
-      <c r="I110" s="123"/>
-      <c r="J110" s="123"/>
-      <c r="K110" s="123"/>
-      <c r="L110" s="123"/>
-      <c r="M110" s="123"/>
-      <c r="N110" s="123"/>
-      <c r="O110" s="123"/>
-      <c r="P110" s="124"/>
+      <c r="C110" s="124"/>
+      <c r="D110" s="124"/>
+      <c r="E110" s="124"/>
+      <c r="F110" s="124"/>
+      <c r="G110" s="124"/>
+      <c r="H110" s="124"/>
+      <c r="I110" s="124"/>
+      <c r="J110" s="124"/>
+      <c r="K110" s="124"/>
+      <c r="L110" s="124"/>
+      <c r="M110" s="124"/>
+      <c r="N110" s="124"/>
+      <c r="O110" s="124"/>
+      <c r="P110" s="125"/>
     </row>
     <row r="111" spans="2:16" x14ac:dyDescent="0.25">
-      <c r="B111" s="125"/>
-      <c r="C111" s="126"/>
-      <c r="D111" s="126"/>
-      <c r="E111" s="126"/>
-      <c r="F111" s="126"/>
-      <c r="G111" s="126"/>
-      <c r="H111" s="126"/>
-      <c r="I111" s="126"/>
-      <c r="J111" s="126"/>
-      <c r="K111" s="126"/>
-      <c r="L111" s="126"/>
-      <c r="M111" s="126"/>
-      <c r="N111" s="126"/>
-      <c r="O111" s="126"/>
-      <c r="P111" s="127"/>
+      <c r="B111" s="137"/>
+      <c r="C111" s="135"/>
+      <c r="D111" s="135"/>
+      <c r="E111" s="135"/>
+      <c r="F111" s="135"/>
+      <c r="G111" s="135"/>
+      <c r="H111" s="135"/>
+      <c r="I111" s="135"/>
+      <c r="J111" s="135"/>
+      <c r="K111" s="135"/>
+      <c r="L111" s="135"/>
+      <c r="M111" s="135"/>
+      <c r="N111" s="135"/>
+      <c r="O111" s="135"/>
+      <c r="P111" s="138"/>
     </row>
     <row r="112" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B112" s="65"/>
@@ -7171,13 +7171,13 @@
       <c r="J112" s="64" t="s">
         <v>38</v>
       </c>
-      <c r="K112" s="120" t="s">
+      <c r="K112" s="143" t="s">
         <v>40</v>
       </c>
-      <c r="L112" s="120"/>
-      <c r="M112" s="120"/>
-      <c r="N112" s="120"/>
-      <c r="O112" s="120"/>
+      <c r="L112" s="143"/>
+      <c r="M112" s="143"/>
+      <c r="N112" s="143"/>
+      <c r="O112" s="143"/>
       <c r="P112" s="60" t="s">
         <v>124</v>
       </c>
@@ -7196,14 +7196,14 @@
         <f>+IF(D113="","",SUM(D113:H113))</f>
         <v/>
       </c>
-      <c r="K113" s="121" t="str">
+      <c r="K113" s="142" t="str">
         <f>+IF(D114="","",IF(D113&lt;0,Sheet2!$C$113,VLOOKUP(D114,Sheet2!$A$110:$C$113,3,TRUE)))</f>
         <v/>
       </c>
-      <c r="L113" s="121"/>
-      <c r="M113" s="121"/>
-      <c r="N113" s="121"/>
-      <c r="O113" s="121"/>
+      <c r="L113" s="142"/>
+      <c r="M113" s="142"/>
+      <c r="N113" s="142"/>
+      <c r="O113" s="142"/>
       <c r="P113" s="28" t="str">
         <f>+IF(K113="","",VLOOKUP(K113,Sheet2!$C$110:$D$117,2,FALSE))</f>
         <v/>
@@ -7235,14 +7235,14 @@
       </c>
       <c r="I114" s="7"/>
       <c r="J114" s="7"/>
-      <c r="K114" s="121" t="str">
+      <c r="K114" s="142" t="str">
         <f>+IF(J114="","",IF(AND(D113&lt;0,E113&lt;0),Sheet2!$C$117,VLOOKUP(J114,Sheet2!$A$114:$C$117,3,TRUE)))</f>
         <v/>
       </c>
-      <c r="L114" s="121"/>
-      <c r="M114" s="121"/>
-      <c r="N114" s="121"/>
-      <c r="O114" s="121"/>
+      <c r="L114" s="142"/>
+      <c r="M114" s="142"/>
+      <c r="N114" s="142"/>
+      <c r="O114" s="142"/>
       <c r="P114" s="28" t="str">
         <f>+IF(K114="","",VLOOKUP(K114,Sheet2!$C$110:$D$117,2,FALSE))</f>
         <v/>
@@ -7288,13 +7288,13 @@
       <c r="J116" s="64" t="s">
         <v>38</v>
       </c>
-      <c r="K116" s="120" t="s">
+      <c r="K116" s="143" t="s">
         <v>40</v>
       </c>
-      <c r="L116" s="120"/>
-      <c r="M116" s="120"/>
-      <c r="N116" s="120"/>
-      <c r="O116" s="120"/>
+      <c r="L116" s="143"/>
+      <c r="M116" s="143"/>
+      <c r="N116" s="143"/>
+      <c r="O116" s="143"/>
       <c r="P116" s="60" t="s">
         <v>124</v>
       </c>
@@ -7310,14 +7310,14 @@
       <c r="H117" s="7"/>
       <c r="I117" s="7"/>
       <c r="J117" s="7"/>
-      <c r="K117" s="121" t="str">
+      <c r="K117" s="142" t="str">
         <f>+IF(D118="","",IF(D117&lt;0,Sheet2!$C$27,VLOOKUP(D118,Sheet2!$A$27:$C$31,3,TRUE)))</f>
         <v/>
       </c>
-      <c r="L117" s="121"/>
-      <c r="M117" s="121"/>
-      <c r="N117" s="121"/>
-      <c r="O117" s="121"/>
+      <c r="L117" s="142"/>
+      <c r="M117" s="142"/>
+      <c r="N117" s="142"/>
+      <c r="O117" s="142"/>
       <c r="P117" s="28" t="str">
         <f>+IF(K117="","",VLOOKUP(K117,Sheet2!$C$27:$D$31,2,FALSE))</f>
         <v/>
@@ -7349,14 +7349,14 @@
         <f>+IF(D118="","",AVERAGE(D118:G118))</f>
         <v/>
       </c>
-      <c r="K118" s="121" t="str">
+      <c r="K118" s="142" t="str">
         <f>+IF(J118="","",IF(AND(D117&lt;0,E117&lt;0),Sheet2!$C$35,VLOOKUP(J118,Sheet2!$A$35:$C$39,3,TRUE)))</f>
         <v/>
       </c>
-      <c r="L118" s="121"/>
-      <c r="M118" s="121"/>
-      <c r="N118" s="121"/>
-      <c r="O118" s="121"/>
+      <c r="L118" s="142"/>
+      <c r="M118" s="142"/>
+      <c r="N118" s="142"/>
+      <c r="O118" s="142"/>
       <c r="P118" s="28" t="str">
         <f>+IF(K118="","",VLOOKUP(K118,Sheet2!$C$35:$D$39,2,FALSE))</f>
         <v/>
@@ -7403,13 +7403,13 @@
       <c r="J120" s="64" t="s">
         <v>38</v>
       </c>
-      <c r="K120" s="120" t="s">
+      <c r="K120" s="143" t="s">
         <v>40</v>
       </c>
-      <c r="L120" s="120"/>
-      <c r="M120" s="120"/>
-      <c r="N120" s="120"/>
-      <c r="O120" s="120"/>
+      <c r="L120" s="143"/>
+      <c r="M120" s="143"/>
+      <c r="N120" s="143"/>
+      <c r="O120" s="143"/>
       <c r="P120" s="60" t="s">
         <v>124</v>
       </c>
@@ -7425,14 +7425,14 @@
       <c r="H121" s="7"/>
       <c r="I121" s="7"/>
       <c r="J121" s="7"/>
-      <c r="K121" s="121" t="str">
+      <c r="K121" s="142" t="str">
         <f>+IF(D122="","",IF(D121&lt;0,Sheet2!$C$27,VLOOKUP(D122,Sheet2!$A$27:$C$31,3,TRUE)))</f>
         <v/>
       </c>
-      <c r="L121" s="121"/>
-      <c r="M121" s="121"/>
-      <c r="N121" s="121"/>
-      <c r="O121" s="121"/>
+      <c r="L121" s="142"/>
+      <c r="M121" s="142"/>
+      <c r="N121" s="142"/>
+      <c r="O121" s="142"/>
       <c r="P121" s="28" t="str">
         <f>+IF(K121="","",VLOOKUP(K121,Sheet2!$C$27:$D$31,2,FALSE))</f>
         <v/>
@@ -7464,14 +7464,14 @@
         <f>+IF(D122="","",AVERAGE(D122:G122))</f>
         <v/>
       </c>
-      <c r="K122" s="121" t="str">
+      <c r="K122" s="142" t="str">
         <f>+IF(J122="","",IF(AND(D121&lt;0,E121&lt;0),Sheet2!$C$35,VLOOKUP(J122,Sheet2!$A$35:$C$39,3,TRUE)))</f>
         <v/>
       </c>
-      <c r="L122" s="121"/>
-      <c r="M122" s="121"/>
-      <c r="N122" s="121"/>
-      <c r="O122" s="121"/>
+      <c r="L122" s="142"/>
+      <c r="M122" s="142"/>
+      <c r="N122" s="142"/>
+      <c r="O122" s="142"/>
       <c r="P122" s="28" t="str">
         <f>+IF(K122="","",VLOOKUP(K122,Sheet2!$C$35:$D$39,2,FALSE))</f>
         <v/>
@@ -7518,13 +7518,13 @@
       <c r="J124" s="64" t="s">
         <v>38</v>
       </c>
-      <c r="K124" s="120" t="s">
+      <c r="K124" s="143" t="s">
         <v>40</v>
       </c>
-      <c r="L124" s="120"/>
-      <c r="M124" s="120"/>
-      <c r="N124" s="120"/>
-      <c r="O124" s="120"/>
+      <c r="L124" s="143"/>
+      <c r="M124" s="143"/>
+      <c r="N124" s="143"/>
+      <c r="O124" s="143"/>
       <c r="P124" s="60" t="s">
         <v>124</v>
       </c>
@@ -7553,14 +7553,14 @@
       <c r="H126" s="7"/>
       <c r="I126" s="7"/>
       <c r="J126" s="7"/>
-      <c r="K126" s="121" t="str">
+      <c r="K126" s="142" t="str">
         <f>+IF(D127="","",IF(D127&lt;0,"Company rebought its stocks in the last year.","Company didn't rebought its stocks in the last year."))</f>
         <v/>
       </c>
-      <c r="L126" s="121"/>
-      <c r="M126" s="121"/>
-      <c r="N126" s="121"/>
-      <c r="O126" s="121"/>
+      <c r="L126" s="142"/>
+      <c r="M126" s="142"/>
+      <c r="N126" s="142"/>
+      <c r="O126" s="142"/>
       <c r="P126" s="28" t="str">
         <f>+IF(D127="","",IF(D127&lt;0,5,1))</f>
         <v/>
@@ -7595,14 +7595,14 @@
         <f>+IF(D127="","",AVERAGE(D127:H127))</f>
         <v/>
       </c>
-      <c r="K127" s="121" t="str">
+      <c r="K127" s="142" t="str">
         <f>+IF(J127="","",IF(J127&lt;0,"Company usually rebuy its stocks","Company usually don't rebuy its stocks"))</f>
         <v/>
       </c>
-      <c r="L127" s="121"/>
-      <c r="M127" s="121"/>
-      <c r="N127" s="121"/>
-      <c r="O127" s="121"/>
+      <c r="L127" s="142"/>
+      <c r="M127" s="142"/>
+      <c r="N127" s="142"/>
+      <c r="O127" s="142"/>
       <c r="P127" s="28" t="str">
         <f>+IF(J127="","",IF(J127&lt;0,5,1))</f>
         <v/>
@@ -7627,40 +7627,40 @@
     </row>
     <row r="129" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="130" spans="2:16" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B130" s="122" t="s">
+      <c r="B130" s="123" t="s">
         <v>50</v>
       </c>
-      <c r="C130" s="123"/>
-      <c r="D130" s="123"/>
-      <c r="E130" s="123"/>
-      <c r="F130" s="123"/>
-      <c r="G130" s="123"/>
-      <c r="H130" s="123"/>
-      <c r="I130" s="123"/>
-      <c r="J130" s="123"/>
-      <c r="K130" s="123"/>
-      <c r="L130" s="123"/>
-      <c r="M130" s="123"/>
-      <c r="N130" s="123"/>
-      <c r="O130" s="123"/>
-      <c r="P130" s="124"/>
+      <c r="C130" s="124"/>
+      <c r="D130" s="124"/>
+      <c r="E130" s="124"/>
+      <c r="F130" s="124"/>
+      <c r="G130" s="124"/>
+      <c r="H130" s="124"/>
+      <c r="I130" s="124"/>
+      <c r="J130" s="124"/>
+      <c r="K130" s="124"/>
+      <c r="L130" s="124"/>
+      <c r="M130" s="124"/>
+      <c r="N130" s="124"/>
+      <c r="O130" s="124"/>
+      <c r="P130" s="125"/>
     </row>
     <row r="131" spans="2:16" x14ac:dyDescent="0.25">
-      <c r="B131" s="125"/>
-      <c r="C131" s="126"/>
-      <c r="D131" s="126"/>
-      <c r="E131" s="126"/>
-      <c r="F131" s="126"/>
-      <c r="G131" s="126"/>
-      <c r="H131" s="126"/>
-      <c r="I131" s="126"/>
-      <c r="J131" s="126"/>
-      <c r="K131" s="126"/>
-      <c r="L131" s="126"/>
-      <c r="M131" s="126"/>
-      <c r="N131" s="126"/>
-      <c r="O131" s="126"/>
-      <c r="P131" s="127"/>
+      <c r="B131" s="137"/>
+      <c r="C131" s="135"/>
+      <c r="D131" s="135"/>
+      <c r="E131" s="135"/>
+      <c r="F131" s="135"/>
+      <c r="G131" s="135"/>
+      <c r="H131" s="135"/>
+      <c r="I131" s="135"/>
+      <c r="J131" s="135"/>
+      <c r="K131" s="135"/>
+      <c r="L131" s="135"/>
+      <c r="M131" s="135"/>
+      <c r="N131" s="135"/>
+      <c r="O131" s="135"/>
+      <c r="P131" s="138"/>
     </row>
     <row r="132" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B132" s="65"/>
@@ -7691,13 +7691,13 @@
       <c r="J132" s="64" t="s">
         <v>38</v>
       </c>
-      <c r="K132" s="120" t="s">
+      <c r="K132" s="143" t="s">
         <v>40</v>
       </c>
-      <c r="L132" s="120"/>
-      <c r="M132" s="120"/>
-      <c r="N132" s="120"/>
-      <c r="O132" s="120"/>
+      <c r="L132" s="143"/>
+      <c r="M132" s="143"/>
+      <c r="N132" s="143"/>
+      <c r="O132" s="143"/>
       <c r="P132" s="60" t="s">
         <v>124</v>
       </c>
@@ -7714,14 +7714,14 @@
       <c r="H133" s="7"/>
       <c r="I133" s="7"/>
       <c r="J133" s="7"/>
-      <c r="K133" s="121" t="str">
+      <c r="K133" s="142" t="str">
         <f>+IF(D134="","",IF(D133&lt;0,Sheet2!$C$121,VLOOKUP(D134,Sheet2!$A$121:$C$125,3,TRUE)))</f>
         <v/>
       </c>
-      <c r="L133" s="121"/>
-      <c r="M133" s="121"/>
-      <c r="N133" s="121"/>
-      <c r="O133" s="121"/>
+      <c r="L133" s="142"/>
+      <c r="M133" s="142"/>
+      <c r="N133" s="142"/>
+      <c r="O133" s="142"/>
       <c r="P133" s="28" t="str">
         <f>+IF(K133="","",VLOOKUP(K133,Sheet2!$C$121:$D$131,2,FALSE))</f>
         <v/>
@@ -7757,14 +7757,14 @@
         <f>+IF(D134="","",AVERAGE(D134:G134))</f>
         <v/>
       </c>
-      <c r="K134" s="121" t="str">
+      <c r="K134" s="142" t="str">
         <f>+IF(J134="","",IF(AND(D133&lt;0,E133&lt;0),Sheet2!$C$127,VLOOKUP(J134,Sheet2!$A$127:$C$131,3,TRUE)))</f>
         <v/>
       </c>
-      <c r="L134" s="121"/>
-      <c r="M134" s="121"/>
-      <c r="N134" s="121"/>
-      <c r="O134" s="121"/>
+      <c r="L134" s="142"/>
+      <c r="M134" s="142"/>
+      <c r="N134" s="142"/>
+      <c r="O134" s="142"/>
       <c r="P134" s="28" t="str">
         <f>+IF(K134="","",VLOOKUP(K134,Sheet2!$C$121:$D$131,2,FALSE))</f>
         <v/>
@@ -7794,14 +7794,14 @@
       <c r="H136" s="7"/>
       <c r="I136" s="7"/>
       <c r="J136" s="7"/>
-      <c r="K136" s="121" t="str">
+      <c r="K136" s="142" t="str">
         <f>+IF(C136="","",IF(C136&gt;C133,Sheet2!$A$133,Sheet2!$A$134))</f>
         <v/>
       </c>
-      <c r="L136" s="121"/>
-      <c r="M136" s="121"/>
-      <c r="N136" s="121"/>
-      <c r="O136" s="121"/>
+      <c r="L136" s="142"/>
+      <c r="M136" s="142"/>
+      <c r="N136" s="142"/>
+      <c r="O136" s="142"/>
       <c r="P136" s="56" t="str">
         <f>+IF(K136="","",VLOOKUP(K136,Sheet2!$A$133:$B$134,2,FALSE))</f>
         <v/>
@@ -7848,13 +7848,13 @@
       <c r="J138" s="64" t="s">
         <v>38</v>
       </c>
-      <c r="K138" s="120" t="s">
+      <c r="K138" s="143" t="s">
         <v>40</v>
       </c>
-      <c r="L138" s="120"/>
-      <c r="M138" s="120"/>
-      <c r="N138" s="120"/>
-      <c r="O138" s="120"/>
+      <c r="L138" s="143"/>
+      <c r="M138" s="143"/>
+      <c r="N138" s="143"/>
+      <c r="O138" s="143"/>
       <c r="P138" s="60" t="s">
         <v>124</v>
       </c>
@@ -7874,14 +7874,14 @@
         <f>+IF(D139="","",AVERAGE(D139:H139))</f>
         <v/>
       </c>
-      <c r="K139" s="121" t="str">
+      <c r="K139" s="142" t="str">
         <f>+IF(C139="","",VLOOKUP(C139,Sheet2!$A$138:$C$145,3,TRUE))</f>
         <v/>
       </c>
-      <c r="L139" s="121"/>
-      <c r="M139" s="121"/>
-      <c r="N139" s="121"/>
-      <c r="O139" s="121"/>
+      <c r="L139" s="142"/>
+      <c r="M139" s="142"/>
+      <c r="N139" s="142"/>
+      <c r="O139" s="142"/>
       <c r="P139" s="28" t="str">
         <f>+IF(C139="","",VLOOKUP(C139,Sheet2!$A$138:$C$145,2,TRUE))</f>
         <v/>
@@ -7915,14 +7915,14 @@
         <f>+IF(D140="","",AVERAGE(D140:G140))</f>
         <v/>
       </c>
-      <c r="K140" s="121" t="str">
+      <c r="K140" s="142" t="str">
         <f>+IF(J139="","",VLOOKUP(J139,Sheet2!$A$147:$C$153,3,TRUE))</f>
         <v/>
       </c>
-      <c r="L140" s="121"/>
-      <c r="M140" s="121"/>
-      <c r="N140" s="121"/>
-      <c r="O140" s="121"/>
+      <c r="L140" s="142"/>
+      <c r="M140" s="142"/>
+      <c r="N140" s="142"/>
+      <c r="O140" s="142"/>
       <c r="P140" s="28" t="str">
         <f>+IF(J139="","",VLOOKUP(J139,Sheet2!$A$147:$C$153,2,TRUE))</f>
         <v/>
@@ -7938,14 +7938,14 @@
       <c r="H141" s="7"/>
       <c r="I141" s="7"/>
       <c r="J141" s="7"/>
-      <c r="K141" s="121" t="str">
+      <c r="K141" s="142" t="str">
         <f>+IF(C139="","",IF(C139&lt;$C$203,Sheet2!$A$155,IF(C139&lt;($C$203*1.1),Sheet2!$A$156,IF(C139&lt;($C$203*1.2),Sheet2!$A$157,Sheet2!A158))))</f>
         <v/>
       </c>
-      <c r="L141" s="121"/>
-      <c r="M141" s="121"/>
-      <c r="N141" s="121"/>
-      <c r="O141" s="121"/>
+      <c r="L141" s="142"/>
+      <c r="M141" s="142"/>
+      <c r="N141" s="142"/>
+      <c r="O141" s="142"/>
       <c r="P141" s="56" t="str">
         <f>+IF(K141="","",VLOOKUP(K141,Sheet2!$A$155:$B$158,2,FALSE))</f>
         <v/>
@@ -7963,14 +7963,14 @@
       <c r="H142" s="7"/>
       <c r="I142" s="7"/>
       <c r="J142" s="7"/>
-      <c r="K142" s="121" t="str">
+      <c r="K142" s="142" t="str">
         <f>+IF(C142="","",IF(C142&gt;C139,Sheet2!$A$161,Sheet2!$A$160))</f>
         <v/>
       </c>
-      <c r="L142" s="121"/>
-      <c r="M142" s="121"/>
-      <c r="N142" s="121"/>
-      <c r="O142" s="121"/>
+      <c r="L142" s="142"/>
+      <c r="M142" s="142"/>
+      <c r="N142" s="142"/>
+      <c r="O142" s="142"/>
       <c r="P142" s="56" t="str">
         <f>+IF(K142="","",VLOOKUP(K142,Sheet2!$A$160:$B$161,2,FALSE))</f>
         <v/>
@@ -8017,13 +8017,13 @@
       <c r="J144" s="64" t="s">
         <v>38</v>
       </c>
-      <c r="K144" s="120" t="s">
+      <c r="K144" s="143" t="s">
         <v>40</v>
       </c>
-      <c r="L144" s="120"/>
-      <c r="M144" s="120"/>
-      <c r="N144" s="120"/>
-      <c r="O144" s="120"/>
+      <c r="L144" s="143"/>
+      <c r="M144" s="143"/>
+      <c r="N144" s="143"/>
+      <c r="O144" s="143"/>
       <c r="P144" s="60" t="s">
         <v>124</v>
       </c>
@@ -8040,14 +8040,14 @@
       <c r="H145" s="7"/>
       <c r="I145" s="7"/>
       <c r="J145" s="7"/>
-      <c r="K145" s="121" t="str">
+      <c r="K145" s="142" t="str">
         <f>+IF(C145="","",VLOOKUP(C145,Sheet2!$A$138:$C$145,3,TRUE))</f>
         <v/>
       </c>
-      <c r="L145" s="121"/>
-      <c r="M145" s="121"/>
-      <c r="N145" s="121"/>
-      <c r="O145" s="121"/>
+      <c r="L145" s="142"/>
+      <c r="M145" s="142"/>
+      <c r="N145" s="142"/>
+      <c r="O145" s="142"/>
       <c r="P145" s="28" t="str">
         <f>+IF(C145="","",VLOOKUP(C145,Sheet2!$A$138:$C$145,2,TRUE))</f>
         <v/>
@@ -8081,14 +8081,14 @@
         <f>+IF(D146="","",AVERAGE(D146:G146))</f>
         <v/>
       </c>
-      <c r="K146" s="121" t="str">
+      <c r="K146" s="142" t="str">
         <f>+IF(C145="","",IF(C145&lt;$D$203,Sheet2!$A$155,IF(C145&lt;($D$203*1.1),Sheet2!$A$156,IF(C145&lt;($D$203*1.2),Sheet2!$A$157,Sheet2!A158))))</f>
         <v/>
       </c>
-      <c r="L146" s="121"/>
-      <c r="M146" s="121"/>
-      <c r="N146" s="121"/>
-      <c r="O146" s="121"/>
+      <c r="L146" s="142"/>
+      <c r="M146" s="142"/>
+      <c r="N146" s="142"/>
+      <c r="O146" s="142"/>
       <c r="P146" s="56" t="str">
         <f>+IF(K146="","",VLOOKUP(K146,Sheet2!$A$155:$B$158,2,FALSE))</f>
         <v/>
@@ -8135,13 +8135,13 @@
       <c r="J148" s="64" t="s">
         <v>38</v>
       </c>
-      <c r="K148" s="120" t="s">
+      <c r="K148" s="143" t="s">
         <v>40</v>
       </c>
-      <c r="L148" s="120"/>
-      <c r="M148" s="120"/>
-      <c r="N148" s="120"/>
-      <c r="O148" s="120"/>
+      <c r="L148" s="143"/>
+      <c r="M148" s="143"/>
+      <c r="N148" s="143"/>
+      <c r="O148" s="143"/>
       <c r="P148" s="60" t="s">
         <v>124</v>
       </c>
@@ -8158,14 +8158,14 @@
       <c r="H149" s="7"/>
       <c r="I149" s="7"/>
       <c r="J149" s="7"/>
-      <c r="K149" s="121" t="str">
+      <c r="K149" s="142" t="str">
         <f>+IF(C149="","",VLOOKUP(C149,Sheet2!$A$164:$C$170,3,TRUE))</f>
         <v/>
       </c>
-      <c r="L149" s="121"/>
-      <c r="M149" s="121"/>
-      <c r="N149" s="121"/>
-      <c r="O149" s="121"/>
+      <c r="L149" s="142"/>
+      <c r="M149" s="142"/>
+      <c r="N149" s="142"/>
+      <c r="O149" s="142"/>
       <c r="P149" s="28" t="str">
         <f>+IF(C149="","",VLOOKUP(C149,Sheet2!$A$164:$C$170,2,TRUE))</f>
         <v/>
@@ -8199,14 +8199,14 @@
         <f>+IF(D150="","",AVERAGE(D150:G150))</f>
         <v/>
       </c>
-      <c r="K150" s="121" t="str">
+      <c r="K150" s="142" t="str">
         <f>+IF(C149="","",IF(C149&lt;$E$203,Sheet2!$A$155,IF(C149&lt;($E$203*1.1),Sheet2!$A$156,IF(C149&lt;($E$203*1.2),Sheet2!$A$157,Sheet2!A158))))</f>
         <v/>
       </c>
-      <c r="L150" s="121"/>
-      <c r="M150" s="121"/>
-      <c r="N150" s="121"/>
-      <c r="O150" s="121"/>
+      <c r="L150" s="142"/>
+      <c r="M150" s="142"/>
+      <c r="N150" s="142"/>
+      <c r="O150" s="142"/>
       <c r="P150" s="56" t="str">
         <f>+IF(K150="","",VLOOKUP(K150,Sheet2!$A$155:$B$158,2,FALSE))</f>
         <v/>
@@ -8253,13 +8253,13 @@
       <c r="J152" s="64" t="s">
         <v>38</v>
       </c>
-      <c r="K152" s="120" t="s">
+      <c r="K152" s="143" t="s">
         <v>40</v>
       </c>
-      <c r="L152" s="120"/>
-      <c r="M152" s="120"/>
-      <c r="N152" s="120"/>
-      <c r="O152" s="120"/>
+      <c r="L152" s="143"/>
+      <c r="M152" s="143"/>
+      <c r="N152" s="143"/>
+      <c r="O152" s="143"/>
       <c r="P152" s="60" t="s">
         <v>124</v>
       </c>
@@ -8276,11 +8276,11 @@
       <c r="H153" s="7"/>
       <c r="I153" s="7"/>
       <c r="J153" s="7"/>
-      <c r="K153" s="121"/>
-      <c r="L153" s="121"/>
-      <c r="M153" s="121"/>
-      <c r="N153" s="121"/>
-      <c r="O153" s="121"/>
+      <c r="K153" s="142"/>
+      <c r="L153" s="142"/>
+      <c r="M153" s="142"/>
+      <c r="N153" s="142"/>
+      <c r="O153" s="142"/>
       <c r="P153" s="28"/>
     </row>
     <row r="154" spans="2:16" x14ac:dyDescent="0.25">
@@ -8311,14 +8311,14 @@
         <f>+IF(D154="","",AVERAGE(D154:G154))</f>
         <v/>
       </c>
-      <c r="K154" s="121" t="str">
+      <c r="K154" s="142" t="str">
         <f>+IF(C153="","",IF(C153&lt;$F$203,Sheet2!$A$155,IF(C153&lt;($F$203*1.1),Sheet2!$A$156,IF(C153&lt;($F$203*1.2),Sheet2!$A$157,Sheet2!A158))))</f>
         <v/>
       </c>
-      <c r="L154" s="121"/>
-      <c r="M154" s="121"/>
-      <c r="N154" s="121"/>
-      <c r="O154" s="121"/>
+      <c r="L154" s="142"/>
+      <c r="M154" s="142"/>
+      <c r="N154" s="142"/>
+      <c r="O154" s="142"/>
       <c r="P154" s="56" t="str">
         <f>+IF(K154="","",VLOOKUP(K154,Sheet2!$A$155:$B$158,2,FALSE))</f>
         <v/>
@@ -8365,13 +8365,13 @@
       <c r="J156" s="64" t="s">
         <v>38</v>
       </c>
-      <c r="K156" s="120" t="s">
+      <c r="K156" s="143" t="s">
         <v>40</v>
       </c>
-      <c r="L156" s="120"/>
-      <c r="M156" s="120"/>
-      <c r="N156" s="120"/>
-      <c r="O156" s="120"/>
+      <c r="L156" s="143"/>
+      <c r="M156" s="143"/>
+      <c r="N156" s="143"/>
+      <c r="O156" s="143"/>
       <c r="P156" s="60" t="s">
         <v>124</v>
       </c>
@@ -8388,14 +8388,14 @@
       <c r="H157" s="7"/>
       <c r="I157" s="7"/>
       <c r="J157" s="7"/>
-      <c r="K157" s="121" t="str">
+      <c r="K157" s="142" t="str">
         <f>+IF(C157="","",VLOOKUP(C157,Sheet2!$A$173:$C$179,3,TRUE))</f>
         <v/>
       </c>
-      <c r="L157" s="121"/>
-      <c r="M157" s="121"/>
-      <c r="N157" s="121"/>
-      <c r="O157" s="121"/>
+      <c r="L157" s="142"/>
+      <c r="M157" s="142"/>
+      <c r="N157" s="142"/>
+      <c r="O157" s="142"/>
       <c r="P157" s="28" t="str">
         <f>+IF(C157="","",VLOOKUP(C157,Sheet2!$A$173:$C$179,2,TRUE))</f>
         <v/>
@@ -8429,14 +8429,14 @@
         <f>+IF(D158="","",AVERAGE(D158:G158))</f>
         <v/>
       </c>
-      <c r="K158" s="121" t="str">
+      <c r="K158" s="142" t="str">
         <f>+IF(C157="","",IF(C157&lt;$G$203,Sheet2!$A$155,IF(C157&lt;($G$203*1.1),Sheet2!$A$156,IF(C157&lt;($G$203*1.2),Sheet2!$A$157,Sheet2!A158))))</f>
         <v/>
       </c>
-      <c r="L158" s="121"/>
-      <c r="M158" s="121"/>
-      <c r="N158" s="121"/>
-      <c r="O158" s="121"/>
+      <c r="L158" s="142"/>
+      <c r="M158" s="142"/>
+      <c r="N158" s="142"/>
+      <c r="O158" s="142"/>
       <c r="P158" s="56" t="str">
         <f>+IF(K158="","",VLOOKUP(K158,Sheet2!$A$155:$B$158,2,FALSE))</f>
         <v/>
@@ -8466,13 +8466,13 @@
       <c r="H160" s="66"/>
       <c r="I160" s="66"/>
       <c r="J160" s="66"/>
-      <c r="K160" s="120" t="s">
+      <c r="K160" s="143" t="s">
         <v>40</v>
       </c>
-      <c r="L160" s="120"/>
-      <c r="M160" s="120"/>
-      <c r="N160" s="120"/>
-      <c r="O160" s="120"/>
+      <c r="L160" s="143"/>
+      <c r="M160" s="143"/>
+      <c r="N160" s="143"/>
+      <c r="O160" s="143"/>
       <c r="P160" s="60" t="s">
         <v>124</v>
       </c>
@@ -8492,14 +8492,14 @@
       <c r="H161" s="7"/>
       <c r="I161" s="7"/>
       <c r="J161" s="7"/>
-      <c r="K161" s="121" t="str">
+      <c r="K161" s="142" t="str">
         <f>+IF(C161="","",IF(C161&gt;($J$203*1.1),Sheet2!$A$182,IF(Sheet1!C161&gt;(Sheet1!$J$203*0.8),Sheet2!A183,IF(Sheet1!C161&gt;(Sheet1!J203*0.6),Sheet2!A184,Sheet2!A185))))</f>
         <v/>
       </c>
-      <c r="L161" s="121"/>
-      <c r="M161" s="121"/>
-      <c r="N161" s="121"/>
-      <c r="O161" s="121"/>
+      <c r="L161" s="142"/>
+      <c r="M161" s="142"/>
+      <c r="N161" s="142"/>
+      <c r="O161" s="142"/>
       <c r="P161" s="56" t="str">
         <f>+IF(K161="","",VLOOKUP(K161,Sheet2!$A$182:$B$185,2,FALSE))</f>
         <v/>
@@ -8520,14 +8520,14 @@
       <c r="H162" s="7"/>
       <c r="I162" s="7"/>
       <c r="J162" s="7"/>
-      <c r="K162" s="121" t="str">
+      <c r="K162" s="142" t="str">
         <f>+IF(C162="","",IF(C162&gt;($K$203*1.1),Sheet2!$A$182,IF(Sheet1!C162&gt;(Sheet1!$K$203*0.8),Sheet2!A183,IF(Sheet1!C162&gt;(Sheet1!K203*0.6),Sheet2!A184,Sheet2!A185))))</f>
         <v/>
       </c>
-      <c r="L162" s="121"/>
-      <c r="M162" s="121"/>
-      <c r="N162" s="121"/>
-      <c r="O162" s="121"/>
+      <c r="L162" s="142"/>
+      <c r="M162" s="142"/>
+      <c r="N162" s="142"/>
+      <c r="O162" s="142"/>
       <c r="P162" s="56" t="str">
         <f>+IF(K162="","",VLOOKUP(K162,Sheet2!$A$182:$B$185,2,FALSE))</f>
         <v/>
@@ -8574,13 +8574,13 @@
       <c r="J164" s="64" t="s">
         <v>38</v>
       </c>
-      <c r="K164" s="120" t="s">
+      <c r="K164" s="143" t="s">
         <v>40</v>
       </c>
-      <c r="L164" s="120"/>
-      <c r="M164" s="120"/>
-      <c r="N164" s="120"/>
-      <c r="O164" s="120"/>
+      <c r="L164" s="143"/>
+      <c r="M164" s="143"/>
+      <c r="N164" s="143"/>
+      <c r="O164" s="143"/>
       <c r="P164" s="60" t="s">
         <v>124</v>
       </c>
@@ -8600,14 +8600,14 @@
         <f>+IF(D165="","",AVERAGE(D165:H165))</f>
         <v/>
       </c>
-      <c r="K165" s="121" t="str">
+      <c r="K165" s="142" t="str">
         <f>+IF(C165="","",VLOOKUP(C165,Sheet2!$A$189:$C$195,3,TRUE))</f>
         <v/>
       </c>
-      <c r="L165" s="121"/>
-      <c r="M165" s="121"/>
-      <c r="N165" s="121"/>
-      <c r="O165" s="121"/>
+      <c r="L165" s="142"/>
+      <c r="M165" s="142"/>
+      <c r="N165" s="142"/>
+      <c r="O165" s="142"/>
       <c r="P165" s="28" t="str">
         <f>+IF(C165="","",VLOOKUP(C165,Sheet2!$A$189:$C$195,2,TRUE))</f>
         <v/>
@@ -8638,14 +8638,14 @@
       <c r="H166" s="7"/>
       <c r="I166" s="7"/>
       <c r="J166" s="5"/>
-      <c r="K166" s="121" t="str">
+      <c r="K166" s="142" t="str">
         <f>+IF(J165="","",VLOOKUP(J165,Sheet2!$A$198:$C$204,3,TRUE))</f>
         <v/>
       </c>
-      <c r="L166" s="121"/>
-      <c r="M166" s="121"/>
-      <c r="N166" s="121"/>
-      <c r="O166" s="121"/>
+      <c r="L166" s="142"/>
+      <c r="M166" s="142"/>
+      <c r="N166" s="142"/>
+      <c r="O166" s="142"/>
       <c r="P166" s="28" t="str">
         <f>+IF(J165="","",VLOOKUP(J165,Sheet2!$A$198:$C$204,2,TRUE))</f>
         <v/>
@@ -8661,14 +8661,14 @@
       <c r="H167" s="7"/>
       <c r="I167" s="7"/>
       <c r="J167" s="7"/>
-      <c r="K167" s="121" t="str">
+      <c r="K167" s="142" t="str">
         <f>+IF(C165="","",IF(C165&gt;(1.15*$L$203),Sheet2!$A$206,IF(Sheet1!C165&gt;Sheet1!$L$203,Sheet2!$A$207,IF(Sheet1!C165&gt;(0.7*Sheet1!$L$203),Sheet2!$A$208,IF(Sheet1!C165&gt;(0.6*Sheet1!$L$203),Sheet2!$A$209,Sheet2!$A$210)))))</f>
         <v/>
       </c>
-      <c r="L167" s="121"/>
-      <c r="M167" s="121"/>
-      <c r="N167" s="121"/>
-      <c r="O167" s="121"/>
+      <c r="L167" s="142"/>
+      <c r="M167" s="142"/>
+      <c r="N167" s="142"/>
+      <c r="O167" s="142"/>
       <c r="P167" s="56" t="str">
         <f>+IF(K167="","",VLOOKUP(K167,Sheet2!$A$206:$B$210,2,FALSE))</f>
         <v/>
@@ -8720,13 +8720,13 @@
       <c r="J169" s="64" t="s">
         <v>38</v>
       </c>
-      <c r="K169" s="120" t="s">
+      <c r="K169" s="143" t="s">
         <v>40</v>
       </c>
-      <c r="L169" s="120"/>
-      <c r="M169" s="120"/>
-      <c r="N169" s="120"/>
-      <c r="O169" s="120"/>
+      <c r="L169" s="143"/>
+      <c r="M169" s="143"/>
+      <c r="N169" s="143"/>
+      <c r="O169" s="143"/>
       <c r="P169" s="60" t="s">
         <v>124</v>
       </c>
@@ -8746,14 +8746,14 @@
         <f>+IF(D170="","",AVERAGE(D170:H170))</f>
         <v/>
       </c>
-      <c r="K170" s="121" t="str">
+      <c r="K170" s="142" t="str">
         <f>+IF(C170="","",VLOOKUP(C170,Sheet2!$A$189:$C$195,3,TRUE))</f>
         <v/>
       </c>
-      <c r="L170" s="121"/>
-      <c r="M170" s="121"/>
-      <c r="N170" s="121"/>
-      <c r="O170" s="121"/>
+      <c r="L170" s="142"/>
+      <c r="M170" s="142"/>
+      <c r="N170" s="142"/>
+      <c r="O170" s="142"/>
       <c r="P170" s="28" t="str">
         <f>+IF(C170="","",VLOOKUP(C170,Sheet2!$A$189:$C$195,2,TRUE))</f>
         <v/>
@@ -8786,14 +8786,14 @@
       <c r="H171" s="7"/>
       <c r="I171" s="7"/>
       <c r="J171" s="5"/>
-      <c r="K171" s="121" t="str">
+      <c r="K171" s="142" t="str">
         <f>+IF(J170="","",VLOOKUP(J170,Sheet2!$A$198:$C$204,3,TRUE))</f>
         <v/>
       </c>
-      <c r="L171" s="121"/>
-      <c r="M171" s="121"/>
-      <c r="N171" s="121"/>
-      <c r="O171" s="121"/>
+      <c r="L171" s="142"/>
+      <c r="M171" s="142"/>
+      <c r="N171" s="142"/>
+      <c r="O171" s="142"/>
       <c r="P171" s="28" t="str">
         <f>+IF(J170="","",VLOOKUP(J170,Sheet2!$A$198:$C$204,2,TRUE))</f>
         <v/>
@@ -8809,14 +8809,14 @@
       <c r="H172" s="7"/>
       <c r="I172" s="7"/>
       <c r="J172" s="7"/>
-      <c r="K172" s="121" t="str">
+      <c r="K172" s="142" t="str">
         <f>+IF(C170="","",IF(C170&gt;(1.15*$M$203),Sheet2!$A$206,IF(Sheet1!C170&gt;Sheet1!$M$203,Sheet2!$A$207,IF(Sheet1!C170&gt;(0.7*Sheet1!$M$203),Sheet2!$A$208,IF(Sheet1!C170&gt;(0.6*Sheet1!$M$203),Sheet2!$A$209,Sheet2!$A$210)))))</f>
         <v/>
       </c>
-      <c r="L172" s="121"/>
-      <c r="M172" s="121"/>
-      <c r="N172" s="121"/>
-      <c r="O172" s="121"/>
+      <c r="L172" s="142"/>
+      <c r="M172" s="142"/>
+      <c r="N172" s="142"/>
+      <c r="O172" s="142"/>
       <c r="P172" s="56" t="str">
         <f>+IF(K172="","",VLOOKUP(K172,Sheet2!$A$206:$B$210,2,FALSE))</f>
         <v/>
@@ -8863,13 +8863,13 @@
       <c r="J174" s="64" t="s">
         <v>38</v>
       </c>
-      <c r="K174" s="120" t="s">
+      <c r="K174" s="143" t="s">
         <v>40</v>
       </c>
-      <c r="L174" s="120"/>
-      <c r="M174" s="120"/>
-      <c r="N174" s="120"/>
-      <c r="O174" s="120"/>
+      <c r="L174" s="143"/>
+      <c r="M174" s="143"/>
+      <c r="N174" s="143"/>
+      <c r="O174" s="143"/>
       <c r="P174" s="60" t="s">
         <v>124</v>
       </c>
@@ -8889,14 +8889,14 @@
         <f>+IF(D175="","",AVERAGE(D175:H175))</f>
         <v/>
       </c>
-      <c r="K175" s="121" t="str">
+      <c r="K175" s="142" t="str">
         <f>+IF(C175="","",VLOOKUP(C175,Sheet2!$A$214:$C$220,3,TRUE))</f>
         <v/>
       </c>
-      <c r="L175" s="121"/>
-      <c r="M175" s="121"/>
-      <c r="N175" s="121"/>
-      <c r="O175" s="121"/>
+      <c r="L175" s="142"/>
+      <c r="M175" s="142"/>
+      <c r="N175" s="142"/>
+      <c r="O175" s="142"/>
       <c r="P175" s="28" t="str">
         <f>+IF(C175="","",VLOOKUP(C175,Sheet2!$A$214:$C$220,2,TRUE))</f>
         <v/>
@@ -8927,14 +8927,14 @@
       <c r="H176" s="7"/>
       <c r="I176" s="7"/>
       <c r="J176" s="5"/>
-      <c r="K176" s="121" t="str">
+      <c r="K176" s="142" t="str">
         <f>+IF(J175="","",VLOOKUP(J175,Sheet2!$A$223:$C$229,3,TRUE))</f>
         <v/>
       </c>
-      <c r="L176" s="121"/>
-      <c r="M176" s="121"/>
-      <c r="N176" s="121"/>
-      <c r="O176" s="121"/>
+      <c r="L176" s="142"/>
+      <c r="M176" s="142"/>
+      <c r="N176" s="142"/>
+      <c r="O176" s="142"/>
       <c r="P176" s="28" t="str">
         <f>+IF(J175="","",VLOOKUP(J175,Sheet2!$A$223:$C$229,2,TRUE))</f>
         <v/>
@@ -8950,14 +8950,14 @@
       <c r="H177" s="7"/>
       <c r="I177" s="7"/>
       <c r="J177" s="7"/>
-      <c r="K177" s="121" t="str">
+      <c r="K177" s="142" t="str">
         <f>+IF(C175="","",IF(C175&gt;(1.15*$N$203),Sheet2!$A$231,IF(Sheet1!C175&gt;Sheet1!$N$203,Sheet2!$A$232,IF(Sheet1!C175&gt;(0.7*Sheet1!$N$203),Sheet2!$A$233,IF(Sheet1!C175&gt;(0.6*Sheet1!$N$203),Sheet2!$A$234,Sheet2!$A$235)))))</f>
         <v/>
       </c>
-      <c r="L177" s="121"/>
-      <c r="M177" s="121"/>
-      <c r="N177" s="121"/>
-      <c r="O177" s="121"/>
+      <c r="L177" s="142"/>
+      <c r="M177" s="142"/>
+      <c r="N177" s="142"/>
+      <c r="O177" s="142"/>
       <c r="P177" s="56" t="str">
         <f>+IF(K177="","",VLOOKUP(K177,Sheet2!$A$231:$B$235,2,FALSE))</f>
         <v/>
@@ -9004,13 +9004,13 @@
       <c r="J179" s="64" t="s">
         <v>38</v>
       </c>
-      <c r="K179" s="120" t="s">
+      <c r="K179" s="143" t="s">
         <v>40</v>
       </c>
-      <c r="L179" s="120"/>
-      <c r="M179" s="120"/>
-      <c r="N179" s="120"/>
-      <c r="O179" s="120"/>
+      <c r="L179" s="143"/>
+      <c r="M179" s="143"/>
+      <c r="N179" s="143"/>
+      <c r="O179" s="143"/>
       <c r="P179" s="60" t="s">
         <v>124</v>
       </c>
@@ -9045,14 +9045,14 @@
         <f>+IF(D180="","",AVERAGE(D180:H180))</f>
         <v/>
       </c>
-      <c r="K180" s="121" t="str">
+      <c r="K180" s="142" t="str">
         <f>+IF(D180="","",VLOOKUP(D180,Sheet2!$A$239:$C$245,3,TRUE))</f>
         <v/>
       </c>
-      <c r="L180" s="121"/>
-      <c r="M180" s="121"/>
-      <c r="N180" s="121"/>
-      <c r="O180" s="121"/>
+      <c r="L180" s="142"/>
+      <c r="M180" s="142"/>
+      <c r="N180" s="142"/>
+      <c r="O180" s="142"/>
       <c r="P180" s="28" t="str">
         <f>+IF(D180="","",VLOOKUP(D180,Sheet2!$A$239:$C$245,2,TRUE))</f>
         <v/>
@@ -9128,13 +9128,13 @@
       <c r="J183" s="64" t="s">
         <v>38</v>
       </c>
-      <c r="K183" s="120" t="s">
+      <c r="K183" s="143" t="s">
         <v>40</v>
       </c>
-      <c r="L183" s="120"/>
-      <c r="M183" s="120"/>
-      <c r="N183" s="120"/>
-      <c r="O183" s="120"/>
+      <c r="L183" s="143"/>
+      <c r="M183" s="143"/>
+      <c r="N183" s="143"/>
+      <c r="O183" s="143"/>
       <c r="P183" s="60" t="s">
         <v>124</v>
       </c>
@@ -9154,14 +9154,14 @@
         <f>+IF(D184="","",AVERAGE(D184:H184))</f>
         <v/>
       </c>
-      <c r="K184" s="121" t="str">
+      <c r="K184" s="142" t="str">
         <f>+IF(C184="","",VLOOKUP(C184,Sheet2!$A$248:$C$252,3,TRUE))</f>
         <v/>
       </c>
-      <c r="L184" s="121"/>
-      <c r="M184" s="121"/>
-      <c r="N184" s="121"/>
-      <c r="O184" s="121"/>
+      <c r="L184" s="142"/>
+      <c r="M184" s="142"/>
+      <c r="N184" s="142"/>
+      <c r="O184" s="142"/>
       <c r="P184" s="28" t="str">
         <f>+IF(C184="","",VLOOKUP(C184,Sheet2!$A$248:$C$252,2,TRUE))</f>
         <v/>
@@ -9240,13 +9240,13 @@
       <c r="J187" s="64" t="s">
         <v>38</v>
       </c>
-      <c r="K187" s="120" t="s">
+      <c r="K187" s="143" t="s">
         <v>40</v>
       </c>
-      <c r="L187" s="120"/>
-      <c r="M187" s="120"/>
-      <c r="N187" s="120"/>
-      <c r="O187" s="120"/>
+      <c r="L187" s="143"/>
+      <c r="M187" s="143"/>
+      <c r="N187" s="143"/>
+      <c r="O187" s="143"/>
       <c r="P187" s="60" t="s">
         <v>124</v>
       </c>
@@ -9266,14 +9266,14 @@
         <f>+IF(D188="","",AVERAGE(D188:H188))</f>
         <v/>
       </c>
-      <c r="K188" s="121" t="str">
+      <c r="K188" s="142" t="str">
         <f>+IF(C188="","",VLOOKUP(C188,Sheet2!$A$255:$C$259,3,TRUE))</f>
         <v/>
       </c>
-      <c r="L188" s="121"/>
-      <c r="M188" s="121"/>
-      <c r="N188" s="121"/>
-      <c r="O188" s="121"/>
+      <c r="L188" s="142"/>
+      <c r="M188" s="142"/>
+      <c r="N188" s="142"/>
+      <c r="O188" s="142"/>
       <c r="P188" s="28" t="str">
         <f>+IF(C188="","",VLOOKUP(C188,Sheet2!$A$255:$C$259,2,TRUE))</f>
         <v/>
@@ -9571,23 +9571,23 @@
     </row>
     <row r="204" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="205" spans="2:16" ht="23.25" x14ac:dyDescent="0.25">
-      <c r="B205" s="122" t="s">
+      <c r="B205" s="123" t="s">
         <v>71</v>
       </c>
-      <c r="C205" s="123"/>
-      <c r="D205" s="123"/>
-      <c r="E205" s="123"/>
-      <c r="F205" s="123"/>
-      <c r="G205" s="123"/>
-      <c r="H205" s="123"/>
-      <c r="I205" s="123"/>
-      <c r="J205" s="123"/>
-      <c r="K205" s="123"/>
-      <c r="L205" s="123"/>
-      <c r="M205" s="123"/>
-      <c r="N205" s="123"/>
-      <c r="O205" s="123"/>
-      <c r="P205" s="124"/>
+      <c r="C205" s="124"/>
+      <c r="D205" s="124"/>
+      <c r="E205" s="124"/>
+      <c r="F205" s="124"/>
+      <c r="G205" s="124"/>
+      <c r="H205" s="124"/>
+      <c r="I205" s="124"/>
+      <c r="J205" s="124"/>
+      <c r="K205" s="124"/>
+      <c r="L205" s="124"/>
+      <c r="M205" s="124"/>
+      <c r="N205" s="124"/>
+      <c r="O205" s="124"/>
+      <c r="P205" s="125"/>
     </row>
     <row r="206" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B206" s="27" t="s">
@@ -9632,13 +9632,13 @@
       <c r="J208" s="64" t="s">
         <v>38</v>
       </c>
-      <c r="K208" s="120" t="s">
+      <c r="K208" s="143" t="s">
         <v>40</v>
       </c>
-      <c r="L208" s="120"/>
-      <c r="M208" s="120"/>
-      <c r="N208" s="120"/>
-      <c r="O208" s="120"/>
+      <c r="L208" s="143"/>
+      <c r="M208" s="143"/>
+      <c r="N208" s="143"/>
+      <c r="O208" s="143"/>
       <c r="P208" s="60" t="s">
         <v>124</v>
       </c>
@@ -9716,14 +9716,14 @@
       </c>
       <c r="I211" s="7"/>
       <c r="J211" s="7"/>
-      <c r="K211" s="121" t="str">
+      <c r="K211" s="142" t="str">
         <f>+IF(D211="","",IF(D211&gt;0,"Company manages to pay their dividends","Company doesn't manage to pay their dividends"))</f>
         <v/>
       </c>
-      <c r="L211" s="121"/>
-      <c r="M211" s="121"/>
-      <c r="N211" s="121"/>
-      <c r="O211" s="121"/>
+      <c r="L211" s="142"/>
+      <c r="M211" s="142"/>
+      <c r="N211" s="142"/>
+      <c r="O211" s="142"/>
       <c r="P211" s="28" t="str">
         <f>+IF(D211="","",IF(D211&gt;0,5,0))</f>
         <v/>
@@ -9770,11 +9770,11 @@
       <c r="J213" s="64" t="s">
         <v>38</v>
       </c>
-      <c r="K213" s="120"/>
-      <c r="L213" s="120"/>
-      <c r="M213" s="120"/>
-      <c r="N213" s="120"/>
-      <c r="O213" s="120"/>
+      <c r="K213" s="143"/>
+      <c r="L213" s="143"/>
+      <c r="M213" s="143"/>
+      <c r="N213" s="143"/>
+      <c r="O213" s="143"/>
       <c r="P213" s="68"/>
     </row>
     <row r="214" spans="2:16" x14ac:dyDescent="0.25">
@@ -9864,13 +9864,13 @@
       <c r="J217" s="64" t="s">
         <v>38</v>
       </c>
-      <c r="K217" s="120" t="s">
+      <c r="K217" s="143" t="s">
         <v>40</v>
       </c>
-      <c r="L217" s="120"/>
-      <c r="M217" s="120"/>
-      <c r="N217" s="120"/>
-      <c r="O217" s="120"/>
+      <c r="L217" s="143"/>
+      <c r="M217" s="143"/>
+      <c r="N217" s="143"/>
+      <c r="O217" s="143"/>
       <c r="P217" s="60" t="s">
         <v>124</v>
       </c>
@@ -9887,14 +9887,14 @@
       <c r="H218" s="7"/>
       <c r="I218" s="7"/>
       <c r="J218" s="7"/>
-      <c r="K218" s="121" t="str">
+      <c r="K218" s="142" t="str">
         <f>+IF(C218="","",IF(C218&gt;60%,"Company's dividends at risk of being cut","Company's dividends are not at risk of being cut"))</f>
         <v/>
       </c>
-      <c r="L218" s="121"/>
-      <c r="M218" s="121"/>
-      <c r="N218" s="121"/>
-      <c r="O218" s="121"/>
+      <c r="L218" s="142"/>
+      <c r="M218" s="142"/>
+      <c r="N218" s="142"/>
+      <c r="O218" s="142"/>
       <c r="P218" s="28" t="str">
         <f>+IF(C218="","",IF(C218&gt;60%,0,5))</f>
         <v/>
@@ -9973,13 +9973,13 @@
       <c r="J221" s="64" t="s">
         <v>38</v>
       </c>
-      <c r="K221" s="120" t="s">
+      <c r="K221" s="143" t="s">
         <v>40</v>
       </c>
-      <c r="L221" s="120"/>
-      <c r="M221" s="120"/>
-      <c r="N221" s="120"/>
-      <c r="O221" s="120"/>
+      <c r="L221" s="143"/>
+      <c r="M221" s="143"/>
+      <c r="N221" s="143"/>
+      <c r="O221" s="143"/>
       <c r="P221" s="60" t="s">
         <v>124</v>
       </c>
@@ -9999,14 +9999,14 @@
         <f>+IF(D222="","",AVERAGE(D222:H222))</f>
         <v/>
       </c>
-      <c r="K222" s="136" t="str">
+      <c r="K222" s="144" t="str">
         <f>+IF(J222="","",VLOOKUP(J222,Sheet2!$A$262:$C$268,3,TRUE))</f>
         <v/>
       </c>
-      <c r="L222" s="136"/>
-      <c r="M222" s="136"/>
-      <c r="N222" s="136"/>
-      <c r="O222" s="136"/>
+      <c r="L222" s="144"/>
+      <c r="M222" s="144"/>
+      <c r="N222" s="144"/>
+      <c r="O222" s="144"/>
       <c r="P222" s="32" t="str">
         <f>+IF(J222="","",VLOOKUP(J222,Sheet2!$A$262:$C$268,2,TRUE))</f>
         <v/>
@@ -10014,23 +10014,23 @@
     </row>
     <row r="223" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="224" spans="2:16" ht="23.25" x14ac:dyDescent="0.25">
-      <c r="B224" s="122" t="s">
+      <c r="B224" s="123" t="s">
         <v>79</v>
       </c>
-      <c r="C224" s="123"/>
-      <c r="D224" s="123"/>
-      <c r="E224" s="123"/>
-      <c r="F224" s="123"/>
-      <c r="G224" s="123"/>
-      <c r="H224" s="123"/>
-      <c r="I224" s="123"/>
-      <c r="J224" s="123"/>
-      <c r="K224" s="123"/>
-      <c r="L224" s="123"/>
-      <c r="M224" s="123"/>
-      <c r="N224" s="123"/>
-      <c r="O224" s="123"/>
-      <c r="P224" s="124"/>
+      <c r="C224" s="124"/>
+      <c r="D224" s="124"/>
+      <c r="E224" s="124"/>
+      <c r="F224" s="124"/>
+      <c r="G224" s="124"/>
+      <c r="H224" s="124"/>
+      <c r="I224" s="124"/>
+      <c r="J224" s="124"/>
+      <c r="K224" s="124"/>
+      <c r="L224" s="124"/>
+      <c r="M224" s="124"/>
+      <c r="N224" s="124"/>
+      <c r="O224" s="124"/>
+      <c r="P224" s="125"/>
     </row>
     <row r="225" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B225" s="27"/>
@@ -10063,13 +10063,13 @@
       </c>
       <c r="I226" s="63"/>
       <c r="J226" s="63"/>
-      <c r="K226" s="120" t="s">
+      <c r="K226" s="143" t="s">
         <v>40</v>
       </c>
-      <c r="L226" s="120"/>
-      <c r="M226" s="120"/>
-      <c r="N226" s="120"/>
-      <c r="O226" s="120"/>
+      <c r="L226" s="143"/>
+      <c r="M226" s="143"/>
+      <c r="N226" s="143"/>
+      <c r="O226" s="143"/>
       <c r="P226" s="60" t="s">
         <v>124</v>
       </c>
@@ -10097,14 +10097,14 @@
         <f>+IF(AND(C227="",D227=""),"",IF(C227="",D227*0.8,C227*0.8))</f>
         <v/>
       </c>
-      <c r="K228" s="121" t="str">
+      <c r="K228" s="142" t="str">
         <f>+IF(C228="","",IF(E11&gt;1.5*C228,Sheet2!A274,IF(E11&gt;1.2*C228,Sheet2!A273,Sheet2!A272)))</f>
         <v/>
       </c>
-      <c r="L228" s="121"/>
-      <c r="M228" s="121"/>
-      <c r="N228" s="121"/>
-      <c r="O228" s="121"/>
+      <c r="L228" s="142"/>
+      <c r="M228" s="142"/>
+      <c r="N228" s="142"/>
+      <c r="O228" s="142"/>
       <c r="P228" s="28" t="str">
         <f>+IF(K228="","",VLOOKUP(K228,Sheet2!$A$272:$B$274,2,FALSE))</f>
         <v/>
@@ -10129,13 +10129,13 @@
       <c r="H230" s="59"/>
       <c r="I230" s="59"/>
       <c r="J230" s="59"/>
-      <c r="K230" s="120" t="s">
+      <c r="K230" s="143" t="s">
         <v>40</v>
       </c>
-      <c r="L230" s="120"/>
-      <c r="M230" s="120"/>
-      <c r="N230" s="120"/>
-      <c r="O230" s="120"/>
+      <c r="L230" s="143"/>
+      <c r="M230" s="143"/>
+      <c r="N230" s="143"/>
+      <c r="O230" s="143"/>
       <c r="P230" s="60" t="s">
         <v>124</v>
       </c>
@@ -10171,14 +10171,14 @@
       <c r="H233" s="31"/>
       <c r="I233" s="31"/>
       <c r="J233" s="31"/>
-      <c r="K233" s="136" t="str">
+      <c r="K233" s="144" t="str">
         <f>+IF(C233="","",IF(C233&gt;$E$11*1.5,Sheet2!$A$272,IF(C233&gt;$E$11*1.1,Sheet2!$A$273,Sheet2!$A$274)))</f>
         <v/>
       </c>
-      <c r="L233" s="136"/>
-      <c r="M233" s="136"/>
-      <c r="N233" s="136"/>
-      <c r="O233" s="136"/>
+      <c r="L233" s="144"/>
+      <c r="M233" s="144"/>
+      <c r="N233" s="144"/>
+      <c r="O233" s="144"/>
       <c r="P233" s="32" t="str">
         <f>+IF(K233="","",VLOOKUP(K233,Sheet2!$A$272:$B$274,2,FALSE))</f>
         <v/>
@@ -10194,13 +10194,13 @@
       <c r="P234" s="10"/>
     </row>
     <row r="235" spans="2:16" ht="15.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="K235" s="135" t="s">
+      <c r="K235" s="170" t="s">
         <v>40</v>
       </c>
-      <c r="L235" s="135"/>
-      <c r="M235" s="135"/>
-      <c r="N235" s="135"/>
-      <c r="O235" s="135"/>
+      <c r="L235" s="170"/>
+      <c r="M235" s="170"/>
+      <c r="N235" s="170"/>
+      <c r="O235" s="170"/>
     </row>
     <row r="236" spans="2:16" ht="15.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B236" s="1" t="s">
@@ -10208,13 +10208,13 @@
       </c>
     </row>
     <row r="237" spans="2:16" ht="15.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="K237" s="135" t="s">
+      <c r="K237" s="170" t="s">
         <v>40</v>
       </c>
-      <c r="L237" s="135"/>
-      <c r="M237" s="135"/>
-      <c r="N237" s="135"/>
-      <c r="O237" s="135"/>
+      <c r="L237" s="170"/>
+      <c r="M237" s="170"/>
+      <c r="N237" s="170"/>
+      <c r="O237" s="170"/>
     </row>
     <row r="238" spans="2:16" ht="15.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B238" s="1" t="s">
@@ -10222,13 +10222,13 @@
       </c>
     </row>
     <row r="239" spans="2:16" ht="15.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="K239" s="135" t="s">
+      <c r="K239" s="170" t="s">
         <v>40</v>
       </c>
-      <c r="L239" s="135"/>
-      <c r="M239" s="135"/>
-      <c r="N239" s="135"/>
-      <c r="O239" s="135"/>
+      <c r="L239" s="170"/>
+      <c r="M239" s="170"/>
+      <c r="N239" s="170"/>
+      <c r="O239" s="170"/>
     </row>
     <row r="240" spans="2:16" ht="15.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B240" s="1" t="s">
@@ -10236,13 +10236,13 @@
       </c>
     </row>
     <row r="241" spans="2:38" ht="15.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="K241" s="135" t="s">
+      <c r="K241" s="170" t="s">
         <v>40</v>
       </c>
-      <c r="L241" s="135"/>
-      <c r="M241" s="135"/>
-      <c r="N241" s="135"/>
-      <c r="O241" s="135"/>
+      <c r="L241" s="170"/>
+      <c r="M241" s="170"/>
+      <c r="N241" s="170"/>
+      <c r="O241" s="170"/>
     </row>
     <row r="242" spans="2:38" ht="15.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B242" s="1" t="s">
@@ -10253,23 +10253,23 @@
     <row r="244" spans="2:38" ht="15.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="245" spans="2:38" ht="15.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="246" spans="2:38" ht="23.25" x14ac:dyDescent="0.25">
-      <c r="B246" s="158" t="s">
+      <c r="B246" s="126" t="s">
         <v>322</v>
       </c>
-      <c r="C246" s="159"/>
-      <c r="D246" s="159"/>
-      <c r="E246" s="159"/>
-      <c r="F246" s="159"/>
-      <c r="G246" s="159"/>
-      <c r="H246" s="159"/>
-      <c r="I246" s="159"/>
-      <c r="J246" s="159"/>
-      <c r="K246" s="159"/>
-      <c r="L246" s="159"/>
-      <c r="M246" s="159"/>
-      <c r="N246" s="159"/>
-      <c r="O246" s="159"/>
-      <c r="P246" s="160"/>
+      <c r="C246" s="127"/>
+      <c r="D246" s="127"/>
+      <c r="E246" s="127"/>
+      <c r="F246" s="127"/>
+      <c r="G246" s="127"/>
+      <c r="H246" s="127"/>
+      <c r="I246" s="127"/>
+      <c r="J246" s="127"/>
+      <c r="K246" s="127"/>
+      <c r="L246" s="127"/>
+      <c r="M246" s="127"/>
+      <c r="N246" s="127"/>
+      <c r="O246" s="127"/>
+      <c r="P246" s="128"/>
       <c r="Y246" s="106"/>
       <c r="Z246" s="106"/>
       <c r="AA246" s="106"/>
@@ -10564,11 +10564,11 @@
         <f t="shared" ref="D254:D265" si="81">+IF(C254="","",U254)</f>
         <v/>
       </c>
-      <c r="E254" s="155" t="s">
+      <c r="E254" s="120" t="s">
         <v>299</v>
       </c>
-      <c r="F254" s="155"/>
-      <c r="G254" s="155"/>
+      <c r="F254" s="120"/>
+      <c r="G254" s="120"/>
       <c r="P254" s="112"/>
       <c r="U254" s="119">
         <v>0.03</v>
@@ -10611,9 +10611,9 @@
         <f t="shared" si="81"/>
         <v/>
       </c>
-      <c r="E255" s="155"/>
-      <c r="F255" s="155"/>
-      <c r="G255" s="155"/>
+      <c r="E255" s="120"/>
+      <c r="F255" s="120"/>
+      <c r="G255" s="120"/>
       <c r="P255" s="112"/>
       <c r="U255" s="119">
         <v>0.01</v>
@@ -10656,14 +10656,14 @@
         <f t="shared" si="81"/>
         <v/>
       </c>
-      <c r="E256" s="155"/>
-      <c r="F256" s="155"/>
-      <c r="G256" s="155"/>
-      <c r="J256" s="156">
+      <c r="E256" s="120"/>
+      <c r="F256" s="120"/>
+      <c r="G256" s="120"/>
+      <c r="J256" s="121">
         <f>+K253</f>
         <v>0</v>
       </c>
-      <c r="K256" s="157"/>
+      <c r="K256" s="122"/>
       <c r="P256" s="112"/>
       <c r="U256" s="119">
         <v>0.05</v>
@@ -10706,11 +10706,11 @@
         <f t="shared" si="81"/>
         <v/>
       </c>
-      <c r="E257" s="155"/>
-      <c r="F257" s="155"/>
-      <c r="G257" s="155"/>
-      <c r="J257" s="157"/>
-      <c r="K257" s="157"/>
+      <c r="E257" s="120"/>
+      <c r="F257" s="120"/>
+      <c r="G257" s="120"/>
+      <c r="J257" s="122"/>
+      <c r="K257" s="122"/>
       <c r="P257" s="112"/>
       <c r="U257" s="119">
         <v>0.05</v>
@@ -10761,9 +10761,9 @@
         <f t="shared" si="81"/>
         <v/>
       </c>
-      <c r="E258" s="155"/>
-      <c r="F258" s="155"/>
-      <c r="G258" s="155"/>
+      <c r="E258" s="120"/>
+      <c r="F258" s="120"/>
+      <c r="G258" s="120"/>
       <c r="P258" s="112"/>
       <c r="U258" s="119">
         <v>0.01</v>
@@ -10814,9 +10814,9 @@
         <f t="shared" si="81"/>
         <v/>
       </c>
-      <c r="E259" s="155"/>
-      <c r="F259" s="155"/>
-      <c r="G259" s="155"/>
+      <c r="E259" s="120"/>
+      <c r="F259" s="120"/>
+      <c r="G259" s="120"/>
       <c r="P259" s="112"/>
       <c r="U259" s="119">
         <v>0.02</v>
@@ -12088,6 +12088,124 @@
     </row>
   </sheetData>
   <mergeCells count="142">
+    <mergeCell ref="K116:O116"/>
+    <mergeCell ref="K114:O114"/>
+    <mergeCell ref="K126:O126"/>
+    <mergeCell ref="K127:O127"/>
+    <mergeCell ref="K102:O102"/>
+    <mergeCell ref="K103:O103"/>
+    <mergeCell ref="K107:O107"/>
+    <mergeCell ref="K175:O175"/>
+    <mergeCell ref="K176:O176"/>
+    <mergeCell ref="K164:O164"/>
+    <mergeCell ref="K169:O169"/>
+    <mergeCell ref="K174:O174"/>
+    <mergeCell ref="K117:O117"/>
+    <mergeCell ref="K118:O118"/>
+    <mergeCell ref="K121:O121"/>
+    <mergeCell ref="K122:O122"/>
+    <mergeCell ref="K179:O179"/>
+    <mergeCell ref="K183:O183"/>
+    <mergeCell ref="B130:P131"/>
+    <mergeCell ref="K166:O166"/>
+    <mergeCell ref="K167:O167"/>
+    <mergeCell ref="K170:O170"/>
+    <mergeCell ref="K171:O171"/>
+    <mergeCell ref="K172:O172"/>
+    <mergeCell ref="K177:O177"/>
+    <mergeCell ref="K180:O180"/>
+    <mergeCell ref="K145:O145"/>
+    <mergeCell ref="K146:O146"/>
+    <mergeCell ref="K149:O149"/>
+    <mergeCell ref="K150:O150"/>
+    <mergeCell ref="K153:O153"/>
+    <mergeCell ref="K132:O132"/>
+    <mergeCell ref="K154:O154"/>
+    <mergeCell ref="K157:O157"/>
+    <mergeCell ref="K158:O158"/>
+    <mergeCell ref="K161:O161"/>
+    <mergeCell ref="K162:O162"/>
+    <mergeCell ref="K165:O165"/>
+    <mergeCell ref="J30:K30"/>
+    <mergeCell ref="J31:K31"/>
+    <mergeCell ref="J13:K13"/>
+    <mergeCell ref="J16:P16"/>
+    <mergeCell ref="K239:O239"/>
+    <mergeCell ref="K241:O241"/>
+    <mergeCell ref="K226:O226"/>
+    <mergeCell ref="K230:O230"/>
+    <mergeCell ref="K235:O235"/>
+    <mergeCell ref="K237:O237"/>
+    <mergeCell ref="K208:O208"/>
+    <mergeCell ref="K213:O213"/>
+    <mergeCell ref="K217:O217"/>
+    <mergeCell ref="K221:O221"/>
+    <mergeCell ref="K211:O211"/>
+    <mergeCell ref="K218:O218"/>
+    <mergeCell ref="K222:O222"/>
+    <mergeCell ref="K228:O228"/>
+    <mergeCell ref="K233:O233"/>
+    <mergeCell ref="K184:O184"/>
+    <mergeCell ref="K188:O188"/>
+    <mergeCell ref="K120:O120"/>
+    <mergeCell ref="K124:O124"/>
+    <mergeCell ref="B110:P111"/>
+    <mergeCell ref="L23:O23"/>
+    <mergeCell ref="B4:C13"/>
+    <mergeCell ref="E4:H4"/>
+    <mergeCell ref="K5:N5"/>
+    <mergeCell ref="M15:O15"/>
+    <mergeCell ref="L22:O22"/>
+    <mergeCell ref="E5:H5"/>
+    <mergeCell ref="G22:H22"/>
+    <mergeCell ref="B16:H20"/>
+    <mergeCell ref="E6:H6"/>
+    <mergeCell ref="E7:H7"/>
+    <mergeCell ref="E9:F9"/>
+    <mergeCell ref="E10:F10"/>
+    <mergeCell ref="L13:O13"/>
+    <mergeCell ref="K40:O40"/>
+    <mergeCell ref="K39:O39"/>
+    <mergeCell ref="K43:O43"/>
+    <mergeCell ref="K47:O47"/>
+    <mergeCell ref="K51:O51"/>
+    <mergeCell ref="K55:O55"/>
+    <mergeCell ref="K101:O101"/>
+    <mergeCell ref="K41:O41"/>
+    <mergeCell ref="K42:O42"/>
+    <mergeCell ref="K45:O45"/>
+    <mergeCell ref="K44:O44"/>
+    <mergeCell ref="K48:O48"/>
+    <mergeCell ref="K49:O49"/>
+    <mergeCell ref="K85:O85"/>
+    <mergeCell ref="K84:O84"/>
+    <mergeCell ref="K90:O90"/>
+    <mergeCell ref="K59:O59"/>
+    <mergeCell ref="K63:O63"/>
+    <mergeCell ref="K67:O67"/>
+    <mergeCell ref="K71:O71"/>
+    <mergeCell ref="K75:O75"/>
+    <mergeCell ref="K79:O79"/>
+    <mergeCell ref="K83:O83"/>
+    <mergeCell ref="K61:O61"/>
+    <mergeCell ref="K64:O64"/>
+    <mergeCell ref="K65:O65"/>
+    <mergeCell ref="K68:O68"/>
+    <mergeCell ref="K69:O69"/>
+    <mergeCell ref="K80:O80"/>
+    <mergeCell ref="K81:O81"/>
+    <mergeCell ref="K108:O108"/>
+    <mergeCell ref="K113:O113"/>
+    <mergeCell ref="K91:O91"/>
+    <mergeCell ref="K94:O94"/>
+    <mergeCell ref="K95:O95"/>
+    <mergeCell ref="K98:O98"/>
+    <mergeCell ref="K88:O88"/>
+    <mergeCell ref="K93:O93"/>
+    <mergeCell ref="K97:O97"/>
+    <mergeCell ref="K99:O99"/>
+    <mergeCell ref="K112:O112"/>
+    <mergeCell ref="K105:O105"/>
     <mergeCell ref="E254:G259"/>
     <mergeCell ref="J256:K257"/>
     <mergeCell ref="B205:P205"/>
@@ -12112,124 +12230,6 @@
     <mergeCell ref="K156:O156"/>
     <mergeCell ref="K160:O160"/>
     <mergeCell ref="K60:O60"/>
-    <mergeCell ref="K64:O64"/>
-    <mergeCell ref="K65:O65"/>
-    <mergeCell ref="K68:O68"/>
-    <mergeCell ref="K69:O69"/>
-    <mergeCell ref="K80:O80"/>
-    <mergeCell ref="K81:O81"/>
-    <mergeCell ref="K108:O108"/>
-    <mergeCell ref="K113:O113"/>
-    <mergeCell ref="K91:O91"/>
-    <mergeCell ref="K94:O94"/>
-    <mergeCell ref="K95:O95"/>
-    <mergeCell ref="K98:O98"/>
-    <mergeCell ref="K88:O88"/>
-    <mergeCell ref="K93:O93"/>
-    <mergeCell ref="K97:O97"/>
-    <mergeCell ref="K99:O99"/>
-    <mergeCell ref="K112:O112"/>
-    <mergeCell ref="K105:O105"/>
-    <mergeCell ref="K40:O40"/>
-    <mergeCell ref="K39:O39"/>
-    <mergeCell ref="K43:O43"/>
-    <mergeCell ref="K47:O47"/>
-    <mergeCell ref="K51:O51"/>
-    <mergeCell ref="K55:O55"/>
-    <mergeCell ref="K101:O101"/>
-    <mergeCell ref="K41:O41"/>
-    <mergeCell ref="K42:O42"/>
-    <mergeCell ref="K45:O45"/>
-    <mergeCell ref="K44:O44"/>
-    <mergeCell ref="K48:O48"/>
-    <mergeCell ref="K49:O49"/>
-    <mergeCell ref="K85:O85"/>
-    <mergeCell ref="K84:O84"/>
-    <mergeCell ref="K90:O90"/>
-    <mergeCell ref="K59:O59"/>
-    <mergeCell ref="K63:O63"/>
-    <mergeCell ref="K67:O67"/>
-    <mergeCell ref="K71:O71"/>
-    <mergeCell ref="K75:O75"/>
-    <mergeCell ref="K79:O79"/>
-    <mergeCell ref="K83:O83"/>
-    <mergeCell ref="K61:O61"/>
-    <mergeCell ref="L23:O23"/>
-    <mergeCell ref="B4:C13"/>
-    <mergeCell ref="E4:H4"/>
-    <mergeCell ref="K5:N5"/>
-    <mergeCell ref="M15:O15"/>
-    <mergeCell ref="L22:O22"/>
-    <mergeCell ref="E5:H5"/>
-    <mergeCell ref="G22:H22"/>
-    <mergeCell ref="B16:H20"/>
-    <mergeCell ref="E6:H6"/>
-    <mergeCell ref="E7:H7"/>
-    <mergeCell ref="E9:F9"/>
-    <mergeCell ref="E10:F10"/>
-    <mergeCell ref="L13:O13"/>
-    <mergeCell ref="J30:K30"/>
-    <mergeCell ref="J31:K31"/>
-    <mergeCell ref="J13:K13"/>
-    <mergeCell ref="J16:P16"/>
-    <mergeCell ref="K239:O239"/>
-    <mergeCell ref="K241:O241"/>
-    <mergeCell ref="K226:O226"/>
-    <mergeCell ref="K230:O230"/>
-    <mergeCell ref="K235:O235"/>
-    <mergeCell ref="K237:O237"/>
-    <mergeCell ref="K208:O208"/>
-    <mergeCell ref="K213:O213"/>
-    <mergeCell ref="K217:O217"/>
-    <mergeCell ref="K221:O221"/>
-    <mergeCell ref="K211:O211"/>
-    <mergeCell ref="K218:O218"/>
-    <mergeCell ref="K222:O222"/>
-    <mergeCell ref="K228:O228"/>
-    <mergeCell ref="K233:O233"/>
-    <mergeCell ref="K184:O184"/>
-    <mergeCell ref="K188:O188"/>
-    <mergeCell ref="K120:O120"/>
-    <mergeCell ref="K124:O124"/>
-    <mergeCell ref="B110:P111"/>
-    <mergeCell ref="K179:O179"/>
-    <mergeCell ref="K183:O183"/>
-    <mergeCell ref="B130:P131"/>
-    <mergeCell ref="K166:O166"/>
-    <mergeCell ref="K167:O167"/>
-    <mergeCell ref="K170:O170"/>
-    <mergeCell ref="K171:O171"/>
-    <mergeCell ref="K172:O172"/>
-    <mergeCell ref="K177:O177"/>
-    <mergeCell ref="K180:O180"/>
-    <mergeCell ref="K145:O145"/>
-    <mergeCell ref="K146:O146"/>
-    <mergeCell ref="K149:O149"/>
-    <mergeCell ref="K150:O150"/>
-    <mergeCell ref="K153:O153"/>
-    <mergeCell ref="K132:O132"/>
-    <mergeCell ref="K154:O154"/>
-    <mergeCell ref="K157:O157"/>
-    <mergeCell ref="K158:O158"/>
-    <mergeCell ref="K161:O161"/>
-    <mergeCell ref="K162:O162"/>
-    <mergeCell ref="K165:O165"/>
-    <mergeCell ref="K116:O116"/>
-    <mergeCell ref="K114:O114"/>
-    <mergeCell ref="K126:O126"/>
-    <mergeCell ref="K127:O127"/>
-    <mergeCell ref="K102:O102"/>
-    <mergeCell ref="K103:O103"/>
-    <mergeCell ref="K107:O107"/>
-    <mergeCell ref="K175:O175"/>
-    <mergeCell ref="K176:O176"/>
-    <mergeCell ref="K164:O164"/>
-    <mergeCell ref="K169:O169"/>
-    <mergeCell ref="K174:O174"/>
-    <mergeCell ref="K117:O117"/>
-    <mergeCell ref="K118:O118"/>
-    <mergeCell ref="K121:O121"/>
-    <mergeCell ref="K122:O122"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <conditionalFormatting sqref="M15:O15">
@@ -12569,7 +12569,7 @@
         <v>-100000000000</v>
       </c>
       <c r="B27">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C27" t="s">
         <v>144</v>
@@ -12678,7 +12678,7 @@
         <v>-100000000000</v>
       </c>
       <c r="B35">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C35" t="s">
         <v>149</v>
@@ -12772,7 +12772,7 @@
         <v>0.8</v>
       </c>
       <c r="B43">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C43" t="s">
         <v>151</v>
@@ -12801,7 +12801,7 @@
         <v>0.8</v>
       </c>
       <c r="B46">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C46" t="s">
         <v>153</v>
@@ -12820,7 +12820,7 @@
         <v>-100000000000</v>
       </c>
       <c r="B50">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C50" t="s">
         <v>154</v>
@@ -12894,7 +12894,7 @@
         <v>-100000000000</v>
       </c>
       <c r="B56">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C56" t="s">
         <v>159</v>
@@ -12973,7 +12973,7 @@
         <v>-100000000000</v>
       </c>
       <c r="B64">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C64" t="s">
         <v>164</v>
@@ -13047,7 +13047,7 @@
         <v>-100000000000</v>
       </c>
       <c r="B70">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C70" t="s">
         <v>169</v>
@@ -13126,7 +13126,7 @@
         <v>-100000000000</v>
       </c>
       <c r="B78">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C78" t="s">
         <v>174</v>
@@ -13200,7 +13200,7 @@
         <v>-100000000000</v>
       </c>
       <c r="B84">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C84" t="s">
         <v>179</v>
@@ -13309,7 +13309,7 @@
         <v>0.39</v>
       </c>
       <c r="B94">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C94" t="s">
         <v>186</v>
@@ -13353,7 +13353,7 @@
         <v>0.39</v>
       </c>
       <c r="B98">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C98" t="s">
         <v>189</v>
@@ -13402,7 +13402,7 @@
         <v>0.2</v>
       </c>
       <c r="B104">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C104" t="s">
         <v>191</v>
@@ -13446,7 +13446,7 @@
         <v>0.2</v>
       </c>
       <c r="B107">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C107" t="s">
         <v>193</v>
@@ -13510,7 +13510,7 @@
         <v>0.55000000000000004</v>
       </c>
       <c r="B113">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C113" t="s">
         <v>198</v>
@@ -13569,7 +13569,7 @@
         <v>0.55000000000000004</v>
       </c>
       <c r="B117">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C117" t="s">
         <v>200</v>
@@ -13588,7 +13588,7 @@
         <v>-100000000000</v>
       </c>
       <c r="B121">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C121" t="s">
         <v>201</v>
@@ -13662,7 +13662,7 @@
         <v>-100000000000</v>
       </c>
       <c r="B127">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C127" t="s">
         <v>206</v>
